--- a/quotes/הצעת-מחיר-חודשית-חוות-רום.xlsx
+++ b/quotes/הצעת-מחיר-חודשית-חוות-רום.xlsx
@@ -10,32 +10,34 @@
   <sheets>
     <sheet name="הוראות" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="הגדרות" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="אוקטובר 2026" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="נובמבר 2026" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="דצמבר 2026" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="ינואר 2027" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="פברואר 2027" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="מרץ 2027" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="אפריל 2027" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="מאי 2027" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="יוני 2027" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="יולי 2027" sheetId="12" state="visible" r:id="rId14"/>
-    <sheet name="אוגוסט 2027" sheetId="13" state="visible" r:id="rId15"/>
-    <sheet name="ספטמבר 2027" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="ספטמבר 2026" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="אוקטובר 2026" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="נובמבר 2026" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="דצמבר 2026" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="ינואר 2027" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="פברואר 2027" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="מרץ 2027" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="אפריל 2027" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="מאי 2027" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="יוני 2027" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="יולי 2027" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="אוגוסט 2027" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="ספטמבר 2027" sheetId="15" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="12" name="_xlnm.Print_Area" vbProcedure="false">'אוגוסט 2027'!$A$1:$I$36</definedName>
-    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">'אוקטובר 2026'!$A$1:$I$36</definedName>
-    <definedName function="false" hidden="false" localSheetId="8" name="_xlnm.Print_Area" vbProcedure="false">'אפריל 2027'!$A$1:$I$36</definedName>
-    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">'דצמבר 2026'!$A$1:$I$36</definedName>
-    <definedName function="false" hidden="false" localSheetId="11" name="_xlnm.Print_Area" vbProcedure="false">'יולי 2027'!$A$1:$I$36</definedName>
-    <definedName function="false" hidden="false" localSheetId="10" name="_xlnm.Print_Area" vbProcedure="false">'יוני 2027'!$A$1:$I$36</definedName>
-    <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">'ינואר 2027'!$A$1:$I$36</definedName>
-    <definedName function="false" hidden="false" localSheetId="9" name="_xlnm.Print_Area" vbProcedure="false">'מאי 2027'!$A$1:$I$36</definedName>
-    <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">'מרץ 2027'!$A$1:$I$36</definedName>
-    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">'נובמבר 2026'!$A$1:$I$36</definedName>
-    <definedName function="false" hidden="false" localSheetId="13" name="_xlnm.Print_Area" vbProcedure="false">'ספטמבר 2027'!$A$1:$I$36</definedName>
-    <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">'פברואר 2027'!$A$1:$I$36</definedName>
+    <definedName function="false" hidden="false" localSheetId="13" name="_xlnm.Print_Area" vbProcedure="false">'אוגוסט 2027'!$A$1:$I$36</definedName>
+    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">'אוקטובר 2026'!$A$1:$I$36</definedName>
+    <definedName function="false" hidden="false" localSheetId="9" name="_xlnm.Print_Area" vbProcedure="false">'אפריל 2027'!$A$1:$I$36</definedName>
+    <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">'דצמבר 2026'!$A$1:$I$36</definedName>
+    <definedName function="false" hidden="false" localSheetId="12" name="_xlnm.Print_Area" vbProcedure="false">'יולי 2027'!$A$1:$I$36</definedName>
+    <definedName function="false" hidden="false" localSheetId="11" name="_xlnm.Print_Area" vbProcedure="false">'יוני 2027'!$A$1:$I$36</definedName>
+    <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">'ינואר 2027'!$A$1:$I$36</definedName>
+    <definedName function="false" hidden="false" localSheetId="10" name="_xlnm.Print_Area" vbProcedure="false">'מאי 2027'!$A$1:$I$36</definedName>
+    <definedName function="false" hidden="false" localSheetId="8" name="_xlnm.Print_Area" vbProcedure="false">'מרץ 2027'!$A$1:$I$36</definedName>
+    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">'נובמבר 2026'!$A$1:$I$36</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">'ספטמבר 2026'!$A$1:$I$36</definedName>
+    <definedName function="false" hidden="false" localSheetId="14" name="_xlnm.Print_Area" vbProcedure="false">'ספטמבר 2027'!$A$1:$I$36</definedName>
+    <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">'פברואר 2027'!$A$1:$I$36</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -247,6 +249,56 @@
 </file>
 
 <file path=xl/comments14.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="B25" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">תאריך ישיבת הצוות – לא חובה</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H11" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">אפשר להקליד כל תאריך בחודש (למשל </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">1/11/2026) – כל התאריכים בטבלה מתעדכנים לפיו.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments15.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
     <author>Unknown Author</author>
@@ -753,7 +805,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="92">
   <si>
     <t xml:space="preserve">איך משתמשים בקובץ</t>
   </si>
@@ -767,7 +819,7 @@
     <t xml:space="preserve">2. בסוף כל חודש</t>
   </si>
   <si>
-    <t xml:space="preserve">פותחים את הגיליון של החודש (למשל "אוקטובר 2026"). התאריכים של ימי ראשון וחמישי בחודש מחושבים אוטומטית, וכך גם השעות והסכומים.</t>
+    <t xml:space="preserve">פותחים את הגיליון של החודש (למשל "ספטמבר 2026"). התאריכים של ימי ראשון וחמישי בחודש מחושבים אוטומטית, וכך גם השעות והסכומים.</t>
   </si>
   <si>
     <t xml:space="preserve">3. ימים שלא התקיימו</t>
@@ -2028,13 +2080,13 @@
       <c r="I1" s="26"/>
       <c r="K1" s="27" t="n">
         <f aca="false">DATE(YEAR($H$11),MONTH($H$11),1)</f>
-        <v>46508</v>
+        <v>46478</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="str">
         <f aca="false">הגדרות!$C$17&amp;" · "&amp;CHOOSE(MONTH($K$1),"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר")&amp;" "&amp;YEAR($K$1)</f>
-        <v>הדרכת שיקום · מאי 2027</v>
+        <v>הדרכת שיקום · אפריל 2027</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -2046,7 +2098,7 @@
       <c r="I2" s="28"/>
       <c r="K2" s="27" t="n">
         <f aca="false">EOMONTH($K$1,0)</f>
-        <v>46538</v>
+        <v>46507</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2154,7 +2206,7 @@
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
         <f aca="false">YEAR($K$1)&amp;"-"&amp;TEXT(MONTH($K$1),"00")</f>
-        <v>2027-05</v>
+        <v>2027-04</v>
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
@@ -2162,7 +2214,7 @@
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
-        <v>46508</v>
+        <v>46478</v>
       </c>
       <c r="I11" s="32"/>
     </row>
@@ -2173,7 +2225,7 @@
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
         <f aca="false">$K$2</f>
-        <v>46538</v>
+        <v>46507</v>
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
@@ -2237,11 +2289,11 @@
       </c>
       <c r="B15" s="39" t="n">
         <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
-        <v>46509</v>
+        <v>46478</v>
       </c>
       <c r="C15" s="38" t="str">
         <f aca="false">IF(B15="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B15)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D15" s="40" t="str">
         <f aca="false">IF(B15="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -2262,7 +2314,7 @@
       <c r="I15" s="45"/>
       <c r="K15" s="27" t="n">
         <f aca="false">IF(B15="","",B15+MIN(MOD(הגדרות!$D$18-WEEKDAY(B15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B15)-1,7)+1))</f>
-        <v>46513</v>
+        <v>46481</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2272,11 +2324,11 @@
       </c>
       <c r="B16" s="39" t="n">
         <f aca="false">IF(K15="","",IF(K15&gt;$K$2,"",K15))</f>
-        <v>46513</v>
+        <v>46481</v>
       </c>
       <c r="C16" s="38" t="str">
         <f aca="false">IF(B16="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B16)))</f>
-        <v>חמישי</v>
+        <v>ראשון</v>
       </c>
       <c r="D16" s="40" t="str">
         <f aca="false">IF(B16="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -2297,7 +2349,7 @@
       <c r="I16" s="45"/>
       <c r="K16" s="27" t="n">
         <f aca="false">IF(B16="","",B16+MIN(MOD(הגדרות!$D$18-WEEKDAY(B16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B16)-1,7)+1))</f>
-        <v>46516</v>
+        <v>46485</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2307,11 +2359,11 @@
       </c>
       <c r="B17" s="39" t="n">
         <f aca="false">IF(K16="","",IF(K16&gt;$K$2,"",K16))</f>
-        <v>46516</v>
+        <v>46485</v>
       </c>
       <c r="C17" s="38" t="str">
         <f aca="false">IF(B17="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B17)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D17" s="40" t="str">
         <f aca="false">IF(B17="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -2332,7 +2384,7 @@
       <c r="I17" s="45"/>
       <c r="K17" s="27" t="n">
         <f aca="false">IF(B17="","",B17+MIN(MOD(הגדרות!$D$18-WEEKDAY(B17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B17)-1,7)+1))</f>
-        <v>46520</v>
+        <v>46488</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2342,11 +2394,11 @@
       </c>
       <c r="B18" s="39" t="n">
         <f aca="false">IF(K17="","",IF(K17&gt;$K$2,"",K17))</f>
-        <v>46520</v>
+        <v>46488</v>
       </c>
       <c r="C18" s="38" t="str">
         <f aca="false">IF(B18="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B18)))</f>
-        <v>חמישי</v>
+        <v>ראשון</v>
       </c>
       <c r="D18" s="40" t="str">
         <f aca="false">IF(B18="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -2367,7 +2419,7 @@
       <c r="I18" s="45"/>
       <c r="K18" s="27" t="n">
         <f aca="false">IF(B18="","",B18+MIN(MOD(הגדרות!$D$18-WEEKDAY(B18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B18)-1,7)+1))</f>
-        <v>46523</v>
+        <v>46492</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2377,11 +2429,11 @@
       </c>
       <c r="B19" s="39" t="n">
         <f aca="false">IF(K18="","",IF(K18&gt;$K$2,"",K18))</f>
-        <v>46523</v>
+        <v>46492</v>
       </c>
       <c r="C19" s="38" t="str">
         <f aca="false">IF(B19="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B19)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D19" s="40" t="str">
         <f aca="false">IF(B19="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -2402,7 +2454,7 @@
       <c r="I19" s="45"/>
       <c r="K19" s="27" t="n">
         <f aca="false">IF(B19="","",B19+MIN(MOD(הגדרות!$D$18-WEEKDAY(B19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B19)-1,7)+1))</f>
-        <v>46527</v>
+        <v>46495</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2412,11 +2464,11 @@
       </c>
       <c r="B20" s="39" t="n">
         <f aca="false">IF(K19="","",IF(K19&gt;$K$2,"",K19))</f>
-        <v>46527</v>
+        <v>46495</v>
       </c>
       <c r="C20" s="38" t="str">
         <f aca="false">IF(B20="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B20)))</f>
-        <v>חמישי</v>
+        <v>ראשון</v>
       </c>
       <c r="D20" s="40" t="str">
         <f aca="false">IF(B20="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -2437,7 +2489,7 @@
       <c r="I20" s="45"/>
       <c r="K20" s="27" t="n">
         <f aca="false">IF(B20="","",B20+MIN(MOD(הגדרות!$D$18-WEEKDAY(B20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B20)-1,7)+1))</f>
-        <v>46530</v>
+        <v>46499</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2447,11 +2499,11 @@
       </c>
       <c r="B21" s="39" t="n">
         <f aca="false">IF(K20="","",IF(K20&gt;$K$2,"",K20))</f>
-        <v>46530</v>
+        <v>46499</v>
       </c>
       <c r="C21" s="38" t="str">
         <f aca="false">IF(B21="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B21)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D21" s="40" t="str">
         <f aca="false">IF(B21="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -2472,7 +2524,7 @@
       <c r="I21" s="45"/>
       <c r="K21" s="27" t="n">
         <f aca="false">IF(B21="","",B21+MIN(MOD(הגדרות!$D$18-WEEKDAY(B21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B21)-1,7)+1))</f>
-        <v>46534</v>
+        <v>46502</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2482,11 +2534,11 @@
       </c>
       <c r="B22" s="39" t="n">
         <f aca="false">IF(K21="","",IF(K21&gt;$K$2,"",K21))</f>
-        <v>46534</v>
+        <v>46502</v>
       </c>
       <c r="C22" s="38" t="str">
         <f aca="false">IF(B22="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B22)))</f>
-        <v>חמישי</v>
+        <v>ראשון</v>
       </c>
       <c r="D22" s="40" t="str">
         <f aca="false">IF(B22="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -2507,7 +2559,7 @@
       <c r="I22" s="45"/>
       <c r="K22" s="27" t="n">
         <f aca="false">IF(B22="","",B22+MIN(MOD(הגדרות!$D$18-WEEKDAY(B22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B22)-1,7)+1))</f>
-        <v>46537</v>
+        <v>46506</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2517,11 +2569,11 @@
       </c>
       <c r="B23" s="39" t="n">
         <f aca="false">IF(K22="","",IF(K22&gt;$K$2,"",K22))</f>
-        <v>46537</v>
+        <v>46506</v>
       </c>
       <c r="C23" s="38" t="str">
         <f aca="false">IF(B23="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B23)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D23" s="40" t="str">
         <f aca="false">IF(B23="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -2542,7 +2594,7 @@
       <c r="I23" s="45"/>
       <c r="K23" s="27" t="n">
         <f aca="false">IF(B23="","",B23+MIN(MOD(הגדרות!$D$18-WEEKDAY(B23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B23)-1,7)+1))</f>
-        <v>46541</v>
+        <v>46509</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2859,13 +2911,13 @@
       <c r="I1" s="26"/>
       <c r="K1" s="27" t="n">
         <f aca="false">DATE(YEAR($H$11),MONTH($H$11),1)</f>
-        <v>46539</v>
+        <v>46508</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="str">
         <f aca="false">הגדרות!$C$17&amp;" · "&amp;CHOOSE(MONTH($K$1),"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר")&amp;" "&amp;YEAR($K$1)</f>
-        <v>הדרכת שיקום · יוני 2027</v>
+        <v>הדרכת שיקום · מאי 2027</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -2877,7 +2929,7 @@
       <c r="I2" s="28"/>
       <c r="K2" s="27" t="n">
         <f aca="false">EOMONTH($K$1,0)</f>
-        <v>46568</v>
+        <v>46538</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2985,7 +3037,7 @@
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
         <f aca="false">YEAR($K$1)&amp;"-"&amp;TEXT(MONTH($K$1),"00")</f>
-        <v>2027-06</v>
+        <v>2027-05</v>
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
@@ -2993,7 +3045,7 @@
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
-        <v>46539</v>
+        <v>46508</v>
       </c>
       <c r="I11" s="32"/>
     </row>
@@ -3004,7 +3056,7 @@
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
         <f aca="false">$K$2</f>
-        <v>46568</v>
+        <v>46538</v>
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
@@ -3068,11 +3120,11 @@
       </c>
       <c r="B15" s="39" t="n">
         <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
-        <v>46541</v>
+        <v>46509</v>
       </c>
       <c r="C15" s="38" t="str">
         <f aca="false">IF(B15="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B15)))</f>
-        <v>חמישי</v>
+        <v>ראשון</v>
       </c>
       <c r="D15" s="40" t="str">
         <f aca="false">IF(B15="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -3093,7 +3145,7 @@
       <c r="I15" s="45"/>
       <c r="K15" s="27" t="n">
         <f aca="false">IF(B15="","",B15+MIN(MOD(הגדרות!$D$18-WEEKDAY(B15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B15)-1,7)+1))</f>
-        <v>46544</v>
+        <v>46513</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3103,11 +3155,11 @@
       </c>
       <c r="B16" s="39" t="n">
         <f aca="false">IF(K15="","",IF(K15&gt;$K$2,"",K15))</f>
-        <v>46544</v>
+        <v>46513</v>
       </c>
       <c r="C16" s="38" t="str">
         <f aca="false">IF(B16="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B16)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D16" s="40" t="str">
         <f aca="false">IF(B16="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -3128,7 +3180,7 @@
       <c r="I16" s="45"/>
       <c r="K16" s="27" t="n">
         <f aca="false">IF(B16="","",B16+MIN(MOD(הגדרות!$D$18-WEEKDAY(B16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B16)-1,7)+1))</f>
-        <v>46548</v>
+        <v>46516</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3138,11 +3190,11 @@
       </c>
       <c r="B17" s="39" t="n">
         <f aca="false">IF(K16="","",IF(K16&gt;$K$2,"",K16))</f>
-        <v>46548</v>
+        <v>46516</v>
       </c>
       <c r="C17" s="38" t="str">
         <f aca="false">IF(B17="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B17)))</f>
-        <v>חמישי</v>
+        <v>ראשון</v>
       </c>
       <c r="D17" s="40" t="str">
         <f aca="false">IF(B17="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -3163,7 +3215,7 @@
       <c r="I17" s="45"/>
       <c r="K17" s="27" t="n">
         <f aca="false">IF(B17="","",B17+MIN(MOD(הגדרות!$D$18-WEEKDAY(B17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B17)-1,7)+1))</f>
-        <v>46551</v>
+        <v>46520</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3173,11 +3225,11 @@
       </c>
       <c r="B18" s="39" t="n">
         <f aca="false">IF(K17="","",IF(K17&gt;$K$2,"",K17))</f>
-        <v>46551</v>
+        <v>46520</v>
       </c>
       <c r="C18" s="38" t="str">
         <f aca="false">IF(B18="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B18)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D18" s="40" t="str">
         <f aca="false">IF(B18="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -3198,7 +3250,7 @@
       <c r="I18" s="45"/>
       <c r="K18" s="27" t="n">
         <f aca="false">IF(B18="","",B18+MIN(MOD(הגדרות!$D$18-WEEKDAY(B18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B18)-1,7)+1))</f>
-        <v>46555</v>
+        <v>46523</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3208,11 +3260,11 @@
       </c>
       <c r="B19" s="39" t="n">
         <f aca="false">IF(K18="","",IF(K18&gt;$K$2,"",K18))</f>
-        <v>46555</v>
+        <v>46523</v>
       </c>
       <c r="C19" s="38" t="str">
         <f aca="false">IF(B19="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B19)))</f>
-        <v>חמישי</v>
+        <v>ראשון</v>
       </c>
       <c r="D19" s="40" t="str">
         <f aca="false">IF(B19="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -3233,7 +3285,7 @@
       <c r="I19" s="45"/>
       <c r="K19" s="27" t="n">
         <f aca="false">IF(B19="","",B19+MIN(MOD(הגדרות!$D$18-WEEKDAY(B19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B19)-1,7)+1))</f>
-        <v>46558</v>
+        <v>46527</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3243,11 +3295,11 @@
       </c>
       <c r="B20" s="39" t="n">
         <f aca="false">IF(K19="","",IF(K19&gt;$K$2,"",K19))</f>
-        <v>46558</v>
+        <v>46527</v>
       </c>
       <c r="C20" s="38" t="str">
         <f aca="false">IF(B20="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B20)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D20" s="40" t="str">
         <f aca="false">IF(B20="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -3268,7 +3320,7 @@
       <c r="I20" s="45"/>
       <c r="K20" s="27" t="n">
         <f aca="false">IF(B20="","",B20+MIN(MOD(הגדרות!$D$18-WEEKDAY(B20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B20)-1,7)+1))</f>
-        <v>46562</v>
+        <v>46530</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3278,11 +3330,11 @@
       </c>
       <c r="B21" s="39" t="n">
         <f aca="false">IF(K20="","",IF(K20&gt;$K$2,"",K20))</f>
-        <v>46562</v>
+        <v>46530</v>
       </c>
       <c r="C21" s="38" t="str">
         <f aca="false">IF(B21="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B21)))</f>
-        <v>חמישי</v>
+        <v>ראשון</v>
       </c>
       <c r="D21" s="40" t="str">
         <f aca="false">IF(B21="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -3303,7 +3355,7 @@
       <c r="I21" s="45"/>
       <c r="K21" s="27" t="n">
         <f aca="false">IF(B21="","",B21+MIN(MOD(הגדרות!$D$18-WEEKDAY(B21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B21)-1,7)+1))</f>
-        <v>46565</v>
+        <v>46534</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3313,11 +3365,11 @@
       </c>
       <c r="B22" s="39" t="n">
         <f aca="false">IF(K21="","",IF(K21&gt;$K$2,"",K21))</f>
-        <v>46565</v>
+        <v>46534</v>
       </c>
       <c r="C22" s="38" t="str">
         <f aca="false">IF(B22="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B22)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D22" s="40" t="str">
         <f aca="false">IF(B22="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -3338,42 +3390,42 @@
       <c r="I22" s="45"/>
       <c r="K22" s="27" t="n">
         <f aca="false">IF(B22="","",B22+MIN(MOD(הגדרות!$D$18-WEEKDAY(B22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B22)-1,7)+1))</f>
-        <v>46569</v>
+        <v>46537</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="38" t="str">
+      <c r="A23" s="38" t="n">
         <f aca="false">IF(B23="","",ROW()-14)</f>
-        <v/>
-      </c>
-      <c r="B23" s="39" t="str">
+        <v>9</v>
+      </c>
+      <c r="B23" s="39" t="n">
         <f aca="false">IF(K22="","",IF(K22&gt;$K$2,"",K22))</f>
-        <v/>
+        <v>46537</v>
       </c>
       <c r="C23" s="38" t="str">
         <f aca="false">IF(B23="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B23)))</f>
-        <v/>
+        <v>ראשון</v>
       </c>
       <c r="D23" s="40" t="str">
         <f aca="false">IF(B23="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
-        <v/>
+        <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E23" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="F23" s="42" t="str">
+      <c r="F23" s="42" t="n">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
-        <v/>
-      </c>
-      <c r="G23" s="43" t="str">
+        <v>3.5</v>
+      </c>
+      <c r="G23" s="43" t="n">
         <f aca="false">IF(B23="","",F23*הגדרות!$C$24)</f>
-        <v/>
+        <v>175</v>
       </c>
       <c r="H23" s="44"/>
       <c r="I23" s="45"/>
-      <c r="K23" s="27" t="str">
+      <c r="K23" s="27" t="n">
         <f aca="false">IF(B23="","",B23+MIN(MOD(הגדרות!$D$18-WEEKDAY(B23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B23)-1,7)+1))</f>
-        <v/>
+        <v>46541</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3414,7 +3466,7 @@
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="38" t="n">
         <f aca="false">COUNT($B$15:$B$24)+1</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B25" s="46"/>
       <c r="C25" s="38" t="str">
@@ -3449,11 +3501,11 @@
       <c r="E26" s="47"/>
       <c r="F26" s="48" t="n">
         <f aca="false">SUM(F15:F25)</f>
-        <v>29</v>
+        <v>32.5</v>
       </c>
       <c r="G26" s="49" t="n">
         <f aca="false">SUM(G15:G25)</f>
-        <v>1450</v>
+        <v>1625</v>
       </c>
       <c r="H26" s="47"/>
       <c r="I26" s="49" t="n">
@@ -3475,7 +3527,7 @@
       <c r="H28" s="40"/>
       <c r="I28" s="42" t="n">
         <f aca="false">F26</f>
-        <v>29</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3489,13 +3541,13 @@
       <c r="E29" s="51"/>
       <c r="F29" s="40" t="str">
         <f aca="false">"הדרכת שיקום ("&amp;TEXT(F26,"0.0")&amp;" שעות × "&amp;הגדרות!$C$24&amp;" ₪)"</f>
-        <v>הדרכת שיקום (29.0 שעות × 50 ₪)</v>
+        <v>הדרכת שיקום (32.5 שעות × 50 ₪)</v>
       </c>
       <c r="G29" s="40"/>
       <c r="H29" s="40"/>
       <c r="I29" s="43" t="n">
         <f aca="false">G26</f>
-        <v>1450</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3533,7 +3585,7 @@
       <c r="H31" s="52"/>
       <c r="I31" s="53" t="n">
         <f aca="false">I29+I30</f>
-        <v>1450</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3553,7 +3605,7 @@
       <c r="H32" s="40"/>
       <c r="I32" s="43" t="n">
         <f aca="false">ROUND(I31*הגדרות!$C$25,2)</f>
-        <v>261</v>
+        <v>292.5</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3564,7 +3616,7 @@
       <c r="H33" s="54"/>
       <c r="I33" s="55" t="n">
         <f aca="false">I31+I32</f>
-        <v>1711</v>
+        <v>1917.5</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3690,13 +3742,13 @@
       <c r="I1" s="26"/>
       <c r="K1" s="27" t="n">
         <f aca="false">DATE(YEAR($H$11),MONTH($H$11),1)</f>
-        <v>46569</v>
+        <v>46539</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="str">
         <f aca="false">הגדרות!$C$17&amp;" · "&amp;CHOOSE(MONTH($K$1),"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר")&amp;" "&amp;YEAR($K$1)</f>
-        <v>הדרכת שיקום · יולי 2027</v>
+        <v>הדרכת שיקום · יוני 2027</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -3708,7 +3760,7 @@
       <c r="I2" s="28"/>
       <c r="K2" s="27" t="n">
         <f aca="false">EOMONTH($K$1,0)</f>
-        <v>46599</v>
+        <v>46568</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3816,7 +3868,7 @@
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
         <f aca="false">YEAR($K$1)&amp;"-"&amp;TEXT(MONTH($K$1),"00")</f>
-        <v>2027-07</v>
+        <v>2027-06</v>
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
@@ -3824,7 +3876,7 @@
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
-        <v>46569</v>
+        <v>46539</v>
       </c>
       <c r="I11" s="32"/>
     </row>
@@ -3835,7 +3887,7 @@
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
         <f aca="false">$K$2</f>
-        <v>46599</v>
+        <v>46568</v>
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
@@ -3899,7 +3951,7 @@
       </c>
       <c r="B15" s="39" t="n">
         <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
-        <v>46569</v>
+        <v>46541</v>
       </c>
       <c r="C15" s="38" t="str">
         <f aca="false">IF(B15="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B15)))</f>
@@ -3924,7 +3976,7 @@
       <c r="I15" s="45"/>
       <c r="K15" s="27" t="n">
         <f aca="false">IF(B15="","",B15+MIN(MOD(הגדרות!$D$18-WEEKDAY(B15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B15)-1,7)+1))</f>
-        <v>46572</v>
+        <v>46544</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3934,7 +3986,7 @@
       </c>
       <c r="B16" s="39" t="n">
         <f aca="false">IF(K15="","",IF(K15&gt;$K$2,"",K15))</f>
-        <v>46572</v>
+        <v>46544</v>
       </c>
       <c r="C16" s="38" t="str">
         <f aca="false">IF(B16="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B16)))</f>
@@ -3959,7 +4011,7 @@
       <c r="I16" s="45"/>
       <c r="K16" s="27" t="n">
         <f aca="false">IF(B16="","",B16+MIN(MOD(הגדרות!$D$18-WEEKDAY(B16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B16)-1,7)+1))</f>
-        <v>46576</v>
+        <v>46548</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3969,7 +4021,7 @@
       </c>
       <c r="B17" s="39" t="n">
         <f aca="false">IF(K16="","",IF(K16&gt;$K$2,"",K16))</f>
-        <v>46576</v>
+        <v>46548</v>
       </c>
       <c r="C17" s="38" t="str">
         <f aca="false">IF(B17="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B17)))</f>
@@ -3994,7 +4046,7 @@
       <c r="I17" s="45"/>
       <c r="K17" s="27" t="n">
         <f aca="false">IF(B17="","",B17+MIN(MOD(הגדרות!$D$18-WEEKDAY(B17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B17)-1,7)+1))</f>
-        <v>46579</v>
+        <v>46551</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4004,7 +4056,7 @@
       </c>
       <c r="B18" s="39" t="n">
         <f aca="false">IF(K17="","",IF(K17&gt;$K$2,"",K17))</f>
-        <v>46579</v>
+        <v>46551</v>
       </c>
       <c r="C18" s="38" t="str">
         <f aca="false">IF(B18="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B18)))</f>
@@ -4029,7 +4081,7 @@
       <c r="I18" s="45"/>
       <c r="K18" s="27" t="n">
         <f aca="false">IF(B18="","",B18+MIN(MOD(הגדרות!$D$18-WEEKDAY(B18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B18)-1,7)+1))</f>
-        <v>46583</v>
+        <v>46555</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4039,7 +4091,7 @@
       </c>
       <c r="B19" s="39" t="n">
         <f aca="false">IF(K18="","",IF(K18&gt;$K$2,"",K18))</f>
-        <v>46583</v>
+        <v>46555</v>
       </c>
       <c r="C19" s="38" t="str">
         <f aca="false">IF(B19="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B19)))</f>
@@ -4064,7 +4116,7 @@
       <c r="I19" s="45"/>
       <c r="K19" s="27" t="n">
         <f aca="false">IF(B19="","",B19+MIN(MOD(הגדרות!$D$18-WEEKDAY(B19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B19)-1,7)+1))</f>
-        <v>46586</v>
+        <v>46558</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4074,7 +4126,7 @@
       </c>
       <c r="B20" s="39" t="n">
         <f aca="false">IF(K19="","",IF(K19&gt;$K$2,"",K19))</f>
-        <v>46586</v>
+        <v>46558</v>
       </c>
       <c r="C20" s="38" t="str">
         <f aca="false">IF(B20="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B20)))</f>
@@ -4099,7 +4151,7 @@
       <c r="I20" s="45"/>
       <c r="K20" s="27" t="n">
         <f aca="false">IF(B20="","",B20+MIN(MOD(הגדרות!$D$18-WEEKDAY(B20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B20)-1,7)+1))</f>
-        <v>46590</v>
+        <v>46562</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4109,7 +4161,7 @@
       </c>
       <c r="B21" s="39" t="n">
         <f aca="false">IF(K20="","",IF(K20&gt;$K$2,"",K20))</f>
-        <v>46590</v>
+        <v>46562</v>
       </c>
       <c r="C21" s="38" t="str">
         <f aca="false">IF(B21="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B21)))</f>
@@ -4134,7 +4186,7 @@
       <c r="I21" s="45"/>
       <c r="K21" s="27" t="n">
         <f aca="false">IF(B21="","",B21+MIN(MOD(הגדרות!$D$18-WEEKDAY(B21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B21)-1,7)+1))</f>
-        <v>46593</v>
+        <v>46565</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4144,7 +4196,7 @@
       </c>
       <c r="B22" s="39" t="n">
         <f aca="false">IF(K21="","",IF(K21&gt;$K$2,"",K21))</f>
-        <v>46593</v>
+        <v>46565</v>
       </c>
       <c r="C22" s="38" t="str">
         <f aca="false">IF(B22="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B22)))</f>
@@ -4169,42 +4221,42 @@
       <c r="I22" s="45"/>
       <c r="K22" s="27" t="n">
         <f aca="false">IF(B22="","",B22+MIN(MOD(הגדרות!$D$18-WEEKDAY(B22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B22)-1,7)+1))</f>
-        <v>46597</v>
+        <v>46569</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="38" t="n">
+      <c r="A23" s="38" t="str">
         <f aca="false">IF(B23="","",ROW()-14)</f>
-        <v>9</v>
-      </c>
-      <c r="B23" s="39" t="n">
+        <v/>
+      </c>
+      <c r="B23" s="39" t="str">
         <f aca="false">IF(K22="","",IF(K22&gt;$K$2,"",K22))</f>
-        <v>46597</v>
+        <v/>
       </c>
       <c r="C23" s="38" t="str">
         <f aca="false">IF(B23="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B23)))</f>
-        <v>חמישי</v>
+        <v/>
       </c>
       <c r="D23" s="40" t="str">
         <f aca="false">IF(B23="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
-        <v>הדרכה 09:00–12:30</v>
+        <v/>
       </c>
       <c r="E23" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="F23" s="42" t="n">
+      <c r="F23" s="42" t="str">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
-        <v>3.5</v>
-      </c>
-      <c r="G23" s="43" t="n">
+        <v/>
+      </c>
+      <c r="G23" s="43" t="str">
         <f aca="false">IF(B23="","",F23*הגדרות!$C$24)</f>
-        <v>175</v>
+        <v/>
       </c>
       <c r="H23" s="44"/>
       <c r="I23" s="45"/>
-      <c r="K23" s="27" t="n">
+      <c r="K23" s="27" t="str">
         <f aca="false">IF(B23="","",B23+MIN(MOD(הגדרות!$D$18-WEEKDAY(B23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B23)-1,7)+1))</f>
-        <v>46600</v>
+        <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4245,7 +4297,7 @@
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="38" t="n">
         <f aca="false">COUNT($B$15:$B$24)+1</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B25" s="46"/>
       <c r="C25" s="38" t="str">
@@ -4280,11 +4332,11 @@
       <c r="E26" s="47"/>
       <c r="F26" s="48" t="n">
         <f aca="false">SUM(F15:F25)</f>
-        <v>32.5</v>
+        <v>29</v>
       </c>
       <c r="G26" s="49" t="n">
         <f aca="false">SUM(G15:G25)</f>
-        <v>1625</v>
+        <v>1450</v>
       </c>
       <c r="H26" s="47"/>
       <c r="I26" s="49" t="n">
@@ -4306,7 +4358,7 @@
       <c r="H28" s="40"/>
       <c r="I28" s="42" t="n">
         <f aca="false">F26</f>
-        <v>32.5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4320,13 +4372,13 @@
       <c r="E29" s="51"/>
       <c r="F29" s="40" t="str">
         <f aca="false">"הדרכת שיקום ("&amp;TEXT(F26,"0.0")&amp;" שעות × "&amp;הגדרות!$C$24&amp;" ₪)"</f>
-        <v>הדרכת שיקום (32.5 שעות × 50 ₪)</v>
+        <v>הדרכת שיקום (29.0 שעות × 50 ₪)</v>
       </c>
       <c r="G29" s="40"/>
       <c r="H29" s="40"/>
       <c r="I29" s="43" t="n">
         <f aca="false">G26</f>
-        <v>1625</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4364,7 +4416,7 @@
       <c r="H31" s="52"/>
       <c r="I31" s="53" t="n">
         <f aca="false">I29+I30</f>
-        <v>1625</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4384,7 +4436,7 @@
       <c r="H32" s="40"/>
       <c r="I32" s="43" t="n">
         <f aca="false">ROUND(I31*הגדרות!$C$25,2)</f>
-        <v>292.5</v>
+        <v>261</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4395,7 +4447,7 @@
       <c r="H33" s="54"/>
       <c r="I33" s="55" t="n">
         <f aca="false">I31+I32</f>
-        <v>1917.5</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4521,13 +4573,13 @@
       <c r="I1" s="26"/>
       <c r="K1" s="27" t="n">
         <f aca="false">DATE(YEAR($H$11),MONTH($H$11),1)</f>
-        <v>46600</v>
+        <v>46569</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="str">
         <f aca="false">הגדרות!$C$17&amp;" · "&amp;CHOOSE(MONTH($K$1),"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר")&amp;" "&amp;YEAR($K$1)</f>
-        <v>הדרכת שיקום · אוגוסט 2027</v>
+        <v>הדרכת שיקום · יולי 2027</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -4539,7 +4591,7 @@
       <c r="I2" s="28"/>
       <c r="K2" s="27" t="n">
         <f aca="false">EOMONTH($K$1,0)</f>
-        <v>46630</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4647,7 +4699,7 @@
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
         <f aca="false">YEAR($K$1)&amp;"-"&amp;TEXT(MONTH($K$1),"00")</f>
-        <v>2027-08</v>
+        <v>2027-07</v>
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
@@ -4655,7 +4707,7 @@
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
-        <v>46600</v>
+        <v>46569</v>
       </c>
       <c r="I11" s="32"/>
     </row>
@@ -4666,7 +4718,7 @@
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
         <f aca="false">$K$2</f>
-        <v>46630</v>
+        <v>46599</v>
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
@@ -4730,11 +4782,11 @@
       </c>
       <c r="B15" s="39" t="n">
         <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
-        <v>46600</v>
+        <v>46569</v>
       </c>
       <c r="C15" s="38" t="str">
         <f aca="false">IF(B15="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B15)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D15" s="40" t="str">
         <f aca="false">IF(B15="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -4755,7 +4807,7 @@
       <c r="I15" s="45"/>
       <c r="K15" s="27" t="n">
         <f aca="false">IF(B15="","",B15+MIN(MOD(הגדרות!$D$18-WEEKDAY(B15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B15)-1,7)+1))</f>
-        <v>46604</v>
+        <v>46572</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4765,11 +4817,11 @@
       </c>
       <c r="B16" s="39" t="n">
         <f aca="false">IF(K15="","",IF(K15&gt;$K$2,"",K15))</f>
-        <v>46604</v>
+        <v>46572</v>
       </c>
       <c r="C16" s="38" t="str">
         <f aca="false">IF(B16="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B16)))</f>
-        <v>חמישי</v>
+        <v>ראשון</v>
       </c>
       <c r="D16" s="40" t="str">
         <f aca="false">IF(B16="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -4790,7 +4842,7 @@
       <c r="I16" s="45"/>
       <c r="K16" s="27" t="n">
         <f aca="false">IF(B16="","",B16+MIN(MOD(הגדרות!$D$18-WEEKDAY(B16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B16)-1,7)+1))</f>
-        <v>46607</v>
+        <v>46576</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4800,11 +4852,11 @@
       </c>
       <c r="B17" s="39" t="n">
         <f aca="false">IF(K16="","",IF(K16&gt;$K$2,"",K16))</f>
-        <v>46607</v>
+        <v>46576</v>
       </c>
       <c r="C17" s="38" t="str">
         <f aca="false">IF(B17="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B17)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D17" s="40" t="str">
         <f aca="false">IF(B17="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -4825,7 +4877,7 @@
       <c r="I17" s="45"/>
       <c r="K17" s="27" t="n">
         <f aca="false">IF(B17="","",B17+MIN(MOD(הגדרות!$D$18-WEEKDAY(B17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B17)-1,7)+1))</f>
-        <v>46611</v>
+        <v>46579</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4835,11 +4887,11 @@
       </c>
       <c r="B18" s="39" t="n">
         <f aca="false">IF(K17="","",IF(K17&gt;$K$2,"",K17))</f>
-        <v>46611</v>
+        <v>46579</v>
       </c>
       <c r="C18" s="38" t="str">
         <f aca="false">IF(B18="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B18)))</f>
-        <v>חמישי</v>
+        <v>ראשון</v>
       </c>
       <c r="D18" s="40" t="str">
         <f aca="false">IF(B18="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -4860,7 +4912,7 @@
       <c r="I18" s="45"/>
       <c r="K18" s="27" t="n">
         <f aca="false">IF(B18="","",B18+MIN(MOD(הגדרות!$D$18-WEEKDAY(B18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B18)-1,7)+1))</f>
-        <v>46614</v>
+        <v>46583</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4870,11 +4922,11 @@
       </c>
       <c r="B19" s="39" t="n">
         <f aca="false">IF(K18="","",IF(K18&gt;$K$2,"",K18))</f>
-        <v>46614</v>
+        <v>46583</v>
       </c>
       <c r="C19" s="38" t="str">
         <f aca="false">IF(B19="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B19)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D19" s="40" t="str">
         <f aca="false">IF(B19="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -4895,7 +4947,7 @@
       <c r="I19" s="45"/>
       <c r="K19" s="27" t="n">
         <f aca="false">IF(B19="","",B19+MIN(MOD(הגדרות!$D$18-WEEKDAY(B19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B19)-1,7)+1))</f>
-        <v>46618</v>
+        <v>46586</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4905,11 +4957,11 @@
       </c>
       <c r="B20" s="39" t="n">
         <f aca="false">IF(K19="","",IF(K19&gt;$K$2,"",K19))</f>
-        <v>46618</v>
+        <v>46586</v>
       </c>
       <c r="C20" s="38" t="str">
         <f aca="false">IF(B20="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B20)))</f>
-        <v>חמישי</v>
+        <v>ראשון</v>
       </c>
       <c r="D20" s="40" t="str">
         <f aca="false">IF(B20="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -4930,7 +4982,7 @@
       <c r="I20" s="45"/>
       <c r="K20" s="27" t="n">
         <f aca="false">IF(B20="","",B20+MIN(MOD(הגדרות!$D$18-WEEKDAY(B20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B20)-1,7)+1))</f>
-        <v>46621</v>
+        <v>46590</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4940,11 +4992,11 @@
       </c>
       <c r="B21" s="39" t="n">
         <f aca="false">IF(K20="","",IF(K20&gt;$K$2,"",K20))</f>
-        <v>46621</v>
+        <v>46590</v>
       </c>
       <c r="C21" s="38" t="str">
         <f aca="false">IF(B21="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B21)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D21" s="40" t="str">
         <f aca="false">IF(B21="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -4965,7 +5017,7 @@
       <c r="I21" s="45"/>
       <c r="K21" s="27" t="n">
         <f aca="false">IF(B21="","",B21+MIN(MOD(הגדרות!$D$18-WEEKDAY(B21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B21)-1,7)+1))</f>
-        <v>46625</v>
+        <v>46593</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4975,11 +5027,11 @@
       </c>
       <c r="B22" s="39" t="n">
         <f aca="false">IF(K21="","",IF(K21&gt;$K$2,"",K21))</f>
-        <v>46625</v>
+        <v>46593</v>
       </c>
       <c r="C22" s="38" t="str">
         <f aca="false">IF(B22="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B22)))</f>
-        <v>חמישי</v>
+        <v>ראשון</v>
       </c>
       <c r="D22" s="40" t="str">
         <f aca="false">IF(B22="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -5000,7 +5052,7 @@
       <c r="I22" s="45"/>
       <c r="K22" s="27" t="n">
         <f aca="false">IF(B22="","",B22+MIN(MOD(הגדרות!$D$18-WEEKDAY(B22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B22)-1,7)+1))</f>
-        <v>46628</v>
+        <v>46597</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5010,11 +5062,11 @@
       </c>
       <c r="B23" s="39" t="n">
         <f aca="false">IF(K22="","",IF(K22&gt;$K$2,"",K22))</f>
-        <v>46628</v>
+        <v>46597</v>
       </c>
       <c r="C23" s="38" t="str">
         <f aca="false">IF(B23="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B23)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D23" s="40" t="str">
         <f aca="false">IF(B23="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -5035,7 +5087,7 @@
       <c r="I23" s="45"/>
       <c r="K23" s="27" t="n">
         <f aca="false">IF(B23="","",B23+MIN(MOD(הגדרות!$D$18-WEEKDAY(B23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B23)-1,7)+1))</f>
-        <v>46632</v>
+        <v>46600</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5352,6 +5404,837 @@
       <c r="I1" s="26"/>
       <c r="K1" s="27" t="n">
         <f aca="false">DATE(YEAR($H$11),MONTH($H$11),1)</f>
+        <v>46600</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="28" t="str">
+        <f aca="false">הגדרות!$C$17&amp;" · "&amp;CHOOSE(MONTH($K$1),"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר")&amp;" "&amp;YEAR($K$1)</f>
+        <v>הדרכת שיקום · אוגוסט 2027</v>
+      </c>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="K2" s="27" t="n">
+        <f aca="false">EOMONTH($K$1,0)</f>
+        <v>46630</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="F4" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="30"/>
+      <c r="C5" s="31" t="str">
+        <f aca="false">הגדרות!$C$5</f>
+        <v>הנגרייה</v>
+      </c>
+      <c r="D5" s="31"/>
+      <c r="F5" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="30"/>
+      <c r="H5" s="31" t="str">
+        <f aca="false">הגדרות!$C$12</f>
+        <v>חוות רום</v>
+      </c>
+      <c r="I5" s="31"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="30"/>
+      <c r="C6" s="31" t="str">
+        <f aca="false">הגדרות!$C$6</f>
+        <v>(למילוי)</v>
+      </c>
+      <c r="D6" s="31"/>
+      <c r="F6" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="30"/>
+      <c r="H6" s="31" t="str">
+        <f aca="false">הגדרות!$C$13</f>
+        <v>הר כמון</v>
+      </c>
+      <c r="I6" s="31"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="30"/>
+      <c r="C7" s="31" t="str">
+        <f aca="false">הגדרות!$C$7</f>
+        <v>(למילוי)</v>
+      </c>
+      <c r="D7" s="31"/>
+      <c r="F7" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="30"/>
+      <c r="H7" s="31" t="str">
+        <f aca="false">הגדרות!$C$14</f>
+        <v>(למילוי)</v>
+      </c>
+      <c r="I7" s="31"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="30"/>
+      <c r="C8" s="31" t="str">
+        <f aca="false">הגדרות!$C$8</f>
+        <v>(למילוי)</v>
+      </c>
+      <c r="D8" s="31"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="30"/>
+      <c r="C9" s="31" t="str">
+        <f aca="false">הגדרות!$C$9</f>
+        <v>nettaamit21@gmail.com</v>
+      </c>
+      <c r="D9" s="31"/>
+    </row>
+    <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="30"/>
+      <c r="C11" s="31" t="str">
+        <f aca="false">YEAR($K$1)&amp;"-"&amp;TEXT(MONTH($K$1),"00")</f>
+        <v>2027-08</v>
+      </c>
+      <c r="D11" s="31"/>
+      <c r="F11" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="G11" s="30"/>
+      <c r="H11" s="32" t="n">
+        <v>46600</v>
+      </c>
+      <c r="I11" s="32"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="30"/>
+      <c r="C12" s="33" t="n">
+        <f aca="false">$K$2</f>
+        <v>46630</v>
+      </c>
+      <c r="D12" s="33"/>
+      <c r="F12" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12" s="30"/>
+      <c r="H12" s="31" t="str">
+        <f aca="false">הגדרות!$C$18&amp;" ו"&amp;הגדרות!$C$19&amp;", "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00")</f>
+        <v>ראשון וחמישי, 09:00–12:30</v>
+      </c>
+      <c r="I12" s="31"/>
+    </row>
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="35" t="s">
+        <v>76</v>
+      </c>
+      <c r="I13" s="35"/>
+    </row>
+    <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="F14" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="G14" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="37" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="38" t="n">
+        <f aca="false">IF(B15="","",ROW()-14)</f>
+        <v>1</v>
+      </c>
+      <c r="B15" s="39" t="n">
+        <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
+        <v>46600</v>
+      </c>
+      <c r="C15" s="38" t="str">
+        <f aca="false">IF(B15="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B15)))</f>
+        <v>ראשון</v>
+      </c>
+      <c r="D15" s="40" t="str">
+        <f aca="false">IF(B15="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
+        <v>הדרכה 09:00–12:30</v>
+      </c>
+      <c r="E15" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="F15" s="42" t="n">
+        <f aca="false">IF(B15="","",IF(E15="לא",0,הגדרות!$C$22))</f>
+        <v>3.5</v>
+      </c>
+      <c r="G15" s="43" t="n">
+        <f aca="false">IF(B15="","",F15*הגדרות!$C$24)</f>
+        <v>175</v>
+      </c>
+      <c r="H15" s="44"/>
+      <c r="I15" s="45"/>
+      <c r="K15" s="27" t="n">
+        <f aca="false">IF(B15="","",B15+MIN(MOD(הגדרות!$D$18-WEEKDAY(B15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B15)-1,7)+1))</f>
+        <v>46604</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="38" t="n">
+        <f aca="false">IF(B16="","",ROW()-14)</f>
+        <v>2</v>
+      </c>
+      <c r="B16" s="39" t="n">
+        <f aca="false">IF(K15="","",IF(K15&gt;$K$2,"",K15))</f>
+        <v>46604</v>
+      </c>
+      <c r="C16" s="38" t="str">
+        <f aca="false">IF(B16="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B16)))</f>
+        <v>חמישי</v>
+      </c>
+      <c r="D16" s="40" t="str">
+        <f aca="false">IF(B16="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
+        <v>הדרכה 09:00–12:30</v>
+      </c>
+      <c r="E16" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="F16" s="42" t="n">
+        <f aca="false">IF(B16="","",IF(E16="לא",0,הגדרות!$C$22))</f>
+        <v>3.5</v>
+      </c>
+      <c r="G16" s="43" t="n">
+        <f aca="false">IF(B16="","",F16*הגדרות!$C$24)</f>
+        <v>175</v>
+      </c>
+      <c r="H16" s="44"/>
+      <c r="I16" s="45"/>
+      <c r="K16" s="27" t="n">
+        <f aca="false">IF(B16="","",B16+MIN(MOD(הגדרות!$D$18-WEEKDAY(B16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B16)-1,7)+1))</f>
+        <v>46607</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="38" t="n">
+        <f aca="false">IF(B17="","",ROW()-14)</f>
+        <v>3</v>
+      </c>
+      <c r="B17" s="39" t="n">
+        <f aca="false">IF(K16="","",IF(K16&gt;$K$2,"",K16))</f>
+        <v>46607</v>
+      </c>
+      <c r="C17" s="38" t="str">
+        <f aca="false">IF(B17="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B17)))</f>
+        <v>ראשון</v>
+      </c>
+      <c r="D17" s="40" t="str">
+        <f aca="false">IF(B17="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
+        <v>הדרכה 09:00–12:30</v>
+      </c>
+      <c r="E17" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="F17" s="42" t="n">
+        <f aca="false">IF(B17="","",IF(E17="לא",0,הגדרות!$C$22))</f>
+        <v>3.5</v>
+      </c>
+      <c r="G17" s="43" t="n">
+        <f aca="false">IF(B17="","",F17*הגדרות!$C$24)</f>
+        <v>175</v>
+      </c>
+      <c r="H17" s="44"/>
+      <c r="I17" s="45"/>
+      <c r="K17" s="27" t="n">
+        <f aca="false">IF(B17="","",B17+MIN(MOD(הגדרות!$D$18-WEEKDAY(B17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B17)-1,7)+1))</f>
+        <v>46611</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="38" t="n">
+        <f aca="false">IF(B18="","",ROW()-14)</f>
+        <v>4</v>
+      </c>
+      <c r="B18" s="39" t="n">
+        <f aca="false">IF(K17="","",IF(K17&gt;$K$2,"",K17))</f>
+        <v>46611</v>
+      </c>
+      <c r="C18" s="38" t="str">
+        <f aca="false">IF(B18="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B18)))</f>
+        <v>חמישי</v>
+      </c>
+      <c r="D18" s="40" t="str">
+        <f aca="false">IF(B18="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
+        <v>הדרכה 09:00–12:30</v>
+      </c>
+      <c r="E18" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="F18" s="42" t="n">
+        <f aca="false">IF(B18="","",IF(E18="לא",0,הגדרות!$C$22))</f>
+        <v>3.5</v>
+      </c>
+      <c r="G18" s="43" t="n">
+        <f aca="false">IF(B18="","",F18*הגדרות!$C$24)</f>
+        <v>175</v>
+      </c>
+      <c r="H18" s="44"/>
+      <c r="I18" s="45"/>
+      <c r="K18" s="27" t="n">
+        <f aca="false">IF(B18="","",B18+MIN(MOD(הגדרות!$D$18-WEEKDAY(B18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B18)-1,7)+1))</f>
+        <v>46614</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="38" t="n">
+        <f aca="false">IF(B19="","",ROW()-14)</f>
+        <v>5</v>
+      </c>
+      <c r="B19" s="39" t="n">
+        <f aca="false">IF(K18="","",IF(K18&gt;$K$2,"",K18))</f>
+        <v>46614</v>
+      </c>
+      <c r="C19" s="38" t="str">
+        <f aca="false">IF(B19="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B19)))</f>
+        <v>ראשון</v>
+      </c>
+      <c r="D19" s="40" t="str">
+        <f aca="false">IF(B19="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
+        <v>הדרכה 09:00–12:30</v>
+      </c>
+      <c r="E19" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="F19" s="42" t="n">
+        <f aca="false">IF(B19="","",IF(E19="לא",0,הגדרות!$C$22))</f>
+        <v>3.5</v>
+      </c>
+      <c r="G19" s="43" t="n">
+        <f aca="false">IF(B19="","",F19*הגדרות!$C$24)</f>
+        <v>175</v>
+      </c>
+      <c r="H19" s="44"/>
+      <c r="I19" s="45"/>
+      <c r="K19" s="27" t="n">
+        <f aca="false">IF(B19="","",B19+MIN(MOD(הגדרות!$D$18-WEEKDAY(B19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B19)-1,7)+1))</f>
+        <v>46618</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="38" t="n">
+        <f aca="false">IF(B20="","",ROW()-14)</f>
+        <v>6</v>
+      </c>
+      <c r="B20" s="39" t="n">
+        <f aca="false">IF(K19="","",IF(K19&gt;$K$2,"",K19))</f>
+        <v>46618</v>
+      </c>
+      <c r="C20" s="38" t="str">
+        <f aca="false">IF(B20="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B20)))</f>
+        <v>חמישי</v>
+      </c>
+      <c r="D20" s="40" t="str">
+        <f aca="false">IF(B20="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
+        <v>הדרכה 09:00–12:30</v>
+      </c>
+      <c r="E20" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="F20" s="42" t="n">
+        <f aca="false">IF(B20="","",IF(E20="לא",0,הגדרות!$C$22))</f>
+        <v>3.5</v>
+      </c>
+      <c r="G20" s="43" t="n">
+        <f aca="false">IF(B20="","",F20*הגדרות!$C$24)</f>
+        <v>175</v>
+      </c>
+      <c r="H20" s="44"/>
+      <c r="I20" s="45"/>
+      <c r="K20" s="27" t="n">
+        <f aca="false">IF(B20="","",B20+MIN(MOD(הגדרות!$D$18-WEEKDAY(B20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B20)-1,7)+1))</f>
+        <v>46621</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="38" t="n">
+        <f aca="false">IF(B21="","",ROW()-14)</f>
+        <v>7</v>
+      </c>
+      <c r="B21" s="39" t="n">
+        <f aca="false">IF(K20="","",IF(K20&gt;$K$2,"",K20))</f>
+        <v>46621</v>
+      </c>
+      <c r="C21" s="38" t="str">
+        <f aca="false">IF(B21="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B21)))</f>
+        <v>ראשון</v>
+      </c>
+      <c r="D21" s="40" t="str">
+        <f aca="false">IF(B21="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
+        <v>הדרכה 09:00–12:30</v>
+      </c>
+      <c r="E21" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="F21" s="42" t="n">
+        <f aca="false">IF(B21="","",IF(E21="לא",0,הגדרות!$C$22))</f>
+        <v>3.5</v>
+      </c>
+      <c r="G21" s="43" t="n">
+        <f aca="false">IF(B21="","",F21*הגדרות!$C$24)</f>
+        <v>175</v>
+      </c>
+      <c r="H21" s="44"/>
+      <c r="I21" s="45"/>
+      <c r="K21" s="27" t="n">
+        <f aca="false">IF(B21="","",B21+MIN(MOD(הגדרות!$D$18-WEEKDAY(B21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B21)-1,7)+1))</f>
+        <v>46625</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="38" t="n">
+        <f aca="false">IF(B22="","",ROW()-14)</f>
+        <v>8</v>
+      </c>
+      <c r="B22" s="39" t="n">
+        <f aca="false">IF(K21="","",IF(K21&gt;$K$2,"",K21))</f>
+        <v>46625</v>
+      </c>
+      <c r="C22" s="38" t="str">
+        <f aca="false">IF(B22="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B22)))</f>
+        <v>חמישי</v>
+      </c>
+      <c r="D22" s="40" t="str">
+        <f aca="false">IF(B22="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
+        <v>הדרכה 09:00–12:30</v>
+      </c>
+      <c r="E22" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="F22" s="42" t="n">
+        <f aca="false">IF(B22="","",IF(E22="לא",0,הגדרות!$C$22))</f>
+        <v>3.5</v>
+      </c>
+      <c r="G22" s="43" t="n">
+        <f aca="false">IF(B22="","",F22*הגדרות!$C$24)</f>
+        <v>175</v>
+      </c>
+      <c r="H22" s="44"/>
+      <c r="I22" s="45"/>
+      <c r="K22" s="27" t="n">
+        <f aca="false">IF(B22="","",B22+MIN(MOD(הגדרות!$D$18-WEEKDAY(B22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B22)-1,7)+1))</f>
+        <v>46628</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="38" t="n">
+        <f aca="false">IF(B23="","",ROW()-14)</f>
+        <v>9</v>
+      </c>
+      <c r="B23" s="39" t="n">
+        <f aca="false">IF(K22="","",IF(K22&gt;$K$2,"",K22))</f>
+        <v>46628</v>
+      </c>
+      <c r="C23" s="38" t="str">
+        <f aca="false">IF(B23="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B23)))</f>
+        <v>ראשון</v>
+      </c>
+      <c r="D23" s="40" t="str">
+        <f aca="false">IF(B23="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
+        <v>הדרכה 09:00–12:30</v>
+      </c>
+      <c r="E23" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="F23" s="42" t="n">
+        <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
+        <v>3.5</v>
+      </c>
+      <c r="G23" s="43" t="n">
+        <f aca="false">IF(B23="","",F23*הגדרות!$C$24)</f>
+        <v>175</v>
+      </c>
+      <c r="H23" s="44"/>
+      <c r="I23" s="45"/>
+      <c r="K23" s="27" t="n">
+        <f aca="false">IF(B23="","",B23+MIN(MOD(הגדרות!$D$18-WEEKDAY(B23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B23)-1,7)+1))</f>
+        <v>46632</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="38" t="str">
+        <f aca="false">IF(B24="","",ROW()-14)</f>
+        <v/>
+      </c>
+      <c r="B24" s="39" t="str">
+        <f aca="false">IF(K23="","",IF(K23&gt;$K$2,"",K23))</f>
+        <v/>
+      </c>
+      <c r="C24" s="38" t="str">
+        <f aca="false">IF(B24="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B24)))</f>
+        <v/>
+      </c>
+      <c r="D24" s="40" t="str">
+        <f aca="false">IF(B24="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
+        <v/>
+      </c>
+      <c r="E24" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="F24" s="42" t="str">
+        <f aca="false">IF(B24="","",IF(E24="לא",0,הגדרות!$C$22))</f>
+        <v/>
+      </c>
+      <c r="G24" s="43" t="str">
+        <f aca="false">IF(B24="","",F24*הגדרות!$C$24)</f>
+        <v/>
+      </c>
+      <c r="H24" s="44"/>
+      <c r="I24" s="45"/>
+      <c r="K24" s="27" t="str">
+        <f aca="false">IF(B24="","",B24+MIN(MOD(הגדרות!$D$18-WEEKDAY(B24)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B24)-1,7)+1))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="38" t="n">
+        <f aca="false">COUNT($B$15:$B$24)+1</f>
+        <v>10</v>
+      </c>
+      <c r="B25" s="46"/>
+      <c r="C25" s="38" t="str">
+        <f aca="false">IF(B25="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B25)))</f>
+        <v/>
+      </c>
+      <c r="D25" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="F25" s="42" t="n">
+        <f aca="false">IF(E25="לא",0,הגדרות!$C$23)</f>
+        <v>1</v>
+      </c>
+      <c r="G25" s="43" t="n">
+        <f aca="false">F25*הגדרות!$C$24</f>
+        <v>50</v>
+      </c>
+      <c r="H25" s="44"/>
+      <c r="I25" s="45"/>
+      <c r="K25" s="27"/>
+    </row>
+    <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" s="47"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="48" t="n">
+        <f aca="false">SUM(F15:F25)</f>
+        <v>32.5</v>
+      </c>
+      <c r="G26" s="49" t="n">
+        <f aca="false">SUM(G15:G25)</f>
+        <v>1625</v>
+      </c>
+      <c r="H26" s="47"/>
+      <c r="I26" s="49" t="n">
+        <f aca="false">SUM(I15:I25)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="B28" s="50"/>
+      <c r="C28" s="50"/>
+      <c r="D28" s="50"/>
+      <c r="F28" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="G28" s="40"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="42" t="n">
+        <f aca="false">F26</f>
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="51" t="str">
+        <f aca="false">"• "&amp;הגדרות!$C$17&amp;": ימי "&amp;הגדרות!$C$18&amp;" ו"&amp;הגדרות!$C$19&amp;", "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00")&amp;" ("&amp;הגדרות!$C$22&amp;" שעות ליום), וישיבת צוות חודשית ("&amp;הגדרות!$C$23&amp;" ש׳)."</f>
+        <v>• הדרכת שיקום: ימי ראשון וחמישי, 09:00–12:30 (3.5 שעות ליום), וישיבת צוות חודשית (1 ש׳).</v>
+      </c>
+      <c r="B29" s="51"/>
+      <c r="C29" s="51"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="51"/>
+      <c r="F29" s="40" t="str">
+        <f aca="false">"הדרכת שיקום ("&amp;TEXT(F26,"0.0")&amp;" שעות × "&amp;הגדרות!$C$24&amp;" ₪)"</f>
+        <v>הדרכת שיקום (32.5 שעות × 50 ₪)</v>
+      </c>
+      <c r="G29" s="40"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="43" t="n">
+        <f aca="false">G26</f>
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="51" t="str">
+        <f aca="false">IF(הגדרות!$C$28="","","• "&amp;הגדרות!$C$28)</f>
+        <v>• התעריף השעתי אינו כולל מע״מ. מע״מ יתווסף כחוק.</v>
+      </c>
+      <c r="B30" s="51"/>
+      <c r="C30" s="51"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="G30" s="40"/>
+      <c r="H30" s="40"/>
+      <c r="I30" s="43" t="n">
+        <f aca="false">I26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="51" t="str">
+        <f aca="false">IF(הגדרות!$C$29="","","• "&amp;הגדרות!$C$29)</f>
+        <v>• פרויקטים פרטיים מתומחרים בנפרד, לפי הזמנת החווה.</v>
+      </c>
+      <c r="B31" s="51"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="52" t="s">
+        <v>89</v>
+      </c>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="53" t="n">
+        <f aca="false">I29+I30</f>
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="51" t="str">
+        <f aca="false">IF(הגדרות!$C$30="","","• "&amp;הגדרות!$C$30)</f>
+        <v/>
+      </c>
+      <c r="B32" s="51"/>
+      <c r="C32" s="51"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="40" t="str">
+        <f aca="false">"מע״מ "&amp;ROUND(הגדרות!$C$25*100,1)&amp;"%"</f>
+        <v>מע״מ 18%</v>
+      </c>
+      <c r="G32" s="40"/>
+      <c r="H32" s="40"/>
+      <c r="I32" s="43" t="n">
+        <f aca="false">ROUND(I31*הגדרות!$C$25,2)</f>
+        <v>292.5</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F33" s="54" t="s">
+        <v>90</v>
+      </c>
+      <c r="G33" s="54"/>
+      <c r="H33" s="54"/>
+      <c r="I33" s="55" t="n">
+        <f aca="false">I31+I32</f>
+        <v>1917.5</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="56" t="str">
+        <f aca="false">"בברכה, "&amp;הגדרות!$C$6</f>
+        <v>בברכה, (למילוי)</v>
+      </c>
+      <c r="B36" s="56"/>
+      <c r="C36" s="56"/>
+      <c r="D36" s="56"/>
+      <c r="F36" s="56" t="s">
+        <v>91</v>
+      </c>
+      <c r="G36" s="56"/>
+      <c r="H36" s="56"/>
+      <c r="I36" s="56"/>
+    </row>
+  </sheetData>
+  <mergeCells count="44">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="F36:I36"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E15:E24">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$B15=""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A15:G25">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>$E15="לא"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E15:E25" type="list">
+      <formula1>"כן,לא"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:K36"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="11" min="11" style="0" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="K1" s="27" t="n">
+        <f aca="false">DATE(YEAR($H$11),MONTH($H$11),1)</f>
         <v>46631</v>
       </c>
     </row>
@@ -6447,13 +7330,13 @@
       <c r="I1" s="26"/>
       <c r="K1" s="27" t="n">
         <f aca="false">DATE(YEAR($H$11),MONTH($H$11),1)</f>
-        <v>46296</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="str">
         <f aca="false">הגדרות!$C$17&amp;" · "&amp;CHOOSE(MONTH($K$1),"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר")&amp;" "&amp;YEAR($K$1)</f>
-        <v>הדרכת שיקום · אוקטובר 2026</v>
+        <v>הדרכת שיקום · ספטמבר 2026</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -6465,7 +7348,7 @@
       <c r="I2" s="28"/>
       <c r="K2" s="27" t="n">
         <f aca="false">EOMONTH($K$1,0)</f>
-        <v>46326</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -6573,7 +7456,7 @@
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
         <f aca="false">YEAR($K$1)&amp;"-"&amp;TEXT(MONTH($K$1),"00")</f>
-        <v>2026-10</v>
+        <v>2026-09</v>
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
@@ -6581,7 +7464,7 @@
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
-        <v>46296</v>
+        <v>46266</v>
       </c>
       <c r="I11" s="32"/>
     </row>
@@ -6592,7 +7475,7 @@
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
         <f aca="false">$K$2</f>
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
@@ -6656,7 +7539,7 @@
       </c>
       <c r="B15" s="39" t="n">
         <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
-        <v>46296</v>
+        <v>46268</v>
       </c>
       <c r="C15" s="38" t="str">
         <f aca="false">IF(B15="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B15)))</f>
@@ -6681,7 +7564,7 @@
       <c r="I15" s="45"/>
       <c r="K15" s="27" t="n">
         <f aca="false">IF(B15="","",B15+MIN(MOD(הגדרות!$D$18-WEEKDAY(B15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B15)-1,7)+1))</f>
-        <v>46299</v>
+        <v>46271</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6691,7 +7574,7 @@
       </c>
       <c r="B16" s="39" t="n">
         <f aca="false">IF(K15="","",IF(K15&gt;$K$2,"",K15))</f>
-        <v>46299</v>
+        <v>46271</v>
       </c>
       <c r="C16" s="38" t="str">
         <f aca="false">IF(B16="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B16)))</f>
@@ -6716,7 +7599,7 @@
       <c r="I16" s="45"/>
       <c r="K16" s="27" t="n">
         <f aca="false">IF(B16="","",B16+MIN(MOD(הגדרות!$D$18-WEEKDAY(B16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B16)-1,7)+1))</f>
-        <v>46303</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6726,7 +7609,7 @@
       </c>
       <c r="B17" s="39" t="n">
         <f aca="false">IF(K16="","",IF(K16&gt;$K$2,"",K16))</f>
-        <v>46303</v>
+        <v>46275</v>
       </c>
       <c r="C17" s="38" t="str">
         <f aca="false">IF(B17="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B17)))</f>
@@ -6751,7 +7634,7 @@
       <c r="I17" s="45"/>
       <c r="K17" s="27" t="n">
         <f aca="false">IF(B17="","",B17+MIN(MOD(הגדרות!$D$18-WEEKDAY(B17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B17)-1,7)+1))</f>
-        <v>46306</v>
+        <v>46278</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6761,7 +7644,7 @@
       </c>
       <c r="B18" s="39" t="n">
         <f aca="false">IF(K17="","",IF(K17&gt;$K$2,"",K17))</f>
-        <v>46306</v>
+        <v>46278</v>
       </c>
       <c r="C18" s="38" t="str">
         <f aca="false">IF(B18="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B18)))</f>
@@ -6786,7 +7669,7 @@
       <c r="I18" s="45"/>
       <c r="K18" s="27" t="n">
         <f aca="false">IF(B18="","",B18+MIN(MOD(הגדרות!$D$18-WEEKDAY(B18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B18)-1,7)+1))</f>
-        <v>46310</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6796,7 +7679,7 @@
       </c>
       <c r="B19" s="39" t="n">
         <f aca="false">IF(K18="","",IF(K18&gt;$K$2,"",K18))</f>
-        <v>46310</v>
+        <v>46282</v>
       </c>
       <c r="C19" s="38" t="str">
         <f aca="false">IF(B19="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B19)))</f>
@@ -6821,7 +7704,7 @@
       <c r="I19" s="45"/>
       <c r="K19" s="27" t="n">
         <f aca="false">IF(B19="","",B19+MIN(MOD(הגדרות!$D$18-WEEKDAY(B19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B19)-1,7)+1))</f>
-        <v>46313</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6831,7 +7714,7 @@
       </c>
       <c r="B20" s="39" t="n">
         <f aca="false">IF(K19="","",IF(K19&gt;$K$2,"",K19))</f>
-        <v>46313</v>
+        <v>46285</v>
       </c>
       <c r="C20" s="38" t="str">
         <f aca="false">IF(B20="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B20)))</f>
@@ -6856,7 +7739,7 @@
       <c r="I20" s="45"/>
       <c r="K20" s="27" t="n">
         <f aca="false">IF(B20="","",B20+MIN(MOD(הגדרות!$D$18-WEEKDAY(B20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B20)-1,7)+1))</f>
-        <v>46317</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6866,7 +7749,7 @@
       </c>
       <c r="B21" s="39" t="n">
         <f aca="false">IF(K20="","",IF(K20&gt;$K$2,"",K20))</f>
-        <v>46317</v>
+        <v>46289</v>
       </c>
       <c r="C21" s="38" t="str">
         <f aca="false">IF(B21="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B21)))</f>
@@ -6891,7 +7774,7 @@
       <c r="I21" s="45"/>
       <c r="K21" s="27" t="n">
         <f aca="false">IF(B21="","",B21+MIN(MOD(הגדרות!$D$18-WEEKDAY(B21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B21)-1,7)+1))</f>
-        <v>46320</v>
+        <v>46292</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6901,7 +7784,7 @@
       </c>
       <c r="B22" s="39" t="n">
         <f aca="false">IF(K21="","",IF(K21&gt;$K$2,"",K21))</f>
-        <v>46320</v>
+        <v>46292</v>
       </c>
       <c r="C22" s="38" t="str">
         <f aca="false">IF(B22="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B22)))</f>
@@ -6926,42 +7809,42 @@
       <c r="I22" s="45"/>
       <c r="K22" s="27" t="n">
         <f aca="false">IF(B22="","",B22+MIN(MOD(הגדרות!$D$18-WEEKDAY(B22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B22)-1,7)+1))</f>
-        <v>46324</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="38" t="n">
+      <c r="A23" s="38" t="str">
         <f aca="false">IF(B23="","",ROW()-14)</f>
-        <v>9</v>
-      </c>
-      <c r="B23" s="39" t="n">
+        <v/>
+      </c>
+      <c r="B23" s="39" t="str">
         <f aca="false">IF(K22="","",IF(K22&gt;$K$2,"",K22))</f>
-        <v>46324</v>
+        <v/>
       </c>
       <c r="C23" s="38" t="str">
         <f aca="false">IF(B23="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B23)))</f>
-        <v>חמישי</v>
+        <v/>
       </c>
       <c r="D23" s="40" t="str">
         <f aca="false">IF(B23="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
-        <v>הדרכה 09:00–12:30</v>
+        <v/>
       </c>
       <c r="E23" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="F23" s="42" t="n">
+      <c r="F23" s="42" t="str">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
-        <v>3.5</v>
-      </c>
-      <c r="G23" s="43" t="n">
+        <v/>
+      </c>
+      <c r="G23" s="43" t="str">
         <f aca="false">IF(B23="","",F23*הגדרות!$C$24)</f>
-        <v>175</v>
+        <v/>
       </c>
       <c r="H23" s="44"/>
       <c r="I23" s="45"/>
-      <c r="K23" s="27" t="n">
+      <c r="K23" s="27" t="str">
         <f aca="false">IF(B23="","",B23+MIN(MOD(הגדרות!$D$18-WEEKDAY(B23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B23)-1,7)+1))</f>
-        <v>46327</v>
+        <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7002,7 +7885,7 @@
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="38" t="n">
         <f aca="false">COUNT($B$15:$B$24)+1</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B25" s="46"/>
       <c r="C25" s="38" t="str">
@@ -7037,11 +7920,11 @@
       <c r="E26" s="47"/>
       <c r="F26" s="48" t="n">
         <f aca="false">SUM(F15:F25)</f>
-        <v>32.5</v>
+        <v>29</v>
       </c>
       <c r="G26" s="49" t="n">
         <f aca="false">SUM(G15:G25)</f>
-        <v>1625</v>
+        <v>1450</v>
       </c>
       <c r="H26" s="47"/>
       <c r="I26" s="49" t="n">
@@ -7063,7 +7946,7 @@
       <c r="H28" s="40"/>
       <c r="I28" s="42" t="n">
         <f aca="false">F26</f>
-        <v>32.5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7077,13 +7960,13 @@
       <c r="E29" s="51"/>
       <c r="F29" s="40" t="str">
         <f aca="false">"הדרכת שיקום ("&amp;TEXT(F26,"0.0")&amp;" שעות × "&amp;הגדרות!$C$24&amp;" ₪)"</f>
-        <v>הדרכת שיקום (32.5 שעות × 50 ₪)</v>
+        <v>הדרכת שיקום (29.0 שעות × 50 ₪)</v>
       </c>
       <c r="G29" s="40"/>
       <c r="H29" s="40"/>
       <c r="I29" s="43" t="n">
         <f aca="false">G26</f>
-        <v>1625</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7121,7 +8004,7 @@
       <c r="H31" s="52"/>
       <c r="I31" s="53" t="n">
         <f aca="false">I29+I30</f>
-        <v>1625</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7141,7 +8024,7 @@
       <c r="H32" s="40"/>
       <c r="I32" s="43" t="n">
         <f aca="false">ROUND(I31*הגדרות!$C$25,2)</f>
-        <v>292.5</v>
+        <v>261</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7152,7 +8035,7 @@
       <c r="H33" s="54"/>
       <c r="I33" s="55" t="n">
         <f aca="false">I31+I32</f>
-        <v>1917.5</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7278,13 +8161,13 @@
       <c r="I1" s="26"/>
       <c r="K1" s="27" t="n">
         <f aca="false">DATE(YEAR($H$11),MONTH($H$11),1)</f>
-        <v>46327</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="str">
         <f aca="false">הגדרות!$C$17&amp;" · "&amp;CHOOSE(MONTH($K$1),"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר")&amp;" "&amp;YEAR($K$1)</f>
-        <v>הדרכת שיקום · נובמבר 2026</v>
+        <v>הדרכת שיקום · אוקטובר 2026</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -7296,7 +8179,7 @@
       <c r="I2" s="28"/>
       <c r="K2" s="27" t="n">
         <f aca="false">EOMONTH($K$1,0)</f>
-        <v>46356</v>
+        <v>46326</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -7404,7 +8287,7 @@
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
         <f aca="false">YEAR($K$1)&amp;"-"&amp;TEXT(MONTH($K$1),"00")</f>
-        <v>2026-11</v>
+        <v>2026-10</v>
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
@@ -7412,7 +8295,7 @@
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
-        <v>46327</v>
+        <v>46296</v>
       </c>
       <c r="I11" s="32"/>
     </row>
@@ -7423,7 +8306,7 @@
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
         <f aca="false">$K$2</f>
-        <v>46356</v>
+        <v>46326</v>
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
@@ -7487,11 +8370,11 @@
       </c>
       <c r="B15" s="39" t="n">
         <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
-        <v>46327</v>
+        <v>46296</v>
       </c>
       <c r="C15" s="38" t="str">
         <f aca="false">IF(B15="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B15)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D15" s="40" t="str">
         <f aca="false">IF(B15="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -7512,7 +8395,7 @@
       <c r="I15" s="45"/>
       <c r="K15" s="27" t="n">
         <f aca="false">IF(B15="","",B15+MIN(MOD(הגדרות!$D$18-WEEKDAY(B15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B15)-1,7)+1))</f>
-        <v>46331</v>
+        <v>46299</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7522,11 +8405,11 @@
       </c>
       <c r="B16" s="39" t="n">
         <f aca="false">IF(K15="","",IF(K15&gt;$K$2,"",K15))</f>
-        <v>46331</v>
+        <v>46299</v>
       </c>
       <c r="C16" s="38" t="str">
         <f aca="false">IF(B16="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B16)))</f>
-        <v>חמישי</v>
+        <v>ראשון</v>
       </c>
       <c r="D16" s="40" t="str">
         <f aca="false">IF(B16="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -7547,7 +8430,7 @@
       <c r="I16" s="45"/>
       <c r="K16" s="27" t="n">
         <f aca="false">IF(B16="","",B16+MIN(MOD(הגדרות!$D$18-WEEKDAY(B16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B16)-1,7)+1))</f>
-        <v>46334</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7557,11 +8440,11 @@
       </c>
       <c r="B17" s="39" t="n">
         <f aca="false">IF(K16="","",IF(K16&gt;$K$2,"",K16))</f>
-        <v>46334</v>
+        <v>46303</v>
       </c>
       <c r="C17" s="38" t="str">
         <f aca="false">IF(B17="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B17)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D17" s="40" t="str">
         <f aca="false">IF(B17="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -7582,7 +8465,7 @@
       <c r="I17" s="45"/>
       <c r="K17" s="27" t="n">
         <f aca="false">IF(B17="","",B17+MIN(MOD(הגדרות!$D$18-WEEKDAY(B17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B17)-1,7)+1))</f>
-        <v>46338</v>
+        <v>46306</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7592,11 +8475,11 @@
       </c>
       <c r="B18" s="39" t="n">
         <f aca="false">IF(K17="","",IF(K17&gt;$K$2,"",K17))</f>
-        <v>46338</v>
+        <v>46306</v>
       </c>
       <c r="C18" s="38" t="str">
         <f aca="false">IF(B18="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B18)))</f>
-        <v>חמישי</v>
+        <v>ראשון</v>
       </c>
       <c r="D18" s="40" t="str">
         <f aca="false">IF(B18="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -7617,7 +8500,7 @@
       <c r="I18" s="45"/>
       <c r="K18" s="27" t="n">
         <f aca="false">IF(B18="","",B18+MIN(MOD(הגדרות!$D$18-WEEKDAY(B18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B18)-1,7)+1))</f>
-        <v>46341</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7627,11 +8510,11 @@
       </c>
       <c r="B19" s="39" t="n">
         <f aca="false">IF(K18="","",IF(K18&gt;$K$2,"",K18))</f>
-        <v>46341</v>
+        <v>46310</v>
       </c>
       <c r="C19" s="38" t="str">
         <f aca="false">IF(B19="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B19)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D19" s="40" t="str">
         <f aca="false">IF(B19="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -7652,7 +8535,7 @@
       <c r="I19" s="45"/>
       <c r="K19" s="27" t="n">
         <f aca="false">IF(B19="","",B19+MIN(MOD(הגדרות!$D$18-WEEKDAY(B19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B19)-1,7)+1))</f>
-        <v>46345</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7662,11 +8545,11 @@
       </c>
       <c r="B20" s="39" t="n">
         <f aca="false">IF(K19="","",IF(K19&gt;$K$2,"",K19))</f>
-        <v>46345</v>
+        <v>46313</v>
       </c>
       <c r="C20" s="38" t="str">
         <f aca="false">IF(B20="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B20)))</f>
-        <v>חמישי</v>
+        <v>ראשון</v>
       </c>
       <c r="D20" s="40" t="str">
         <f aca="false">IF(B20="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -7687,7 +8570,7 @@
       <c r="I20" s="45"/>
       <c r="K20" s="27" t="n">
         <f aca="false">IF(B20="","",B20+MIN(MOD(הגדרות!$D$18-WEEKDAY(B20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B20)-1,7)+1))</f>
-        <v>46348</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7697,11 +8580,11 @@
       </c>
       <c r="B21" s="39" t="n">
         <f aca="false">IF(K20="","",IF(K20&gt;$K$2,"",K20))</f>
-        <v>46348</v>
+        <v>46317</v>
       </c>
       <c r="C21" s="38" t="str">
         <f aca="false">IF(B21="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B21)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D21" s="40" t="str">
         <f aca="false">IF(B21="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -7722,7 +8605,7 @@
       <c r="I21" s="45"/>
       <c r="K21" s="27" t="n">
         <f aca="false">IF(B21="","",B21+MIN(MOD(הגדרות!$D$18-WEEKDAY(B21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B21)-1,7)+1))</f>
-        <v>46352</v>
+        <v>46320</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7732,11 +8615,11 @@
       </c>
       <c r="B22" s="39" t="n">
         <f aca="false">IF(K21="","",IF(K21&gt;$K$2,"",K21))</f>
-        <v>46352</v>
+        <v>46320</v>
       </c>
       <c r="C22" s="38" t="str">
         <f aca="false">IF(B22="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B22)))</f>
-        <v>חמישי</v>
+        <v>ראשון</v>
       </c>
       <c r="D22" s="40" t="str">
         <f aca="false">IF(B22="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -7757,7 +8640,7 @@
       <c r="I22" s="45"/>
       <c r="K22" s="27" t="n">
         <f aca="false">IF(B22="","",B22+MIN(MOD(הגדרות!$D$18-WEEKDAY(B22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B22)-1,7)+1))</f>
-        <v>46355</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7767,11 +8650,11 @@
       </c>
       <c r="B23" s="39" t="n">
         <f aca="false">IF(K22="","",IF(K22&gt;$K$2,"",K22))</f>
-        <v>46355</v>
+        <v>46324</v>
       </c>
       <c r="C23" s="38" t="str">
         <f aca="false">IF(B23="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B23)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D23" s="40" t="str">
         <f aca="false">IF(B23="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -7792,7 +8675,7 @@
       <c r="I23" s="45"/>
       <c r="K23" s="27" t="n">
         <f aca="false">IF(B23="","",B23+MIN(MOD(הגדרות!$D$18-WEEKDAY(B23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B23)-1,7)+1))</f>
-        <v>46359</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8109,13 +8992,13 @@
       <c r="I1" s="26"/>
       <c r="K1" s="27" t="n">
         <f aca="false">DATE(YEAR($H$11),MONTH($H$11),1)</f>
-        <v>46357</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="str">
         <f aca="false">הגדרות!$C$17&amp;" · "&amp;CHOOSE(MONTH($K$1),"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר")&amp;" "&amp;YEAR($K$1)</f>
-        <v>הדרכת שיקום · דצמבר 2026</v>
+        <v>הדרכת שיקום · נובמבר 2026</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -8127,7 +9010,7 @@
       <c r="I2" s="28"/>
       <c r="K2" s="27" t="n">
         <f aca="false">EOMONTH($K$1,0)</f>
-        <v>46387</v>
+        <v>46356</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -8235,7 +9118,7 @@
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
         <f aca="false">YEAR($K$1)&amp;"-"&amp;TEXT(MONTH($K$1),"00")</f>
-        <v>2026-12</v>
+        <v>2026-11</v>
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
@@ -8243,7 +9126,7 @@
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
-        <v>46357</v>
+        <v>46327</v>
       </c>
       <c r="I11" s="32"/>
     </row>
@@ -8254,7 +9137,7 @@
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
         <f aca="false">$K$2</f>
-        <v>46387</v>
+        <v>46356</v>
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
@@ -8318,11 +9201,11 @@
       </c>
       <c r="B15" s="39" t="n">
         <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
-        <v>46359</v>
+        <v>46327</v>
       </c>
       <c r="C15" s="38" t="str">
         <f aca="false">IF(B15="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B15)))</f>
-        <v>חמישי</v>
+        <v>ראשון</v>
       </c>
       <c r="D15" s="40" t="str">
         <f aca="false">IF(B15="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -8343,7 +9226,7 @@
       <c r="I15" s="45"/>
       <c r="K15" s="27" t="n">
         <f aca="false">IF(B15="","",B15+MIN(MOD(הגדרות!$D$18-WEEKDAY(B15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B15)-1,7)+1))</f>
-        <v>46362</v>
+        <v>46331</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8353,11 +9236,11 @@
       </c>
       <c r="B16" s="39" t="n">
         <f aca="false">IF(K15="","",IF(K15&gt;$K$2,"",K15))</f>
-        <v>46362</v>
+        <v>46331</v>
       </c>
       <c r="C16" s="38" t="str">
         <f aca="false">IF(B16="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B16)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D16" s="40" t="str">
         <f aca="false">IF(B16="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -8378,7 +9261,7 @@
       <c r="I16" s="45"/>
       <c r="K16" s="27" t="n">
         <f aca="false">IF(B16="","",B16+MIN(MOD(הגדרות!$D$18-WEEKDAY(B16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B16)-1,7)+1))</f>
-        <v>46366</v>
+        <v>46334</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8388,11 +9271,11 @@
       </c>
       <c r="B17" s="39" t="n">
         <f aca="false">IF(K16="","",IF(K16&gt;$K$2,"",K16))</f>
-        <v>46366</v>
+        <v>46334</v>
       </c>
       <c r="C17" s="38" t="str">
         <f aca="false">IF(B17="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B17)))</f>
-        <v>חמישי</v>
+        <v>ראשון</v>
       </c>
       <c r="D17" s="40" t="str">
         <f aca="false">IF(B17="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -8413,7 +9296,7 @@
       <c r="I17" s="45"/>
       <c r="K17" s="27" t="n">
         <f aca="false">IF(B17="","",B17+MIN(MOD(הגדרות!$D$18-WEEKDAY(B17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B17)-1,7)+1))</f>
-        <v>46369</v>
+        <v>46338</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8423,11 +9306,11 @@
       </c>
       <c r="B18" s="39" t="n">
         <f aca="false">IF(K17="","",IF(K17&gt;$K$2,"",K17))</f>
-        <v>46369</v>
+        <v>46338</v>
       </c>
       <c r="C18" s="38" t="str">
         <f aca="false">IF(B18="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B18)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D18" s="40" t="str">
         <f aca="false">IF(B18="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -8448,7 +9331,7 @@
       <c r="I18" s="45"/>
       <c r="K18" s="27" t="n">
         <f aca="false">IF(B18="","",B18+MIN(MOD(הגדרות!$D$18-WEEKDAY(B18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B18)-1,7)+1))</f>
-        <v>46373</v>
+        <v>46341</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8458,11 +9341,11 @@
       </c>
       <c r="B19" s="39" t="n">
         <f aca="false">IF(K18="","",IF(K18&gt;$K$2,"",K18))</f>
-        <v>46373</v>
+        <v>46341</v>
       </c>
       <c r="C19" s="38" t="str">
         <f aca="false">IF(B19="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B19)))</f>
-        <v>חמישי</v>
+        <v>ראשון</v>
       </c>
       <c r="D19" s="40" t="str">
         <f aca="false">IF(B19="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -8483,7 +9366,7 @@
       <c r="I19" s="45"/>
       <c r="K19" s="27" t="n">
         <f aca="false">IF(B19="","",B19+MIN(MOD(הגדרות!$D$18-WEEKDAY(B19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B19)-1,7)+1))</f>
-        <v>46376</v>
+        <v>46345</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8493,11 +9376,11 @@
       </c>
       <c r="B20" s="39" t="n">
         <f aca="false">IF(K19="","",IF(K19&gt;$K$2,"",K19))</f>
-        <v>46376</v>
+        <v>46345</v>
       </c>
       <c r="C20" s="38" t="str">
         <f aca="false">IF(B20="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B20)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D20" s="40" t="str">
         <f aca="false">IF(B20="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -8518,7 +9401,7 @@
       <c r="I20" s="45"/>
       <c r="K20" s="27" t="n">
         <f aca="false">IF(B20="","",B20+MIN(MOD(הגדרות!$D$18-WEEKDAY(B20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B20)-1,7)+1))</f>
-        <v>46380</v>
+        <v>46348</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8528,11 +9411,11 @@
       </c>
       <c r="B21" s="39" t="n">
         <f aca="false">IF(K20="","",IF(K20&gt;$K$2,"",K20))</f>
-        <v>46380</v>
+        <v>46348</v>
       </c>
       <c r="C21" s="38" t="str">
         <f aca="false">IF(B21="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B21)))</f>
-        <v>חמישי</v>
+        <v>ראשון</v>
       </c>
       <c r="D21" s="40" t="str">
         <f aca="false">IF(B21="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -8553,7 +9436,7 @@
       <c r="I21" s="45"/>
       <c r="K21" s="27" t="n">
         <f aca="false">IF(B21="","",B21+MIN(MOD(הגדרות!$D$18-WEEKDAY(B21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B21)-1,7)+1))</f>
-        <v>46383</v>
+        <v>46352</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8563,11 +9446,11 @@
       </c>
       <c r="B22" s="39" t="n">
         <f aca="false">IF(K21="","",IF(K21&gt;$K$2,"",K21))</f>
-        <v>46383</v>
+        <v>46352</v>
       </c>
       <c r="C22" s="38" t="str">
         <f aca="false">IF(B22="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B22)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D22" s="40" t="str">
         <f aca="false">IF(B22="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -8588,7 +9471,7 @@
       <c r="I22" s="45"/>
       <c r="K22" s="27" t="n">
         <f aca="false">IF(B22="","",B22+MIN(MOD(הגדרות!$D$18-WEEKDAY(B22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B22)-1,7)+1))</f>
-        <v>46387</v>
+        <v>46355</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8598,11 +9481,11 @@
       </c>
       <c r="B23" s="39" t="n">
         <f aca="false">IF(K22="","",IF(K22&gt;$K$2,"",K22))</f>
-        <v>46387</v>
+        <v>46355</v>
       </c>
       <c r="C23" s="38" t="str">
         <f aca="false">IF(B23="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B23)))</f>
-        <v>חמישי</v>
+        <v>ראשון</v>
       </c>
       <c r="D23" s="40" t="str">
         <f aca="false">IF(B23="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -8623,7 +9506,7 @@
       <c r="I23" s="45"/>
       <c r="K23" s="27" t="n">
         <f aca="false">IF(B23="","",B23+MIN(MOD(הגדרות!$D$18-WEEKDAY(B23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B23)-1,7)+1))</f>
-        <v>46390</v>
+        <v>46359</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8940,13 +9823,13 @@
       <c r="I1" s="26"/>
       <c r="K1" s="27" t="n">
         <f aca="false">DATE(YEAR($H$11),MONTH($H$11),1)</f>
-        <v>46388</v>
+        <v>46357</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="str">
         <f aca="false">הגדרות!$C$17&amp;" · "&amp;CHOOSE(MONTH($K$1),"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר")&amp;" "&amp;YEAR($K$1)</f>
-        <v>הדרכת שיקום · ינואר 2027</v>
+        <v>הדרכת שיקום · דצמבר 2026</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -8958,7 +9841,7 @@
       <c r="I2" s="28"/>
       <c r="K2" s="27" t="n">
         <f aca="false">EOMONTH($K$1,0)</f>
-        <v>46418</v>
+        <v>46387</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -9066,7 +9949,7 @@
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
         <f aca="false">YEAR($K$1)&amp;"-"&amp;TEXT(MONTH($K$1),"00")</f>
-        <v>2027-01</v>
+        <v>2026-12</v>
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
@@ -9074,7 +9957,7 @@
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
-        <v>46388</v>
+        <v>46357</v>
       </c>
       <c r="I11" s="32"/>
     </row>
@@ -9085,7 +9968,7 @@
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
         <f aca="false">$K$2</f>
-        <v>46418</v>
+        <v>46387</v>
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
@@ -9149,11 +10032,11 @@
       </c>
       <c r="B15" s="39" t="n">
         <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
-        <v>46390</v>
+        <v>46359</v>
       </c>
       <c r="C15" s="38" t="str">
         <f aca="false">IF(B15="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B15)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D15" s="40" t="str">
         <f aca="false">IF(B15="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -9174,7 +10057,7 @@
       <c r="I15" s="45"/>
       <c r="K15" s="27" t="n">
         <f aca="false">IF(B15="","",B15+MIN(MOD(הגדרות!$D$18-WEEKDAY(B15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B15)-1,7)+1))</f>
-        <v>46394</v>
+        <v>46362</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9184,11 +10067,11 @@
       </c>
       <c r="B16" s="39" t="n">
         <f aca="false">IF(K15="","",IF(K15&gt;$K$2,"",K15))</f>
-        <v>46394</v>
+        <v>46362</v>
       </c>
       <c r="C16" s="38" t="str">
         <f aca="false">IF(B16="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B16)))</f>
-        <v>חמישי</v>
+        <v>ראשון</v>
       </c>
       <c r="D16" s="40" t="str">
         <f aca="false">IF(B16="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -9209,7 +10092,7 @@
       <c r="I16" s="45"/>
       <c r="K16" s="27" t="n">
         <f aca="false">IF(B16="","",B16+MIN(MOD(הגדרות!$D$18-WEEKDAY(B16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B16)-1,7)+1))</f>
-        <v>46397</v>
+        <v>46366</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9219,11 +10102,11 @@
       </c>
       <c r="B17" s="39" t="n">
         <f aca="false">IF(K16="","",IF(K16&gt;$K$2,"",K16))</f>
-        <v>46397</v>
+        <v>46366</v>
       </c>
       <c r="C17" s="38" t="str">
         <f aca="false">IF(B17="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B17)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D17" s="40" t="str">
         <f aca="false">IF(B17="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -9244,7 +10127,7 @@
       <c r="I17" s="45"/>
       <c r="K17" s="27" t="n">
         <f aca="false">IF(B17="","",B17+MIN(MOD(הגדרות!$D$18-WEEKDAY(B17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B17)-1,7)+1))</f>
-        <v>46401</v>
+        <v>46369</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9254,11 +10137,11 @@
       </c>
       <c r="B18" s="39" t="n">
         <f aca="false">IF(K17="","",IF(K17&gt;$K$2,"",K17))</f>
-        <v>46401</v>
+        <v>46369</v>
       </c>
       <c r="C18" s="38" t="str">
         <f aca="false">IF(B18="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B18)))</f>
-        <v>חמישי</v>
+        <v>ראשון</v>
       </c>
       <c r="D18" s="40" t="str">
         <f aca="false">IF(B18="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -9279,7 +10162,7 @@
       <c r="I18" s="45"/>
       <c r="K18" s="27" t="n">
         <f aca="false">IF(B18="","",B18+MIN(MOD(הגדרות!$D$18-WEEKDAY(B18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B18)-1,7)+1))</f>
-        <v>46404</v>
+        <v>46373</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9289,11 +10172,11 @@
       </c>
       <c r="B19" s="39" t="n">
         <f aca="false">IF(K18="","",IF(K18&gt;$K$2,"",K18))</f>
-        <v>46404</v>
+        <v>46373</v>
       </c>
       <c r="C19" s="38" t="str">
         <f aca="false">IF(B19="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B19)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D19" s="40" t="str">
         <f aca="false">IF(B19="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -9314,7 +10197,7 @@
       <c r="I19" s="45"/>
       <c r="K19" s="27" t="n">
         <f aca="false">IF(B19="","",B19+MIN(MOD(הגדרות!$D$18-WEEKDAY(B19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B19)-1,7)+1))</f>
-        <v>46408</v>
+        <v>46376</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9324,11 +10207,11 @@
       </c>
       <c r="B20" s="39" t="n">
         <f aca="false">IF(K19="","",IF(K19&gt;$K$2,"",K19))</f>
-        <v>46408</v>
+        <v>46376</v>
       </c>
       <c r="C20" s="38" t="str">
         <f aca="false">IF(B20="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B20)))</f>
-        <v>חמישי</v>
+        <v>ראשון</v>
       </c>
       <c r="D20" s="40" t="str">
         <f aca="false">IF(B20="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -9349,7 +10232,7 @@
       <c r="I20" s="45"/>
       <c r="K20" s="27" t="n">
         <f aca="false">IF(B20="","",B20+MIN(MOD(הגדרות!$D$18-WEEKDAY(B20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B20)-1,7)+1))</f>
-        <v>46411</v>
+        <v>46380</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9359,11 +10242,11 @@
       </c>
       <c r="B21" s="39" t="n">
         <f aca="false">IF(K20="","",IF(K20&gt;$K$2,"",K20))</f>
-        <v>46411</v>
+        <v>46380</v>
       </c>
       <c r="C21" s="38" t="str">
         <f aca="false">IF(B21="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B21)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D21" s="40" t="str">
         <f aca="false">IF(B21="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -9384,7 +10267,7 @@
       <c r="I21" s="45"/>
       <c r="K21" s="27" t="n">
         <f aca="false">IF(B21="","",B21+MIN(MOD(הגדרות!$D$18-WEEKDAY(B21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B21)-1,7)+1))</f>
-        <v>46415</v>
+        <v>46383</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9394,11 +10277,11 @@
       </c>
       <c r="B22" s="39" t="n">
         <f aca="false">IF(K21="","",IF(K21&gt;$K$2,"",K21))</f>
-        <v>46415</v>
+        <v>46383</v>
       </c>
       <c r="C22" s="38" t="str">
         <f aca="false">IF(B22="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B22)))</f>
-        <v>חמישי</v>
+        <v>ראשון</v>
       </c>
       <c r="D22" s="40" t="str">
         <f aca="false">IF(B22="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -9419,7 +10302,7 @@
       <c r="I22" s="45"/>
       <c r="K22" s="27" t="n">
         <f aca="false">IF(B22="","",B22+MIN(MOD(הגדרות!$D$18-WEEKDAY(B22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B22)-1,7)+1))</f>
-        <v>46418</v>
+        <v>46387</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9429,11 +10312,11 @@
       </c>
       <c r="B23" s="39" t="n">
         <f aca="false">IF(K22="","",IF(K22&gt;$K$2,"",K22))</f>
-        <v>46418</v>
+        <v>46387</v>
       </c>
       <c r="C23" s="38" t="str">
         <f aca="false">IF(B23="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B23)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D23" s="40" t="str">
         <f aca="false">IF(B23="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -9454,7 +10337,7 @@
       <c r="I23" s="45"/>
       <c r="K23" s="27" t="n">
         <f aca="false">IF(B23="","",B23+MIN(MOD(הגדרות!$D$18-WEEKDAY(B23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B23)-1,7)+1))</f>
-        <v>46422</v>
+        <v>46390</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9771,13 +10654,13 @@
       <c r="I1" s="26"/>
       <c r="K1" s="27" t="n">
         <f aca="false">DATE(YEAR($H$11),MONTH($H$11),1)</f>
-        <v>46419</v>
+        <v>46388</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="str">
         <f aca="false">הגדרות!$C$17&amp;" · "&amp;CHOOSE(MONTH($K$1),"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר")&amp;" "&amp;YEAR($K$1)</f>
-        <v>הדרכת שיקום · פברואר 2027</v>
+        <v>הדרכת שיקום · ינואר 2027</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -9789,7 +10672,7 @@
       <c r="I2" s="28"/>
       <c r="K2" s="27" t="n">
         <f aca="false">EOMONTH($K$1,0)</f>
-        <v>46446</v>
+        <v>46418</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -9897,7 +10780,7 @@
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
         <f aca="false">YEAR($K$1)&amp;"-"&amp;TEXT(MONTH($K$1),"00")</f>
-        <v>2027-02</v>
+        <v>2027-01</v>
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
@@ -9905,7 +10788,7 @@
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
-        <v>46419</v>
+        <v>46388</v>
       </c>
       <c r="I11" s="32"/>
     </row>
@@ -9916,7 +10799,7 @@
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
         <f aca="false">$K$2</f>
-        <v>46446</v>
+        <v>46418</v>
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
@@ -9980,11 +10863,11 @@
       </c>
       <c r="B15" s="39" t="n">
         <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
-        <v>46422</v>
+        <v>46390</v>
       </c>
       <c r="C15" s="38" t="str">
         <f aca="false">IF(B15="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B15)))</f>
-        <v>חמישי</v>
+        <v>ראשון</v>
       </c>
       <c r="D15" s="40" t="str">
         <f aca="false">IF(B15="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -10005,7 +10888,7 @@
       <c r="I15" s="45"/>
       <c r="K15" s="27" t="n">
         <f aca="false">IF(B15="","",B15+MIN(MOD(הגדרות!$D$18-WEEKDAY(B15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B15)-1,7)+1))</f>
-        <v>46425</v>
+        <v>46394</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10015,11 +10898,11 @@
       </c>
       <c r="B16" s="39" t="n">
         <f aca="false">IF(K15="","",IF(K15&gt;$K$2,"",K15))</f>
-        <v>46425</v>
+        <v>46394</v>
       </c>
       <c r="C16" s="38" t="str">
         <f aca="false">IF(B16="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B16)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D16" s="40" t="str">
         <f aca="false">IF(B16="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -10040,7 +10923,7 @@
       <c r="I16" s="45"/>
       <c r="K16" s="27" t="n">
         <f aca="false">IF(B16="","",B16+MIN(MOD(הגדרות!$D$18-WEEKDAY(B16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B16)-1,7)+1))</f>
-        <v>46429</v>
+        <v>46397</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10050,11 +10933,11 @@
       </c>
       <c r="B17" s="39" t="n">
         <f aca="false">IF(K16="","",IF(K16&gt;$K$2,"",K16))</f>
-        <v>46429</v>
+        <v>46397</v>
       </c>
       <c r="C17" s="38" t="str">
         <f aca="false">IF(B17="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B17)))</f>
-        <v>חמישי</v>
+        <v>ראשון</v>
       </c>
       <c r="D17" s="40" t="str">
         <f aca="false">IF(B17="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -10075,7 +10958,7 @@
       <c r="I17" s="45"/>
       <c r="K17" s="27" t="n">
         <f aca="false">IF(B17="","",B17+MIN(MOD(הגדרות!$D$18-WEEKDAY(B17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B17)-1,7)+1))</f>
-        <v>46432</v>
+        <v>46401</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10085,11 +10968,11 @@
       </c>
       <c r="B18" s="39" t="n">
         <f aca="false">IF(K17="","",IF(K17&gt;$K$2,"",K17))</f>
-        <v>46432</v>
+        <v>46401</v>
       </c>
       <c r="C18" s="38" t="str">
         <f aca="false">IF(B18="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B18)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D18" s="40" t="str">
         <f aca="false">IF(B18="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -10110,7 +10993,7 @@
       <c r="I18" s="45"/>
       <c r="K18" s="27" t="n">
         <f aca="false">IF(B18="","",B18+MIN(MOD(הגדרות!$D$18-WEEKDAY(B18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B18)-1,7)+1))</f>
-        <v>46436</v>
+        <v>46404</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10120,11 +11003,11 @@
       </c>
       <c r="B19" s="39" t="n">
         <f aca="false">IF(K18="","",IF(K18&gt;$K$2,"",K18))</f>
-        <v>46436</v>
+        <v>46404</v>
       </c>
       <c r="C19" s="38" t="str">
         <f aca="false">IF(B19="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B19)))</f>
-        <v>חמישי</v>
+        <v>ראשון</v>
       </c>
       <c r="D19" s="40" t="str">
         <f aca="false">IF(B19="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -10145,7 +11028,7 @@
       <c r="I19" s="45"/>
       <c r="K19" s="27" t="n">
         <f aca="false">IF(B19="","",B19+MIN(MOD(הגדרות!$D$18-WEEKDAY(B19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B19)-1,7)+1))</f>
-        <v>46439</v>
+        <v>46408</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10155,11 +11038,11 @@
       </c>
       <c r="B20" s="39" t="n">
         <f aca="false">IF(K19="","",IF(K19&gt;$K$2,"",K19))</f>
-        <v>46439</v>
+        <v>46408</v>
       </c>
       <c r="C20" s="38" t="str">
         <f aca="false">IF(B20="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B20)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D20" s="40" t="str">
         <f aca="false">IF(B20="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -10180,7 +11063,7 @@
       <c r="I20" s="45"/>
       <c r="K20" s="27" t="n">
         <f aca="false">IF(B20="","",B20+MIN(MOD(הגדרות!$D$18-WEEKDAY(B20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B20)-1,7)+1))</f>
-        <v>46443</v>
+        <v>46411</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10190,11 +11073,11 @@
       </c>
       <c r="B21" s="39" t="n">
         <f aca="false">IF(K20="","",IF(K20&gt;$K$2,"",K20))</f>
-        <v>46443</v>
+        <v>46411</v>
       </c>
       <c r="C21" s="38" t="str">
         <f aca="false">IF(B21="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B21)))</f>
-        <v>חמישי</v>
+        <v>ראשון</v>
       </c>
       <c r="D21" s="40" t="str">
         <f aca="false">IF(B21="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -10215,7 +11098,7 @@
       <c r="I21" s="45"/>
       <c r="K21" s="27" t="n">
         <f aca="false">IF(B21="","",B21+MIN(MOD(הגדרות!$D$18-WEEKDAY(B21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B21)-1,7)+1))</f>
-        <v>46446</v>
+        <v>46415</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10225,11 +11108,11 @@
       </c>
       <c r="B22" s="39" t="n">
         <f aca="false">IF(K21="","",IF(K21&gt;$K$2,"",K21))</f>
-        <v>46446</v>
+        <v>46415</v>
       </c>
       <c r="C22" s="38" t="str">
         <f aca="false">IF(B22="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B22)))</f>
-        <v>ראשון</v>
+        <v>חמישי</v>
       </c>
       <c r="D22" s="40" t="str">
         <f aca="false">IF(B22="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
@@ -10250,42 +11133,42 @@
       <c r="I22" s="45"/>
       <c r="K22" s="27" t="n">
         <f aca="false">IF(B22="","",B22+MIN(MOD(הגדרות!$D$18-WEEKDAY(B22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B22)-1,7)+1))</f>
-        <v>46450</v>
+        <v>46418</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="38" t="str">
+      <c r="A23" s="38" t="n">
         <f aca="false">IF(B23="","",ROW()-14)</f>
-        <v/>
-      </c>
-      <c r="B23" s="39" t="str">
+        <v>9</v>
+      </c>
+      <c r="B23" s="39" t="n">
         <f aca="false">IF(K22="","",IF(K22&gt;$K$2,"",K22))</f>
-        <v/>
+        <v>46418</v>
       </c>
       <c r="C23" s="38" t="str">
         <f aca="false">IF(B23="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B23)))</f>
-        <v/>
+        <v>ראשון</v>
       </c>
       <c r="D23" s="40" t="str">
         <f aca="false">IF(B23="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
-        <v/>
+        <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E23" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="F23" s="42" t="str">
+      <c r="F23" s="42" t="n">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
-        <v/>
-      </c>
-      <c r="G23" s="43" t="str">
+        <v>3.5</v>
+      </c>
+      <c r="G23" s="43" t="n">
         <f aca="false">IF(B23="","",F23*הגדרות!$C$24)</f>
-        <v/>
+        <v>175</v>
       </c>
       <c r="H23" s="44"/>
       <c r="I23" s="45"/>
-      <c r="K23" s="27" t="str">
+      <c r="K23" s="27" t="n">
         <f aca="false">IF(B23="","",B23+MIN(MOD(הגדרות!$D$18-WEEKDAY(B23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B23)-1,7)+1))</f>
-        <v/>
+        <v>46422</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10326,7 +11209,7 @@
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="38" t="n">
         <f aca="false">COUNT($B$15:$B$24)+1</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B25" s="46"/>
       <c r="C25" s="38" t="str">
@@ -10361,11 +11244,11 @@
       <c r="E26" s="47"/>
       <c r="F26" s="48" t="n">
         <f aca="false">SUM(F15:F25)</f>
-        <v>29</v>
+        <v>32.5</v>
       </c>
       <c r="G26" s="49" t="n">
         <f aca="false">SUM(G15:G25)</f>
-        <v>1450</v>
+        <v>1625</v>
       </c>
       <c r="H26" s="47"/>
       <c r="I26" s="49" t="n">
@@ -10387,7 +11270,7 @@
       <c r="H28" s="40"/>
       <c r="I28" s="42" t="n">
         <f aca="false">F26</f>
-        <v>29</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10401,13 +11284,13 @@
       <c r="E29" s="51"/>
       <c r="F29" s="40" t="str">
         <f aca="false">"הדרכת שיקום ("&amp;TEXT(F26,"0.0")&amp;" שעות × "&amp;הגדרות!$C$24&amp;" ₪)"</f>
-        <v>הדרכת שיקום (29.0 שעות × 50 ₪)</v>
+        <v>הדרכת שיקום (32.5 שעות × 50 ₪)</v>
       </c>
       <c r="G29" s="40"/>
       <c r="H29" s="40"/>
       <c r="I29" s="43" t="n">
         <f aca="false">G26</f>
-        <v>1450</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10445,7 +11328,7 @@
       <c r="H31" s="52"/>
       <c r="I31" s="53" t="n">
         <f aca="false">I29+I30</f>
-        <v>1450</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10465,7 +11348,7 @@
       <c r="H32" s="40"/>
       <c r="I32" s="43" t="n">
         <f aca="false">ROUND(I31*הגדרות!$C$25,2)</f>
-        <v>261</v>
+        <v>292.5</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10476,7 +11359,7 @@
       <c r="H33" s="54"/>
       <c r="I33" s="55" t="n">
         <f aca="false">I31+I32</f>
-        <v>1711</v>
+        <v>1917.5</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10602,13 +11485,13 @@
       <c r="I1" s="26"/>
       <c r="K1" s="27" t="n">
         <f aca="false">DATE(YEAR($H$11),MONTH($H$11),1)</f>
-        <v>46447</v>
+        <v>46419</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="str">
         <f aca="false">הגדרות!$C$17&amp;" · "&amp;CHOOSE(MONTH($K$1),"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר")&amp;" "&amp;YEAR($K$1)</f>
-        <v>הדרכת שיקום · מרץ 2027</v>
+        <v>הדרכת שיקום · פברואר 2027</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -10620,7 +11503,7 @@
       <c r="I2" s="28"/>
       <c r="K2" s="27" t="n">
         <f aca="false">EOMONTH($K$1,0)</f>
-        <v>46477</v>
+        <v>46446</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -10728,7 +11611,7 @@
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
         <f aca="false">YEAR($K$1)&amp;"-"&amp;TEXT(MONTH($K$1),"00")</f>
-        <v>2027-03</v>
+        <v>2027-02</v>
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
@@ -10736,7 +11619,7 @@
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
-        <v>46447</v>
+        <v>46419</v>
       </c>
       <c r="I11" s="32"/>
     </row>
@@ -10747,7 +11630,7 @@
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
         <f aca="false">$K$2</f>
-        <v>46477</v>
+        <v>46446</v>
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
@@ -10811,7 +11694,7 @@
       </c>
       <c r="B15" s="39" t="n">
         <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
-        <v>46450</v>
+        <v>46422</v>
       </c>
       <c r="C15" s="38" t="str">
         <f aca="false">IF(B15="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B15)))</f>
@@ -10836,7 +11719,7 @@
       <c r="I15" s="45"/>
       <c r="K15" s="27" t="n">
         <f aca="false">IF(B15="","",B15+MIN(MOD(הגדרות!$D$18-WEEKDAY(B15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B15)-1,7)+1))</f>
-        <v>46453</v>
+        <v>46425</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10846,7 +11729,7 @@
       </c>
       <c r="B16" s="39" t="n">
         <f aca="false">IF(K15="","",IF(K15&gt;$K$2,"",K15))</f>
-        <v>46453</v>
+        <v>46425</v>
       </c>
       <c r="C16" s="38" t="str">
         <f aca="false">IF(B16="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B16)))</f>
@@ -10871,7 +11754,7 @@
       <c r="I16" s="45"/>
       <c r="K16" s="27" t="n">
         <f aca="false">IF(B16="","",B16+MIN(MOD(הגדרות!$D$18-WEEKDAY(B16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B16)-1,7)+1))</f>
-        <v>46457</v>
+        <v>46429</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10881,7 +11764,7 @@
       </c>
       <c r="B17" s="39" t="n">
         <f aca="false">IF(K16="","",IF(K16&gt;$K$2,"",K16))</f>
-        <v>46457</v>
+        <v>46429</v>
       </c>
       <c r="C17" s="38" t="str">
         <f aca="false">IF(B17="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B17)))</f>
@@ -10906,7 +11789,7 @@
       <c r="I17" s="45"/>
       <c r="K17" s="27" t="n">
         <f aca="false">IF(B17="","",B17+MIN(MOD(הגדרות!$D$18-WEEKDAY(B17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B17)-1,7)+1))</f>
-        <v>46460</v>
+        <v>46432</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10916,7 +11799,7 @@
       </c>
       <c r="B18" s="39" t="n">
         <f aca="false">IF(K17="","",IF(K17&gt;$K$2,"",K17))</f>
-        <v>46460</v>
+        <v>46432</v>
       </c>
       <c r="C18" s="38" t="str">
         <f aca="false">IF(B18="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B18)))</f>
@@ -10941,7 +11824,7 @@
       <c r="I18" s="45"/>
       <c r="K18" s="27" t="n">
         <f aca="false">IF(B18="","",B18+MIN(MOD(הגדרות!$D$18-WEEKDAY(B18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B18)-1,7)+1))</f>
-        <v>46464</v>
+        <v>46436</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10951,7 +11834,7 @@
       </c>
       <c r="B19" s="39" t="n">
         <f aca="false">IF(K18="","",IF(K18&gt;$K$2,"",K18))</f>
-        <v>46464</v>
+        <v>46436</v>
       </c>
       <c r="C19" s="38" t="str">
         <f aca="false">IF(B19="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B19)))</f>
@@ -10976,7 +11859,7 @@
       <c r="I19" s="45"/>
       <c r="K19" s="27" t="n">
         <f aca="false">IF(B19="","",B19+MIN(MOD(הגדרות!$D$18-WEEKDAY(B19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B19)-1,7)+1))</f>
-        <v>46467</v>
+        <v>46439</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10986,7 +11869,7 @@
       </c>
       <c r="B20" s="39" t="n">
         <f aca="false">IF(K19="","",IF(K19&gt;$K$2,"",K19))</f>
-        <v>46467</v>
+        <v>46439</v>
       </c>
       <c r="C20" s="38" t="str">
         <f aca="false">IF(B20="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B20)))</f>
@@ -11011,7 +11894,7 @@
       <c r="I20" s="45"/>
       <c r="K20" s="27" t="n">
         <f aca="false">IF(B20="","",B20+MIN(MOD(הגדרות!$D$18-WEEKDAY(B20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B20)-1,7)+1))</f>
-        <v>46471</v>
+        <v>46443</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11021,7 +11904,7 @@
       </c>
       <c r="B21" s="39" t="n">
         <f aca="false">IF(K20="","",IF(K20&gt;$K$2,"",K20))</f>
-        <v>46471</v>
+        <v>46443</v>
       </c>
       <c r="C21" s="38" t="str">
         <f aca="false">IF(B21="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B21)))</f>
@@ -11046,7 +11929,7 @@
       <c r="I21" s="45"/>
       <c r="K21" s="27" t="n">
         <f aca="false">IF(B21="","",B21+MIN(MOD(הגדרות!$D$18-WEEKDAY(B21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B21)-1,7)+1))</f>
-        <v>46474</v>
+        <v>46446</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11056,7 +11939,7 @@
       </c>
       <c r="B22" s="39" t="n">
         <f aca="false">IF(K21="","",IF(K21&gt;$K$2,"",K21))</f>
-        <v>46474</v>
+        <v>46446</v>
       </c>
       <c r="C22" s="38" t="str">
         <f aca="false">IF(B22="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B22)))</f>
@@ -11081,7 +11964,7 @@
       <c r="I22" s="45"/>
       <c r="K22" s="27" t="n">
         <f aca="false">IF(B22="","",B22+MIN(MOD(הגדרות!$D$18-WEEKDAY(B22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B22)-1,7)+1))</f>
-        <v>46478</v>
+        <v>46450</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11433,13 +12316,13 @@
       <c r="I1" s="26"/>
       <c r="K1" s="27" t="n">
         <f aca="false">DATE(YEAR($H$11),MONTH($H$11),1)</f>
-        <v>46478</v>
+        <v>46447</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="str">
         <f aca="false">הגדרות!$C$17&amp;" · "&amp;CHOOSE(MONTH($K$1),"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר")&amp;" "&amp;YEAR($K$1)</f>
-        <v>הדרכת שיקום · אפריל 2027</v>
+        <v>הדרכת שיקום · מרץ 2027</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -11451,7 +12334,7 @@
       <c r="I2" s="28"/>
       <c r="K2" s="27" t="n">
         <f aca="false">EOMONTH($K$1,0)</f>
-        <v>46507</v>
+        <v>46477</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -11559,7 +12442,7 @@
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
         <f aca="false">YEAR($K$1)&amp;"-"&amp;TEXT(MONTH($K$1),"00")</f>
-        <v>2027-04</v>
+        <v>2027-03</v>
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
@@ -11567,7 +12450,7 @@
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
-        <v>46478</v>
+        <v>46447</v>
       </c>
       <c r="I11" s="32"/>
     </row>
@@ -11578,7 +12461,7 @@
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
         <f aca="false">$K$2</f>
-        <v>46507</v>
+        <v>46477</v>
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
@@ -11642,7 +12525,7 @@
       </c>
       <c r="B15" s="39" t="n">
         <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
-        <v>46478</v>
+        <v>46450</v>
       </c>
       <c r="C15" s="38" t="str">
         <f aca="false">IF(B15="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B15)))</f>
@@ -11667,7 +12550,7 @@
       <c r="I15" s="45"/>
       <c r="K15" s="27" t="n">
         <f aca="false">IF(B15="","",B15+MIN(MOD(הגדרות!$D$18-WEEKDAY(B15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B15)-1,7)+1))</f>
-        <v>46481</v>
+        <v>46453</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11677,7 +12560,7 @@
       </c>
       <c r="B16" s="39" t="n">
         <f aca="false">IF(K15="","",IF(K15&gt;$K$2,"",K15))</f>
-        <v>46481</v>
+        <v>46453</v>
       </c>
       <c r="C16" s="38" t="str">
         <f aca="false">IF(B16="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B16)))</f>
@@ -11702,7 +12585,7 @@
       <c r="I16" s="45"/>
       <c r="K16" s="27" t="n">
         <f aca="false">IF(B16="","",B16+MIN(MOD(הגדרות!$D$18-WEEKDAY(B16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B16)-1,7)+1))</f>
-        <v>46485</v>
+        <v>46457</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11712,7 +12595,7 @@
       </c>
       <c r="B17" s="39" t="n">
         <f aca="false">IF(K16="","",IF(K16&gt;$K$2,"",K16))</f>
-        <v>46485</v>
+        <v>46457</v>
       </c>
       <c r="C17" s="38" t="str">
         <f aca="false">IF(B17="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B17)))</f>
@@ -11737,7 +12620,7 @@
       <c r="I17" s="45"/>
       <c r="K17" s="27" t="n">
         <f aca="false">IF(B17="","",B17+MIN(MOD(הגדרות!$D$18-WEEKDAY(B17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B17)-1,7)+1))</f>
-        <v>46488</v>
+        <v>46460</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11747,7 +12630,7 @@
       </c>
       <c r="B18" s="39" t="n">
         <f aca="false">IF(K17="","",IF(K17&gt;$K$2,"",K17))</f>
-        <v>46488</v>
+        <v>46460</v>
       </c>
       <c r="C18" s="38" t="str">
         <f aca="false">IF(B18="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B18)))</f>
@@ -11772,7 +12655,7 @@
       <c r="I18" s="45"/>
       <c r="K18" s="27" t="n">
         <f aca="false">IF(B18="","",B18+MIN(MOD(הגדרות!$D$18-WEEKDAY(B18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B18)-1,7)+1))</f>
-        <v>46492</v>
+        <v>46464</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11782,7 +12665,7 @@
       </c>
       <c r="B19" s="39" t="n">
         <f aca="false">IF(K18="","",IF(K18&gt;$K$2,"",K18))</f>
-        <v>46492</v>
+        <v>46464</v>
       </c>
       <c r="C19" s="38" t="str">
         <f aca="false">IF(B19="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B19)))</f>
@@ -11807,7 +12690,7 @@
       <c r="I19" s="45"/>
       <c r="K19" s="27" t="n">
         <f aca="false">IF(B19="","",B19+MIN(MOD(הגדרות!$D$18-WEEKDAY(B19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B19)-1,7)+1))</f>
-        <v>46495</v>
+        <v>46467</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11817,7 +12700,7 @@
       </c>
       <c r="B20" s="39" t="n">
         <f aca="false">IF(K19="","",IF(K19&gt;$K$2,"",K19))</f>
-        <v>46495</v>
+        <v>46467</v>
       </c>
       <c r="C20" s="38" t="str">
         <f aca="false">IF(B20="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B20)))</f>
@@ -11842,7 +12725,7 @@
       <c r="I20" s="45"/>
       <c r="K20" s="27" t="n">
         <f aca="false">IF(B20="","",B20+MIN(MOD(הגדרות!$D$18-WEEKDAY(B20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B20)-1,7)+1))</f>
-        <v>46499</v>
+        <v>46471</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11852,7 +12735,7 @@
       </c>
       <c r="B21" s="39" t="n">
         <f aca="false">IF(K20="","",IF(K20&gt;$K$2,"",K20))</f>
-        <v>46499</v>
+        <v>46471</v>
       </c>
       <c r="C21" s="38" t="str">
         <f aca="false">IF(B21="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B21)))</f>
@@ -11877,7 +12760,7 @@
       <c r="I21" s="45"/>
       <c r="K21" s="27" t="n">
         <f aca="false">IF(B21="","",B21+MIN(MOD(הגדרות!$D$18-WEEKDAY(B21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B21)-1,7)+1))</f>
-        <v>46502</v>
+        <v>46474</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11887,7 +12770,7 @@
       </c>
       <c r="B22" s="39" t="n">
         <f aca="false">IF(K21="","",IF(K21&gt;$K$2,"",K21))</f>
-        <v>46502</v>
+        <v>46474</v>
       </c>
       <c r="C22" s="38" t="str">
         <f aca="false">IF(B22="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B22)))</f>
@@ -11912,42 +12795,42 @@
       <c r="I22" s="45"/>
       <c r="K22" s="27" t="n">
         <f aca="false">IF(B22="","",B22+MIN(MOD(הגדרות!$D$18-WEEKDAY(B22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B22)-1,7)+1))</f>
-        <v>46506</v>
+        <v>46478</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="38" t="n">
+      <c r="A23" s="38" t="str">
         <f aca="false">IF(B23="","",ROW()-14)</f>
-        <v>9</v>
-      </c>
-      <c r="B23" s="39" t="n">
+        <v/>
+      </c>
+      <c r="B23" s="39" t="str">
         <f aca="false">IF(K22="","",IF(K22&gt;$K$2,"",K22))</f>
-        <v>46506</v>
+        <v/>
       </c>
       <c r="C23" s="38" t="str">
         <f aca="false">IF(B23="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B23)))</f>
-        <v>חמישי</v>
+        <v/>
       </c>
       <c r="D23" s="40" t="str">
         <f aca="false">IF(B23="","","הדרכה "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00"))</f>
-        <v>הדרכה 09:00–12:30</v>
+        <v/>
       </c>
       <c r="E23" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="F23" s="42" t="n">
+      <c r="F23" s="42" t="str">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
-        <v>3.5</v>
-      </c>
-      <c r="G23" s="43" t="n">
+        <v/>
+      </c>
+      <c r="G23" s="43" t="str">
         <f aca="false">IF(B23="","",F23*הגדרות!$C$24)</f>
-        <v>175</v>
+        <v/>
       </c>
       <c r="H23" s="44"/>
       <c r="I23" s="45"/>
-      <c r="K23" s="27" t="n">
+      <c r="K23" s="27" t="str">
         <f aca="false">IF(B23="","",B23+MIN(MOD(הגדרות!$D$18-WEEKDAY(B23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B23)-1,7)+1))</f>
-        <v>46509</v>
+        <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11988,7 +12871,7 @@
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="38" t="n">
         <f aca="false">COUNT($B$15:$B$24)+1</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B25" s="46"/>
       <c r="C25" s="38" t="str">
@@ -12023,11 +12906,11 @@
       <c r="E26" s="47"/>
       <c r="F26" s="48" t="n">
         <f aca="false">SUM(F15:F25)</f>
-        <v>32.5</v>
+        <v>29</v>
       </c>
       <c r="G26" s="49" t="n">
         <f aca="false">SUM(G15:G25)</f>
-        <v>1625</v>
+        <v>1450</v>
       </c>
       <c r="H26" s="47"/>
       <c r="I26" s="49" t="n">
@@ -12049,7 +12932,7 @@
       <c r="H28" s="40"/>
       <c r="I28" s="42" t="n">
         <f aca="false">F26</f>
-        <v>32.5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12063,13 +12946,13 @@
       <c r="E29" s="51"/>
       <c r="F29" s="40" t="str">
         <f aca="false">"הדרכת שיקום ("&amp;TEXT(F26,"0.0")&amp;" שעות × "&amp;הגדרות!$C$24&amp;" ₪)"</f>
-        <v>הדרכת שיקום (32.5 שעות × 50 ₪)</v>
+        <v>הדרכת שיקום (29.0 שעות × 50 ₪)</v>
       </c>
       <c r="G29" s="40"/>
       <c r="H29" s="40"/>
       <c r="I29" s="43" t="n">
         <f aca="false">G26</f>
-        <v>1625</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12107,7 +12990,7 @@
       <c r="H31" s="52"/>
       <c r="I31" s="53" t="n">
         <f aca="false">I29+I30</f>
-        <v>1625</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12127,7 +13010,7 @@
       <c r="H32" s="40"/>
       <c r="I32" s="43" t="n">
         <f aca="false">ROUND(I31*הגדרות!$C$25,2)</f>
-        <v>292.5</v>
+        <v>261</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12138,7 +13021,7 @@
       <c r="H33" s="54"/>
       <c r="I33" s="55" t="n">
         <f aca="false">I31+I32</f>
-        <v>1917.5</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/quotes/הצעת-מחיר-חודשית-חוות-רום.xlsx
+++ b/quotes/הצעת-מחיר-חודשית-חוות-רום.xlsx
@@ -805,7 +805,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="94">
   <si>
     <t xml:space="preserve">איך משתמשים בקובץ</t>
   </si>
@@ -826,6 +826,12 @@
   </si>
   <si>
     <t xml:space="preserve">בעמודה "התקיים?" בוחרים "לא" (חג, מחלה, ביטול) – השורה תימחק בקו והשעות יתאפסו.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">תאריך שהשתנה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מקלידים תאריך אחר מעל התאריך שבשורה, או מוחקים אותו (Delete) – השורה מתרוקנת ולא מחויבת. שאר התאריכים לא זזים.</t>
   </si>
   <si>
     <t xml:space="preserve">4. ישיבת צוות</t>
@@ -864,7 +870,7 @@
     <t xml:space="preserve">תא צהוב בגיליון "הגדרות" – למילוי פעם אחת</t>
   </si>
   <si>
-    <t xml:space="preserve">תא ברקע שמנת בגיליון החודש – למילוי חודשי (חודש, ישיבת צוות, התקיים?, פרויקטים)</t>
+    <t xml:space="preserve">תא ברקע שמנת בגיליון החודש – למילוי או לעריכה (חודש, תאריכים, התקיים?, פרויקטים)</t>
   </si>
   <si>
     <t xml:space="preserve">דוגמה לשורת פרויקט פרטי</t>
@@ -1421,7 +1427,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="56">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1578,7 +1584,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1603,10 +1609,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1920,7 +1922,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:C18"/>
+  <dimension ref="B1:C19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1997,41 +1999,49 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="4" t="s">
+    <row r="11" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="C11" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="5"/>
-      <c r="C13" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7"/>
-      <c r="C14" s="8" t="s">
+      <c r="B13" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="4" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="5"/>
+      <c r="C14" s="6" t="s">
         <v>20</v>
       </c>
     </row>
+    <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="7"/>
+      <c r="C15" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="9" t="s">
+      <c r="B17" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="11" t="n">
+      <c r="C18" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="11" t="n">
         <v>600</v>
       </c>
     </row>
@@ -2068,7 +2078,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -2104,13 +2114,13 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
       <c r="F4" s="29" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
@@ -2118,7 +2128,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
@@ -2127,7 +2137,7 @@
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="31" t="str">
@@ -2138,7 +2148,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="31" t="str">
@@ -2147,7 +2157,7 @@
       </c>
       <c r="D6" s="31"/>
       <c r="F6" s="30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="31" t="str">
@@ -2158,7 +2168,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="31" t="str">
@@ -2167,7 +2177,7 @@
       </c>
       <c r="D7" s="31"/>
       <c r="F7" s="30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="31" t="str">
@@ -2178,7 +2188,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="31" t="str">
@@ -2189,7 +2199,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="str">
@@ -2201,7 +2211,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
@@ -2210,7 +2220,7 @@
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
@@ -2220,7 +2230,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
@@ -2229,7 +2239,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31" t="str">
@@ -2240,7 +2250,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -2249,46 +2259,46 @@
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="35" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="38" t="n">
-        <f aca="false">IF(B15="","",ROW()-14)</f>
+        <f aca="false">IF(B15="","",COUNT($B$15:B15))</f>
         <v>1</v>
       </c>
       <c r="B15" s="39" t="n">
-        <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
+        <f aca="false">IF(K15="","",K15)</f>
         <v>46478</v>
       </c>
       <c r="C15" s="38" t="str">
@@ -2300,7 +2310,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F15" s="42" t="n">
         <f aca="false">IF(B15="","",IF(E15="לא",0,הגדרות!$C$22))</f>
@@ -2313,17 +2323,17 @@
       <c r="H15" s="44"/>
       <c r="I15" s="45"/>
       <c r="K15" s="27" t="n">
-        <f aca="false">IF(B15="","",B15+MIN(MOD(הגדרות!$D$18-WEEKDAY(B15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B15)-1,7)+1))</f>
-        <v>46481</v>
+        <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
+        <v>46478</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="38" t="n">
-        <f aca="false">IF(B16="","",ROW()-14)</f>
+        <f aca="false">IF(B16="","",COUNT($B$15:B16))</f>
         <v>2</v>
       </c>
       <c r="B16" s="39" t="n">
-        <f aca="false">IF(K15="","",IF(K15&gt;$K$2,"",K15))</f>
+        <f aca="false">IF(K16="","",K16)</f>
         <v>46481</v>
       </c>
       <c r="C16" s="38" t="str">
@@ -2335,7 +2345,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F16" s="42" t="n">
         <f aca="false">IF(B16="","",IF(E16="לא",0,הגדרות!$C$22))</f>
@@ -2348,17 +2358,17 @@
       <c r="H16" s="44"/>
       <c r="I16" s="45"/>
       <c r="K16" s="27" t="n">
-        <f aca="false">IF(B16="","",B16+MIN(MOD(הגדרות!$D$18-WEEKDAY(B16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B16)-1,7)+1))</f>
-        <v>46485</v>
+        <f aca="false">IF(K15="","",IF(K15+MIN(MOD(הגדרות!$D$18-WEEKDAY(K15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K15)-1,7)+1)&gt;$K$2,"",K15+MIN(MOD(הגדרות!$D$18-WEEKDAY(K15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K15)-1,7)+1)))</f>
+        <v>46481</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="38" t="n">
-        <f aca="false">IF(B17="","",ROW()-14)</f>
+        <f aca="false">IF(B17="","",COUNT($B$15:B17))</f>
         <v>3</v>
       </c>
       <c r="B17" s="39" t="n">
-        <f aca="false">IF(K16="","",IF(K16&gt;$K$2,"",K16))</f>
+        <f aca="false">IF(K17="","",K17)</f>
         <v>46485</v>
       </c>
       <c r="C17" s="38" t="str">
@@ -2370,7 +2380,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F17" s="42" t="n">
         <f aca="false">IF(B17="","",IF(E17="לא",0,הגדרות!$C$22))</f>
@@ -2383,17 +2393,17 @@
       <c r="H17" s="44"/>
       <c r="I17" s="45"/>
       <c r="K17" s="27" t="n">
-        <f aca="false">IF(B17="","",B17+MIN(MOD(הגדרות!$D$18-WEEKDAY(B17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B17)-1,7)+1))</f>
-        <v>46488</v>
+        <f aca="false">IF(K16="","",IF(K16+MIN(MOD(הגדרות!$D$18-WEEKDAY(K16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K16)-1,7)+1)&gt;$K$2,"",K16+MIN(MOD(הגדרות!$D$18-WEEKDAY(K16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K16)-1,7)+1)))</f>
+        <v>46485</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="38" t="n">
-        <f aca="false">IF(B18="","",ROW()-14)</f>
+        <f aca="false">IF(B18="","",COUNT($B$15:B18))</f>
         <v>4</v>
       </c>
       <c r="B18" s="39" t="n">
-        <f aca="false">IF(K17="","",IF(K17&gt;$K$2,"",K17))</f>
+        <f aca="false">IF(K18="","",K18)</f>
         <v>46488</v>
       </c>
       <c r="C18" s="38" t="str">
@@ -2405,7 +2415,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F18" s="42" t="n">
         <f aca="false">IF(B18="","",IF(E18="לא",0,הגדרות!$C$22))</f>
@@ -2418,17 +2428,17 @@
       <c r="H18" s="44"/>
       <c r="I18" s="45"/>
       <c r="K18" s="27" t="n">
-        <f aca="false">IF(B18="","",B18+MIN(MOD(הגדרות!$D$18-WEEKDAY(B18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B18)-1,7)+1))</f>
-        <v>46492</v>
+        <f aca="false">IF(K17="","",IF(K17+MIN(MOD(הגדרות!$D$18-WEEKDAY(K17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K17)-1,7)+1)&gt;$K$2,"",K17+MIN(MOD(הגדרות!$D$18-WEEKDAY(K17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K17)-1,7)+1)))</f>
+        <v>46488</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="38" t="n">
-        <f aca="false">IF(B19="","",ROW()-14)</f>
+        <f aca="false">IF(B19="","",COUNT($B$15:B19))</f>
         <v>5</v>
       </c>
       <c r="B19" s="39" t="n">
-        <f aca="false">IF(K18="","",IF(K18&gt;$K$2,"",K18))</f>
+        <f aca="false">IF(K19="","",K19)</f>
         <v>46492</v>
       </c>
       <c r="C19" s="38" t="str">
@@ -2440,7 +2450,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F19" s="42" t="n">
         <f aca="false">IF(B19="","",IF(E19="לא",0,הגדרות!$C$22))</f>
@@ -2453,17 +2463,17 @@
       <c r="H19" s="44"/>
       <c r="I19" s="45"/>
       <c r="K19" s="27" t="n">
-        <f aca="false">IF(B19="","",B19+MIN(MOD(הגדרות!$D$18-WEEKDAY(B19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B19)-1,7)+1))</f>
-        <v>46495</v>
+        <f aca="false">IF(K18="","",IF(K18+MIN(MOD(הגדרות!$D$18-WEEKDAY(K18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K18)-1,7)+1)&gt;$K$2,"",K18+MIN(MOD(הגדרות!$D$18-WEEKDAY(K18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K18)-1,7)+1)))</f>
+        <v>46492</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="38" t="n">
-        <f aca="false">IF(B20="","",ROW()-14)</f>
+        <f aca="false">IF(B20="","",COUNT($B$15:B20))</f>
         <v>6</v>
       </c>
       <c r="B20" s="39" t="n">
-        <f aca="false">IF(K19="","",IF(K19&gt;$K$2,"",K19))</f>
+        <f aca="false">IF(K20="","",K20)</f>
         <v>46495</v>
       </c>
       <c r="C20" s="38" t="str">
@@ -2475,7 +2485,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F20" s="42" t="n">
         <f aca="false">IF(B20="","",IF(E20="לא",0,הגדרות!$C$22))</f>
@@ -2488,17 +2498,17 @@
       <c r="H20" s="44"/>
       <c r="I20" s="45"/>
       <c r="K20" s="27" t="n">
-        <f aca="false">IF(B20="","",B20+MIN(MOD(הגדרות!$D$18-WEEKDAY(B20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B20)-1,7)+1))</f>
-        <v>46499</v>
+        <f aca="false">IF(K19="","",IF(K19+MIN(MOD(הגדרות!$D$18-WEEKDAY(K19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K19)-1,7)+1)&gt;$K$2,"",K19+MIN(MOD(הגדרות!$D$18-WEEKDAY(K19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K19)-1,7)+1)))</f>
+        <v>46495</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="38" t="n">
-        <f aca="false">IF(B21="","",ROW()-14)</f>
+        <f aca="false">IF(B21="","",COUNT($B$15:B21))</f>
         <v>7</v>
       </c>
       <c r="B21" s="39" t="n">
-        <f aca="false">IF(K20="","",IF(K20&gt;$K$2,"",K20))</f>
+        <f aca="false">IF(K21="","",K21)</f>
         <v>46499</v>
       </c>
       <c r="C21" s="38" t="str">
@@ -2510,7 +2520,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F21" s="42" t="n">
         <f aca="false">IF(B21="","",IF(E21="לא",0,הגדרות!$C$22))</f>
@@ -2523,17 +2533,17 @@
       <c r="H21" s="44"/>
       <c r="I21" s="45"/>
       <c r="K21" s="27" t="n">
-        <f aca="false">IF(B21="","",B21+MIN(MOD(הגדרות!$D$18-WEEKDAY(B21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B21)-1,7)+1))</f>
-        <v>46502</v>
+        <f aca="false">IF(K20="","",IF(K20+MIN(MOD(הגדרות!$D$18-WEEKDAY(K20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K20)-1,7)+1)&gt;$K$2,"",K20+MIN(MOD(הגדרות!$D$18-WEEKDAY(K20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K20)-1,7)+1)))</f>
+        <v>46499</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="38" t="n">
-        <f aca="false">IF(B22="","",ROW()-14)</f>
+        <f aca="false">IF(B22="","",COUNT($B$15:B22))</f>
         <v>8</v>
       </c>
       <c r="B22" s="39" t="n">
-        <f aca="false">IF(K21="","",IF(K21&gt;$K$2,"",K21))</f>
+        <f aca="false">IF(K22="","",K22)</f>
         <v>46502</v>
       </c>
       <c r="C22" s="38" t="str">
@@ -2545,7 +2555,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F22" s="42" t="n">
         <f aca="false">IF(B22="","",IF(E22="לא",0,הגדרות!$C$22))</f>
@@ -2558,17 +2568,17 @@
       <c r="H22" s="44"/>
       <c r="I22" s="45"/>
       <c r="K22" s="27" t="n">
-        <f aca="false">IF(B22="","",B22+MIN(MOD(הגדרות!$D$18-WEEKDAY(B22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B22)-1,7)+1))</f>
-        <v>46506</v>
+        <f aca="false">IF(K21="","",IF(K21+MIN(MOD(הגדרות!$D$18-WEEKDAY(K21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K21)-1,7)+1)&gt;$K$2,"",K21+MIN(MOD(הגדרות!$D$18-WEEKDAY(K21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K21)-1,7)+1)))</f>
+        <v>46502</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="38" t="n">
-        <f aca="false">IF(B23="","",ROW()-14)</f>
+        <f aca="false">IF(B23="","",COUNT($B$15:B23))</f>
         <v>9</v>
       </c>
       <c r="B23" s="39" t="n">
-        <f aca="false">IF(K22="","",IF(K22&gt;$K$2,"",K22))</f>
+        <f aca="false">IF(K23="","",K23)</f>
         <v>46506</v>
       </c>
       <c r="C23" s="38" t="str">
@@ -2580,7 +2590,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F23" s="42" t="n">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
@@ -2593,17 +2603,17 @@
       <c r="H23" s="44"/>
       <c r="I23" s="45"/>
       <c r="K23" s="27" t="n">
-        <f aca="false">IF(B23="","",B23+MIN(MOD(הגדרות!$D$18-WEEKDAY(B23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B23)-1,7)+1))</f>
-        <v>46509</v>
+        <f aca="false">IF(K22="","",IF(K22+MIN(MOD(הגדרות!$D$18-WEEKDAY(K22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K22)-1,7)+1)&gt;$K$2,"",K22+MIN(MOD(הגדרות!$D$18-WEEKDAY(K22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K22)-1,7)+1)))</f>
+        <v>46506</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="38" t="str">
-        <f aca="false">IF(B24="","",ROW()-14)</f>
+        <f aca="false">IF(B24="","",COUNT($B$15:B24))</f>
         <v/>
       </c>
       <c r="B24" s="39" t="str">
-        <f aca="false">IF(K23="","",IF(K23&gt;$K$2,"",K23))</f>
+        <f aca="false">IF(K24="","",K24)</f>
         <v/>
       </c>
       <c r="C24" s="38" t="str">
@@ -2615,7 +2625,7 @@
         <v/>
       </c>
       <c r="E24" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F24" s="42" t="str">
         <f aca="false">IF(B24="","",IF(E24="לא",0,הגדרות!$C$22))</f>
@@ -2628,7 +2638,7 @@
       <c r="H24" s="44"/>
       <c r="I24" s="45"/>
       <c r="K24" s="27" t="str">
-        <f aca="false">IF(B24="","",B24+MIN(MOD(הגדרות!$D$18-WEEKDAY(B24)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B24)-1,7)+1))</f>
+        <f aca="false">IF(K23="","",IF(K23+MIN(MOD(הגדרות!$D$18-WEEKDAY(K23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K23)-1,7)+1)&gt;$K$2,"",K23+MIN(MOD(הגדרות!$D$18-WEEKDAY(K23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K23)-1,7)+1)))</f>
         <v/>
       </c>
     </row>
@@ -2637,16 +2647,16 @@
         <f aca="false">COUNT($B$15:$B$24)+1</f>
         <v>10</v>
       </c>
-      <c r="B25" s="46"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="38" t="str">
         <f aca="false">IF(B25="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B25)))</f>
         <v/>
       </c>
       <c r="D25" s="40" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F25" s="42" t="n">
         <f aca="false">IF(E25="לא",0,הגדרות!$C$23)</f>
@@ -2661,36 +2671,36 @@
       <c r="K25" s="27"/>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="B26" s="47"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="48" t="n">
+      <c r="A26" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" s="46"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="47" t="n">
         <f aca="false">SUM(F15:F25)</f>
         <v>32.5</v>
       </c>
-      <c r="G26" s="49" t="n">
+      <c r="G26" s="48" t="n">
         <f aca="false">SUM(G15:G25)</f>
         <v>1625</v>
       </c>
-      <c r="H26" s="47"/>
-      <c r="I26" s="49" t="n">
+      <c r="H26" s="46"/>
+      <c r="I26" s="48" t="n">
         <f aca="false">SUM(I15:I25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
+      <c r="A28" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="49"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="49"/>
       <c r="F28" s="40" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G28" s="40"/>
       <c r="H28" s="40"/>
@@ -2700,14 +2710,14 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="51" t="str">
+      <c r="A29" s="50" t="str">
         <f aca="false">"• "&amp;הגדרות!$C$17&amp;": ימי "&amp;הגדרות!$C$18&amp;" ו"&amp;הגדרות!$C$19&amp;", "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00")&amp;" ("&amp;הגדרות!$C$22&amp;" שעות ליום), וישיבת צוות חודשית ("&amp;הגדרות!$C$23&amp;" ש׳)."</f>
         <v>• הדרכת שיקום: ימי ראשון וחמישי, 09:00–12:30 (3.5 שעות ליום), וישיבת צוות חודשית (1 ש׳).</v>
       </c>
-      <c r="B29" s="51"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
       <c r="F29" s="40" t="str">
         <f aca="false">"הדרכת שיקום ("&amp;TEXT(F26,"0.0")&amp;" שעות × "&amp;הגדרות!$C$24&amp;" ₪)"</f>
         <v>הדרכת שיקום (32.5 שעות × 50 ₪)</v>
@@ -2720,16 +2730,16 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="51" t="str">
+      <c r="A30" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$28="","","• "&amp;הגדרות!$C$28)</f>
         <v>• התעריף השעתי אינו כולל מע״מ. מע״מ יתווסף כחוק.</v>
       </c>
-      <c r="B30" s="51"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
       <c r="F30" s="40" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="40"/>
@@ -2739,33 +2749,33 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="51" t="str">
+      <c r="A31" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$29="","","• "&amp;הגדרות!$C$29)</f>
         <v>• פרויקטים פרטיים מתומחרים בנפרד, לפי הזמנת החווה.</v>
       </c>
-      <c r="B31" s="51"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="52" t="s">
-        <v>89</v>
-      </c>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="53" t="n">
+      <c r="B31" s="50"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="52" t="n">
         <f aca="false">I29+I30</f>
         <v>1625</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="51" t="str">
+      <c r="A32" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$30="","","• "&amp;הגדרות!$C$30)</f>
         <v/>
       </c>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
       <c r="F32" s="40" t="str">
         <f aca="false">"מע״מ "&amp;ROUND(הגדרות!$C$25*100,1)&amp;"%"</f>
         <v>מע״מ 18%</v>
@@ -2778,30 +2788,30 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F33" s="54" t="s">
-        <v>90</v>
-      </c>
-      <c r="G33" s="54"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="55" t="n">
+      <c r="F33" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="54" t="n">
         <f aca="false">I31+I32</f>
         <v>1917.5</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="56" t="str">
+      <c r="A36" s="55" t="str">
         <f aca="false">"בברכה, "&amp;הגדרות!$C$6</f>
         <v>בברכה, (למילוי)</v>
       </c>
-      <c r="B36" s="56"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="F36" s="56" t="s">
-        <v>91</v>
-      </c>
-      <c r="G36" s="56"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="56"/>
+      <c r="B36" s="55"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="F36" s="55" t="s">
+        <v>93</v>
+      </c>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="44">
@@ -2899,7 +2909,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -2935,13 +2945,13 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
       <c r="F4" s="29" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
@@ -2949,7 +2959,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
@@ -2958,7 +2968,7 @@
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="31" t="str">
@@ -2969,7 +2979,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="31" t="str">
@@ -2978,7 +2988,7 @@
       </c>
       <c r="D6" s="31"/>
       <c r="F6" s="30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="31" t="str">
@@ -2989,7 +2999,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="31" t="str">
@@ -2998,7 +3008,7 @@
       </c>
       <c r="D7" s="31"/>
       <c r="F7" s="30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="31" t="str">
@@ -3009,7 +3019,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="31" t="str">
@@ -3020,7 +3030,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="str">
@@ -3032,7 +3042,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
@@ -3041,7 +3051,7 @@
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
@@ -3051,7 +3061,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
@@ -3060,7 +3070,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31" t="str">
@@ -3071,7 +3081,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -3080,46 +3090,46 @@
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="35" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="38" t="n">
-        <f aca="false">IF(B15="","",ROW()-14)</f>
+        <f aca="false">IF(B15="","",COUNT($B$15:B15))</f>
         <v>1</v>
       </c>
       <c r="B15" s="39" t="n">
-        <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
+        <f aca="false">IF(K15="","",K15)</f>
         <v>46509</v>
       </c>
       <c r="C15" s="38" t="str">
@@ -3131,7 +3141,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F15" s="42" t="n">
         <f aca="false">IF(B15="","",IF(E15="לא",0,הגדרות!$C$22))</f>
@@ -3144,17 +3154,17 @@
       <c r="H15" s="44"/>
       <c r="I15" s="45"/>
       <c r="K15" s="27" t="n">
-        <f aca="false">IF(B15="","",B15+MIN(MOD(הגדרות!$D$18-WEEKDAY(B15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B15)-1,7)+1))</f>
-        <v>46513</v>
+        <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
+        <v>46509</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="38" t="n">
-        <f aca="false">IF(B16="","",ROW()-14)</f>
+        <f aca="false">IF(B16="","",COUNT($B$15:B16))</f>
         <v>2</v>
       </c>
       <c r="B16" s="39" t="n">
-        <f aca="false">IF(K15="","",IF(K15&gt;$K$2,"",K15))</f>
+        <f aca="false">IF(K16="","",K16)</f>
         <v>46513</v>
       </c>
       <c r="C16" s="38" t="str">
@@ -3166,7 +3176,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F16" s="42" t="n">
         <f aca="false">IF(B16="","",IF(E16="לא",0,הגדרות!$C$22))</f>
@@ -3179,17 +3189,17 @@
       <c r="H16" s="44"/>
       <c r="I16" s="45"/>
       <c r="K16" s="27" t="n">
-        <f aca="false">IF(B16="","",B16+MIN(MOD(הגדרות!$D$18-WEEKDAY(B16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B16)-1,7)+1))</f>
-        <v>46516</v>
+        <f aca="false">IF(K15="","",IF(K15+MIN(MOD(הגדרות!$D$18-WEEKDAY(K15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K15)-1,7)+1)&gt;$K$2,"",K15+MIN(MOD(הגדרות!$D$18-WEEKDAY(K15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K15)-1,7)+1)))</f>
+        <v>46513</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="38" t="n">
-        <f aca="false">IF(B17="","",ROW()-14)</f>
+        <f aca="false">IF(B17="","",COUNT($B$15:B17))</f>
         <v>3</v>
       </c>
       <c r="B17" s="39" t="n">
-        <f aca="false">IF(K16="","",IF(K16&gt;$K$2,"",K16))</f>
+        <f aca="false">IF(K17="","",K17)</f>
         <v>46516</v>
       </c>
       <c r="C17" s="38" t="str">
@@ -3201,7 +3211,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F17" s="42" t="n">
         <f aca="false">IF(B17="","",IF(E17="לא",0,הגדרות!$C$22))</f>
@@ -3214,17 +3224,17 @@
       <c r="H17" s="44"/>
       <c r="I17" s="45"/>
       <c r="K17" s="27" t="n">
-        <f aca="false">IF(B17="","",B17+MIN(MOD(הגדרות!$D$18-WEEKDAY(B17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B17)-1,7)+1))</f>
-        <v>46520</v>
+        <f aca="false">IF(K16="","",IF(K16+MIN(MOD(הגדרות!$D$18-WEEKDAY(K16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K16)-1,7)+1)&gt;$K$2,"",K16+MIN(MOD(הגדרות!$D$18-WEEKDAY(K16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K16)-1,7)+1)))</f>
+        <v>46516</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="38" t="n">
-        <f aca="false">IF(B18="","",ROW()-14)</f>
+        <f aca="false">IF(B18="","",COUNT($B$15:B18))</f>
         <v>4</v>
       </c>
       <c r="B18" s="39" t="n">
-        <f aca="false">IF(K17="","",IF(K17&gt;$K$2,"",K17))</f>
+        <f aca="false">IF(K18="","",K18)</f>
         <v>46520</v>
       </c>
       <c r="C18" s="38" t="str">
@@ -3236,7 +3246,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F18" s="42" t="n">
         <f aca="false">IF(B18="","",IF(E18="לא",0,הגדרות!$C$22))</f>
@@ -3249,17 +3259,17 @@
       <c r="H18" s="44"/>
       <c r="I18" s="45"/>
       <c r="K18" s="27" t="n">
-        <f aca="false">IF(B18="","",B18+MIN(MOD(הגדרות!$D$18-WEEKDAY(B18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B18)-1,7)+1))</f>
-        <v>46523</v>
+        <f aca="false">IF(K17="","",IF(K17+MIN(MOD(הגדרות!$D$18-WEEKDAY(K17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K17)-1,7)+1)&gt;$K$2,"",K17+MIN(MOD(הגדרות!$D$18-WEEKDAY(K17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K17)-1,7)+1)))</f>
+        <v>46520</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="38" t="n">
-        <f aca="false">IF(B19="","",ROW()-14)</f>
+        <f aca="false">IF(B19="","",COUNT($B$15:B19))</f>
         <v>5</v>
       </c>
       <c r="B19" s="39" t="n">
-        <f aca="false">IF(K18="","",IF(K18&gt;$K$2,"",K18))</f>
+        <f aca="false">IF(K19="","",K19)</f>
         <v>46523</v>
       </c>
       <c r="C19" s="38" t="str">
@@ -3271,7 +3281,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F19" s="42" t="n">
         <f aca="false">IF(B19="","",IF(E19="לא",0,הגדרות!$C$22))</f>
@@ -3284,17 +3294,17 @@
       <c r="H19" s="44"/>
       <c r="I19" s="45"/>
       <c r="K19" s="27" t="n">
-        <f aca="false">IF(B19="","",B19+MIN(MOD(הגדרות!$D$18-WEEKDAY(B19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B19)-1,7)+1))</f>
-        <v>46527</v>
+        <f aca="false">IF(K18="","",IF(K18+MIN(MOD(הגדרות!$D$18-WEEKDAY(K18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K18)-1,7)+1)&gt;$K$2,"",K18+MIN(MOD(הגדרות!$D$18-WEEKDAY(K18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K18)-1,7)+1)))</f>
+        <v>46523</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="38" t="n">
-        <f aca="false">IF(B20="","",ROW()-14)</f>
+        <f aca="false">IF(B20="","",COUNT($B$15:B20))</f>
         <v>6</v>
       </c>
       <c r="B20" s="39" t="n">
-        <f aca="false">IF(K19="","",IF(K19&gt;$K$2,"",K19))</f>
+        <f aca="false">IF(K20="","",K20)</f>
         <v>46527</v>
       </c>
       <c r="C20" s="38" t="str">
@@ -3306,7 +3316,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F20" s="42" t="n">
         <f aca="false">IF(B20="","",IF(E20="לא",0,הגדרות!$C$22))</f>
@@ -3319,17 +3329,17 @@
       <c r="H20" s="44"/>
       <c r="I20" s="45"/>
       <c r="K20" s="27" t="n">
-        <f aca="false">IF(B20="","",B20+MIN(MOD(הגדרות!$D$18-WEEKDAY(B20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B20)-1,7)+1))</f>
-        <v>46530</v>
+        <f aca="false">IF(K19="","",IF(K19+MIN(MOD(הגדרות!$D$18-WEEKDAY(K19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K19)-1,7)+1)&gt;$K$2,"",K19+MIN(MOD(הגדרות!$D$18-WEEKDAY(K19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K19)-1,7)+1)))</f>
+        <v>46527</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="38" t="n">
-        <f aca="false">IF(B21="","",ROW()-14)</f>
+        <f aca="false">IF(B21="","",COUNT($B$15:B21))</f>
         <v>7</v>
       </c>
       <c r="B21" s="39" t="n">
-        <f aca="false">IF(K20="","",IF(K20&gt;$K$2,"",K20))</f>
+        <f aca="false">IF(K21="","",K21)</f>
         <v>46530</v>
       </c>
       <c r="C21" s="38" t="str">
@@ -3341,7 +3351,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F21" s="42" t="n">
         <f aca="false">IF(B21="","",IF(E21="לא",0,הגדרות!$C$22))</f>
@@ -3354,17 +3364,17 @@
       <c r="H21" s="44"/>
       <c r="I21" s="45"/>
       <c r="K21" s="27" t="n">
-        <f aca="false">IF(B21="","",B21+MIN(MOD(הגדרות!$D$18-WEEKDAY(B21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B21)-1,7)+1))</f>
-        <v>46534</v>
+        <f aca="false">IF(K20="","",IF(K20+MIN(MOD(הגדרות!$D$18-WEEKDAY(K20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K20)-1,7)+1)&gt;$K$2,"",K20+MIN(MOD(הגדרות!$D$18-WEEKDAY(K20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K20)-1,7)+1)))</f>
+        <v>46530</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="38" t="n">
-        <f aca="false">IF(B22="","",ROW()-14)</f>
+        <f aca="false">IF(B22="","",COUNT($B$15:B22))</f>
         <v>8</v>
       </c>
       <c r="B22" s="39" t="n">
-        <f aca="false">IF(K21="","",IF(K21&gt;$K$2,"",K21))</f>
+        <f aca="false">IF(K22="","",K22)</f>
         <v>46534</v>
       </c>
       <c r="C22" s="38" t="str">
@@ -3376,7 +3386,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F22" s="42" t="n">
         <f aca="false">IF(B22="","",IF(E22="לא",0,הגדרות!$C$22))</f>
@@ -3389,17 +3399,17 @@
       <c r="H22" s="44"/>
       <c r="I22" s="45"/>
       <c r="K22" s="27" t="n">
-        <f aca="false">IF(B22="","",B22+MIN(MOD(הגדרות!$D$18-WEEKDAY(B22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B22)-1,7)+1))</f>
-        <v>46537</v>
+        <f aca="false">IF(K21="","",IF(K21+MIN(MOD(הגדרות!$D$18-WEEKDAY(K21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K21)-1,7)+1)&gt;$K$2,"",K21+MIN(MOD(הגדרות!$D$18-WEEKDAY(K21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K21)-1,7)+1)))</f>
+        <v>46534</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="38" t="n">
-        <f aca="false">IF(B23="","",ROW()-14)</f>
+        <f aca="false">IF(B23="","",COUNT($B$15:B23))</f>
         <v>9</v>
       </c>
       <c r="B23" s="39" t="n">
-        <f aca="false">IF(K22="","",IF(K22&gt;$K$2,"",K22))</f>
+        <f aca="false">IF(K23="","",K23)</f>
         <v>46537</v>
       </c>
       <c r="C23" s="38" t="str">
@@ -3411,7 +3421,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F23" s="42" t="n">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
@@ -3424,17 +3434,17 @@
       <c r="H23" s="44"/>
       <c r="I23" s="45"/>
       <c r="K23" s="27" t="n">
-        <f aca="false">IF(B23="","",B23+MIN(MOD(הגדרות!$D$18-WEEKDAY(B23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B23)-1,7)+1))</f>
-        <v>46541</v>
+        <f aca="false">IF(K22="","",IF(K22+MIN(MOD(הגדרות!$D$18-WEEKDAY(K22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K22)-1,7)+1)&gt;$K$2,"",K22+MIN(MOD(הגדרות!$D$18-WEEKDAY(K22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K22)-1,7)+1)))</f>
+        <v>46537</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="38" t="str">
-        <f aca="false">IF(B24="","",ROW()-14)</f>
+        <f aca="false">IF(B24="","",COUNT($B$15:B24))</f>
         <v/>
       </c>
       <c r="B24" s="39" t="str">
-        <f aca="false">IF(K23="","",IF(K23&gt;$K$2,"",K23))</f>
+        <f aca="false">IF(K24="","",K24)</f>
         <v/>
       </c>
       <c r="C24" s="38" t="str">
@@ -3446,7 +3456,7 @@
         <v/>
       </c>
       <c r="E24" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F24" s="42" t="str">
         <f aca="false">IF(B24="","",IF(E24="לא",0,הגדרות!$C$22))</f>
@@ -3459,7 +3469,7 @@
       <c r="H24" s="44"/>
       <c r="I24" s="45"/>
       <c r="K24" s="27" t="str">
-        <f aca="false">IF(B24="","",B24+MIN(MOD(הגדרות!$D$18-WEEKDAY(B24)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B24)-1,7)+1))</f>
+        <f aca="false">IF(K23="","",IF(K23+MIN(MOD(הגדרות!$D$18-WEEKDAY(K23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K23)-1,7)+1)&gt;$K$2,"",K23+MIN(MOD(הגדרות!$D$18-WEEKDAY(K23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K23)-1,7)+1)))</f>
         <v/>
       </c>
     </row>
@@ -3468,16 +3478,16 @@
         <f aca="false">COUNT($B$15:$B$24)+1</f>
         <v>10</v>
       </c>
-      <c r="B25" s="46"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="38" t="str">
         <f aca="false">IF(B25="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B25)))</f>
         <v/>
       </c>
       <c r="D25" s="40" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F25" s="42" t="n">
         <f aca="false">IF(E25="לא",0,הגדרות!$C$23)</f>
@@ -3492,36 +3502,36 @@
       <c r="K25" s="27"/>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="B26" s="47"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="48" t="n">
+      <c r="A26" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" s="46"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="47" t="n">
         <f aca="false">SUM(F15:F25)</f>
         <v>32.5</v>
       </c>
-      <c r="G26" s="49" t="n">
+      <c r="G26" s="48" t="n">
         <f aca="false">SUM(G15:G25)</f>
         <v>1625</v>
       </c>
-      <c r="H26" s="47"/>
-      <c r="I26" s="49" t="n">
+      <c r="H26" s="46"/>
+      <c r="I26" s="48" t="n">
         <f aca="false">SUM(I15:I25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
+      <c r="A28" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="49"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="49"/>
       <c r="F28" s="40" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G28" s="40"/>
       <c r="H28" s="40"/>
@@ -3531,14 +3541,14 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="51" t="str">
+      <c r="A29" s="50" t="str">
         <f aca="false">"• "&amp;הגדרות!$C$17&amp;": ימי "&amp;הגדרות!$C$18&amp;" ו"&amp;הגדרות!$C$19&amp;", "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00")&amp;" ("&amp;הגדרות!$C$22&amp;" שעות ליום), וישיבת צוות חודשית ("&amp;הגדרות!$C$23&amp;" ש׳)."</f>
         <v>• הדרכת שיקום: ימי ראשון וחמישי, 09:00–12:30 (3.5 שעות ליום), וישיבת צוות חודשית (1 ש׳).</v>
       </c>
-      <c r="B29" s="51"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
       <c r="F29" s="40" t="str">
         <f aca="false">"הדרכת שיקום ("&amp;TEXT(F26,"0.0")&amp;" שעות × "&amp;הגדרות!$C$24&amp;" ₪)"</f>
         <v>הדרכת שיקום (32.5 שעות × 50 ₪)</v>
@@ -3551,16 +3561,16 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="51" t="str">
+      <c r="A30" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$28="","","• "&amp;הגדרות!$C$28)</f>
         <v>• התעריף השעתי אינו כולל מע״מ. מע״מ יתווסף כחוק.</v>
       </c>
-      <c r="B30" s="51"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
       <c r="F30" s="40" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="40"/>
@@ -3570,33 +3580,33 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="51" t="str">
+      <c r="A31" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$29="","","• "&amp;הגדרות!$C$29)</f>
         <v>• פרויקטים פרטיים מתומחרים בנפרד, לפי הזמנת החווה.</v>
       </c>
-      <c r="B31" s="51"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="52" t="s">
-        <v>89</v>
-      </c>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="53" t="n">
+      <c r="B31" s="50"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="52" t="n">
         <f aca="false">I29+I30</f>
         <v>1625</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="51" t="str">
+      <c r="A32" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$30="","","• "&amp;הגדרות!$C$30)</f>
         <v/>
       </c>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
       <c r="F32" s="40" t="str">
         <f aca="false">"מע״מ "&amp;ROUND(הגדרות!$C$25*100,1)&amp;"%"</f>
         <v>מע״מ 18%</v>
@@ -3609,30 +3619,30 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F33" s="54" t="s">
-        <v>90</v>
-      </c>
-      <c r="G33" s="54"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="55" t="n">
+      <c r="F33" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="54" t="n">
         <f aca="false">I31+I32</f>
         <v>1917.5</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="56" t="str">
+      <c r="A36" s="55" t="str">
         <f aca="false">"בברכה, "&amp;הגדרות!$C$6</f>
         <v>בברכה, (למילוי)</v>
       </c>
-      <c r="B36" s="56"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="F36" s="56" t="s">
-        <v>91</v>
-      </c>
-      <c r="G36" s="56"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="56"/>
+      <c r="B36" s="55"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="F36" s="55" t="s">
+        <v>93</v>
+      </c>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="44">
@@ -3730,7 +3740,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -3766,13 +3776,13 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
       <c r="F4" s="29" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
@@ -3780,7 +3790,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
@@ -3789,7 +3799,7 @@
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="31" t="str">
@@ -3800,7 +3810,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="31" t="str">
@@ -3809,7 +3819,7 @@
       </c>
       <c r="D6" s="31"/>
       <c r="F6" s="30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="31" t="str">
@@ -3820,7 +3830,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="31" t="str">
@@ -3829,7 +3839,7 @@
       </c>
       <c r="D7" s="31"/>
       <c r="F7" s="30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="31" t="str">
@@ -3840,7 +3850,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="31" t="str">
@@ -3851,7 +3861,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="str">
@@ -3863,7 +3873,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
@@ -3872,7 +3882,7 @@
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
@@ -3882,7 +3892,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
@@ -3891,7 +3901,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31" t="str">
@@ -3902,7 +3912,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -3911,46 +3921,46 @@
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="35" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="38" t="n">
-        <f aca="false">IF(B15="","",ROW()-14)</f>
+        <f aca="false">IF(B15="","",COUNT($B$15:B15))</f>
         <v>1</v>
       </c>
       <c r="B15" s="39" t="n">
-        <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
+        <f aca="false">IF(K15="","",K15)</f>
         <v>46541</v>
       </c>
       <c r="C15" s="38" t="str">
@@ -3962,7 +3972,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F15" s="42" t="n">
         <f aca="false">IF(B15="","",IF(E15="לא",0,הגדרות!$C$22))</f>
@@ -3975,17 +3985,17 @@
       <c r="H15" s="44"/>
       <c r="I15" s="45"/>
       <c r="K15" s="27" t="n">
-        <f aca="false">IF(B15="","",B15+MIN(MOD(הגדרות!$D$18-WEEKDAY(B15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B15)-1,7)+1))</f>
-        <v>46544</v>
+        <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
+        <v>46541</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="38" t="n">
-        <f aca="false">IF(B16="","",ROW()-14)</f>
+        <f aca="false">IF(B16="","",COUNT($B$15:B16))</f>
         <v>2</v>
       </c>
       <c r="B16" s="39" t="n">
-        <f aca="false">IF(K15="","",IF(K15&gt;$K$2,"",K15))</f>
+        <f aca="false">IF(K16="","",K16)</f>
         <v>46544</v>
       </c>
       <c r="C16" s="38" t="str">
@@ -3997,7 +4007,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F16" s="42" t="n">
         <f aca="false">IF(B16="","",IF(E16="לא",0,הגדרות!$C$22))</f>
@@ -4010,17 +4020,17 @@
       <c r="H16" s="44"/>
       <c r="I16" s="45"/>
       <c r="K16" s="27" t="n">
-        <f aca="false">IF(B16="","",B16+MIN(MOD(הגדרות!$D$18-WEEKDAY(B16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B16)-1,7)+1))</f>
-        <v>46548</v>
+        <f aca="false">IF(K15="","",IF(K15+MIN(MOD(הגדרות!$D$18-WEEKDAY(K15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K15)-1,7)+1)&gt;$K$2,"",K15+MIN(MOD(הגדרות!$D$18-WEEKDAY(K15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K15)-1,7)+1)))</f>
+        <v>46544</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="38" t="n">
-        <f aca="false">IF(B17="","",ROW()-14)</f>
+        <f aca="false">IF(B17="","",COUNT($B$15:B17))</f>
         <v>3</v>
       </c>
       <c r="B17" s="39" t="n">
-        <f aca="false">IF(K16="","",IF(K16&gt;$K$2,"",K16))</f>
+        <f aca="false">IF(K17="","",K17)</f>
         <v>46548</v>
       </c>
       <c r="C17" s="38" t="str">
@@ -4032,7 +4042,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F17" s="42" t="n">
         <f aca="false">IF(B17="","",IF(E17="לא",0,הגדרות!$C$22))</f>
@@ -4045,17 +4055,17 @@
       <c r="H17" s="44"/>
       <c r="I17" s="45"/>
       <c r="K17" s="27" t="n">
-        <f aca="false">IF(B17="","",B17+MIN(MOD(הגדרות!$D$18-WEEKDAY(B17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B17)-1,7)+1))</f>
-        <v>46551</v>
+        <f aca="false">IF(K16="","",IF(K16+MIN(MOD(הגדרות!$D$18-WEEKDAY(K16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K16)-1,7)+1)&gt;$K$2,"",K16+MIN(MOD(הגדרות!$D$18-WEEKDAY(K16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K16)-1,7)+1)))</f>
+        <v>46548</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="38" t="n">
-        <f aca="false">IF(B18="","",ROW()-14)</f>
+        <f aca="false">IF(B18="","",COUNT($B$15:B18))</f>
         <v>4</v>
       </c>
       <c r="B18" s="39" t="n">
-        <f aca="false">IF(K17="","",IF(K17&gt;$K$2,"",K17))</f>
+        <f aca="false">IF(K18="","",K18)</f>
         <v>46551</v>
       </c>
       <c r="C18" s="38" t="str">
@@ -4067,7 +4077,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F18" s="42" t="n">
         <f aca="false">IF(B18="","",IF(E18="לא",0,הגדרות!$C$22))</f>
@@ -4080,17 +4090,17 @@
       <c r="H18" s="44"/>
       <c r="I18" s="45"/>
       <c r="K18" s="27" t="n">
-        <f aca="false">IF(B18="","",B18+MIN(MOD(הגדרות!$D$18-WEEKDAY(B18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B18)-1,7)+1))</f>
-        <v>46555</v>
+        <f aca="false">IF(K17="","",IF(K17+MIN(MOD(הגדרות!$D$18-WEEKDAY(K17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K17)-1,7)+1)&gt;$K$2,"",K17+MIN(MOD(הגדרות!$D$18-WEEKDAY(K17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K17)-1,7)+1)))</f>
+        <v>46551</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="38" t="n">
-        <f aca="false">IF(B19="","",ROW()-14)</f>
+        <f aca="false">IF(B19="","",COUNT($B$15:B19))</f>
         <v>5</v>
       </c>
       <c r="B19" s="39" t="n">
-        <f aca="false">IF(K18="","",IF(K18&gt;$K$2,"",K18))</f>
+        <f aca="false">IF(K19="","",K19)</f>
         <v>46555</v>
       </c>
       <c r="C19" s="38" t="str">
@@ -4102,7 +4112,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F19" s="42" t="n">
         <f aca="false">IF(B19="","",IF(E19="לא",0,הגדרות!$C$22))</f>
@@ -4115,17 +4125,17 @@
       <c r="H19" s="44"/>
       <c r="I19" s="45"/>
       <c r="K19" s="27" t="n">
-        <f aca="false">IF(B19="","",B19+MIN(MOD(הגדרות!$D$18-WEEKDAY(B19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B19)-1,7)+1))</f>
-        <v>46558</v>
+        <f aca="false">IF(K18="","",IF(K18+MIN(MOD(הגדרות!$D$18-WEEKDAY(K18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K18)-1,7)+1)&gt;$K$2,"",K18+MIN(MOD(הגדרות!$D$18-WEEKDAY(K18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K18)-1,7)+1)))</f>
+        <v>46555</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="38" t="n">
-        <f aca="false">IF(B20="","",ROW()-14)</f>
+        <f aca="false">IF(B20="","",COUNT($B$15:B20))</f>
         <v>6</v>
       </c>
       <c r="B20" s="39" t="n">
-        <f aca="false">IF(K19="","",IF(K19&gt;$K$2,"",K19))</f>
+        <f aca="false">IF(K20="","",K20)</f>
         <v>46558</v>
       </c>
       <c r="C20" s="38" t="str">
@@ -4137,7 +4147,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F20" s="42" t="n">
         <f aca="false">IF(B20="","",IF(E20="לא",0,הגדרות!$C$22))</f>
@@ -4150,17 +4160,17 @@
       <c r="H20" s="44"/>
       <c r="I20" s="45"/>
       <c r="K20" s="27" t="n">
-        <f aca="false">IF(B20="","",B20+MIN(MOD(הגדרות!$D$18-WEEKDAY(B20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B20)-1,7)+1))</f>
-        <v>46562</v>
+        <f aca="false">IF(K19="","",IF(K19+MIN(MOD(הגדרות!$D$18-WEEKDAY(K19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K19)-1,7)+1)&gt;$K$2,"",K19+MIN(MOD(הגדרות!$D$18-WEEKDAY(K19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K19)-1,7)+1)))</f>
+        <v>46558</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="38" t="n">
-        <f aca="false">IF(B21="","",ROW()-14)</f>
+        <f aca="false">IF(B21="","",COUNT($B$15:B21))</f>
         <v>7</v>
       </c>
       <c r="B21" s="39" t="n">
-        <f aca="false">IF(K20="","",IF(K20&gt;$K$2,"",K20))</f>
+        <f aca="false">IF(K21="","",K21)</f>
         <v>46562</v>
       </c>
       <c r="C21" s="38" t="str">
@@ -4172,7 +4182,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F21" s="42" t="n">
         <f aca="false">IF(B21="","",IF(E21="לא",0,הגדרות!$C$22))</f>
@@ -4185,17 +4195,17 @@
       <c r="H21" s="44"/>
       <c r="I21" s="45"/>
       <c r="K21" s="27" t="n">
-        <f aca="false">IF(B21="","",B21+MIN(MOD(הגדרות!$D$18-WEEKDAY(B21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B21)-1,7)+1))</f>
-        <v>46565</v>
+        <f aca="false">IF(K20="","",IF(K20+MIN(MOD(הגדרות!$D$18-WEEKDAY(K20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K20)-1,7)+1)&gt;$K$2,"",K20+MIN(MOD(הגדרות!$D$18-WEEKDAY(K20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K20)-1,7)+1)))</f>
+        <v>46562</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="38" t="n">
-        <f aca="false">IF(B22="","",ROW()-14)</f>
+        <f aca="false">IF(B22="","",COUNT($B$15:B22))</f>
         <v>8</v>
       </c>
       <c r="B22" s="39" t="n">
-        <f aca="false">IF(K21="","",IF(K21&gt;$K$2,"",K21))</f>
+        <f aca="false">IF(K22="","",K22)</f>
         <v>46565</v>
       </c>
       <c r="C22" s="38" t="str">
@@ -4207,7 +4217,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F22" s="42" t="n">
         <f aca="false">IF(B22="","",IF(E22="לא",0,הגדרות!$C$22))</f>
@@ -4220,17 +4230,17 @@
       <c r="H22" s="44"/>
       <c r="I22" s="45"/>
       <c r="K22" s="27" t="n">
-        <f aca="false">IF(B22="","",B22+MIN(MOD(הגדרות!$D$18-WEEKDAY(B22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B22)-1,7)+1))</f>
-        <v>46569</v>
+        <f aca="false">IF(K21="","",IF(K21+MIN(MOD(הגדרות!$D$18-WEEKDAY(K21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K21)-1,7)+1)&gt;$K$2,"",K21+MIN(MOD(הגדרות!$D$18-WEEKDAY(K21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K21)-1,7)+1)))</f>
+        <v>46565</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="38" t="str">
-        <f aca="false">IF(B23="","",ROW()-14)</f>
+        <f aca="false">IF(B23="","",COUNT($B$15:B23))</f>
         <v/>
       </c>
       <c r="B23" s="39" t="str">
-        <f aca="false">IF(K22="","",IF(K22&gt;$K$2,"",K22))</f>
+        <f aca="false">IF(K23="","",K23)</f>
         <v/>
       </c>
       <c r="C23" s="38" t="str">
@@ -4242,7 +4252,7 @@
         <v/>
       </c>
       <c r="E23" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F23" s="42" t="str">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
@@ -4255,17 +4265,17 @@
       <c r="H23" s="44"/>
       <c r="I23" s="45"/>
       <c r="K23" s="27" t="str">
-        <f aca="false">IF(B23="","",B23+MIN(MOD(הגדרות!$D$18-WEEKDAY(B23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B23)-1,7)+1))</f>
+        <f aca="false">IF(K22="","",IF(K22+MIN(MOD(הגדרות!$D$18-WEEKDAY(K22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K22)-1,7)+1)&gt;$K$2,"",K22+MIN(MOD(הגדרות!$D$18-WEEKDAY(K22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K22)-1,7)+1)))</f>
         <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="38" t="str">
-        <f aca="false">IF(B24="","",ROW()-14)</f>
+        <f aca="false">IF(B24="","",COUNT($B$15:B24))</f>
         <v/>
       </c>
       <c r="B24" s="39" t="str">
-        <f aca="false">IF(K23="","",IF(K23&gt;$K$2,"",K23))</f>
+        <f aca="false">IF(K24="","",K24)</f>
         <v/>
       </c>
       <c r="C24" s="38" t="str">
@@ -4277,7 +4287,7 @@
         <v/>
       </c>
       <c r="E24" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F24" s="42" t="str">
         <f aca="false">IF(B24="","",IF(E24="לא",0,הגדרות!$C$22))</f>
@@ -4290,7 +4300,7 @@
       <c r="H24" s="44"/>
       <c r="I24" s="45"/>
       <c r="K24" s="27" t="str">
-        <f aca="false">IF(B24="","",B24+MIN(MOD(הגדרות!$D$18-WEEKDAY(B24)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B24)-1,7)+1))</f>
+        <f aca="false">IF(K23="","",IF(K23+MIN(MOD(הגדרות!$D$18-WEEKDAY(K23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K23)-1,7)+1)&gt;$K$2,"",K23+MIN(MOD(הגדרות!$D$18-WEEKDAY(K23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K23)-1,7)+1)))</f>
         <v/>
       </c>
     </row>
@@ -4299,16 +4309,16 @@
         <f aca="false">COUNT($B$15:$B$24)+1</f>
         <v>9</v>
       </c>
-      <c r="B25" s="46"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="38" t="str">
         <f aca="false">IF(B25="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B25)))</f>
         <v/>
       </c>
       <c r="D25" s="40" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F25" s="42" t="n">
         <f aca="false">IF(E25="לא",0,הגדרות!$C$23)</f>
@@ -4323,36 +4333,36 @@
       <c r="K25" s="27"/>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="B26" s="47"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="48" t="n">
+      <c r="A26" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" s="46"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="47" t="n">
         <f aca="false">SUM(F15:F25)</f>
         <v>29</v>
       </c>
-      <c r="G26" s="49" t="n">
+      <c r="G26" s="48" t="n">
         <f aca="false">SUM(G15:G25)</f>
         <v>1450</v>
       </c>
-      <c r="H26" s="47"/>
-      <c r="I26" s="49" t="n">
+      <c r="H26" s="46"/>
+      <c r="I26" s="48" t="n">
         <f aca="false">SUM(I15:I25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
+      <c r="A28" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="49"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="49"/>
       <c r="F28" s="40" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G28" s="40"/>
       <c r="H28" s="40"/>
@@ -4362,14 +4372,14 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="51" t="str">
+      <c r="A29" s="50" t="str">
         <f aca="false">"• "&amp;הגדרות!$C$17&amp;": ימי "&amp;הגדרות!$C$18&amp;" ו"&amp;הגדרות!$C$19&amp;", "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00")&amp;" ("&amp;הגדרות!$C$22&amp;" שעות ליום), וישיבת צוות חודשית ("&amp;הגדרות!$C$23&amp;" ש׳)."</f>
         <v>• הדרכת שיקום: ימי ראשון וחמישי, 09:00–12:30 (3.5 שעות ליום), וישיבת צוות חודשית (1 ש׳).</v>
       </c>
-      <c r="B29" s="51"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
       <c r="F29" s="40" t="str">
         <f aca="false">"הדרכת שיקום ("&amp;TEXT(F26,"0.0")&amp;" שעות × "&amp;הגדרות!$C$24&amp;" ₪)"</f>
         <v>הדרכת שיקום (29.0 שעות × 50 ₪)</v>
@@ -4382,16 +4392,16 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="51" t="str">
+      <c r="A30" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$28="","","• "&amp;הגדרות!$C$28)</f>
         <v>• התעריף השעתי אינו כולל מע״מ. מע״מ יתווסף כחוק.</v>
       </c>
-      <c r="B30" s="51"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
       <c r="F30" s="40" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="40"/>
@@ -4401,33 +4411,33 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="51" t="str">
+      <c r="A31" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$29="","","• "&amp;הגדרות!$C$29)</f>
         <v>• פרויקטים פרטיים מתומחרים בנפרד, לפי הזמנת החווה.</v>
       </c>
-      <c r="B31" s="51"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="52" t="s">
-        <v>89</v>
-      </c>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="53" t="n">
+      <c r="B31" s="50"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="52" t="n">
         <f aca="false">I29+I30</f>
         <v>1450</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="51" t="str">
+      <c r="A32" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$30="","","• "&amp;הגדרות!$C$30)</f>
         <v/>
       </c>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
       <c r="F32" s="40" t="str">
         <f aca="false">"מע״מ "&amp;ROUND(הגדרות!$C$25*100,1)&amp;"%"</f>
         <v>מע״מ 18%</v>
@@ -4440,30 +4450,30 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F33" s="54" t="s">
-        <v>90</v>
-      </c>
-      <c r="G33" s="54"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="55" t="n">
+      <c r="F33" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="54" t="n">
         <f aca="false">I31+I32</f>
         <v>1711</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="56" t="str">
+      <c r="A36" s="55" t="str">
         <f aca="false">"בברכה, "&amp;הגדרות!$C$6</f>
         <v>בברכה, (למילוי)</v>
       </c>
-      <c r="B36" s="56"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="F36" s="56" t="s">
-        <v>91</v>
-      </c>
-      <c r="G36" s="56"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="56"/>
+      <c r="B36" s="55"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="F36" s="55" t="s">
+        <v>93</v>
+      </c>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="44">
@@ -4561,7 +4571,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -4597,13 +4607,13 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
       <c r="F4" s="29" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
@@ -4611,7 +4621,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
@@ -4620,7 +4630,7 @@
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="31" t="str">
@@ -4631,7 +4641,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="31" t="str">
@@ -4640,7 +4650,7 @@
       </c>
       <c r="D6" s="31"/>
       <c r="F6" s="30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="31" t="str">
@@ -4651,7 +4661,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="31" t="str">
@@ -4660,7 +4670,7 @@
       </c>
       <c r="D7" s="31"/>
       <c r="F7" s="30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="31" t="str">
@@ -4671,7 +4681,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="31" t="str">
@@ -4682,7 +4692,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="str">
@@ -4694,7 +4704,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
@@ -4703,7 +4713,7 @@
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
@@ -4713,7 +4723,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
@@ -4722,7 +4732,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31" t="str">
@@ -4733,7 +4743,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -4742,46 +4752,46 @@
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="35" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="38" t="n">
-        <f aca="false">IF(B15="","",ROW()-14)</f>
+        <f aca="false">IF(B15="","",COUNT($B$15:B15))</f>
         <v>1</v>
       </c>
       <c r="B15" s="39" t="n">
-        <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
+        <f aca="false">IF(K15="","",K15)</f>
         <v>46569</v>
       </c>
       <c r="C15" s="38" t="str">
@@ -4793,7 +4803,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F15" s="42" t="n">
         <f aca="false">IF(B15="","",IF(E15="לא",0,הגדרות!$C$22))</f>
@@ -4806,17 +4816,17 @@
       <c r="H15" s="44"/>
       <c r="I15" s="45"/>
       <c r="K15" s="27" t="n">
-        <f aca="false">IF(B15="","",B15+MIN(MOD(הגדרות!$D$18-WEEKDAY(B15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B15)-1,7)+1))</f>
-        <v>46572</v>
+        <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
+        <v>46569</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="38" t="n">
-        <f aca="false">IF(B16="","",ROW()-14)</f>
+        <f aca="false">IF(B16="","",COUNT($B$15:B16))</f>
         <v>2</v>
       </c>
       <c r="B16" s="39" t="n">
-        <f aca="false">IF(K15="","",IF(K15&gt;$K$2,"",K15))</f>
+        <f aca="false">IF(K16="","",K16)</f>
         <v>46572</v>
       </c>
       <c r="C16" s="38" t="str">
@@ -4828,7 +4838,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F16" s="42" t="n">
         <f aca="false">IF(B16="","",IF(E16="לא",0,הגדרות!$C$22))</f>
@@ -4841,17 +4851,17 @@
       <c r="H16" s="44"/>
       <c r="I16" s="45"/>
       <c r="K16" s="27" t="n">
-        <f aca="false">IF(B16="","",B16+MIN(MOD(הגדרות!$D$18-WEEKDAY(B16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B16)-1,7)+1))</f>
-        <v>46576</v>
+        <f aca="false">IF(K15="","",IF(K15+MIN(MOD(הגדרות!$D$18-WEEKDAY(K15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K15)-1,7)+1)&gt;$K$2,"",K15+MIN(MOD(הגדרות!$D$18-WEEKDAY(K15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K15)-1,7)+1)))</f>
+        <v>46572</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="38" t="n">
-        <f aca="false">IF(B17="","",ROW()-14)</f>
+        <f aca="false">IF(B17="","",COUNT($B$15:B17))</f>
         <v>3</v>
       </c>
       <c r="B17" s="39" t="n">
-        <f aca="false">IF(K16="","",IF(K16&gt;$K$2,"",K16))</f>
+        <f aca="false">IF(K17="","",K17)</f>
         <v>46576</v>
       </c>
       <c r="C17" s="38" t="str">
@@ -4863,7 +4873,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F17" s="42" t="n">
         <f aca="false">IF(B17="","",IF(E17="לא",0,הגדרות!$C$22))</f>
@@ -4876,17 +4886,17 @@
       <c r="H17" s="44"/>
       <c r="I17" s="45"/>
       <c r="K17" s="27" t="n">
-        <f aca="false">IF(B17="","",B17+MIN(MOD(הגדרות!$D$18-WEEKDAY(B17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B17)-1,7)+1))</f>
-        <v>46579</v>
+        <f aca="false">IF(K16="","",IF(K16+MIN(MOD(הגדרות!$D$18-WEEKDAY(K16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K16)-1,7)+1)&gt;$K$2,"",K16+MIN(MOD(הגדרות!$D$18-WEEKDAY(K16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K16)-1,7)+1)))</f>
+        <v>46576</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="38" t="n">
-        <f aca="false">IF(B18="","",ROW()-14)</f>
+        <f aca="false">IF(B18="","",COUNT($B$15:B18))</f>
         <v>4</v>
       </c>
       <c r="B18" s="39" t="n">
-        <f aca="false">IF(K17="","",IF(K17&gt;$K$2,"",K17))</f>
+        <f aca="false">IF(K18="","",K18)</f>
         <v>46579</v>
       </c>
       <c r="C18" s="38" t="str">
@@ -4898,7 +4908,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F18" s="42" t="n">
         <f aca="false">IF(B18="","",IF(E18="לא",0,הגדרות!$C$22))</f>
@@ -4911,17 +4921,17 @@
       <c r="H18" s="44"/>
       <c r="I18" s="45"/>
       <c r="K18" s="27" t="n">
-        <f aca="false">IF(B18="","",B18+MIN(MOD(הגדרות!$D$18-WEEKDAY(B18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B18)-1,7)+1))</f>
-        <v>46583</v>
+        <f aca="false">IF(K17="","",IF(K17+MIN(MOD(הגדרות!$D$18-WEEKDAY(K17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K17)-1,7)+1)&gt;$K$2,"",K17+MIN(MOD(הגדרות!$D$18-WEEKDAY(K17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K17)-1,7)+1)))</f>
+        <v>46579</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="38" t="n">
-        <f aca="false">IF(B19="","",ROW()-14)</f>
+        <f aca="false">IF(B19="","",COUNT($B$15:B19))</f>
         <v>5</v>
       </c>
       <c r="B19" s="39" t="n">
-        <f aca="false">IF(K18="","",IF(K18&gt;$K$2,"",K18))</f>
+        <f aca="false">IF(K19="","",K19)</f>
         <v>46583</v>
       </c>
       <c r="C19" s="38" t="str">
@@ -4933,7 +4943,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F19" s="42" t="n">
         <f aca="false">IF(B19="","",IF(E19="לא",0,הגדרות!$C$22))</f>
@@ -4946,17 +4956,17 @@
       <c r="H19" s="44"/>
       <c r="I19" s="45"/>
       <c r="K19" s="27" t="n">
-        <f aca="false">IF(B19="","",B19+MIN(MOD(הגדרות!$D$18-WEEKDAY(B19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B19)-1,7)+1))</f>
-        <v>46586</v>
+        <f aca="false">IF(K18="","",IF(K18+MIN(MOD(הגדרות!$D$18-WEEKDAY(K18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K18)-1,7)+1)&gt;$K$2,"",K18+MIN(MOD(הגדרות!$D$18-WEEKDAY(K18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K18)-1,7)+1)))</f>
+        <v>46583</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="38" t="n">
-        <f aca="false">IF(B20="","",ROW()-14)</f>
+        <f aca="false">IF(B20="","",COUNT($B$15:B20))</f>
         <v>6</v>
       </c>
       <c r="B20" s="39" t="n">
-        <f aca="false">IF(K19="","",IF(K19&gt;$K$2,"",K19))</f>
+        <f aca="false">IF(K20="","",K20)</f>
         <v>46586</v>
       </c>
       <c r="C20" s="38" t="str">
@@ -4968,7 +4978,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F20" s="42" t="n">
         <f aca="false">IF(B20="","",IF(E20="לא",0,הגדרות!$C$22))</f>
@@ -4981,17 +4991,17 @@
       <c r="H20" s="44"/>
       <c r="I20" s="45"/>
       <c r="K20" s="27" t="n">
-        <f aca="false">IF(B20="","",B20+MIN(MOD(הגדרות!$D$18-WEEKDAY(B20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B20)-1,7)+1))</f>
-        <v>46590</v>
+        <f aca="false">IF(K19="","",IF(K19+MIN(MOD(הגדרות!$D$18-WEEKDAY(K19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K19)-1,7)+1)&gt;$K$2,"",K19+MIN(MOD(הגדרות!$D$18-WEEKDAY(K19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K19)-1,7)+1)))</f>
+        <v>46586</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="38" t="n">
-        <f aca="false">IF(B21="","",ROW()-14)</f>
+        <f aca="false">IF(B21="","",COUNT($B$15:B21))</f>
         <v>7</v>
       </c>
       <c r="B21" s="39" t="n">
-        <f aca="false">IF(K20="","",IF(K20&gt;$K$2,"",K20))</f>
+        <f aca="false">IF(K21="","",K21)</f>
         <v>46590</v>
       </c>
       <c r="C21" s="38" t="str">
@@ -5003,7 +5013,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F21" s="42" t="n">
         <f aca="false">IF(B21="","",IF(E21="לא",0,הגדרות!$C$22))</f>
@@ -5016,17 +5026,17 @@
       <c r="H21" s="44"/>
       <c r="I21" s="45"/>
       <c r="K21" s="27" t="n">
-        <f aca="false">IF(B21="","",B21+MIN(MOD(הגדרות!$D$18-WEEKDAY(B21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B21)-1,7)+1))</f>
-        <v>46593</v>
+        <f aca="false">IF(K20="","",IF(K20+MIN(MOD(הגדרות!$D$18-WEEKDAY(K20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K20)-1,7)+1)&gt;$K$2,"",K20+MIN(MOD(הגדרות!$D$18-WEEKDAY(K20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K20)-1,7)+1)))</f>
+        <v>46590</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="38" t="n">
-        <f aca="false">IF(B22="","",ROW()-14)</f>
+        <f aca="false">IF(B22="","",COUNT($B$15:B22))</f>
         <v>8</v>
       </c>
       <c r="B22" s="39" t="n">
-        <f aca="false">IF(K21="","",IF(K21&gt;$K$2,"",K21))</f>
+        <f aca="false">IF(K22="","",K22)</f>
         <v>46593</v>
       </c>
       <c r="C22" s="38" t="str">
@@ -5038,7 +5048,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F22" s="42" t="n">
         <f aca="false">IF(B22="","",IF(E22="לא",0,הגדרות!$C$22))</f>
@@ -5051,17 +5061,17 @@
       <c r="H22" s="44"/>
       <c r="I22" s="45"/>
       <c r="K22" s="27" t="n">
-        <f aca="false">IF(B22="","",B22+MIN(MOD(הגדרות!$D$18-WEEKDAY(B22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B22)-1,7)+1))</f>
-        <v>46597</v>
+        <f aca="false">IF(K21="","",IF(K21+MIN(MOD(הגדרות!$D$18-WEEKDAY(K21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K21)-1,7)+1)&gt;$K$2,"",K21+MIN(MOD(הגדרות!$D$18-WEEKDAY(K21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K21)-1,7)+1)))</f>
+        <v>46593</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="38" t="n">
-        <f aca="false">IF(B23="","",ROW()-14)</f>
+        <f aca="false">IF(B23="","",COUNT($B$15:B23))</f>
         <v>9</v>
       </c>
       <c r="B23" s="39" t="n">
-        <f aca="false">IF(K22="","",IF(K22&gt;$K$2,"",K22))</f>
+        <f aca="false">IF(K23="","",K23)</f>
         <v>46597</v>
       </c>
       <c r="C23" s="38" t="str">
@@ -5073,7 +5083,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F23" s="42" t="n">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
@@ -5086,17 +5096,17 @@
       <c r="H23" s="44"/>
       <c r="I23" s="45"/>
       <c r="K23" s="27" t="n">
-        <f aca="false">IF(B23="","",B23+MIN(MOD(הגדרות!$D$18-WEEKDAY(B23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B23)-1,7)+1))</f>
-        <v>46600</v>
+        <f aca="false">IF(K22="","",IF(K22+MIN(MOD(הגדרות!$D$18-WEEKDAY(K22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K22)-1,7)+1)&gt;$K$2,"",K22+MIN(MOD(הגדרות!$D$18-WEEKDAY(K22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K22)-1,7)+1)))</f>
+        <v>46597</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="38" t="str">
-        <f aca="false">IF(B24="","",ROW()-14)</f>
+        <f aca="false">IF(B24="","",COUNT($B$15:B24))</f>
         <v/>
       </c>
       <c r="B24" s="39" t="str">
-        <f aca="false">IF(K23="","",IF(K23&gt;$K$2,"",K23))</f>
+        <f aca="false">IF(K24="","",K24)</f>
         <v/>
       </c>
       <c r="C24" s="38" t="str">
@@ -5108,7 +5118,7 @@
         <v/>
       </c>
       <c r="E24" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F24" s="42" t="str">
         <f aca="false">IF(B24="","",IF(E24="לא",0,הגדרות!$C$22))</f>
@@ -5121,7 +5131,7 @@
       <c r="H24" s="44"/>
       <c r="I24" s="45"/>
       <c r="K24" s="27" t="str">
-        <f aca="false">IF(B24="","",B24+MIN(MOD(הגדרות!$D$18-WEEKDAY(B24)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B24)-1,7)+1))</f>
+        <f aca="false">IF(K23="","",IF(K23+MIN(MOD(הגדרות!$D$18-WEEKDAY(K23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K23)-1,7)+1)&gt;$K$2,"",K23+MIN(MOD(הגדרות!$D$18-WEEKDAY(K23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K23)-1,7)+1)))</f>
         <v/>
       </c>
     </row>
@@ -5130,16 +5140,16 @@
         <f aca="false">COUNT($B$15:$B$24)+1</f>
         <v>10</v>
       </c>
-      <c r="B25" s="46"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="38" t="str">
         <f aca="false">IF(B25="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B25)))</f>
         <v/>
       </c>
       <c r="D25" s="40" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F25" s="42" t="n">
         <f aca="false">IF(E25="לא",0,הגדרות!$C$23)</f>
@@ -5154,36 +5164,36 @@
       <c r="K25" s="27"/>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="B26" s="47"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="48" t="n">
+      <c r="A26" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" s="46"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="47" t="n">
         <f aca="false">SUM(F15:F25)</f>
         <v>32.5</v>
       </c>
-      <c r="G26" s="49" t="n">
+      <c r="G26" s="48" t="n">
         <f aca="false">SUM(G15:G25)</f>
         <v>1625</v>
       </c>
-      <c r="H26" s="47"/>
-      <c r="I26" s="49" t="n">
+      <c r="H26" s="46"/>
+      <c r="I26" s="48" t="n">
         <f aca="false">SUM(I15:I25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
+      <c r="A28" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="49"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="49"/>
       <c r="F28" s="40" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G28" s="40"/>
       <c r="H28" s="40"/>
@@ -5193,14 +5203,14 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="51" t="str">
+      <c r="A29" s="50" t="str">
         <f aca="false">"• "&amp;הגדרות!$C$17&amp;": ימי "&amp;הגדרות!$C$18&amp;" ו"&amp;הגדרות!$C$19&amp;", "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00")&amp;" ("&amp;הגדרות!$C$22&amp;" שעות ליום), וישיבת צוות חודשית ("&amp;הגדרות!$C$23&amp;" ש׳)."</f>
         <v>• הדרכת שיקום: ימי ראשון וחמישי, 09:00–12:30 (3.5 שעות ליום), וישיבת צוות חודשית (1 ש׳).</v>
       </c>
-      <c r="B29" s="51"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
       <c r="F29" s="40" t="str">
         <f aca="false">"הדרכת שיקום ("&amp;TEXT(F26,"0.0")&amp;" שעות × "&amp;הגדרות!$C$24&amp;" ₪)"</f>
         <v>הדרכת שיקום (32.5 שעות × 50 ₪)</v>
@@ -5213,16 +5223,16 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="51" t="str">
+      <c r="A30" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$28="","","• "&amp;הגדרות!$C$28)</f>
         <v>• התעריף השעתי אינו כולל מע״מ. מע״מ יתווסף כחוק.</v>
       </c>
-      <c r="B30" s="51"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
       <c r="F30" s="40" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="40"/>
@@ -5232,33 +5242,33 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="51" t="str">
+      <c r="A31" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$29="","","• "&amp;הגדרות!$C$29)</f>
         <v>• פרויקטים פרטיים מתומחרים בנפרד, לפי הזמנת החווה.</v>
       </c>
-      <c r="B31" s="51"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="52" t="s">
-        <v>89</v>
-      </c>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="53" t="n">
+      <c r="B31" s="50"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="52" t="n">
         <f aca="false">I29+I30</f>
         <v>1625</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="51" t="str">
+      <c r="A32" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$30="","","• "&amp;הגדרות!$C$30)</f>
         <v/>
       </c>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
       <c r="F32" s="40" t="str">
         <f aca="false">"מע״מ "&amp;ROUND(הגדרות!$C$25*100,1)&amp;"%"</f>
         <v>מע״מ 18%</v>
@@ -5271,30 +5281,30 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F33" s="54" t="s">
-        <v>90</v>
-      </c>
-      <c r="G33" s="54"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="55" t="n">
+      <c r="F33" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="54" t="n">
         <f aca="false">I31+I32</f>
         <v>1917.5</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="56" t="str">
+      <c r="A36" s="55" t="str">
         <f aca="false">"בברכה, "&amp;הגדרות!$C$6</f>
         <v>בברכה, (למילוי)</v>
       </c>
-      <c r="B36" s="56"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="F36" s="56" t="s">
-        <v>91</v>
-      </c>
-      <c r="G36" s="56"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="56"/>
+      <c r="B36" s="55"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="F36" s="55" t="s">
+        <v>93</v>
+      </c>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="44">
@@ -5392,7 +5402,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -5428,13 +5438,13 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
       <c r="F4" s="29" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
@@ -5442,7 +5452,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
@@ -5451,7 +5461,7 @@
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="31" t="str">
@@ -5462,7 +5472,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="31" t="str">
@@ -5471,7 +5481,7 @@
       </c>
       <c r="D6" s="31"/>
       <c r="F6" s="30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="31" t="str">
@@ -5482,7 +5492,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="31" t="str">
@@ -5491,7 +5501,7 @@
       </c>
       <c r="D7" s="31"/>
       <c r="F7" s="30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="31" t="str">
@@ -5502,7 +5512,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="31" t="str">
@@ -5513,7 +5523,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="str">
@@ -5525,7 +5535,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
@@ -5534,7 +5544,7 @@
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
@@ -5544,7 +5554,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
@@ -5553,7 +5563,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31" t="str">
@@ -5564,7 +5574,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -5573,46 +5583,46 @@
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="35" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="38" t="n">
-        <f aca="false">IF(B15="","",ROW()-14)</f>
+        <f aca="false">IF(B15="","",COUNT($B$15:B15))</f>
         <v>1</v>
       </c>
       <c r="B15" s="39" t="n">
-        <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
+        <f aca="false">IF(K15="","",K15)</f>
         <v>46600</v>
       </c>
       <c r="C15" s="38" t="str">
@@ -5624,7 +5634,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F15" s="42" t="n">
         <f aca="false">IF(B15="","",IF(E15="לא",0,הגדרות!$C$22))</f>
@@ -5637,17 +5647,17 @@
       <c r="H15" s="44"/>
       <c r="I15" s="45"/>
       <c r="K15" s="27" t="n">
-        <f aca="false">IF(B15="","",B15+MIN(MOD(הגדרות!$D$18-WEEKDAY(B15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B15)-1,7)+1))</f>
-        <v>46604</v>
+        <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
+        <v>46600</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="38" t="n">
-        <f aca="false">IF(B16="","",ROW()-14)</f>
+        <f aca="false">IF(B16="","",COUNT($B$15:B16))</f>
         <v>2</v>
       </c>
       <c r="B16" s="39" t="n">
-        <f aca="false">IF(K15="","",IF(K15&gt;$K$2,"",K15))</f>
+        <f aca="false">IF(K16="","",K16)</f>
         <v>46604</v>
       </c>
       <c r="C16" s="38" t="str">
@@ -5659,7 +5669,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F16" s="42" t="n">
         <f aca="false">IF(B16="","",IF(E16="לא",0,הגדרות!$C$22))</f>
@@ -5672,17 +5682,17 @@
       <c r="H16" s="44"/>
       <c r="I16" s="45"/>
       <c r="K16" s="27" t="n">
-        <f aca="false">IF(B16="","",B16+MIN(MOD(הגדרות!$D$18-WEEKDAY(B16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B16)-1,7)+1))</f>
-        <v>46607</v>
+        <f aca="false">IF(K15="","",IF(K15+MIN(MOD(הגדרות!$D$18-WEEKDAY(K15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K15)-1,7)+1)&gt;$K$2,"",K15+MIN(MOD(הגדרות!$D$18-WEEKDAY(K15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K15)-1,7)+1)))</f>
+        <v>46604</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="38" t="n">
-        <f aca="false">IF(B17="","",ROW()-14)</f>
+        <f aca="false">IF(B17="","",COUNT($B$15:B17))</f>
         <v>3</v>
       </c>
       <c r="B17" s="39" t="n">
-        <f aca="false">IF(K16="","",IF(K16&gt;$K$2,"",K16))</f>
+        <f aca="false">IF(K17="","",K17)</f>
         <v>46607</v>
       </c>
       <c r="C17" s="38" t="str">
@@ -5694,7 +5704,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F17" s="42" t="n">
         <f aca="false">IF(B17="","",IF(E17="לא",0,הגדרות!$C$22))</f>
@@ -5707,17 +5717,17 @@
       <c r="H17" s="44"/>
       <c r="I17" s="45"/>
       <c r="K17" s="27" t="n">
-        <f aca="false">IF(B17="","",B17+MIN(MOD(הגדרות!$D$18-WEEKDAY(B17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B17)-1,7)+1))</f>
-        <v>46611</v>
+        <f aca="false">IF(K16="","",IF(K16+MIN(MOD(הגדרות!$D$18-WEEKDAY(K16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K16)-1,7)+1)&gt;$K$2,"",K16+MIN(MOD(הגדרות!$D$18-WEEKDAY(K16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K16)-1,7)+1)))</f>
+        <v>46607</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="38" t="n">
-        <f aca="false">IF(B18="","",ROW()-14)</f>
+        <f aca="false">IF(B18="","",COUNT($B$15:B18))</f>
         <v>4</v>
       </c>
       <c r="B18" s="39" t="n">
-        <f aca="false">IF(K17="","",IF(K17&gt;$K$2,"",K17))</f>
+        <f aca="false">IF(K18="","",K18)</f>
         <v>46611</v>
       </c>
       <c r="C18" s="38" t="str">
@@ -5729,7 +5739,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F18" s="42" t="n">
         <f aca="false">IF(B18="","",IF(E18="לא",0,הגדרות!$C$22))</f>
@@ -5742,17 +5752,17 @@
       <c r="H18" s="44"/>
       <c r="I18" s="45"/>
       <c r="K18" s="27" t="n">
-        <f aca="false">IF(B18="","",B18+MIN(MOD(הגדרות!$D$18-WEEKDAY(B18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B18)-1,7)+1))</f>
-        <v>46614</v>
+        <f aca="false">IF(K17="","",IF(K17+MIN(MOD(הגדרות!$D$18-WEEKDAY(K17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K17)-1,7)+1)&gt;$K$2,"",K17+MIN(MOD(הגדרות!$D$18-WEEKDAY(K17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K17)-1,7)+1)))</f>
+        <v>46611</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="38" t="n">
-        <f aca="false">IF(B19="","",ROW()-14)</f>
+        <f aca="false">IF(B19="","",COUNT($B$15:B19))</f>
         <v>5</v>
       </c>
       <c r="B19" s="39" t="n">
-        <f aca="false">IF(K18="","",IF(K18&gt;$K$2,"",K18))</f>
+        <f aca="false">IF(K19="","",K19)</f>
         <v>46614</v>
       </c>
       <c r="C19" s="38" t="str">
@@ -5764,7 +5774,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F19" s="42" t="n">
         <f aca="false">IF(B19="","",IF(E19="לא",0,הגדרות!$C$22))</f>
@@ -5777,17 +5787,17 @@
       <c r="H19" s="44"/>
       <c r="I19" s="45"/>
       <c r="K19" s="27" t="n">
-        <f aca="false">IF(B19="","",B19+MIN(MOD(הגדרות!$D$18-WEEKDAY(B19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B19)-1,7)+1))</f>
-        <v>46618</v>
+        <f aca="false">IF(K18="","",IF(K18+MIN(MOD(הגדרות!$D$18-WEEKDAY(K18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K18)-1,7)+1)&gt;$K$2,"",K18+MIN(MOD(הגדרות!$D$18-WEEKDAY(K18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K18)-1,7)+1)))</f>
+        <v>46614</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="38" t="n">
-        <f aca="false">IF(B20="","",ROW()-14)</f>
+        <f aca="false">IF(B20="","",COUNT($B$15:B20))</f>
         <v>6</v>
       </c>
       <c r="B20" s="39" t="n">
-        <f aca="false">IF(K19="","",IF(K19&gt;$K$2,"",K19))</f>
+        <f aca="false">IF(K20="","",K20)</f>
         <v>46618</v>
       </c>
       <c r="C20" s="38" t="str">
@@ -5799,7 +5809,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F20" s="42" t="n">
         <f aca="false">IF(B20="","",IF(E20="לא",0,הגדרות!$C$22))</f>
@@ -5812,17 +5822,17 @@
       <c r="H20" s="44"/>
       <c r="I20" s="45"/>
       <c r="K20" s="27" t="n">
-        <f aca="false">IF(B20="","",B20+MIN(MOD(הגדרות!$D$18-WEEKDAY(B20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B20)-1,7)+1))</f>
-        <v>46621</v>
+        <f aca="false">IF(K19="","",IF(K19+MIN(MOD(הגדרות!$D$18-WEEKDAY(K19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K19)-1,7)+1)&gt;$K$2,"",K19+MIN(MOD(הגדרות!$D$18-WEEKDAY(K19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K19)-1,7)+1)))</f>
+        <v>46618</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="38" t="n">
-        <f aca="false">IF(B21="","",ROW()-14)</f>
+        <f aca="false">IF(B21="","",COUNT($B$15:B21))</f>
         <v>7</v>
       </c>
       <c r="B21" s="39" t="n">
-        <f aca="false">IF(K20="","",IF(K20&gt;$K$2,"",K20))</f>
+        <f aca="false">IF(K21="","",K21)</f>
         <v>46621</v>
       </c>
       <c r="C21" s="38" t="str">
@@ -5834,7 +5844,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F21" s="42" t="n">
         <f aca="false">IF(B21="","",IF(E21="לא",0,הגדרות!$C$22))</f>
@@ -5847,17 +5857,17 @@
       <c r="H21" s="44"/>
       <c r="I21" s="45"/>
       <c r="K21" s="27" t="n">
-        <f aca="false">IF(B21="","",B21+MIN(MOD(הגדרות!$D$18-WEEKDAY(B21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B21)-1,7)+1))</f>
-        <v>46625</v>
+        <f aca="false">IF(K20="","",IF(K20+MIN(MOD(הגדרות!$D$18-WEEKDAY(K20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K20)-1,7)+1)&gt;$K$2,"",K20+MIN(MOD(הגדרות!$D$18-WEEKDAY(K20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K20)-1,7)+1)))</f>
+        <v>46621</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="38" t="n">
-        <f aca="false">IF(B22="","",ROW()-14)</f>
+        <f aca="false">IF(B22="","",COUNT($B$15:B22))</f>
         <v>8</v>
       </c>
       <c r="B22" s="39" t="n">
-        <f aca="false">IF(K21="","",IF(K21&gt;$K$2,"",K21))</f>
+        <f aca="false">IF(K22="","",K22)</f>
         <v>46625</v>
       </c>
       <c r="C22" s="38" t="str">
@@ -5869,7 +5879,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F22" s="42" t="n">
         <f aca="false">IF(B22="","",IF(E22="לא",0,הגדרות!$C$22))</f>
@@ -5882,17 +5892,17 @@
       <c r="H22" s="44"/>
       <c r="I22" s="45"/>
       <c r="K22" s="27" t="n">
-        <f aca="false">IF(B22="","",B22+MIN(MOD(הגדרות!$D$18-WEEKDAY(B22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B22)-1,7)+1))</f>
-        <v>46628</v>
+        <f aca="false">IF(K21="","",IF(K21+MIN(MOD(הגדרות!$D$18-WEEKDAY(K21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K21)-1,7)+1)&gt;$K$2,"",K21+MIN(MOD(הגדרות!$D$18-WEEKDAY(K21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K21)-1,7)+1)))</f>
+        <v>46625</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="38" t="n">
-        <f aca="false">IF(B23="","",ROW()-14)</f>
+        <f aca="false">IF(B23="","",COUNT($B$15:B23))</f>
         <v>9</v>
       </c>
       <c r="B23" s="39" t="n">
-        <f aca="false">IF(K22="","",IF(K22&gt;$K$2,"",K22))</f>
+        <f aca="false">IF(K23="","",K23)</f>
         <v>46628</v>
       </c>
       <c r="C23" s="38" t="str">
@@ -5904,7 +5914,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F23" s="42" t="n">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
@@ -5917,17 +5927,17 @@
       <c r="H23" s="44"/>
       <c r="I23" s="45"/>
       <c r="K23" s="27" t="n">
-        <f aca="false">IF(B23="","",B23+MIN(MOD(הגדרות!$D$18-WEEKDAY(B23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B23)-1,7)+1))</f>
-        <v>46632</v>
+        <f aca="false">IF(K22="","",IF(K22+MIN(MOD(הגדרות!$D$18-WEEKDAY(K22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K22)-1,7)+1)&gt;$K$2,"",K22+MIN(MOD(הגדרות!$D$18-WEEKDAY(K22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K22)-1,7)+1)))</f>
+        <v>46628</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="38" t="str">
-        <f aca="false">IF(B24="","",ROW()-14)</f>
+        <f aca="false">IF(B24="","",COUNT($B$15:B24))</f>
         <v/>
       </c>
       <c r="B24" s="39" t="str">
-        <f aca="false">IF(K23="","",IF(K23&gt;$K$2,"",K23))</f>
+        <f aca="false">IF(K24="","",K24)</f>
         <v/>
       </c>
       <c r="C24" s="38" t="str">
@@ -5939,7 +5949,7 @@
         <v/>
       </c>
       <c r="E24" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F24" s="42" t="str">
         <f aca="false">IF(B24="","",IF(E24="לא",0,הגדרות!$C$22))</f>
@@ -5952,7 +5962,7 @@
       <c r="H24" s="44"/>
       <c r="I24" s="45"/>
       <c r="K24" s="27" t="str">
-        <f aca="false">IF(B24="","",B24+MIN(MOD(הגדרות!$D$18-WEEKDAY(B24)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B24)-1,7)+1))</f>
+        <f aca="false">IF(K23="","",IF(K23+MIN(MOD(הגדרות!$D$18-WEEKDAY(K23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K23)-1,7)+1)&gt;$K$2,"",K23+MIN(MOD(הגדרות!$D$18-WEEKDAY(K23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K23)-1,7)+1)))</f>
         <v/>
       </c>
     </row>
@@ -5961,16 +5971,16 @@
         <f aca="false">COUNT($B$15:$B$24)+1</f>
         <v>10</v>
       </c>
-      <c r="B25" s="46"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="38" t="str">
         <f aca="false">IF(B25="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B25)))</f>
         <v/>
       </c>
       <c r="D25" s="40" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F25" s="42" t="n">
         <f aca="false">IF(E25="לא",0,הגדרות!$C$23)</f>
@@ -5985,36 +5995,36 @@
       <c r="K25" s="27"/>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="B26" s="47"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="48" t="n">
+      <c r="A26" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" s="46"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="47" t="n">
         <f aca="false">SUM(F15:F25)</f>
         <v>32.5</v>
       </c>
-      <c r="G26" s="49" t="n">
+      <c r="G26" s="48" t="n">
         <f aca="false">SUM(G15:G25)</f>
         <v>1625</v>
       </c>
-      <c r="H26" s="47"/>
-      <c r="I26" s="49" t="n">
+      <c r="H26" s="46"/>
+      <c r="I26" s="48" t="n">
         <f aca="false">SUM(I15:I25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
+      <c r="A28" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="49"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="49"/>
       <c r="F28" s="40" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G28" s="40"/>
       <c r="H28" s="40"/>
@@ -6024,14 +6034,14 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="51" t="str">
+      <c r="A29" s="50" t="str">
         <f aca="false">"• "&amp;הגדרות!$C$17&amp;": ימי "&amp;הגדרות!$C$18&amp;" ו"&amp;הגדרות!$C$19&amp;", "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00")&amp;" ("&amp;הגדרות!$C$22&amp;" שעות ליום), וישיבת צוות חודשית ("&amp;הגדרות!$C$23&amp;" ש׳)."</f>
         <v>• הדרכת שיקום: ימי ראשון וחמישי, 09:00–12:30 (3.5 שעות ליום), וישיבת צוות חודשית (1 ש׳).</v>
       </c>
-      <c r="B29" s="51"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
       <c r="F29" s="40" t="str">
         <f aca="false">"הדרכת שיקום ("&amp;TEXT(F26,"0.0")&amp;" שעות × "&amp;הגדרות!$C$24&amp;" ₪)"</f>
         <v>הדרכת שיקום (32.5 שעות × 50 ₪)</v>
@@ -6044,16 +6054,16 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="51" t="str">
+      <c r="A30" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$28="","","• "&amp;הגדרות!$C$28)</f>
         <v>• התעריף השעתי אינו כולל מע״מ. מע״מ יתווסף כחוק.</v>
       </c>
-      <c r="B30" s="51"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
       <c r="F30" s="40" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="40"/>
@@ -6063,33 +6073,33 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="51" t="str">
+      <c r="A31" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$29="","","• "&amp;הגדרות!$C$29)</f>
         <v>• פרויקטים פרטיים מתומחרים בנפרד, לפי הזמנת החווה.</v>
       </c>
-      <c r="B31" s="51"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="52" t="s">
-        <v>89</v>
-      </c>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="53" t="n">
+      <c r="B31" s="50"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="52" t="n">
         <f aca="false">I29+I30</f>
         <v>1625</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="51" t="str">
+      <c r="A32" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$30="","","• "&amp;הגדרות!$C$30)</f>
         <v/>
       </c>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
       <c r="F32" s="40" t="str">
         <f aca="false">"מע״מ "&amp;ROUND(הגדרות!$C$25*100,1)&amp;"%"</f>
         <v>מע״מ 18%</v>
@@ -6102,30 +6112,30 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F33" s="54" t="s">
-        <v>90</v>
-      </c>
-      <c r="G33" s="54"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="55" t="n">
+      <c r="F33" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="54" t="n">
         <f aca="false">I31+I32</f>
         <v>1917.5</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="56" t="str">
+      <c r="A36" s="55" t="str">
         <f aca="false">"בברכה, "&amp;הגדרות!$C$6</f>
         <v>בברכה, (למילוי)</v>
       </c>
-      <c r="B36" s="56"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="F36" s="56" t="s">
-        <v>91</v>
-      </c>
-      <c r="G36" s="56"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="56"/>
+      <c r="B36" s="55"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="F36" s="55" t="s">
+        <v>93</v>
+      </c>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="44">
@@ -6223,7 +6233,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -6259,13 +6269,13 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
       <c r="F4" s="29" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
@@ -6273,7 +6283,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
@@ -6282,7 +6292,7 @@
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="31" t="str">
@@ -6293,7 +6303,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="31" t="str">
@@ -6302,7 +6312,7 @@
       </c>
       <c r="D6" s="31"/>
       <c r="F6" s="30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="31" t="str">
@@ -6313,7 +6323,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="31" t="str">
@@ -6322,7 +6332,7 @@
       </c>
       <c r="D7" s="31"/>
       <c r="F7" s="30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="31" t="str">
@@ -6333,7 +6343,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="31" t="str">
@@ -6344,7 +6354,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="str">
@@ -6356,7 +6366,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
@@ -6365,7 +6375,7 @@
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
@@ -6375,7 +6385,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
@@ -6384,7 +6394,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31" t="str">
@@ -6395,7 +6405,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -6404,46 +6414,46 @@
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="35" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="38" t="n">
-        <f aca="false">IF(B15="","",ROW()-14)</f>
+        <f aca="false">IF(B15="","",COUNT($B$15:B15))</f>
         <v>1</v>
       </c>
       <c r="B15" s="39" t="n">
-        <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
+        <f aca="false">IF(K15="","",K15)</f>
         <v>46632</v>
       </c>
       <c r="C15" s="38" t="str">
@@ -6455,7 +6465,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F15" s="42" t="n">
         <f aca="false">IF(B15="","",IF(E15="לא",0,הגדרות!$C$22))</f>
@@ -6468,17 +6478,17 @@
       <c r="H15" s="44"/>
       <c r="I15" s="45"/>
       <c r="K15" s="27" t="n">
-        <f aca="false">IF(B15="","",B15+MIN(MOD(הגדרות!$D$18-WEEKDAY(B15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B15)-1,7)+1))</f>
-        <v>46635</v>
+        <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
+        <v>46632</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="38" t="n">
-        <f aca="false">IF(B16="","",ROW()-14)</f>
+        <f aca="false">IF(B16="","",COUNT($B$15:B16))</f>
         <v>2</v>
       </c>
       <c r="B16" s="39" t="n">
-        <f aca="false">IF(K15="","",IF(K15&gt;$K$2,"",K15))</f>
+        <f aca="false">IF(K16="","",K16)</f>
         <v>46635</v>
       </c>
       <c r="C16" s="38" t="str">
@@ -6490,7 +6500,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F16" s="42" t="n">
         <f aca="false">IF(B16="","",IF(E16="לא",0,הגדרות!$C$22))</f>
@@ -6503,17 +6513,17 @@
       <c r="H16" s="44"/>
       <c r="I16" s="45"/>
       <c r="K16" s="27" t="n">
-        <f aca="false">IF(B16="","",B16+MIN(MOD(הגדרות!$D$18-WEEKDAY(B16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B16)-1,7)+1))</f>
-        <v>46639</v>
+        <f aca="false">IF(K15="","",IF(K15+MIN(MOD(הגדרות!$D$18-WEEKDAY(K15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K15)-1,7)+1)&gt;$K$2,"",K15+MIN(MOD(הגדרות!$D$18-WEEKDAY(K15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K15)-1,7)+1)))</f>
+        <v>46635</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="38" t="n">
-        <f aca="false">IF(B17="","",ROW()-14)</f>
+        <f aca="false">IF(B17="","",COUNT($B$15:B17))</f>
         <v>3</v>
       </c>
       <c r="B17" s="39" t="n">
-        <f aca="false">IF(K16="","",IF(K16&gt;$K$2,"",K16))</f>
+        <f aca="false">IF(K17="","",K17)</f>
         <v>46639</v>
       </c>
       <c r="C17" s="38" t="str">
@@ -6525,7 +6535,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F17" s="42" t="n">
         <f aca="false">IF(B17="","",IF(E17="לא",0,הגדרות!$C$22))</f>
@@ -6538,17 +6548,17 @@
       <c r="H17" s="44"/>
       <c r="I17" s="45"/>
       <c r="K17" s="27" t="n">
-        <f aca="false">IF(B17="","",B17+MIN(MOD(הגדרות!$D$18-WEEKDAY(B17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B17)-1,7)+1))</f>
-        <v>46642</v>
+        <f aca="false">IF(K16="","",IF(K16+MIN(MOD(הגדרות!$D$18-WEEKDAY(K16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K16)-1,7)+1)&gt;$K$2,"",K16+MIN(MOD(הגדרות!$D$18-WEEKDAY(K16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K16)-1,7)+1)))</f>
+        <v>46639</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="38" t="n">
-        <f aca="false">IF(B18="","",ROW()-14)</f>
+        <f aca="false">IF(B18="","",COUNT($B$15:B18))</f>
         <v>4</v>
       </c>
       <c r="B18" s="39" t="n">
-        <f aca="false">IF(K17="","",IF(K17&gt;$K$2,"",K17))</f>
+        <f aca="false">IF(K18="","",K18)</f>
         <v>46642</v>
       </c>
       <c r="C18" s="38" t="str">
@@ -6560,7 +6570,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F18" s="42" t="n">
         <f aca="false">IF(B18="","",IF(E18="לא",0,הגדרות!$C$22))</f>
@@ -6573,17 +6583,17 @@
       <c r="H18" s="44"/>
       <c r="I18" s="45"/>
       <c r="K18" s="27" t="n">
-        <f aca="false">IF(B18="","",B18+MIN(MOD(הגדרות!$D$18-WEEKDAY(B18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B18)-1,7)+1))</f>
-        <v>46646</v>
+        <f aca="false">IF(K17="","",IF(K17+MIN(MOD(הגדרות!$D$18-WEEKDAY(K17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K17)-1,7)+1)&gt;$K$2,"",K17+MIN(MOD(הגדרות!$D$18-WEEKDAY(K17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K17)-1,7)+1)))</f>
+        <v>46642</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="38" t="n">
-        <f aca="false">IF(B19="","",ROW()-14)</f>
+        <f aca="false">IF(B19="","",COUNT($B$15:B19))</f>
         <v>5</v>
       </c>
       <c r="B19" s="39" t="n">
-        <f aca="false">IF(K18="","",IF(K18&gt;$K$2,"",K18))</f>
+        <f aca="false">IF(K19="","",K19)</f>
         <v>46646</v>
       </c>
       <c r="C19" s="38" t="str">
@@ -6595,7 +6605,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F19" s="42" t="n">
         <f aca="false">IF(B19="","",IF(E19="לא",0,הגדרות!$C$22))</f>
@@ -6608,17 +6618,17 @@
       <c r="H19" s="44"/>
       <c r="I19" s="45"/>
       <c r="K19" s="27" t="n">
-        <f aca="false">IF(B19="","",B19+MIN(MOD(הגדרות!$D$18-WEEKDAY(B19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B19)-1,7)+1))</f>
-        <v>46649</v>
+        <f aca="false">IF(K18="","",IF(K18+MIN(MOD(הגדרות!$D$18-WEEKDAY(K18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K18)-1,7)+1)&gt;$K$2,"",K18+MIN(MOD(הגדרות!$D$18-WEEKDAY(K18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K18)-1,7)+1)))</f>
+        <v>46646</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="38" t="n">
-        <f aca="false">IF(B20="","",ROW()-14)</f>
+        <f aca="false">IF(B20="","",COUNT($B$15:B20))</f>
         <v>6</v>
       </c>
       <c r="B20" s="39" t="n">
-        <f aca="false">IF(K19="","",IF(K19&gt;$K$2,"",K19))</f>
+        <f aca="false">IF(K20="","",K20)</f>
         <v>46649</v>
       </c>
       <c r="C20" s="38" t="str">
@@ -6630,7 +6640,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F20" s="42" t="n">
         <f aca="false">IF(B20="","",IF(E20="לא",0,הגדרות!$C$22))</f>
@@ -6643,17 +6653,17 @@
       <c r="H20" s="44"/>
       <c r="I20" s="45"/>
       <c r="K20" s="27" t="n">
-        <f aca="false">IF(B20="","",B20+MIN(MOD(הגדרות!$D$18-WEEKDAY(B20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B20)-1,7)+1))</f>
-        <v>46653</v>
+        <f aca="false">IF(K19="","",IF(K19+MIN(MOD(הגדרות!$D$18-WEEKDAY(K19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K19)-1,7)+1)&gt;$K$2,"",K19+MIN(MOD(הגדרות!$D$18-WEEKDAY(K19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K19)-1,7)+1)))</f>
+        <v>46649</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="38" t="n">
-        <f aca="false">IF(B21="","",ROW()-14)</f>
+        <f aca="false">IF(B21="","",COUNT($B$15:B21))</f>
         <v>7</v>
       </c>
       <c r="B21" s="39" t="n">
-        <f aca="false">IF(K20="","",IF(K20&gt;$K$2,"",K20))</f>
+        <f aca="false">IF(K21="","",K21)</f>
         <v>46653</v>
       </c>
       <c r="C21" s="38" t="str">
@@ -6665,7 +6675,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F21" s="42" t="n">
         <f aca="false">IF(B21="","",IF(E21="לא",0,הגדרות!$C$22))</f>
@@ -6678,17 +6688,17 @@
       <c r="H21" s="44"/>
       <c r="I21" s="45"/>
       <c r="K21" s="27" t="n">
-        <f aca="false">IF(B21="","",B21+MIN(MOD(הגדרות!$D$18-WEEKDAY(B21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B21)-1,7)+1))</f>
-        <v>46656</v>
+        <f aca="false">IF(K20="","",IF(K20+MIN(MOD(הגדרות!$D$18-WEEKDAY(K20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K20)-1,7)+1)&gt;$K$2,"",K20+MIN(MOD(הגדרות!$D$18-WEEKDAY(K20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K20)-1,7)+1)))</f>
+        <v>46653</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="38" t="n">
-        <f aca="false">IF(B22="","",ROW()-14)</f>
+        <f aca="false">IF(B22="","",COUNT($B$15:B22))</f>
         <v>8</v>
       </c>
       <c r="B22" s="39" t="n">
-        <f aca="false">IF(K21="","",IF(K21&gt;$K$2,"",K21))</f>
+        <f aca="false">IF(K22="","",K22)</f>
         <v>46656</v>
       </c>
       <c r="C22" s="38" t="str">
@@ -6700,7 +6710,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F22" s="42" t="n">
         <f aca="false">IF(B22="","",IF(E22="לא",0,הגדרות!$C$22))</f>
@@ -6713,17 +6723,17 @@
       <c r="H22" s="44"/>
       <c r="I22" s="45"/>
       <c r="K22" s="27" t="n">
-        <f aca="false">IF(B22="","",B22+MIN(MOD(הגדרות!$D$18-WEEKDAY(B22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B22)-1,7)+1))</f>
-        <v>46660</v>
+        <f aca="false">IF(K21="","",IF(K21+MIN(MOD(הגדרות!$D$18-WEEKDAY(K21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K21)-1,7)+1)&gt;$K$2,"",K21+MIN(MOD(הגדרות!$D$18-WEEKDAY(K21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K21)-1,7)+1)))</f>
+        <v>46656</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="38" t="n">
-        <f aca="false">IF(B23="","",ROW()-14)</f>
+        <f aca="false">IF(B23="","",COUNT($B$15:B23))</f>
         <v>9</v>
       </c>
       <c r="B23" s="39" t="n">
-        <f aca="false">IF(K22="","",IF(K22&gt;$K$2,"",K22))</f>
+        <f aca="false">IF(K23="","",K23)</f>
         <v>46660</v>
       </c>
       <c r="C23" s="38" t="str">
@@ -6735,7 +6745,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F23" s="42" t="n">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
@@ -6748,17 +6758,17 @@
       <c r="H23" s="44"/>
       <c r="I23" s="45"/>
       <c r="K23" s="27" t="n">
-        <f aca="false">IF(B23="","",B23+MIN(MOD(הגדרות!$D$18-WEEKDAY(B23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B23)-1,7)+1))</f>
-        <v>46663</v>
+        <f aca="false">IF(K22="","",IF(K22+MIN(MOD(הגדרות!$D$18-WEEKDAY(K22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K22)-1,7)+1)&gt;$K$2,"",K22+MIN(MOD(הגדרות!$D$18-WEEKDAY(K22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K22)-1,7)+1)))</f>
+        <v>46660</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="38" t="str">
-        <f aca="false">IF(B24="","",ROW()-14)</f>
+        <f aca="false">IF(B24="","",COUNT($B$15:B24))</f>
         <v/>
       </c>
       <c r="B24" s="39" t="str">
-        <f aca="false">IF(K23="","",IF(K23&gt;$K$2,"",K23))</f>
+        <f aca="false">IF(K24="","",K24)</f>
         <v/>
       </c>
       <c r="C24" s="38" t="str">
@@ -6770,7 +6780,7 @@
         <v/>
       </c>
       <c r="E24" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F24" s="42" t="str">
         <f aca="false">IF(B24="","",IF(E24="לא",0,הגדרות!$C$22))</f>
@@ -6783,7 +6793,7 @@
       <c r="H24" s="44"/>
       <c r="I24" s="45"/>
       <c r="K24" s="27" t="str">
-        <f aca="false">IF(B24="","",B24+MIN(MOD(הגדרות!$D$18-WEEKDAY(B24)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B24)-1,7)+1))</f>
+        <f aca="false">IF(K23="","",IF(K23+MIN(MOD(הגדרות!$D$18-WEEKDAY(K23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K23)-1,7)+1)&gt;$K$2,"",K23+MIN(MOD(הגדרות!$D$18-WEEKDAY(K23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K23)-1,7)+1)))</f>
         <v/>
       </c>
     </row>
@@ -6792,16 +6802,16 @@
         <f aca="false">COUNT($B$15:$B$24)+1</f>
         <v>10</v>
       </c>
-      <c r="B25" s="46"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="38" t="str">
         <f aca="false">IF(B25="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B25)))</f>
         <v/>
       </c>
       <c r="D25" s="40" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F25" s="42" t="n">
         <f aca="false">IF(E25="לא",0,הגדרות!$C$23)</f>
@@ -6816,36 +6826,36 @@
       <c r="K25" s="27"/>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="B26" s="47"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="48" t="n">
+      <c r="A26" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" s="46"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="47" t="n">
         <f aca="false">SUM(F15:F25)</f>
         <v>32.5</v>
       </c>
-      <c r="G26" s="49" t="n">
+      <c r="G26" s="48" t="n">
         <f aca="false">SUM(G15:G25)</f>
         <v>1625</v>
       </c>
-      <c r="H26" s="47"/>
-      <c r="I26" s="49" t="n">
+      <c r="H26" s="46"/>
+      <c r="I26" s="48" t="n">
         <f aca="false">SUM(I15:I25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
+      <c r="A28" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="49"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="49"/>
       <c r="F28" s="40" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G28" s="40"/>
       <c r="H28" s="40"/>
@@ -6855,14 +6865,14 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="51" t="str">
+      <c r="A29" s="50" t="str">
         <f aca="false">"• "&amp;הגדרות!$C$17&amp;": ימי "&amp;הגדרות!$C$18&amp;" ו"&amp;הגדרות!$C$19&amp;", "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00")&amp;" ("&amp;הגדרות!$C$22&amp;" שעות ליום), וישיבת צוות חודשית ("&amp;הגדרות!$C$23&amp;" ש׳)."</f>
         <v>• הדרכת שיקום: ימי ראשון וחמישי, 09:00–12:30 (3.5 שעות ליום), וישיבת צוות חודשית (1 ש׳).</v>
       </c>
-      <c r="B29" s="51"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
       <c r="F29" s="40" t="str">
         <f aca="false">"הדרכת שיקום ("&amp;TEXT(F26,"0.0")&amp;" שעות × "&amp;הגדרות!$C$24&amp;" ₪)"</f>
         <v>הדרכת שיקום (32.5 שעות × 50 ₪)</v>
@@ -6875,16 +6885,16 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="51" t="str">
+      <c r="A30" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$28="","","• "&amp;הגדרות!$C$28)</f>
         <v>• התעריף השעתי אינו כולל מע״מ. מע״מ יתווסף כחוק.</v>
       </c>
-      <c r="B30" s="51"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
       <c r="F30" s="40" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="40"/>
@@ -6894,33 +6904,33 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="51" t="str">
+      <c r="A31" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$29="","","• "&amp;הגדרות!$C$29)</f>
         <v>• פרויקטים פרטיים מתומחרים בנפרד, לפי הזמנת החווה.</v>
       </c>
-      <c r="B31" s="51"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="52" t="s">
-        <v>89</v>
-      </c>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="53" t="n">
+      <c r="B31" s="50"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="52" t="n">
         <f aca="false">I29+I30</f>
         <v>1625</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="51" t="str">
+      <c r="A32" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$30="","","• "&amp;הגדרות!$C$30)</f>
         <v/>
       </c>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
       <c r="F32" s="40" t="str">
         <f aca="false">"מע״מ "&amp;ROUND(הגדרות!$C$25*100,1)&amp;"%"</f>
         <v>מע״מ 18%</v>
@@ -6933,30 +6943,30 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F33" s="54" t="s">
-        <v>90</v>
-      </c>
-      <c r="G33" s="54"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="55" t="n">
+      <c r="F33" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="54" t="n">
         <f aca="false">I31+I32</f>
         <v>1917.5</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="56" t="str">
+      <c r="A36" s="55" t="str">
         <f aca="false">"בברכה, "&amp;הגדרות!$C$6</f>
         <v>בברכה, (למילוי)</v>
       </c>
-      <c r="B36" s="56"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="F36" s="56" t="s">
-        <v>91</v>
-      </c>
-      <c r="G36" s="56"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="56"/>
+      <c r="B36" s="55"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="F36" s="55" t="s">
+        <v>93</v>
+      </c>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="44">
@@ -7050,139 +7060,139 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C4" s="14"/>
       <c r="F4" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="16" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="16" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="17" t="s">
-        <v>32</v>
-      </c>
       <c r="F7" s="18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="16" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F10" s="18" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C11" s="14"/>
       <c r="F11" s="18" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C16" s="14"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D18" s="19" t="n">
         <f aca="false">MATCH(C18,$F$5:$F$11,0)</f>
@@ -7191,10 +7201,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D19" s="19" t="n">
         <f aca="false">MATCH(C19,$F$5:$F$11,0)</f>
@@ -7203,7 +7213,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C20" s="20" t="n">
         <v>0.375</v>
@@ -7211,7 +7221,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C21" s="20" t="n">
         <v>0.520833333333333</v>
@@ -7219,7 +7229,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="16" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C22" s="21" t="n">
         <f aca="false">(C21-C20)*24</f>
@@ -7228,7 +7238,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C23" s="22" t="n">
         <v>1</v>
@@ -7236,7 +7246,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C24" s="23" t="n">
         <v>50</v>
@@ -7244,7 +7254,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>0.18</v>
@@ -7252,29 +7262,29 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C27" s="14"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="16" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C28" s="25" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C30" s="25"/>
     </row>
@@ -7318,7 +7328,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -7354,13 +7364,13 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
       <c r="F4" s="29" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
@@ -7368,7 +7378,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
@@ -7377,7 +7387,7 @@
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="31" t="str">
@@ -7388,7 +7398,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="31" t="str">
@@ -7397,7 +7407,7 @@
       </c>
       <c r="D6" s="31"/>
       <c r="F6" s="30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="31" t="str">
@@ -7408,7 +7418,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="31" t="str">
@@ -7417,7 +7427,7 @@
       </c>
       <c r="D7" s="31"/>
       <c r="F7" s="30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="31" t="str">
@@ -7428,7 +7438,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="31" t="str">
@@ -7439,7 +7449,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="str">
@@ -7451,7 +7461,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
@@ -7460,7 +7470,7 @@
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
@@ -7470,7 +7480,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
@@ -7479,7 +7489,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31" t="str">
@@ -7490,7 +7500,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -7499,46 +7509,46 @@
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="35" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="38" t="n">
-        <f aca="false">IF(B15="","",ROW()-14)</f>
+        <f aca="false">IF(B15="","",COUNT($B$15:B15))</f>
         <v>1</v>
       </c>
       <c r="B15" s="39" t="n">
-        <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
+        <f aca="false">IF(K15="","",K15)</f>
         <v>46268</v>
       </c>
       <c r="C15" s="38" t="str">
@@ -7550,7 +7560,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F15" s="42" t="n">
         <f aca="false">IF(B15="","",IF(E15="לא",0,הגדרות!$C$22))</f>
@@ -7563,17 +7573,17 @@
       <c r="H15" s="44"/>
       <c r="I15" s="45"/>
       <c r="K15" s="27" t="n">
-        <f aca="false">IF(B15="","",B15+MIN(MOD(הגדרות!$D$18-WEEKDAY(B15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B15)-1,7)+1))</f>
-        <v>46271</v>
+        <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
+        <v>46268</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="38" t="n">
-        <f aca="false">IF(B16="","",ROW()-14)</f>
+        <f aca="false">IF(B16="","",COUNT($B$15:B16))</f>
         <v>2</v>
       </c>
       <c r="B16" s="39" t="n">
-        <f aca="false">IF(K15="","",IF(K15&gt;$K$2,"",K15))</f>
+        <f aca="false">IF(K16="","",K16)</f>
         <v>46271</v>
       </c>
       <c r="C16" s="38" t="str">
@@ -7585,7 +7595,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F16" s="42" t="n">
         <f aca="false">IF(B16="","",IF(E16="לא",0,הגדרות!$C$22))</f>
@@ -7598,17 +7608,17 @@
       <c r="H16" s="44"/>
       <c r="I16" s="45"/>
       <c r="K16" s="27" t="n">
-        <f aca="false">IF(B16="","",B16+MIN(MOD(הגדרות!$D$18-WEEKDAY(B16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B16)-1,7)+1))</f>
-        <v>46275</v>
+        <f aca="false">IF(K15="","",IF(K15+MIN(MOD(הגדרות!$D$18-WEEKDAY(K15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K15)-1,7)+1)&gt;$K$2,"",K15+MIN(MOD(הגדרות!$D$18-WEEKDAY(K15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K15)-1,7)+1)))</f>
+        <v>46271</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="38" t="n">
-        <f aca="false">IF(B17="","",ROW()-14)</f>
+        <f aca="false">IF(B17="","",COUNT($B$15:B17))</f>
         <v>3</v>
       </c>
       <c r="B17" s="39" t="n">
-        <f aca="false">IF(K16="","",IF(K16&gt;$K$2,"",K16))</f>
+        <f aca="false">IF(K17="","",K17)</f>
         <v>46275</v>
       </c>
       <c r="C17" s="38" t="str">
@@ -7620,7 +7630,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F17" s="42" t="n">
         <f aca="false">IF(B17="","",IF(E17="לא",0,הגדרות!$C$22))</f>
@@ -7633,17 +7643,17 @@
       <c r="H17" s="44"/>
       <c r="I17" s="45"/>
       <c r="K17" s="27" t="n">
-        <f aca="false">IF(B17="","",B17+MIN(MOD(הגדרות!$D$18-WEEKDAY(B17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B17)-1,7)+1))</f>
-        <v>46278</v>
+        <f aca="false">IF(K16="","",IF(K16+MIN(MOD(הגדרות!$D$18-WEEKDAY(K16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K16)-1,7)+1)&gt;$K$2,"",K16+MIN(MOD(הגדרות!$D$18-WEEKDAY(K16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K16)-1,7)+1)))</f>
+        <v>46275</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="38" t="n">
-        <f aca="false">IF(B18="","",ROW()-14)</f>
+        <f aca="false">IF(B18="","",COUNT($B$15:B18))</f>
         <v>4</v>
       </c>
       <c r="B18" s="39" t="n">
-        <f aca="false">IF(K17="","",IF(K17&gt;$K$2,"",K17))</f>
+        <f aca="false">IF(K18="","",K18)</f>
         <v>46278</v>
       </c>
       <c r="C18" s="38" t="str">
@@ -7655,7 +7665,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F18" s="42" t="n">
         <f aca="false">IF(B18="","",IF(E18="לא",0,הגדרות!$C$22))</f>
@@ -7668,17 +7678,17 @@
       <c r="H18" s="44"/>
       <c r="I18" s="45"/>
       <c r="K18" s="27" t="n">
-        <f aca="false">IF(B18="","",B18+MIN(MOD(הגדרות!$D$18-WEEKDAY(B18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B18)-1,7)+1))</f>
-        <v>46282</v>
+        <f aca="false">IF(K17="","",IF(K17+MIN(MOD(הגדרות!$D$18-WEEKDAY(K17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K17)-1,7)+1)&gt;$K$2,"",K17+MIN(MOD(הגדרות!$D$18-WEEKDAY(K17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K17)-1,7)+1)))</f>
+        <v>46278</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="38" t="n">
-        <f aca="false">IF(B19="","",ROW()-14)</f>
+        <f aca="false">IF(B19="","",COUNT($B$15:B19))</f>
         <v>5</v>
       </c>
       <c r="B19" s="39" t="n">
-        <f aca="false">IF(K18="","",IF(K18&gt;$K$2,"",K18))</f>
+        <f aca="false">IF(K19="","",K19)</f>
         <v>46282</v>
       </c>
       <c r="C19" s="38" t="str">
@@ -7690,7 +7700,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F19" s="42" t="n">
         <f aca="false">IF(B19="","",IF(E19="לא",0,הגדרות!$C$22))</f>
@@ -7703,17 +7713,17 @@
       <c r="H19" s="44"/>
       <c r="I19" s="45"/>
       <c r="K19" s="27" t="n">
-        <f aca="false">IF(B19="","",B19+MIN(MOD(הגדרות!$D$18-WEEKDAY(B19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B19)-1,7)+1))</f>
-        <v>46285</v>
+        <f aca="false">IF(K18="","",IF(K18+MIN(MOD(הגדרות!$D$18-WEEKDAY(K18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K18)-1,7)+1)&gt;$K$2,"",K18+MIN(MOD(הגדרות!$D$18-WEEKDAY(K18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K18)-1,7)+1)))</f>
+        <v>46282</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="38" t="n">
-        <f aca="false">IF(B20="","",ROW()-14)</f>
+        <f aca="false">IF(B20="","",COUNT($B$15:B20))</f>
         <v>6</v>
       </c>
       <c r="B20" s="39" t="n">
-        <f aca="false">IF(K19="","",IF(K19&gt;$K$2,"",K19))</f>
+        <f aca="false">IF(K20="","",K20)</f>
         <v>46285</v>
       </c>
       <c r="C20" s="38" t="str">
@@ -7725,7 +7735,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F20" s="42" t="n">
         <f aca="false">IF(B20="","",IF(E20="לא",0,הגדרות!$C$22))</f>
@@ -7738,17 +7748,17 @@
       <c r="H20" s="44"/>
       <c r="I20" s="45"/>
       <c r="K20" s="27" t="n">
-        <f aca="false">IF(B20="","",B20+MIN(MOD(הגדרות!$D$18-WEEKDAY(B20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B20)-1,7)+1))</f>
-        <v>46289</v>
+        <f aca="false">IF(K19="","",IF(K19+MIN(MOD(הגדרות!$D$18-WEEKDAY(K19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K19)-1,7)+1)&gt;$K$2,"",K19+MIN(MOD(הגדרות!$D$18-WEEKDAY(K19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K19)-1,7)+1)))</f>
+        <v>46285</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="38" t="n">
-        <f aca="false">IF(B21="","",ROW()-14)</f>
+        <f aca="false">IF(B21="","",COUNT($B$15:B21))</f>
         <v>7</v>
       </c>
       <c r="B21" s="39" t="n">
-        <f aca="false">IF(K20="","",IF(K20&gt;$K$2,"",K20))</f>
+        <f aca="false">IF(K21="","",K21)</f>
         <v>46289</v>
       </c>
       <c r="C21" s="38" t="str">
@@ -7760,7 +7770,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F21" s="42" t="n">
         <f aca="false">IF(B21="","",IF(E21="לא",0,הגדרות!$C$22))</f>
@@ -7773,17 +7783,17 @@
       <c r="H21" s="44"/>
       <c r="I21" s="45"/>
       <c r="K21" s="27" t="n">
-        <f aca="false">IF(B21="","",B21+MIN(MOD(הגדרות!$D$18-WEEKDAY(B21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B21)-1,7)+1))</f>
-        <v>46292</v>
+        <f aca="false">IF(K20="","",IF(K20+MIN(MOD(הגדרות!$D$18-WEEKDAY(K20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K20)-1,7)+1)&gt;$K$2,"",K20+MIN(MOD(הגדרות!$D$18-WEEKDAY(K20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K20)-1,7)+1)))</f>
+        <v>46289</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="38" t="n">
-        <f aca="false">IF(B22="","",ROW()-14)</f>
+        <f aca="false">IF(B22="","",COUNT($B$15:B22))</f>
         <v>8</v>
       </c>
       <c r="B22" s="39" t="n">
-        <f aca="false">IF(K21="","",IF(K21&gt;$K$2,"",K21))</f>
+        <f aca="false">IF(K22="","",K22)</f>
         <v>46292</v>
       </c>
       <c r="C22" s="38" t="str">
@@ -7795,7 +7805,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F22" s="42" t="n">
         <f aca="false">IF(B22="","",IF(E22="לא",0,הגדרות!$C$22))</f>
@@ -7808,17 +7818,17 @@
       <c r="H22" s="44"/>
       <c r="I22" s="45"/>
       <c r="K22" s="27" t="n">
-        <f aca="false">IF(B22="","",B22+MIN(MOD(הגדרות!$D$18-WEEKDAY(B22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B22)-1,7)+1))</f>
-        <v>46296</v>
+        <f aca="false">IF(K21="","",IF(K21+MIN(MOD(הגדרות!$D$18-WEEKDAY(K21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K21)-1,7)+1)&gt;$K$2,"",K21+MIN(MOD(הגדרות!$D$18-WEEKDAY(K21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K21)-1,7)+1)))</f>
+        <v>46292</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="38" t="str">
-        <f aca="false">IF(B23="","",ROW()-14)</f>
+        <f aca="false">IF(B23="","",COUNT($B$15:B23))</f>
         <v/>
       </c>
       <c r="B23" s="39" t="str">
-        <f aca="false">IF(K22="","",IF(K22&gt;$K$2,"",K22))</f>
+        <f aca="false">IF(K23="","",K23)</f>
         <v/>
       </c>
       <c r="C23" s="38" t="str">
@@ -7830,7 +7840,7 @@
         <v/>
       </c>
       <c r="E23" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F23" s="42" t="str">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
@@ -7843,17 +7853,17 @@
       <c r="H23" s="44"/>
       <c r="I23" s="45"/>
       <c r="K23" s="27" t="str">
-        <f aca="false">IF(B23="","",B23+MIN(MOD(הגדרות!$D$18-WEEKDAY(B23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B23)-1,7)+1))</f>
+        <f aca="false">IF(K22="","",IF(K22+MIN(MOD(הגדרות!$D$18-WEEKDAY(K22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K22)-1,7)+1)&gt;$K$2,"",K22+MIN(MOD(הגדרות!$D$18-WEEKDAY(K22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K22)-1,7)+1)))</f>
         <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="38" t="str">
-        <f aca="false">IF(B24="","",ROW()-14)</f>
+        <f aca="false">IF(B24="","",COUNT($B$15:B24))</f>
         <v/>
       </c>
       <c r="B24" s="39" t="str">
-        <f aca="false">IF(K23="","",IF(K23&gt;$K$2,"",K23))</f>
+        <f aca="false">IF(K24="","",K24)</f>
         <v/>
       </c>
       <c r="C24" s="38" t="str">
@@ -7865,7 +7875,7 @@
         <v/>
       </c>
       <c r="E24" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F24" s="42" t="str">
         <f aca="false">IF(B24="","",IF(E24="לא",0,הגדרות!$C$22))</f>
@@ -7878,7 +7888,7 @@
       <c r="H24" s="44"/>
       <c r="I24" s="45"/>
       <c r="K24" s="27" t="str">
-        <f aca="false">IF(B24="","",B24+MIN(MOD(הגדרות!$D$18-WEEKDAY(B24)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B24)-1,7)+1))</f>
+        <f aca="false">IF(K23="","",IF(K23+MIN(MOD(הגדרות!$D$18-WEEKDAY(K23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K23)-1,7)+1)&gt;$K$2,"",K23+MIN(MOD(הגדרות!$D$18-WEEKDAY(K23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K23)-1,7)+1)))</f>
         <v/>
       </c>
     </row>
@@ -7887,16 +7897,16 @@
         <f aca="false">COUNT($B$15:$B$24)+1</f>
         <v>9</v>
       </c>
-      <c r="B25" s="46"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="38" t="str">
         <f aca="false">IF(B25="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B25)))</f>
         <v/>
       </c>
       <c r="D25" s="40" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F25" s="42" t="n">
         <f aca="false">IF(E25="לא",0,הגדרות!$C$23)</f>
@@ -7911,36 +7921,36 @@
       <c r="K25" s="27"/>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="B26" s="47"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="48" t="n">
+      <c r="A26" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" s="46"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="47" t="n">
         <f aca="false">SUM(F15:F25)</f>
         <v>29</v>
       </c>
-      <c r="G26" s="49" t="n">
+      <c r="G26" s="48" t="n">
         <f aca="false">SUM(G15:G25)</f>
         <v>1450</v>
       </c>
-      <c r="H26" s="47"/>
-      <c r="I26" s="49" t="n">
+      <c r="H26" s="46"/>
+      <c r="I26" s="48" t="n">
         <f aca="false">SUM(I15:I25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
+      <c r="A28" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="49"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="49"/>
       <c r="F28" s="40" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G28" s="40"/>
       <c r="H28" s="40"/>
@@ -7950,14 +7960,14 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="51" t="str">
+      <c r="A29" s="50" t="str">
         <f aca="false">"• "&amp;הגדרות!$C$17&amp;": ימי "&amp;הגדרות!$C$18&amp;" ו"&amp;הגדרות!$C$19&amp;", "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00")&amp;" ("&amp;הגדרות!$C$22&amp;" שעות ליום), וישיבת צוות חודשית ("&amp;הגדרות!$C$23&amp;" ש׳)."</f>
         <v>• הדרכת שיקום: ימי ראשון וחמישי, 09:00–12:30 (3.5 שעות ליום), וישיבת צוות חודשית (1 ש׳).</v>
       </c>
-      <c r="B29" s="51"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
       <c r="F29" s="40" t="str">
         <f aca="false">"הדרכת שיקום ("&amp;TEXT(F26,"0.0")&amp;" שעות × "&amp;הגדרות!$C$24&amp;" ₪)"</f>
         <v>הדרכת שיקום (29.0 שעות × 50 ₪)</v>
@@ -7970,16 +7980,16 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="51" t="str">
+      <c r="A30" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$28="","","• "&amp;הגדרות!$C$28)</f>
         <v>• התעריף השעתי אינו כולל מע״מ. מע״מ יתווסף כחוק.</v>
       </c>
-      <c r="B30" s="51"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
       <c r="F30" s="40" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="40"/>
@@ -7989,33 +7999,33 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="51" t="str">
+      <c r="A31" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$29="","","• "&amp;הגדרות!$C$29)</f>
         <v>• פרויקטים פרטיים מתומחרים בנפרד, לפי הזמנת החווה.</v>
       </c>
-      <c r="B31" s="51"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="52" t="s">
-        <v>89</v>
-      </c>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="53" t="n">
+      <c r="B31" s="50"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="52" t="n">
         <f aca="false">I29+I30</f>
         <v>1450</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="51" t="str">
+      <c r="A32" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$30="","","• "&amp;הגדרות!$C$30)</f>
         <v/>
       </c>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
       <c r="F32" s="40" t="str">
         <f aca="false">"מע״מ "&amp;ROUND(הגדרות!$C$25*100,1)&amp;"%"</f>
         <v>מע״מ 18%</v>
@@ -8028,30 +8038,30 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F33" s="54" t="s">
-        <v>90</v>
-      </c>
-      <c r="G33" s="54"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="55" t="n">
+      <c r="F33" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="54" t="n">
         <f aca="false">I31+I32</f>
         <v>1711</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="56" t="str">
+      <c r="A36" s="55" t="str">
         <f aca="false">"בברכה, "&amp;הגדרות!$C$6</f>
         <v>בברכה, (למילוי)</v>
       </c>
-      <c r="B36" s="56"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="F36" s="56" t="s">
-        <v>91</v>
-      </c>
-      <c r="G36" s="56"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="56"/>
+      <c r="B36" s="55"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="F36" s="55" t="s">
+        <v>93</v>
+      </c>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="44">
@@ -8149,7 +8159,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -8185,13 +8195,13 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
       <c r="F4" s="29" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
@@ -8199,7 +8209,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
@@ -8208,7 +8218,7 @@
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="31" t="str">
@@ -8219,7 +8229,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="31" t="str">
@@ -8228,7 +8238,7 @@
       </c>
       <c r="D6" s="31"/>
       <c r="F6" s="30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="31" t="str">
@@ -8239,7 +8249,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="31" t="str">
@@ -8248,7 +8258,7 @@
       </c>
       <c r="D7" s="31"/>
       <c r="F7" s="30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="31" t="str">
@@ -8259,7 +8269,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="31" t="str">
@@ -8270,7 +8280,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="str">
@@ -8282,7 +8292,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
@@ -8291,7 +8301,7 @@
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
@@ -8301,7 +8311,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
@@ -8310,7 +8320,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31" t="str">
@@ -8321,7 +8331,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -8330,46 +8340,46 @@
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="35" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="38" t="n">
-        <f aca="false">IF(B15="","",ROW()-14)</f>
+        <f aca="false">IF(B15="","",COUNT($B$15:B15))</f>
         <v>1</v>
       </c>
       <c r="B15" s="39" t="n">
-        <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
+        <f aca="false">IF(K15="","",K15)</f>
         <v>46296</v>
       </c>
       <c r="C15" s="38" t="str">
@@ -8381,7 +8391,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F15" s="42" t="n">
         <f aca="false">IF(B15="","",IF(E15="לא",0,הגדרות!$C$22))</f>
@@ -8394,17 +8404,17 @@
       <c r="H15" s="44"/>
       <c r="I15" s="45"/>
       <c r="K15" s="27" t="n">
-        <f aca="false">IF(B15="","",B15+MIN(MOD(הגדרות!$D$18-WEEKDAY(B15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B15)-1,7)+1))</f>
-        <v>46299</v>
+        <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
+        <v>46296</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="38" t="n">
-        <f aca="false">IF(B16="","",ROW()-14)</f>
+        <f aca="false">IF(B16="","",COUNT($B$15:B16))</f>
         <v>2</v>
       </c>
       <c r="B16" s="39" t="n">
-        <f aca="false">IF(K15="","",IF(K15&gt;$K$2,"",K15))</f>
+        <f aca="false">IF(K16="","",K16)</f>
         <v>46299</v>
       </c>
       <c r="C16" s="38" t="str">
@@ -8416,7 +8426,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F16" s="42" t="n">
         <f aca="false">IF(B16="","",IF(E16="לא",0,הגדרות!$C$22))</f>
@@ -8429,17 +8439,17 @@
       <c r="H16" s="44"/>
       <c r="I16" s="45"/>
       <c r="K16" s="27" t="n">
-        <f aca="false">IF(B16="","",B16+MIN(MOD(הגדרות!$D$18-WEEKDAY(B16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B16)-1,7)+1))</f>
-        <v>46303</v>
+        <f aca="false">IF(K15="","",IF(K15+MIN(MOD(הגדרות!$D$18-WEEKDAY(K15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K15)-1,7)+1)&gt;$K$2,"",K15+MIN(MOD(הגדרות!$D$18-WEEKDAY(K15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K15)-1,7)+1)))</f>
+        <v>46299</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="38" t="n">
-        <f aca="false">IF(B17="","",ROW()-14)</f>
+        <f aca="false">IF(B17="","",COUNT($B$15:B17))</f>
         <v>3</v>
       </c>
       <c r="B17" s="39" t="n">
-        <f aca="false">IF(K16="","",IF(K16&gt;$K$2,"",K16))</f>
+        <f aca="false">IF(K17="","",K17)</f>
         <v>46303</v>
       </c>
       <c r="C17" s="38" t="str">
@@ -8451,7 +8461,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F17" s="42" t="n">
         <f aca="false">IF(B17="","",IF(E17="לא",0,הגדרות!$C$22))</f>
@@ -8464,17 +8474,17 @@
       <c r="H17" s="44"/>
       <c r="I17" s="45"/>
       <c r="K17" s="27" t="n">
-        <f aca="false">IF(B17="","",B17+MIN(MOD(הגדרות!$D$18-WEEKDAY(B17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B17)-1,7)+1))</f>
-        <v>46306</v>
+        <f aca="false">IF(K16="","",IF(K16+MIN(MOD(הגדרות!$D$18-WEEKDAY(K16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K16)-1,7)+1)&gt;$K$2,"",K16+MIN(MOD(הגדרות!$D$18-WEEKDAY(K16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K16)-1,7)+1)))</f>
+        <v>46303</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="38" t="n">
-        <f aca="false">IF(B18="","",ROW()-14)</f>
+        <f aca="false">IF(B18="","",COUNT($B$15:B18))</f>
         <v>4</v>
       </c>
       <c r="B18" s="39" t="n">
-        <f aca="false">IF(K17="","",IF(K17&gt;$K$2,"",K17))</f>
+        <f aca="false">IF(K18="","",K18)</f>
         <v>46306</v>
       </c>
       <c r="C18" s="38" t="str">
@@ -8486,7 +8496,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F18" s="42" t="n">
         <f aca="false">IF(B18="","",IF(E18="לא",0,הגדרות!$C$22))</f>
@@ -8499,17 +8509,17 @@
       <c r="H18" s="44"/>
       <c r="I18" s="45"/>
       <c r="K18" s="27" t="n">
-        <f aca="false">IF(B18="","",B18+MIN(MOD(הגדרות!$D$18-WEEKDAY(B18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B18)-1,7)+1))</f>
-        <v>46310</v>
+        <f aca="false">IF(K17="","",IF(K17+MIN(MOD(הגדרות!$D$18-WEEKDAY(K17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K17)-1,7)+1)&gt;$K$2,"",K17+MIN(MOD(הגדרות!$D$18-WEEKDAY(K17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K17)-1,7)+1)))</f>
+        <v>46306</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="38" t="n">
-        <f aca="false">IF(B19="","",ROW()-14)</f>
+        <f aca="false">IF(B19="","",COUNT($B$15:B19))</f>
         <v>5</v>
       </c>
       <c r="B19" s="39" t="n">
-        <f aca="false">IF(K18="","",IF(K18&gt;$K$2,"",K18))</f>
+        <f aca="false">IF(K19="","",K19)</f>
         <v>46310</v>
       </c>
       <c r="C19" s="38" t="str">
@@ -8521,7 +8531,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F19" s="42" t="n">
         <f aca="false">IF(B19="","",IF(E19="לא",0,הגדרות!$C$22))</f>
@@ -8534,17 +8544,17 @@
       <c r="H19" s="44"/>
       <c r="I19" s="45"/>
       <c r="K19" s="27" t="n">
-        <f aca="false">IF(B19="","",B19+MIN(MOD(הגדרות!$D$18-WEEKDAY(B19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B19)-1,7)+1))</f>
-        <v>46313</v>
+        <f aca="false">IF(K18="","",IF(K18+MIN(MOD(הגדרות!$D$18-WEEKDAY(K18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K18)-1,7)+1)&gt;$K$2,"",K18+MIN(MOD(הגדרות!$D$18-WEEKDAY(K18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K18)-1,7)+1)))</f>
+        <v>46310</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="38" t="n">
-        <f aca="false">IF(B20="","",ROW()-14)</f>
+        <f aca="false">IF(B20="","",COUNT($B$15:B20))</f>
         <v>6</v>
       </c>
       <c r="B20" s="39" t="n">
-        <f aca="false">IF(K19="","",IF(K19&gt;$K$2,"",K19))</f>
+        <f aca="false">IF(K20="","",K20)</f>
         <v>46313</v>
       </c>
       <c r="C20" s="38" t="str">
@@ -8556,7 +8566,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F20" s="42" t="n">
         <f aca="false">IF(B20="","",IF(E20="לא",0,הגדרות!$C$22))</f>
@@ -8569,17 +8579,17 @@
       <c r="H20" s="44"/>
       <c r="I20" s="45"/>
       <c r="K20" s="27" t="n">
-        <f aca="false">IF(B20="","",B20+MIN(MOD(הגדרות!$D$18-WEEKDAY(B20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B20)-1,7)+1))</f>
-        <v>46317</v>
+        <f aca="false">IF(K19="","",IF(K19+MIN(MOD(הגדרות!$D$18-WEEKDAY(K19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K19)-1,7)+1)&gt;$K$2,"",K19+MIN(MOD(הגדרות!$D$18-WEEKDAY(K19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K19)-1,7)+1)))</f>
+        <v>46313</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="38" t="n">
-        <f aca="false">IF(B21="","",ROW()-14)</f>
+        <f aca="false">IF(B21="","",COUNT($B$15:B21))</f>
         <v>7</v>
       </c>
       <c r="B21" s="39" t="n">
-        <f aca="false">IF(K20="","",IF(K20&gt;$K$2,"",K20))</f>
+        <f aca="false">IF(K21="","",K21)</f>
         <v>46317</v>
       </c>
       <c r="C21" s="38" t="str">
@@ -8591,7 +8601,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F21" s="42" t="n">
         <f aca="false">IF(B21="","",IF(E21="לא",0,הגדרות!$C$22))</f>
@@ -8604,17 +8614,17 @@
       <c r="H21" s="44"/>
       <c r="I21" s="45"/>
       <c r="K21" s="27" t="n">
-        <f aca="false">IF(B21="","",B21+MIN(MOD(הגדרות!$D$18-WEEKDAY(B21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B21)-1,7)+1))</f>
-        <v>46320</v>
+        <f aca="false">IF(K20="","",IF(K20+MIN(MOD(הגדרות!$D$18-WEEKDAY(K20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K20)-1,7)+1)&gt;$K$2,"",K20+MIN(MOD(הגדרות!$D$18-WEEKDAY(K20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K20)-1,7)+1)))</f>
+        <v>46317</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="38" t="n">
-        <f aca="false">IF(B22="","",ROW()-14)</f>
+        <f aca="false">IF(B22="","",COUNT($B$15:B22))</f>
         <v>8</v>
       </c>
       <c r="B22" s="39" t="n">
-        <f aca="false">IF(K21="","",IF(K21&gt;$K$2,"",K21))</f>
+        <f aca="false">IF(K22="","",K22)</f>
         <v>46320</v>
       </c>
       <c r="C22" s="38" t="str">
@@ -8626,7 +8636,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F22" s="42" t="n">
         <f aca="false">IF(B22="","",IF(E22="לא",0,הגדרות!$C$22))</f>
@@ -8639,17 +8649,17 @@
       <c r="H22" s="44"/>
       <c r="I22" s="45"/>
       <c r="K22" s="27" t="n">
-        <f aca="false">IF(B22="","",B22+MIN(MOD(הגדרות!$D$18-WEEKDAY(B22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B22)-1,7)+1))</f>
-        <v>46324</v>
+        <f aca="false">IF(K21="","",IF(K21+MIN(MOD(הגדרות!$D$18-WEEKDAY(K21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K21)-1,7)+1)&gt;$K$2,"",K21+MIN(MOD(הגדרות!$D$18-WEEKDAY(K21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K21)-1,7)+1)))</f>
+        <v>46320</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="38" t="n">
-        <f aca="false">IF(B23="","",ROW()-14)</f>
+        <f aca="false">IF(B23="","",COUNT($B$15:B23))</f>
         <v>9</v>
       </c>
       <c r="B23" s="39" t="n">
-        <f aca="false">IF(K22="","",IF(K22&gt;$K$2,"",K22))</f>
+        <f aca="false">IF(K23="","",K23)</f>
         <v>46324</v>
       </c>
       <c r="C23" s="38" t="str">
@@ -8661,7 +8671,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F23" s="42" t="n">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
@@ -8674,17 +8684,17 @@
       <c r="H23" s="44"/>
       <c r="I23" s="45"/>
       <c r="K23" s="27" t="n">
-        <f aca="false">IF(B23="","",B23+MIN(MOD(הגדרות!$D$18-WEEKDAY(B23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B23)-1,7)+1))</f>
-        <v>46327</v>
+        <f aca="false">IF(K22="","",IF(K22+MIN(MOD(הגדרות!$D$18-WEEKDAY(K22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K22)-1,7)+1)&gt;$K$2,"",K22+MIN(MOD(הגדרות!$D$18-WEEKDAY(K22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K22)-1,7)+1)))</f>
+        <v>46324</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="38" t="str">
-        <f aca="false">IF(B24="","",ROW()-14)</f>
+        <f aca="false">IF(B24="","",COUNT($B$15:B24))</f>
         <v/>
       </c>
       <c r="B24" s="39" t="str">
-        <f aca="false">IF(K23="","",IF(K23&gt;$K$2,"",K23))</f>
+        <f aca="false">IF(K24="","",K24)</f>
         <v/>
       </c>
       <c r="C24" s="38" t="str">
@@ -8696,7 +8706,7 @@
         <v/>
       </c>
       <c r="E24" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F24" s="42" t="str">
         <f aca="false">IF(B24="","",IF(E24="לא",0,הגדרות!$C$22))</f>
@@ -8709,7 +8719,7 @@
       <c r="H24" s="44"/>
       <c r="I24" s="45"/>
       <c r="K24" s="27" t="str">
-        <f aca="false">IF(B24="","",B24+MIN(MOD(הגדרות!$D$18-WEEKDAY(B24)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B24)-1,7)+1))</f>
+        <f aca="false">IF(K23="","",IF(K23+MIN(MOD(הגדרות!$D$18-WEEKDAY(K23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K23)-1,7)+1)&gt;$K$2,"",K23+MIN(MOD(הגדרות!$D$18-WEEKDAY(K23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K23)-1,7)+1)))</f>
         <v/>
       </c>
     </row>
@@ -8718,16 +8728,16 @@
         <f aca="false">COUNT($B$15:$B$24)+1</f>
         <v>10</v>
       </c>
-      <c r="B25" s="46"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="38" t="str">
         <f aca="false">IF(B25="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B25)))</f>
         <v/>
       </c>
       <c r="D25" s="40" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F25" s="42" t="n">
         <f aca="false">IF(E25="לא",0,הגדרות!$C$23)</f>
@@ -8742,36 +8752,36 @@
       <c r="K25" s="27"/>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="B26" s="47"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="48" t="n">
+      <c r="A26" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" s="46"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="47" t="n">
         <f aca="false">SUM(F15:F25)</f>
         <v>32.5</v>
       </c>
-      <c r="G26" s="49" t="n">
+      <c r="G26" s="48" t="n">
         <f aca="false">SUM(G15:G25)</f>
         <v>1625</v>
       </c>
-      <c r="H26" s="47"/>
-      <c r="I26" s="49" t="n">
+      <c r="H26" s="46"/>
+      <c r="I26" s="48" t="n">
         <f aca="false">SUM(I15:I25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
+      <c r="A28" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="49"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="49"/>
       <c r="F28" s="40" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G28" s="40"/>
       <c r="H28" s="40"/>
@@ -8781,14 +8791,14 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="51" t="str">
+      <c r="A29" s="50" t="str">
         <f aca="false">"• "&amp;הגדרות!$C$17&amp;": ימי "&amp;הגדרות!$C$18&amp;" ו"&amp;הגדרות!$C$19&amp;", "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00")&amp;" ("&amp;הגדרות!$C$22&amp;" שעות ליום), וישיבת צוות חודשית ("&amp;הגדרות!$C$23&amp;" ש׳)."</f>
         <v>• הדרכת שיקום: ימי ראשון וחמישי, 09:00–12:30 (3.5 שעות ליום), וישיבת צוות חודשית (1 ש׳).</v>
       </c>
-      <c r="B29" s="51"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
       <c r="F29" s="40" t="str">
         <f aca="false">"הדרכת שיקום ("&amp;TEXT(F26,"0.0")&amp;" שעות × "&amp;הגדרות!$C$24&amp;" ₪)"</f>
         <v>הדרכת שיקום (32.5 שעות × 50 ₪)</v>
@@ -8801,16 +8811,16 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="51" t="str">
+      <c r="A30" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$28="","","• "&amp;הגדרות!$C$28)</f>
         <v>• התעריף השעתי אינו כולל מע״מ. מע״מ יתווסף כחוק.</v>
       </c>
-      <c r="B30" s="51"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
       <c r="F30" s="40" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="40"/>
@@ -8820,33 +8830,33 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="51" t="str">
+      <c r="A31" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$29="","","• "&amp;הגדרות!$C$29)</f>
         <v>• פרויקטים פרטיים מתומחרים בנפרד, לפי הזמנת החווה.</v>
       </c>
-      <c r="B31" s="51"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="52" t="s">
-        <v>89</v>
-      </c>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="53" t="n">
+      <c r="B31" s="50"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="52" t="n">
         <f aca="false">I29+I30</f>
         <v>1625</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="51" t="str">
+      <c r="A32" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$30="","","• "&amp;הגדרות!$C$30)</f>
         <v/>
       </c>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
       <c r="F32" s="40" t="str">
         <f aca="false">"מע״מ "&amp;ROUND(הגדרות!$C$25*100,1)&amp;"%"</f>
         <v>מע״מ 18%</v>
@@ -8859,30 +8869,30 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F33" s="54" t="s">
-        <v>90</v>
-      </c>
-      <c r="G33" s="54"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="55" t="n">
+      <c r="F33" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="54" t="n">
         <f aca="false">I31+I32</f>
         <v>1917.5</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="56" t="str">
+      <c r="A36" s="55" t="str">
         <f aca="false">"בברכה, "&amp;הגדרות!$C$6</f>
         <v>בברכה, (למילוי)</v>
       </c>
-      <c r="B36" s="56"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="F36" s="56" t="s">
-        <v>91</v>
-      </c>
-      <c r="G36" s="56"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="56"/>
+      <c r="B36" s="55"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="F36" s="55" t="s">
+        <v>93</v>
+      </c>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="44">
@@ -8980,7 +8990,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -9016,13 +9026,13 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
       <c r="F4" s="29" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
@@ -9030,7 +9040,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
@@ -9039,7 +9049,7 @@
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="31" t="str">
@@ -9050,7 +9060,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="31" t="str">
@@ -9059,7 +9069,7 @@
       </c>
       <c r="D6" s="31"/>
       <c r="F6" s="30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="31" t="str">
@@ -9070,7 +9080,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="31" t="str">
@@ -9079,7 +9089,7 @@
       </c>
       <c r="D7" s="31"/>
       <c r="F7" s="30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="31" t="str">
@@ -9090,7 +9100,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="31" t="str">
@@ -9101,7 +9111,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="str">
@@ -9113,7 +9123,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
@@ -9122,7 +9132,7 @@
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
@@ -9132,7 +9142,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
@@ -9141,7 +9151,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31" t="str">
@@ -9152,7 +9162,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -9161,46 +9171,46 @@
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="35" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="38" t="n">
-        <f aca="false">IF(B15="","",ROW()-14)</f>
+        <f aca="false">IF(B15="","",COUNT($B$15:B15))</f>
         <v>1</v>
       </c>
       <c r="B15" s="39" t="n">
-        <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
+        <f aca="false">IF(K15="","",K15)</f>
         <v>46327</v>
       </c>
       <c r="C15" s="38" t="str">
@@ -9212,7 +9222,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F15" s="42" t="n">
         <f aca="false">IF(B15="","",IF(E15="לא",0,הגדרות!$C$22))</f>
@@ -9225,17 +9235,17 @@
       <c r="H15" s="44"/>
       <c r="I15" s="45"/>
       <c r="K15" s="27" t="n">
-        <f aca="false">IF(B15="","",B15+MIN(MOD(הגדרות!$D$18-WEEKDAY(B15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B15)-1,7)+1))</f>
-        <v>46331</v>
+        <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
+        <v>46327</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="38" t="n">
-        <f aca="false">IF(B16="","",ROW()-14)</f>
+        <f aca="false">IF(B16="","",COUNT($B$15:B16))</f>
         <v>2</v>
       </c>
       <c r="B16" s="39" t="n">
-        <f aca="false">IF(K15="","",IF(K15&gt;$K$2,"",K15))</f>
+        <f aca="false">IF(K16="","",K16)</f>
         <v>46331</v>
       </c>
       <c r="C16" s="38" t="str">
@@ -9247,7 +9257,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F16" s="42" t="n">
         <f aca="false">IF(B16="","",IF(E16="לא",0,הגדרות!$C$22))</f>
@@ -9260,17 +9270,17 @@
       <c r="H16" s="44"/>
       <c r="I16" s="45"/>
       <c r="K16" s="27" t="n">
-        <f aca="false">IF(B16="","",B16+MIN(MOD(הגדרות!$D$18-WEEKDAY(B16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B16)-1,7)+1))</f>
-        <v>46334</v>
+        <f aca="false">IF(K15="","",IF(K15+MIN(MOD(הגדרות!$D$18-WEEKDAY(K15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K15)-1,7)+1)&gt;$K$2,"",K15+MIN(MOD(הגדרות!$D$18-WEEKDAY(K15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K15)-1,7)+1)))</f>
+        <v>46331</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="38" t="n">
-        <f aca="false">IF(B17="","",ROW()-14)</f>
+        <f aca="false">IF(B17="","",COUNT($B$15:B17))</f>
         <v>3</v>
       </c>
       <c r="B17" s="39" t="n">
-        <f aca="false">IF(K16="","",IF(K16&gt;$K$2,"",K16))</f>
+        <f aca="false">IF(K17="","",K17)</f>
         <v>46334</v>
       </c>
       <c r="C17" s="38" t="str">
@@ -9282,7 +9292,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F17" s="42" t="n">
         <f aca="false">IF(B17="","",IF(E17="לא",0,הגדרות!$C$22))</f>
@@ -9295,17 +9305,17 @@
       <c r="H17" s="44"/>
       <c r="I17" s="45"/>
       <c r="K17" s="27" t="n">
-        <f aca="false">IF(B17="","",B17+MIN(MOD(הגדרות!$D$18-WEEKDAY(B17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B17)-1,7)+1))</f>
-        <v>46338</v>
+        <f aca="false">IF(K16="","",IF(K16+MIN(MOD(הגדרות!$D$18-WEEKDAY(K16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K16)-1,7)+1)&gt;$K$2,"",K16+MIN(MOD(הגדרות!$D$18-WEEKDAY(K16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K16)-1,7)+1)))</f>
+        <v>46334</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="38" t="n">
-        <f aca="false">IF(B18="","",ROW()-14)</f>
+        <f aca="false">IF(B18="","",COUNT($B$15:B18))</f>
         <v>4</v>
       </c>
       <c r="B18" s="39" t="n">
-        <f aca="false">IF(K17="","",IF(K17&gt;$K$2,"",K17))</f>
+        <f aca="false">IF(K18="","",K18)</f>
         <v>46338</v>
       </c>
       <c r="C18" s="38" t="str">
@@ -9317,7 +9327,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F18" s="42" t="n">
         <f aca="false">IF(B18="","",IF(E18="לא",0,הגדרות!$C$22))</f>
@@ -9330,17 +9340,17 @@
       <c r="H18" s="44"/>
       <c r="I18" s="45"/>
       <c r="K18" s="27" t="n">
-        <f aca="false">IF(B18="","",B18+MIN(MOD(הגדרות!$D$18-WEEKDAY(B18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B18)-1,7)+1))</f>
-        <v>46341</v>
+        <f aca="false">IF(K17="","",IF(K17+MIN(MOD(הגדרות!$D$18-WEEKDAY(K17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K17)-1,7)+1)&gt;$K$2,"",K17+MIN(MOD(הגדרות!$D$18-WEEKDAY(K17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K17)-1,7)+1)))</f>
+        <v>46338</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="38" t="n">
-        <f aca="false">IF(B19="","",ROW()-14)</f>
+        <f aca="false">IF(B19="","",COUNT($B$15:B19))</f>
         <v>5</v>
       </c>
       <c r="B19" s="39" t="n">
-        <f aca="false">IF(K18="","",IF(K18&gt;$K$2,"",K18))</f>
+        <f aca="false">IF(K19="","",K19)</f>
         <v>46341</v>
       </c>
       <c r="C19" s="38" t="str">
@@ -9352,7 +9362,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F19" s="42" t="n">
         <f aca="false">IF(B19="","",IF(E19="לא",0,הגדרות!$C$22))</f>
@@ -9365,17 +9375,17 @@
       <c r="H19" s="44"/>
       <c r="I19" s="45"/>
       <c r="K19" s="27" t="n">
-        <f aca="false">IF(B19="","",B19+MIN(MOD(הגדרות!$D$18-WEEKDAY(B19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B19)-1,7)+1))</f>
-        <v>46345</v>
+        <f aca="false">IF(K18="","",IF(K18+MIN(MOD(הגדרות!$D$18-WEEKDAY(K18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K18)-1,7)+1)&gt;$K$2,"",K18+MIN(MOD(הגדרות!$D$18-WEEKDAY(K18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K18)-1,7)+1)))</f>
+        <v>46341</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="38" t="n">
-        <f aca="false">IF(B20="","",ROW()-14)</f>
+        <f aca="false">IF(B20="","",COUNT($B$15:B20))</f>
         <v>6</v>
       </c>
       <c r="B20" s="39" t="n">
-        <f aca="false">IF(K19="","",IF(K19&gt;$K$2,"",K19))</f>
+        <f aca="false">IF(K20="","",K20)</f>
         <v>46345</v>
       </c>
       <c r="C20" s="38" t="str">
@@ -9387,7 +9397,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F20" s="42" t="n">
         <f aca="false">IF(B20="","",IF(E20="לא",0,הגדרות!$C$22))</f>
@@ -9400,17 +9410,17 @@
       <c r="H20" s="44"/>
       <c r="I20" s="45"/>
       <c r="K20" s="27" t="n">
-        <f aca="false">IF(B20="","",B20+MIN(MOD(הגדרות!$D$18-WEEKDAY(B20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B20)-1,7)+1))</f>
-        <v>46348</v>
+        <f aca="false">IF(K19="","",IF(K19+MIN(MOD(הגדרות!$D$18-WEEKDAY(K19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K19)-1,7)+1)&gt;$K$2,"",K19+MIN(MOD(הגדרות!$D$18-WEEKDAY(K19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K19)-1,7)+1)))</f>
+        <v>46345</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="38" t="n">
-        <f aca="false">IF(B21="","",ROW()-14)</f>
+        <f aca="false">IF(B21="","",COUNT($B$15:B21))</f>
         <v>7</v>
       </c>
       <c r="B21" s="39" t="n">
-        <f aca="false">IF(K20="","",IF(K20&gt;$K$2,"",K20))</f>
+        <f aca="false">IF(K21="","",K21)</f>
         <v>46348</v>
       </c>
       <c r="C21" s="38" t="str">
@@ -9422,7 +9432,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F21" s="42" t="n">
         <f aca="false">IF(B21="","",IF(E21="לא",0,הגדרות!$C$22))</f>
@@ -9435,17 +9445,17 @@
       <c r="H21" s="44"/>
       <c r="I21" s="45"/>
       <c r="K21" s="27" t="n">
-        <f aca="false">IF(B21="","",B21+MIN(MOD(הגדרות!$D$18-WEEKDAY(B21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B21)-1,7)+1))</f>
-        <v>46352</v>
+        <f aca="false">IF(K20="","",IF(K20+MIN(MOD(הגדרות!$D$18-WEEKDAY(K20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K20)-1,7)+1)&gt;$K$2,"",K20+MIN(MOD(הגדרות!$D$18-WEEKDAY(K20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K20)-1,7)+1)))</f>
+        <v>46348</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="38" t="n">
-        <f aca="false">IF(B22="","",ROW()-14)</f>
+        <f aca="false">IF(B22="","",COUNT($B$15:B22))</f>
         <v>8</v>
       </c>
       <c r="B22" s="39" t="n">
-        <f aca="false">IF(K21="","",IF(K21&gt;$K$2,"",K21))</f>
+        <f aca="false">IF(K22="","",K22)</f>
         <v>46352</v>
       </c>
       <c r="C22" s="38" t="str">
@@ -9457,7 +9467,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F22" s="42" t="n">
         <f aca="false">IF(B22="","",IF(E22="לא",0,הגדרות!$C$22))</f>
@@ -9470,17 +9480,17 @@
       <c r="H22" s="44"/>
       <c r="I22" s="45"/>
       <c r="K22" s="27" t="n">
-        <f aca="false">IF(B22="","",B22+MIN(MOD(הגדרות!$D$18-WEEKDAY(B22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B22)-1,7)+1))</f>
-        <v>46355</v>
+        <f aca="false">IF(K21="","",IF(K21+MIN(MOD(הגדרות!$D$18-WEEKDAY(K21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K21)-1,7)+1)&gt;$K$2,"",K21+MIN(MOD(הגדרות!$D$18-WEEKDAY(K21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K21)-1,7)+1)))</f>
+        <v>46352</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="38" t="n">
-        <f aca="false">IF(B23="","",ROW()-14)</f>
+        <f aca="false">IF(B23="","",COUNT($B$15:B23))</f>
         <v>9</v>
       </c>
       <c r="B23" s="39" t="n">
-        <f aca="false">IF(K22="","",IF(K22&gt;$K$2,"",K22))</f>
+        <f aca="false">IF(K23="","",K23)</f>
         <v>46355</v>
       </c>
       <c r="C23" s="38" t="str">
@@ -9492,7 +9502,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F23" s="42" t="n">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
@@ -9505,17 +9515,17 @@
       <c r="H23" s="44"/>
       <c r="I23" s="45"/>
       <c r="K23" s="27" t="n">
-        <f aca="false">IF(B23="","",B23+MIN(MOD(הגדרות!$D$18-WEEKDAY(B23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B23)-1,7)+1))</f>
-        <v>46359</v>
+        <f aca="false">IF(K22="","",IF(K22+MIN(MOD(הגדרות!$D$18-WEEKDAY(K22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K22)-1,7)+1)&gt;$K$2,"",K22+MIN(MOD(הגדרות!$D$18-WEEKDAY(K22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K22)-1,7)+1)))</f>
+        <v>46355</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="38" t="str">
-        <f aca="false">IF(B24="","",ROW()-14)</f>
+        <f aca="false">IF(B24="","",COUNT($B$15:B24))</f>
         <v/>
       </c>
       <c r="B24" s="39" t="str">
-        <f aca="false">IF(K23="","",IF(K23&gt;$K$2,"",K23))</f>
+        <f aca="false">IF(K24="","",K24)</f>
         <v/>
       </c>
       <c r="C24" s="38" t="str">
@@ -9527,7 +9537,7 @@
         <v/>
       </c>
       <c r="E24" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F24" s="42" t="str">
         <f aca="false">IF(B24="","",IF(E24="לא",0,הגדרות!$C$22))</f>
@@ -9540,7 +9550,7 @@
       <c r="H24" s="44"/>
       <c r="I24" s="45"/>
       <c r="K24" s="27" t="str">
-        <f aca="false">IF(B24="","",B24+MIN(MOD(הגדרות!$D$18-WEEKDAY(B24)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B24)-1,7)+1))</f>
+        <f aca="false">IF(K23="","",IF(K23+MIN(MOD(הגדרות!$D$18-WEEKDAY(K23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K23)-1,7)+1)&gt;$K$2,"",K23+MIN(MOD(הגדרות!$D$18-WEEKDAY(K23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K23)-1,7)+1)))</f>
         <v/>
       </c>
     </row>
@@ -9549,16 +9559,16 @@
         <f aca="false">COUNT($B$15:$B$24)+1</f>
         <v>10</v>
       </c>
-      <c r="B25" s="46"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="38" t="str">
         <f aca="false">IF(B25="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B25)))</f>
         <v/>
       </c>
       <c r="D25" s="40" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F25" s="42" t="n">
         <f aca="false">IF(E25="לא",0,הגדרות!$C$23)</f>
@@ -9573,36 +9583,36 @@
       <c r="K25" s="27"/>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="B26" s="47"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="48" t="n">
+      <c r="A26" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" s="46"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="47" t="n">
         <f aca="false">SUM(F15:F25)</f>
         <v>32.5</v>
       </c>
-      <c r="G26" s="49" t="n">
+      <c r="G26" s="48" t="n">
         <f aca="false">SUM(G15:G25)</f>
         <v>1625</v>
       </c>
-      <c r="H26" s="47"/>
-      <c r="I26" s="49" t="n">
+      <c r="H26" s="46"/>
+      <c r="I26" s="48" t="n">
         <f aca="false">SUM(I15:I25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
+      <c r="A28" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="49"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="49"/>
       <c r="F28" s="40" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G28" s="40"/>
       <c r="H28" s="40"/>
@@ -9612,14 +9622,14 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="51" t="str">
+      <c r="A29" s="50" t="str">
         <f aca="false">"• "&amp;הגדרות!$C$17&amp;": ימי "&amp;הגדרות!$C$18&amp;" ו"&amp;הגדרות!$C$19&amp;", "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00")&amp;" ("&amp;הגדרות!$C$22&amp;" שעות ליום), וישיבת צוות חודשית ("&amp;הגדרות!$C$23&amp;" ש׳)."</f>
         <v>• הדרכת שיקום: ימי ראשון וחמישי, 09:00–12:30 (3.5 שעות ליום), וישיבת צוות חודשית (1 ש׳).</v>
       </c>
-      <c r="B29" s="51"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
       <c r="F29" s="40" t="str">
         <f aca="false">"הדרכת שיקום ("&amp;TEXT(F26,"0.0")&amp;" שעות × "&amp;הגדרות!$C$24&amp;" ₪)"</f>
         <v>הדרכת שיקום (32.5 שעות × 50 ₪)</v>
@@ -9632,16 +9642,16 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="51" t="str">
+      <c r="A30" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$28="","","• "&amp;הגדרות!$C$28)</f>
         <v>• התעריף השעתי אינו כולל מע״מ. מע״מ יתווסף כחוק.</v>
       </c>
-      <c r="B30" s="51"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
       <c r="F30" s="40" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="40"/>
@@ -9651,33 +9661,33 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="51" t="str">
+      <c r="A31" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$29="","","• "&amp;הגדרות!$C$29)</f>
         <v>• פרויקטים פרטיים מתומחרים בנפרד, לפי הזמנת החווה.</v>
       </c>
-      <c r="B31" s="51"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="52" t="s">
-        <v>89</v>
-      </c>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="53" t="n">
+      <c r="B31" s="50"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="52" t="n">
         <f aca="false">I29+I30</f>
         <v>1625</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="51" t="str">
+      <c r="A32" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$30="","","• "&amp;הגדרות!$C$30)</f>
         <v/>
       </c>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
       <c r="F32" s="40" t="str">
         <f aca="false">"מע״מ "&amp;ROUND(הגדרות!$C$25*100,1)&amp;"%"</f>
         <v>מע״מ 18%</v>
@@ -9690,30 +9700,30 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F33" s="54" t="s">
-        <v>90</v>
-      </c>
-      <c r="G33" s="54"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="55" t="n">
+      <c r="F33" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="54" t="n">
         <f aca="false">I31+I32</f>
         <v>1917.5</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="56" t="str">
+      <c r="A36" s="55" t="str">
         <f aca="false">"בברכה, "&amp;הגדרות!$C$6</f>
         <v>בברכה, (למילוי)</v>
       </c>
-      <c r="B36" s="56"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="F36" s="56" t="s">
-        <v>91</v>
-      </c>
-      <c r="G36" s="56"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="56"/>
+      <c r="B36" s="55"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="F36" s="55" t="s">
+        <v>93</v>
+      </c>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="44">
@@ -9811,7 +9821,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -9847,13 +9857,13 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
       <c r="F4" s="29" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
@@ -9861,7 +9871,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
@@ -9870,7 +9880,7 @@
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="31" t="str">
@@ -9881,7 +9891,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="31" t="str">
@@ -9890,7 +9900,7 @@
       </c>
       <c r="D6" s="31"/>
       <c r="F6" s="30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="31" t="str">
@@ -9901,7 +9911,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="31" t="str">
@@ -9910,7 +9920,7 @@
       </c>
       <c r="D7" s="31"/>
       <c r="F7" s="30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="31" t="str">
@@ -9921,7 +9931,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="31" t="str">
@@ -9932,7 +9942,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="str">
@@ -9944,7 +9954,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
@@ -9953,7 +9963,7 @@
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
@@ -9963,7 +9973,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
@@ -9972,7 +9982,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31" t="str">
@@ -9983,7 +9993,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -9992,46 +10002,46 @@
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="35" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="38" t="n">
-        <f aca="false">IF(B15="","",ROW()-14)</f>
+        <f aca="false">IF(B15="","",COUNT($B$15:B15))</f>
         <v>1</v>
       </c>
       <c r="B15" s="39" t="n">
-        <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
+        <f aca="false">IF(K15="","",K15)</f>
         <v>46359</v>
       </c>
       <c r="C15" s="38" t="str">
@@ -10043,7 +10053,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F15" s="42" t="n">
         <f aca="false">IF(B15="","",IF(E15="לא",0,הגדרות!$C$22))</f>
@@ -10056,17 +10066,17 @@
       <c r="H15" s="44"/>
       <c r="I15" s="45"/>
       <c r="K15" s="27" t="n">
-        <f aca="false">IF(B15="","",B15+MIN(MOD(הגדרות!$D$18-WEEKDAY(B15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B15)-1,7)+1))</f>
-        <v>46362</v>
+        <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
+        <v>46359</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="38" t="n">
-        <f aca="false">IF(B16="","",ROW()-14)</f>
+        <f aca="false">IF(B16="","",COUNT($B$15:B16))</f>
         <v>2</v>
       </c>
       <c r="B16" s="39" t="n">
-        <f aca="false">IF(K15="","",IF(K15&gt;$K$2,"",K15))</f>
+        <f aca="false">IF(K16="","",K16)</f>
         <v>46362</v>
       </c>
       <c r="C16" s="38" t="str">
@@ -10078,7 +10088,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F16" s="42" t="n">
         <f aca="false">IF(B16="","",IF(E16="לא",0,הגדרות!$C$22))</f>
@@ -10091,17 +10101,17 @@
       <c r="H16" s="44"/>
       <c r="I16" s="45"/>
       <c r="K16" s="27" t="n">
-        <f aca="false">IF(B16="","",B16+MIN(MOD(הגדרות!$D$18-WEEKDAY(B16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B16)-1,7)+1))</f>
-        <v>46366</v>
+        <f aca="false">IF(K15="","",IF(K15+MIN(MOD(הגדרות!$D$18-WEEKDAY(K15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K15)-1,7)+1)&gt;$K$2,"",K15+MIN(MOD(הגדרות!$D$18-WEEKDAY(K15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K15)-1,7)+1)))</f>
+        <v>46362</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="38" t="n">
-        <f aca="false">IF(B17="","",ROW()-14)</f>
+        <f aca="false">IF(B17="","",COUNT($B$15:B17))</f>
         <v>3</v>
       </c>
       <c r="B17" s="39" t="n">
-        <f aca="false">IF(K16="","",IF(K16&gt;$K$2,"",K16))</f>
+        <f aca="false">IF(K17="","",K17)</f>
         <v>46366</v>
       </c>
       <c r="C17" s="38" t="str">
@@ -10113,7 +10123,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F17" s="42" t="n">
         <f aca="false">IF(B17="","",IF(E17="לא",0,הגדרות!$C$22))</f>
@@ -10126,17 +10136,17 @@
       <c r="H17" s="44"/>
       <c r="I17" s="45"/>
       <c r="K17" s="27" t="n">
-        <f aca="false">IF(B17="","",B17+MIN(MOD(הגדרות!$D$18-WEEKDAY(B17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B17)-1,7)+1))</f>
-        <v>46369</v>
+        <f aca="false">IF(K16="","",IF(K16+MIN(MOD(הגדרות!$D$18-WEEKDAY(K16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K16)-1,7)+1)&gt;$K$2,"",K16+MIN(MOD(הגדרות!$D$18-WEEKDAY(K16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K16)-1,7)+1)))</f>
+        <v>46366</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="38" t="n">
-        <f aca="false">IF(B18="","",ROW()-14)</f>
+        <f aca="false">IF(B18="","",COUNT($B$15:B18))</f>
         <v>4</v>
       </c>
       <c r="B18" s="39" t="n">
-        <f aca="false">IF(K17="","",IF(K17&gt;$K$2,"",K17))</f>
+        <f aca="false">IF(K18="","",K18)</f>
         <v>46369</v>
       </c>
       <c r="C18" s="38" t="str">
@@ -10148,7 +10158,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F18" s="42" t="n">
         <f aca="false">IF(B18="","",IF(E18="לא",0,הגדרות!$C$22))</f>
@@ -10161,17 +10171,17 @@
       <c r="H18" s="44"/>
       <c r="I18" s="45"/>
       <c r="K18" s="27" t="n">
-        <f aca="false">IF(B18="","",B18+MIN(MOD(הגדרות!$D$18-WEEKDAY(B18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B18)-1,7)+1))</f>
-        <v>46373</v>
+        <f aca="false">IF(K17="","",IF(K17+MIN(MOD(הגדרות!$D$18-WEEKDAY(K17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K17)-1,7)+1)&gt;$K$2,"",K17+MIN(MOD(הגדרות!$D$18-WEEKDAY(K17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K17)-1,7)+1)))</f>
+        <v>46369</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="38" t="n">
-        <f aca="false">IF(B19="","",ROW()-14)</f>
+        <f aca="false">IF(B19="","",COUNT($B$15:B19))</f>
         <v>5</v>
       </c>
       <c r="B19" s="39" t="n">
-        <f aca="false">IF(K18="","",IF(K18&gt;$K$2,"",K18))</f>
+        <f aca="false">IF(K19="","",K19)</f>
         <v>46373</v>
       </c>
       <c r="C19" s="38" t="str">
@@ -10183,7 +10193,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F19" s="42" t="n">
         <f aca="false">IF(B19="","",IF(E19="לא",0,הגדרות!$C$22))</f>
@@ -10196,17 +10206,17 @@
       <c r="H19" s="44"/>
       <c r="I19" s="45"/>
       <c r="K19" s="27" t="n">
-        <f aca="false">IF(B19="","",B19+MIN(MOD(הגדרות!$D$18-WEEKDAY(B19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B19)-1,7)+1))</f>
-        <v>46376</v>
+        <f aca="false">IF(K18="","",IF(K18+MIN(MOD(הגדרות!$D$18-WEEKDAY(K18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K18)-1,7)+1)&gt;$K$2,"",K18+MIN(MOD(הגדרות!$D$18-WEEKDAY(K18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K18)-1,7)+1)))</f>
+        <v>46373</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="38" t="n">
-        <f aca="false">IF(B20="","",ROW()-14)</f>
+        <f aca="false">IF(B20="","",COUNT($B$15:B20))</f>
         <v>6</v>
       </c>
       <c r="B20" s="39" t="n">
-        <f aca="false">IF(K19="","",IF(K19&gt;$K$2,"",K19))</f>
+        <f aca="false">IF(K20="","",K20)</f>
         <v>46376</v>
       </c>
       <c r="C20" s="38" t="str">
@@ -10218,7 +10228,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F20" s="42" t="n">
         <f aca="false">IF(B20="","",IF(E20="לא",0,הגדרות!$C$22))</f>
@@ -10231,17 +10241,17 @@
       <c r="H20" s="44"/>
       <c r="I20" s="45"/>
       <c r="K20" s="27" t="n">
-        <f aca="false">IF(B20="","",B20+MIN(MOD(הגדרות!$D$18-WEEKDAY(B20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B20)-1,7)+1))</f>
-        <v>46380</v>
+        <f aca="false">IF(K19="","",IF(K19+MIN(MOD(הגדרות!$D$18-WEEKDAY(K19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K19)-1,7)+1)&gt;$K$2,"",K19+MIN(MOD(הגדרות!$D$18-WEEKDAY(K19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K19)-1,7)+1)))</f>
+        <v>46376</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="38" t="n">
-        <f aca="false">IF(B21="","",ROW()-14)</f>
+        <f aca="false">IF(B21="","",COUNT($B$15:B21))</f>
         <v>7</v>
       </c>
       <c r="B21" s="39" t="n">
-        <f aca="false">IF(K20="","",IF(K20&gt;$K$2,"",K20))</f>
+        <f aca="false">IF(K21="","",K21)</f>
         <v>46380</v>
       </c>
       <c r="C21" s="38" t="str">
@@ -10253,7 +10263,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F21" s="42" t="n">
         <f aca="false">IF(B21="","",IF(E21="לא",0,הגדרות!$C$22))</f>
@@ -10266,17 +10276,17 @@
       <c r="H21" s="44"/>
       <c r="I21" s="45"/>
       <c r="K21" s="27" t="n">
-        <f aca="false">IF(B21="","",B21+MIN(MOD(הגדרות!$D$18-WEEKDAY(B21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B21)-1,7)+1))</f>
-        <v>46383</v>
+        <f aca="false">IF(K20="","",IF(K20+MIN(MOD(הגדרות!$D$18-WEEKDAY(K20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K20)-1,7)+1)&gt;$K$2,"",K20+MIN(MOD(הגדרות!$D$18-WEEKDAY(K20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K20)-1,7)+1)))</f>
+        <v>46380</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="38" t="n">
-        <f aca="false">IF(B22="","",ROW()-14)</f>
+        <f aca="false">IF(B22="","",COUNT($B$15:B22))</f>
         <v>8</v>
       </c>
       <c r="B22" s="39" t="n">
-        <f aca="false">IF(K21="","",IF(K21&gt;$K$2,"",K21))</f>
+        <f aca="false">IF(K22="","",K22)</f>
         <v>46383</v>
       </c>
       <c r="C22" s="38" t="str">
@@ -10288,7 +10298,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F22" s="42" t="n">
         <f aca="false">IF(B22="","",IF(E22="לא",0,הגדרות!$C$22))</f>
@@ -10301,17 +10311,17 @@
       <c r="H22" s="44"/>
       <c r="I22" s="45"/>
       <c r="K22" s="27" t="n">
-        <f aca="false">IF(B22="","",B22+MIN(MOD(הגדרות!$D$18-WEEKDAY(B22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B22)-1,7)+1))</f>
-        <v>46387</v>
+        <f aca="false">IF(K21="","",IF(K21+MIN(MOD(הגדרות!$D$18-WEEKDAY(K21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K21)-1,7)+1)&gt;$K$2,"",K21+MIN(MOD(הגדרות!$D$18-WEEKDAY(K21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K21)-1,7)+1)))</f>
+        <v>46383</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="38" t="n">
-        <f aca="false">IF(B23="","",ROW()-14)</f>
+        <f aca="false">IF(B23="","",COUNT($B$15:B23))</f>
         <v>9</v>
       </c>
       <c r="B23" s="39" t="n">
-        <f aca="false">IF(K22="","",IF(K22&gt;$K$2,"",K22))</f>
+        <f aca="false">IF(K23="","",K23)</f>
         <v>46387</v>
       </c>
       <c r="C23" s="38" t="str">
@@ -10323,7 +10333,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F23" s="42" t="n">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
@@ -10336,17 +10346,17 @@
       <c r="H23" s="44"/>
       <c r="I23" s="45"/>
       <c r="K23" s="27" t="n">
-        <f aca="false">IF(B23="","",B23+MIN(MOD(הגדרות!$D$18-WEEKDAY(B23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B23)-1,7)+1))</f>
-        <v>46390</v>
+        <f aca="false">IF(K22="","",IF(K22+MIN(MOD(הגדרות!$D$18-WEEKDAY(K22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K22)-1,7)+1)&gt;$K$2,"",K22+MIN(MOD(הגדרות!$D$18-WEEKDAY(K22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K22)-1,7)+1)))</f>
+        <v>46387</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="38" t="str">
-        <f aca="false">IF(B24="","",ROW()-14)</f>
+        <f aca="false">IF(B24="","",COUNT($B$15:B24))</f>
         <v/>
       </c>
       <c r="B24" s="39" t="str">
-        <f aca="false">IF(K23="","",IF(K23&gt;$K$2,"",K23))</f>
+        <f aca="false">IF(K24="","",K24)</f>
         <v/>
       </c>
       <c r="C24" s="38" t="str">
@@ -10358,7 +10368,7 @@
         <v/>
       </c>
       <c r="E24" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F24" s="42" t="str">
         <f aca="false">IF(B24="","",IF(E24="לא",0,הגדרות!$C$22))</f>
@@ -10371,7 +10381,7 @@
       <c r="H24" s="44"/>
       <c r="I24" s="45"/>
       <c r="K24" s="27" t="str">
-        <f aca="false">IF(B24="","",B24+MIN(MOD(הגדרות!$D$18-WEEKDAY(B24)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B24)-1,7)+1))</f>
+        <f aca="false">IF(K23="","",IF(K23+MIN(MOD(הגדרות!$D$18-WEEKDAY(K23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K23)-1,7)+1)&gt;$K$2,"",K23+MIN(MOD(הגדרות!$D$18-WEEKDAY(K23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K23)-1,7)+1)))</f>
         <v/>
       </c>
     </row>
@@ -10380,16 +10390,16 @@
         <f aca="false">COUNT($B$15:$B$24)+1</f>
         <v>10</v>
       </c>
-      <c r="B25" s="46"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="38" t="str">
         <f aca="false">IF(B25="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B25)))</f>
         <v/>
       </c>
       <c r="D25" s="40" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F25" s="42" t="n">
         <f aca="false">IF(E25="לא",0,הגדרות!$C$23)</f>
@@ -10404,36 +10414,36 @@
       <c r="K25" s="27"/>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="B26" s="47"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="48" t="n">
+      <c r="A26" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" s="46"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="47" t="n">
         <f aca="false">SUM(F15:F25)</f>
         <v>32.5</v>
       </c>
-      <c r="G26" s="49" t="n">
+      <c r="G26" s="48" t="n">
         <f aca="false">SUM(G15:G25)</f>
         <v>1625</v>
       </c>
-      <c r="H26" s="47"/>
-      <c r="I26" s="49" t="n">
+      <c r="H26" s="46"/>
+      <c r="I26" s="48" t="n">
         <f aca="false">SUM(I15:I25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
+      <c r="A28" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="49"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="49"/>
       <c r="F28" s="40" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G28" s="40"/>
       <c r="H28" s="40"/>
@@ -10443,14 +10453,14 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="51" t="str">
+      <c r="A29" s="50" t="str">
         <f aca="false">"• "&amp;הגדרות!$C$17&amp;": ימי "&amp;הגדרות!$C$18&amp;" ו"&amp;הגדרות!$C$19&amp;", "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00")&amp;" ("&amp;הגדרות!$C$22&amp;" שעות ליום), וישיבת צוות חודשית ("&amp;הגדרות!$C$23&amp;" ש׳)."</f>
         <v>• הדרכת שיקום: ימי ראשון וחמישי, 09:00–12:30 (3.5 שעות ליום), וישיבת צוות חודשית (1 ש׳).</v>
       </c>
-      <c r="B29" s="51"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
       <c r="F29" s="40" t="str">
         <f aca="false">"הדרכת שיקום ("&amp;TEXT(F26,"0.0")&amp;" שעות × "&amp;הגדרות!$C$24&amp;" ₪)"</f>
         <v>הדרכת שיקום (32.5 שעות × 50 ₪)</v>
@@ -10463,16 +10473,16 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="51" t="str">
+      <c r="A30" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$28="","","• "&amp;הגדרות!$C$28)</f>
         <v>• התעריף השעתי אינו כולל מע״מ. מע״מ יתווסף כחוק.</v>
       </c>
-      <c r="B30" s="51"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
       <c r="F30" s="40" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="40"/>
@@ -10482,33 +10492,33 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="51" t="str">
+      <c r="A31" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$29="","","• "&amp;הגדרות!$C$29)</f>
         <v>• פרויקטים פרטיים מתומחרים בנפרד, לפי הזמנת החווה.</v>
       </c>
-      <c r="B31" s="51"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="52" t="s">
-        <v>89</v>
-      </c>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="53" t="n">
+      <c r="B31" s="50"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="52" t="n">
         <f aca="false">I29+I30</f>
         <v>1625</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="51" t="str">
+      <c r="A32" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$30="","","• "&amp;הגדרות!$C$30)</f>
         <v/>
       </c>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
       <c r="F32" s="40" t="str">
         <f aca="false">"מע״מ "&amp;ROUND(הגדרות!$C$25*100,1)&amp;"%"</f>
         <v>מע״מ 18%</v>
@@ -10521,30 +10531,30 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F33" s="54" t="s">
-        <v>90</v>
-      </c>
-      <c r="G33" s="54"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="55" t="n">
+      <c r="F33" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="54" t="n">
         <f aca="false">I31+I32</f>
         <v>1917.5</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="56" t="str">
+      <c r="A36" s="55" t="str">
         <f aca="false">"בברכה, "&amp;הגדרות!$C$6</f>
         <v>בברכה, (למילוי)</v>
       </c>
-      <c r="B36" s="56"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="F36" s="56" t="s">
-        <v>91</v>
-      </c>
-      <c r="G36" s="56"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="56"/>
+      <c r="B36" s="55"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="F36" s="55" t="s">
+        <v>93</v>
+      </c>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="44">
@@ -10642,7 +10652,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -10678,13 +10688,13 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
       <c r="F4" s="29" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
@@ -10692,7 +10702,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
@@ -10701,7 +10711,7 @@
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="31" t="str">
@@ -10712,7 +10722,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="31" t="str">
@@ -10721,7 +10731,7 @@
       </c>
       <c r="D6" s="31"/>
       <c r="F6" s="30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="31" t="str">
@@ -10732,7 +10742,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="31" t="str">
@@ -10741,7 +10751,7 @@
       </c>
       <c r="D7" s="31"/>
       <c r="F7" s="30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="31" t="str">
@@ -10752,7 +10762,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="31" t="str">
@@ -10763,7 +10773,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="str">
@@ -10775,7 +10785,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
@@ -10784,7 +10794,7 @@
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
@@ -10794,7 +10804,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
@@ -10803,7 +10813,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31" t="str">
@@ -10814,7 +10824,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -10823,46 +10833,46 @@
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="35" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="38" t="n">
-        <f aca="false">IF(B15="","",ROW()-14)</f>
+        <f aca="false">IF(B15="","",COUNT($B$15:B15))</f>
         <v>1</v>
       </c>
       <c r="B15" s="39" t="n">
-        <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
+        <f aca="false">IF(K15="","",K15)</f>
         <v>46390</v>
       </c>
       <c r="C15" s="38" t="str">
@@ -10874,7 +10884,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F15" s="42" t="n">
         <f aca="false">IF(B15="","",IF(E15="לא",0,הגדרות!$C$22))</f>
@@ -10887,17 +10897,17 @@
       <c r="H15" s="44"/>
       <c r="I15" s="45"/>
       <c r="K15" s="27" t="n">
-        <f aca="false">IF(B15="","",B15+MIN(MOD(הגדרות!$D$18-WEEKDAY(B15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B15)-1,7)+1))</f>
-        <v>46394</v>
+        <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
+        <v>46390</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="38" t="n">
-        <f aca="false">IF(B16="","",ROW()-14)</f>
+        <f aca="false">IF(B16="","",COUNT($B$15:B16))</f>
         <v>2</v>
       </c>
       <c r="B16" s="39" t="n">
-        <f aca="false">IF(K15="","",IF(K15&gt;$K$2,"",K15))</f>
+        <f aca="false">IF(K16="","",K16)</f>
         <v>46394</v>
       </c>
       <c r="C16" s="38" t="str">
@@ -10909,7 +10919,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F16" s="42" t="n">
         <f aca="false">IF(B16="","",IF(E16="לא",0,הגדרות!$C$22))</f>
@@ -10922,17 +10932,17 @@
       <c r="H16" s="44"/>
       <c r="I16" s="45"/>
       <c r="K16" s="27" t="n">
-        <f aca="false">IF(B16="","",B16+MIN(MOD(הגדרות!$D$18-WEEKDAY(B16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B16)-1,7)+1))</f>
-        <v>46397</v>
+        <f aca="false">IF(K15="","",IF(K15+MIN(MOD(הגדרות!$D$18-WEEKDAY(K15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K15)-1,7)+1)&gt;$K$2,"",K15+MIN(MOD(הגדרות!$D$18-WEEKDAY(K15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K15)-1,7)+1)))</f>
+        <v>46394</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="38" t="n">
-        <f aca="false">IF(B17="","",ROW()-14)</f>
+        <f aca="false">IF(B17="","",COUNT($B$15:B17))</f>
         <v>3</v>
       </c>
       <c r="B17" s="39" t="n">
-        <f aca="false">IF(K16="","",IF(K16&gt;$K$2,"",K16))</f>
+        <f aca="false">IF(K17="","",K17)</f>
         <v>46397</v>
       </c>
       <c r="C17" s="38" t="str">
@@ -10944,7 +10954,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F17" s="42" t="n">
         <f aca="false">IF(B17="","",IF(E17="לא",0,הגדרות!$C$22))</f>
@@ -10957,17 +10967,17 @@
       <c r="H17" s="44"/>
       <c r="I17" s="45"/>
       <c r="K17" s="27" t="n">
-        <f aca="false">IF(B17="","",B17+MIN(MOD(הגדרות!$D$18-WEEKDAY(B17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B17)-1,7)+1))</f>
-        <v>46401</v>
+        <f aca="false">IF(K16="","",IF(K16+MIN(MOD(הגדרות!$D$18-WEEKDAY(K16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K16)-1,7)+1)&gt;$K$2,"",K16+MIN(MOD(הגדרות!$D$18-WEEKDAY(K16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K16)-1,7)+1)))</f>
+        <v>46397</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="38" t="n">
-        <f aca="false">IF(B18="","",ROW()-14)</f>
+        <f aca="false">IF(B18="","",COUNT($B$15:B18))</f>
         <v>4</v>
       </c>
       <c r="B18" s="39" t="n">
-        <f aca="false">IF(K17="","",IF(K17&gt;$K$2,"",K17))</f>
+        <f aca="false">IF(K18="","",K18)</f>
         <v>46401</v>
       </c>
       <c r="C18" s="38" t="str">
@@ -10979,7 +10989,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F18" s="42" t="n">
         <f aca="false">IF(B18="","",IF(E18="לא",0,הגדרות!$C$22))</f>
@@ -10992,17 +11002,17 @@
       <c r="H18" s="44"/>
       <c r="I18" s="45"/>
       <c r="K18" s="27" t="n">
-        <f aca="false">IF(B18="","",B18+MIN(MOD(הגדרות!$D$18-WEEKDAY(B18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B18)-1,7)+1))</f>
-        <v>46404</v>
+        <f aca="false">IF(K17="","",IF(K17+MIN(MOD(הגדרות!$D$18-WEEKDAY(K17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K17)-1,7)+1)&gt;$K$2,"",K17+MIN(MOD(הגדרות!$D$18-WEEKDAY(K17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K17)-1,7)+1)))</f>
+        <v>46401</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="38" t="n">
-        <f aca="false">IF(B19="","",ROW()-14)</f>
+        <f aca="false">IF(B19="","",COUNT($B$15:B19))</f>
         <v>5</v>
       </c>
       <c r="B19" s="39" t="n">
-        <f aca="false">IF(K18="","",IF(K18&gt;$K$2,"",K18))</f>
+        <f aca="false">IF(K19="","",K19)</f>
         <v>46404</v>
       </c>
       <c r="C19" s="38" t="str">
@@ -11014,7 +11024,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F19" s="42" t="n">
         <f aca="false">IF(B19="","",IF(E19="לא",0,הגדרות!$C$22))</f>
@@ -11027,17 +11037,17 @@
       <c r="H19" s="44"/>
       <c r="I19" s="45"/>
       <c r="K19" s="27" t="n">
-        <f aca="false">IF(B19="","",B19+MIN(MOD(הגדרות!$D$18-WEEKDAY(B19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B19)-1,7)+1))</f>
-        <v>46408</v>
+        <f aca="false">IF(K18="","",IF(K18+MIN(MOD(הגדרות!$D$18-WEEKDAY(K18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K18)-1,7)+1)&gt;$K$2,"",K18+MIN(MOD(הגדרות!$D$18-WEEKDAY(K18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K18)-1,7)+1)))</f>
+        <v>46404</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="38" t="n">
-        <f aca="false">IF(B20="","",ROW()-14)</f>
+        <f aca="false">IF(B20="","",COUNT($B$15:B20))</f>
         <v>6</v>
       </c>
       <c r="B20" s="39" t="n">
-        <f aca="false">IF(K19="","",IF(K19&gt;$K$2,"",K19))</f>
+        <f aca="false">IF(K20="","",K20)</f>
         <v>46408</v>
       </c>
       <c r="C20" s="38" t="str">
@@ -11049,7 +11059,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F20" s="42" t="n">
         <f aca="false">IF(B20="","",IF(E20="לא",0,הגדרות!$C$22))</f>
@@ -11062,17 +11072,17 @@
       <c r="H20" s="44"/>
       <c r="I20" s="45"/>
       <c r="K20" s="27" t="n">
-        <f aca="false">IF(B20="","",B20+MIN(MOD(הגדרות!$D$18-WEEKDAY(B20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B20)-1,7)+1))</f>
-        <v>46411</v>
+        <f aca="false">IF(K19="","",IF(K19+MIN(MOD(הגדרות!$D$18-WEEKDAY(K19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K19)-1,7)+1)&gt;$K$2,"",K19+MIN(MOD(הגדרות!$D$18-WEEKDAY(K19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K19)-1,7)+1)))</f>
+        <v>46408</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="38" t="n">
-        <f aca="false">IF(B21="","",ROW()-14)</f>
+        <f aca="false">IF(B21="","",COUNT($B$15:B21))</f>
         <v>7</v>
       </c>
       <c r="B21" s="39" t="n">
-        <f aca="false">IF(K20="","",IF(K20&gt;$K$2,"",K20))</f>
+        <f aca="false">IF(K21="","",K21)</f>
         <v>46411</v>
       </c>
       <c r="C21" s="38" t="str">
@@ -11084,7 +11094,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F21" s="42" t="n">
         <f aca="false">IF(B21="","",IF(E21="לא",0,הגדרות!$C$22))</f>
@@ -11097,17 +11107,17 @@
       <c r="H21" s="44"/>
       <c r="I21" s="45"/>
       <c r="K21" s="27" t="n">
-        <f aca="false">IF(B21="","",B21+MIN(MOD(הגדרות!$D$18-WEEKDAY(B21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B21)-1,7)+1))</f>
-        <v>46415</v>
+        <f aca="false">IF(K20="","",IF(K20+MIN(MOD(הגדרות!$D$18-WEEKDAY(K20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K20)-1,7)+1)&gt;$K$2,"",K20+MIN(MOD(הגדרות!$D$18-WEEKDAY(K20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K20)-1,7)+1)))</f>
+        <v>46411</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="38" t="n">
-        <f aca="false">IF(B22="","",ROW()-14)</f>
+        <f aca="false">IF(B22="","",COUNT($B$15:B22))</f>
         <v>8</v>
       </c>
       <c r="B22" s="39" t="n">
-        <f aca="false">IF(K21="","",IF(K21&gt;$K$2,"",K21))</f>
+        <f aca="false">IF(K22="","",K22)</f>
         <v>46415</v>
       </c>
       <c r="C22" s="38" t="str">
@@ -11119,7 +11129,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F22" s="42" t="n">
         <f aca="false">IF(B22="","",IF(E22="לא",0,הגדרות!$C$22))</f>
@@ -11132,17 +11142,17 @@
       <c r="H22" s="44"/>
       <c r="I22" s="45"/>
       <c r="K22" s="27" t="n">
-        <f aca="false">IF(B22="","",B22+MIN(MOD(הגדרות!$D$18-WEEKDAY(B22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B22)-1,7)+1))</f>
-        <v>46418</v>
+        <f aca="false">IF(K21="","",IF(K21+MIN(MOD(הגדרות!$D$18-WEEKDAY(K21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K21)-1,7)+1)&gt;$K$2,"",K21+MIN(MOD(הגדרות!$D$18-WEEKDAY(K21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K21)-1,7)+1)))</f>
+        <v>46415</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="38" t="n">
-        <f aca="false">IF(B23="","",ROW()-14)</f>
+        <f aca="false">IF(B23="","",COUNT($B$15:B23))</f>
         <v>9</v>
       </c>
       <c r="B23" s="39" t="n">
-        <f aca="false">IF(K22="","",IF(K22&gt;$K$2,"",K22))</f>
+        <f aca="false">IF(K23="","",K23)</f>
         <v>46418</v>
       </c>
       <c r="C23" s="38" t="str">
@@ -11154,7 +11164,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F23" s="42" t="n">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
@@ -11167,17 +11177,17 @@
       <c r="H23" s="44"/>
       <c r="I23" s="45"/>
       <c r="K23" s="27" t="n">
-        <f aca="false">IF(B23="","",B23+MIN(MOD(הגדרות!$D$18-WEEKDAY(B23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B23)-1,7)+1))</f>
-        <v>46422</v>
+        <f aca="false">IF(K22="","",IF(K22+MIN(MOD(הגדרות!$D$18-WEEKDAY(K22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K22)-1,7)+1)&gt;$K$2,"",K22+MIN(MOD(הגדרות!$D$18-WEEKDAY(K22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K22)-1,7)+1)))</f>
+        <v>46418</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="38" t="str">
-        <f aca="false">IF(B24="","",ROW()-14)</f>
+        <f aca="false">IF(B24="","",COUNT($B$15:B24))</f>
         <v/>
       </c>
       <c r="B24" s="39" t="str">
-        <f aca="false">IF(K23="","",IF(K23&gt;$K$2,"",K23))</f>
+        <f aca="false">IF(K24="","",K24)</f>
         <v/>
       </c>
       <c r="C24" s="38" t="str">
@@ -11189,7 +11199,7 @@
         <v/>
       </c>
       <c r="E24" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F24" s="42" t="str">
         <f aca="false">IF(B24="","",IF(E24="לא",0,הגדרות!$C$22))</f>
@@ -11202,7 +11212,7 @@
       <c r="H24" s="44"/>
       <c r="I24" s="45"/>
       <c r="K24" s="27" t="str">
-        <f aca="false">IF(B24="","",B24+MIN(MOD(הגדרות!$D$18-WEEKDAY(B24)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B24)-1,7)+1))</f>
+        <f aca="false">IF(K23="","",IF(K23+MIN(MOD(הגדרות!$D$18-WEEKDAY(K23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K23)-1,7)+1)&gt;$K$2,"",K23+MIN(MOD(הגדרות!$D$18-WEEKDAY(K23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K23)-1,7)+1)))</f>
         <v/>
       </c>
     </row>
@@ -11211,16 +11221,16 @@
         <f aca="false">COUNT($B$15:$B$24)+1</f>
         <v>10</v>
       </c>
-      <c r="B25" s="46"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="38" t="str">
         <f aca="false">IF(B25="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B25)))</f>
         <v/>
       </c>
       <c r="D25" s="40" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F25" s="42" t="n">
         <f aca="false">IF(E25="לא",0,הגדרות!$C$23)</f>
@@ -11235,36 +11245,36 @@
       <c r="K25" s="27"/>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="B26" s="47"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="48" t="n">
+      <c r="A26" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" s="46"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="47" t="n">
         <f aca="false">SUM(F15:F25)</f>
         <v>32.5</v>
       </c>
-      <c r="G26" s="49" t="n">
+      <c r="G26" s="48" t="n">
         <f aca="false">SUM(G15:G25)</f>
         <v>1625</v>
       </c>
-      <c r="H26" s="47"/>
-      <c r="I26" s="49" t="n">
+      <c r="H26" s="46"/>
+      <c r="I26" s="48" t="n">
         <f aca="false">SUM(I15:I25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
+      <c r="A28" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="49"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="49"/>
       <c r="F28" s="40" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G28" s="40"/>
       <c r="H28" s="40"/>
@@ -11274,14 +11284,14 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="51" t="str">
+      <c r="A29" s="50" t="str">
         <f aca="false">"• "&amp;הגדרות!$C$17&amp;": ימי "&amp;הגדרות!$C$18&amp;" ו"&amp;הגדרות!$C$19&amp;", "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00")&amp;" ("&amp;הגדרות!$C$22&amp;" שעות ליום), וישיבת צוות חודשית ("&amp;הגדרות!$C$23&amp;" ש׳)."</f>
         <v>• הדרכת שיקום: ימי ראשון וחמישי, 09:00–12:30 (3.5 שעות ליום), וישיבת צוות חודשית (1 ש׳).</v>
       </c>
-      <c r="B29" s="51"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
       <c r="F29" s="40" t="str">
         <f aca="false">"הדרכת שיקום ("&amp;TEXT(F26,"0.0")&amp;" שעות × "&amp;הגדרות!$C$24&amp;" ₪)"</f>
         <v>הדרכת שיקום (32.5 שעות × 50 ₪)</v>
@@ -11294,16 +11304,16 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="51" t="str">
+      <c r="A30" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$28="","","• "&amp;הגדרות!$C$28)</f>
         <v>• התעריף השעתי אינו כולל מע״מ. מע״מ יתווסף כחוק.</v>
       </c>
-      <c r="B30" s="51"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
       <c r="F30" s="40" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="40"/>
@@ -11313,33 +11323,33 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="51" t="str">
+      <c r="A31" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$29="","","• "&amp;הגדרות!$C$29)</f>
         <v>• פרויקטים פרטיים מתומחרים בנפרד, לפי הזמנת החווה.</v>
       </c>
-      <c r="B31" s="51"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="52" t="s">
-        <v>89</v>
-      </c>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="53" t="n">
+      <c r="B31" s="50"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="52" t="n">
         <f aca="false">I29+I30</f>
         <v>1625</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="51" t="str">
+      <c r="A32" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$30="","","• "&amp;הגדרות!$C$30)</f>
         <v/>
       </c>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
       <c r="F32" s="40" t="str">
         <f aca="false">"מע״מ "&amp;ROUND(הגדרות!$C$25*100,1)&amp;"%"</f>
         <v>מע״מ 18%</v>
@@ -11352,30 +11362,30 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F33" s="54" t="s">
-        <v>90</v>
-      </c>
-      <c r="G33" s="54"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="55" t="n">
+      <c r="F33" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="54" t="n">
         <f aca="false">I31+I32</f>
         <v>1917.5</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="56" t="str">
+      <c r="A36" s="55" t="str">
         <f aca="false">"בברכה, "&amp;הגדרות!$C$6</f>
         <v>בברכה, (למילוי)</v>
       </c>
-      <c r="B36" s="56"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="F36" s="56" t="s">
-        <v>91</v>
-      </c>
-      <c r="G36" s="56"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="56"/>
+      <c r="B36" s="55"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="F36" s="55" t="s">
+        <v>93</v>
+      </c>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="44">
@@ -11473,7 +11483,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -11509,13 +11519,13 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
       <c r="F4" s="29" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
@@ -11523,7 +11533,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
@@ -11532,7 +11542,7 @@
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="31" t="str">
@@ -11543,7 +11553,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="31" t="str">
@@ -11552,7 +11562,7 @@
       </c>
       <c r="D6" s="31"/>
       <c r="F6" s="30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="31" t="str">
@@ -11563,7 +11573,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="31" t="str">
@@ -11572,7 +11582,7 @@
       </c>
       <c r="D7" s="31"/>
       <c r="F7" s="30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="31" t="str">
@@ -11583,7 +11593,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="31" t="str">
@@ -11594,7 +11604,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="str">
@@ -11606,7 +11616,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
@@ -11615,7 +11625,7 @@
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
@@ -11625,7 +11635,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
@@ -11634,7 +11644,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31" t="str">
@@ -11645,7 +11655,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -11654,46 +11664,46 @@
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="35" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="38" t="n">
-        <f aca="false">IF(B15="","",ROW()-14)</f>
+        <f aca="false">IF(B15="","",COUNT($B$15:B15))</f>
         <v>1</v>
       </c>
       <c r="B15" s="39" t="n">
-        <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
+        <f aca="false">IF(K15="","",K15)</f>
         <v>46422</v>
       </c>
       <c r="C15" s="38" t="str">
@@ -11705,7 +11715,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F15" s="42" t="n">
         <f aca="false">IF(B15="","",IF(E15="לא",0,הגדרות!$C$22))</f>
@@ -11718,17 +11728,17 @@
       <c r="H15" s="44"/>
       <c r="I15" s="45"/>
       <c r="K15" s="27" t="n">
-        <f aca="false">IF(B15="","",B15+MIN(MOD(הגדרות!$D$18-WEEKDAY(B15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B15)-1,7)+1))</f>
-        <v>46425</v>
+        <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
+        <v>46422</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="38" t="n">
-        <f aca="false">IF(B16="","",ROW()-14)</f>
+        <f aca="false">IF(B16="","",COUNT($B$15:B16))</f>
         <v>2</v>
       </c>
       <c r="B16" s="39" t="n">
-        <f aca="false">IF(K15="","",IF(K15&gt;$K$2,"",K15))</f>
+        <f aca="false">IF(K16="","",K16)</f>
         <v>46425</v>
       </c>
       <c r="C16" s="38" t="str">
@@ -11740,7 +11750,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F16" s="42" t="n">
         <f aca="false">IF(B16="","",IF(E16="לא",0,הגדרות!$C$22))</f>
@@ -11753,17 +11763,17 @@
       <c r="H16" s="44"/>
       <c r="I16" s="45"/>
       <c r="K16" s="27" t="n">
-        <f aca="false">IF(B16="","",B16+MIN(MOD(הגדרות!$D$18-WEEKDAY(B16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B16)-1,7)+1))</f>
-        <v>46429</v>
+        <f aca="false">IF(K15="","",IF(K15+MIN(MOD(הגדרות!$D$18-WEEKDAY(K15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K15)-1,7)+1)&gt;$K$2,"",K15+MIN(MOD(הגדרות!$D$18-WEEKDAY(K15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K15)-1,7)+1)))</f>
+        <v>46425</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="38" t="n">
-        <f aca="false">IF(B17="","",ROW()-14)</f>
+        <f aca="false">IF(B17="","",COUNT($B$15:B17))</f>
         <v>3</v>
       </c>
       <c r="B17" s="39" t="n">
-        <f aca="false">IF(K16="","",IF(K16&gt;$K$2,"",K16))</f>
+        <f aca="false">IF(K17="","",K17)</f>
         <v>46429</v>
       </c>
       <c r="C17" s="38" t="str">
@@ -11775,7 +11785,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F17" s="42" t="n">
         <f aca="false">IF(B17="","",IF(E17="לא",0,הגדרות!$C$22))</f>
@@ -11788,17 +11798,17 @@
       <c r="H17" s="44"/>
       <c r="I17" s="45"/>
       <c r="K17" s="27" t="n">
-        <f aca="false">IF(B17="","",B17+MIN(MOD(הגדרות!$D$18-WEEKDAY(B17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B17)-1,7)+1))</f>
-        <v>46432</v>
+        <f aca="false">IF(K16="","",IF(K16+MIN(MOD(הגדרות!$D$18-WEEKDAY(K16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K16)-1,7)+1)&gt;$K$2,"",K16+MIN(MOD(הגדרות!$D$18-WEEKDAY(K16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K16)-1,7)+1)))</f>
+        <v>46429</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="38" t="n">
-        <f aca="false">IF(B18="","",ROW()-14)</f>
+        <f aca="false">IF(B18="","",COUNT($B$15:B18))</f>
         <v>4</v>
       </c>
       <c r="B18" s="39" t="n">
-        <f aca="false">IF(K17="","",IF(K17&gt;$K$2,"",K17))</f>
+        <f aca="false">IF(K18="","",K18)</f>
         <v>46432</v>
       </c>
       <c r="C18" s="38" t="str">
@@ -11810,7 +11820,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F18" s="42" t="n">
         <f aca="false">IF(B18="","",IF(E18="לא",0,הגדרות!$C$22))</f>
@@ -11823,17 +11833,17 @@
       <c r="H18" s="44"/>
       <c r="I18" s="45"/>
       <c r="K18" s="27" t="n">
-        <f aca="false">IF(B18="","",B18+MIN(MOD(הגדרות!$D$18-WEEKDAY(B18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B18)-1,7)+1))</f>
-        <v>46436</v>
+        <f aca="false">IF(K17="","",IF(K17+MIN(MOD(הגדרות!$D$18-WEEKDAY(K17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K17)-1,7)+1)&gt;$K$2,"",K17+MIN(MOD(הגדרות!$D$18-WEEKDAY(K17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K17)-1,7)+1)))</f>
+        <v>46432</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="38" t="n">
-        <f aca="false">IF(B19="","",ROW()-14)</f>
+        <f aca="false">IF(B19="","",COUNT($B$15:B19))</f>
         <v>5</v>
       </c>
       <c r="B19" s="39" t="n">
-        <f aca="false">IF(K18="","",IF(K18&gt;$K$2,"",K18))</f>
+        <f aca="false">IF(K19="","",K19)</f>
         <v>46436</v>
       </c>
       <c r="C19" s="38" t="str">
@@ -11845,7 +11855,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F19" s="42" t="n">
         <f aca="false">IF(B19="","",IF(E19="לא",0,הגדרות!$C$22))</f>
@@ -11858,17 +11868,17 @@
       <c r="H19" s="44"/>
       <c r="I19" s="45"/>
       <c r="K19" s="27" t="n">
-        <f aca="false">IF(B19="","",B19+MIN(MOD(הגדרות!$D$18-WEEKDAY(B19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B19)-1,7)+1))</f>
-        <v>46439</v>
+        <f aca="false">IF(K18="","",IF(K18+MIN(MOD(הגדרות!$D$18-WEEKDAY(K18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K18)-1,7)+1)&gt;$K$2,"",K18+MIN(MOD(הגדרות!$D$18-WEEKDAY(K18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K18)-1,7)+1)))</f>
+        <v>46436</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="38" t="n">
-        <f aca="false">IF(B20="","",ROW()-14)</f>
+        <f aca="false">IF(B20="","",COUNT($B$15:B20))</f>
         <v>6</v>
       </c>
       <c r="B20" s="39" t="n">
-        <f aca="false">IF(K19="","",IF(K19&gt;$K$2,"",K19))</f>
+        <f aca="false">IF(K20="","",K20)</f>
         <v>46439</v>
       </c>
       <c r="C20" s="38" t="str">
@@ -11880,7 +11890,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F20" s="42" t="n">
         <f aca="false">IF(B20="","",IF(E20="לא",0,הגדרות!$C$22))</f>
@@ -11893,17 +11903,17 @@
       <c r="H20" s="44"/>
       <c r="I20" s="45"/>
       <c r="K20" s="27" t="n">
-        <f aca="false">IF(B20="","",B20+MIN(MOD(הגדרות!$D$18-WEEKDAY(B20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B20)-1,7)+1))</f>
-        <v>46443</v>
+        <f aca="false">IF(K19="","",IF(K19+MIN(MOD(הגדרות!$D$18-WEEKDAY(K19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K19)-1,7)+1)&gt;$K$2,"",K19+MIN(MOD(הגדרות!$D$18-WEEKDAY(K19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K19)-1,7)+1)))</f>
+        <v>46439</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="38" t="n">
-        <f aca="false">IF(B21="","",ROW()-14)</f>
+        <f aca="false">IF(B21="","",COUNT($B$15:B21))</f>
         <v>7</v>
       </c>
       <c r="B21" s="39" t="n">
-        <f aca="false">IF(K20="","",IF(K20&gt;$K$2,"",K20))</f>
+        <f aca="false">IF(K21="","",K21)</f>
         <v>46443</v>
       </c>
       <c r="C21" s="38" t="str">
@@ -11915,7 +11925,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F21" s="42" t="n">
         <f aca="false">IF(B21="","",IF(E21="לא",0,הגדרות!$C$22))</f>
@@ -11928,17 +11938,17 @@
       <c r="H21" s="44"/>
       <c r="I21" s="45"/>
       <c r="K21" s="27" t="n">
-        <f aca="false">IF(B21="","",B21+MIN(MOD(הגדרות!$D$18-WEEKDAY(B21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B21)-1,7)+1))</f>
-        <v>46446</v>
+        <f aca="false">IF(K20="","",IF(K20+MIN(MOD(הגדרות!$D$18-WEEKDAY(K20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K20)-1,7)+1)&gt;$K$2,"",K20+MIN(MOD(הגדרות!$D$18-WEEKDAY(K20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K20)-1,7)+1)))</f>
+        <v>46443</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="38" t="n">
-        <f aca="false">IF(B22="","",ROW()-14)</f>
+        <f aca="false">IF(B22="","",COUNT($B$15:B22))</f>
         <v>8</v>
       </c>
       <c r="B22" s="39" t="n">
-        <f aca="false">IF(K21="","",IF(K21&gt;$K$2,"",K21))</f>
+        <f aca="false">IF(K22="","",K22)</f>
         <v>46446</v>
       </c>
       <c r="C22" s="38" t="str">
@@ -11950,7 +11960,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F22" s="42" t="n">
         <f aca="false">IF(B22="","",IF(E22="לא",0,הגדרות!$C$22))</f>
@@ -11963,17 +11973,17 @@
       <c r="H22" s="44"/>
       <c r="I22" s="45"/>
       <c r="K22" s="27" t="n">
-        <f aca="false">IF(B22="","",B22+MIN(MOD(הגדרות!$D$18-WEEKDAY(B22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B22)-1,7)+1))</f>
-        <v>46450</v>
+        <f aca="false">IF(K21="","",IF(K21+MIN(MOD(הגדרות!$D$18-WEEKDAY(K21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K21)-1,7)+1)&gt;$K$2,"",K21+MIN(MOD(הגדרות!$D$18-WEEKDAY(K21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K21)-1,7)+1)))</f>
+        <v>46446</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="38" t="str">
-        <f aca="false">IF(B23="","",ROW()-14)</f>
+        <f aca="false">IF(B23="","",COUNT($B$15:B23))</f>
         <v/>
       </c>
       <c r="B23" s="39" t="str">
-        <f aca="false">IF(K22="","",IF(K22&gt;$K$2,"",K22))</f>
+        <f aca="false">IF(K23="","",K23)</f>
         <v/>
       </c>
       <c r="C23" s="38" t="str">
@@ -11985,7 +11995,7 @@
         <v/>
       </c>
       <c r="E23" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F23" s="42" t="str">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
@@ -11998,17 +12008,17 @@
       <c r="H23" s="44"/>
       <c r="I23" s="45"/>
       <c r="K23" s="27" t="str">
-        <f aca="false">IF(B23="","",B23+MIN(MOD(הגדרות!$D$18-WEEKDAY(B23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B23)-1,7)+1))</f>
+        <f aca="false">IF(K22="","",IF(K22+MIN(MOD(הגדרות!$D$18-WEEKDAY(K22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K22)-1,7)+1)&gt;$K$2,"",K22+MIN(MOD(הגדרות!$D$18-WEEKDAY(K22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K22)-1,7)+1)))</f>
         <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="38" t="str">
-        <f aca="false">IF(B24="","",ROW()-14)</f>
+        <f aca="false">IF(B24="","",COUNT($B$15:B24))</f>
         <v/>
       </c>
       <c r="B24" s="39" t="str">
-        <f aca="false">IF(K23="","",IF(K23&gt;$K$2,"",K23))</f>
+        <f aca="false">IF(K24="","",K24)</f>
         <v/>
       </c>
       <c r="C24" s="38" t="str">
@@ -12020,7 +12030,7 @@
         <v/>
       </c>
       <c r="E24" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F24" s="42" t="str">
         <f aca="false">IF(B24="","",IF(E24="לא",0,הגדרות!$C$22))</f>
@@ -12033,7 +12043,7 @@
       <c r="H24" s="44"/>
       <c r="I24" s="45"/>
       <c r="K24" s="27" t="str">
-        <f aca="false">IF(B24="","",B24+MIN(MOD(הגדרות!$D$18-WEEKDAY(B24)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B24)-1,7)+1))</f>
+        <f aca="false">IF(K23="","",IF(K23+MIN(MOD(הגדרות!$D$18-WEEKDAY(K23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K23)-1,7)+1)&gt;$K$2,"",K23+MIN(MOD(הגדרות!$D$18-WEEKDAY(K23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K23)-1,7)+1)))</f>
         <v/>
       </c>
     </row>
@@ -12042,16 +12052,16 @@
         <f aca="false">COUNT($B$15:$B$24)+1</f>
         <v>9</v>
       </c>
-      <c r="B25" s="46"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="38" t="str">
         <f aca="false">IF(B25="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B25)))</f>
         <v/>
       </c>
       <c r="D25" s="40" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F25" s="42" t="n">
         <f aca="false">IF(E25="לא",0,הגדרות!$C$23)</f>
@@ -12066,36 +12076,36 @@
       <c r="K25" s="27"/>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="B26" s="47"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="48" t="n">
+      <c r="A26" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" s="46"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="47" t="n">
         <f aca="false">SUM(F15:F25)</f>
         <v>29</v>
       </c>
-      <c r="G26" s="49" t="n">
+      <c r="G26" s="48" t="n">
         <f aca="false">SUM(G15:G25)</f>
         <v>1450</v>
       </c>
-      <c r="H26" s="47"/>
-      <c r="I26" s="49" t="n">
+      <c r="H26" s="46"/>
+      <c r="I26" s="48" t="n">
         <f aca="false">SUM(I15:I25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
+      <c r="A28" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="49"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="49"/>
       <c r="F28" s="40" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G28" s="40"/>
       <c r="H28" s="40"/>
@@ -12105,14 +12115,14 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="51" t="str">
+      <c r="A29" s="50" t="str">
         <f aca="false">"• "&amp;הגדרות!$C$17&amp;": ימי "&amp;הגדרות!$C$18&amp;" ו"&amp;הגדרות!$C$19&amp;", "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00")&amp;" ("&amp;הגדרות!$C$22&amp;" שעות ליום), וישיבת צוות חודשית ("&amp;הגדרות!$C$23&amp;" ש׳)."</f>
         <v>• הדרכת שיקום: ימי ראשון וחמישי, 09:00–12:30 (3.5 שעות ליום), וישיבת צוות חודשית (1 ש׳).</v>
       </c>
-      <c r="B29" s="51"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
       <c r="F29" s="40" t="str">
         <f aca="false">"הדרכת שיקום ("&amp;TEXT(F26,"0.0")&amp;" שעות × "&amp;הגדרות!$C$24&amp;" ₪)"</f>
         <v>הדרכת שיקום (29.0 שעות × 50 ₪)</v>
@@ -12125,16 +12135,16 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="51" t="str">
+      <c r="A30" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$28="","","• "&amp;הגדרות!$C$28)</f>
         <v>• התעריף השעתי אינו כולל מע״מ. מע״מ יתווסף כחוק.</v>
       </c>
-      <c r="B30" s="51"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
       <c r="F30" s="40" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="40"/>
@@ -12144,33 +12154,33 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="51" t="str">
+      <c r="A31" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$29="","","• "&amp;הגדרות!$C$29)</f>
         <v>• פרויקטים פרטיים מתומחרים בנפרד, לפי הזמנת החווה.</v>
       </c>
-      <c r="B31" s="51"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="52" t="s">
-        <v>89</v>
-      </c>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="53" t="n">
+      <c r="B31" s="50"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="52" t="n">
         <f aca="false">I29+I30</f>
         <v>1450</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="51" t="str">
+      <c r="A32" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$30="","","• "&amp;הגדרות!$C$30)</f>
         <v/>
       </c>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
       <c r="F32" s="40" t="str">
         <f aca="false">"מע״מ "&amp;ROUND(הגדרות!$C$25*100,1)&amp;"%"</f>
         <v>מע״מ 18%</v>
@@ -12183,30 +12193,30 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F33" s="54" t="s">
-        <v>90</v>
-      </c>
-      <c r="G33" s="54"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="55" t="n">
+      <c r="F33" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="54" t="n">
         <f aca="false">I31+I32</f>
         <v>1711</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="56" t="str">
+      <c r="A36" s="55" t="str">
         <f aca="false">"בברכה, "&amp;הגדרות!$C$6</f>
         <v>בברכה, (למילוי)</v>
       </c>
-      <c r="B36" s="56"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="F36" s="56" t="s">
-        <v>91</v>
-      </c>
-      <c r="G36" s="56"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="56"/>
+      <c r="B36" s="55"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="F36" s="55" t="s">
+        <v>93</v>
+      </c>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="44">
@@ -12304,7 +12314,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -12340,13 +12350,13 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
       <c r="F4" s="29" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
@@ -12354,7 +12364,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
@@ -12363,7 +12373,7 @@
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="31" t="str">
@@ -12374,7 +12384,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="31" t="str">
@@ -12383,7 +12393,7 @@
       </c>
       <c r="D6" s="31"/>
       <c r="F6" s="30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="31" t="str">
@@ -12394,7 +12404,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="31" t="str">
@@ -12403,7 +12413,7 @@
       </c>
       <c r="D7" s="31"/>
       <c r="F7" s="30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="31" t="str">
@@ -12414,7 +12424,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="31" t="str">
@@ -12425,7 +12435,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="str">
@@ -12437,7 +12447,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
@@ -12446,7 +12456,7 @@
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
@@ -12456,7 +12466,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
@@ -12465,7 +12475,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31" t="str">
@@ -12476,7 +12486,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -12485,46 +12495,46 @@
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="35" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="38" t="n">
-        <f aca="false">IF(B15="","",ROW()-14)</f>
+        <f aca="false">IF(B15="","",COUNT($B$15:B15))</f>
         <v>1</v>
       </c>
       <c r="B15" s="39" t="n">
-        <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
+        <f aca="false">IF(K15="","",K15)</f>
         <v>46450</v>
       </c>
       <c r="C15" s="38" t="str">
@@ -12536,7 +12546,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F15" s="42" t="n">
         <f aca="false">IF(B15="","",IF(E15="לא",0,הגדרות!$C$22))</f>
@@ -12549,17 +12559,17 @@
       <c r="H15" s="44"/>
       <c r="I15" s="45"/>
       <c r="K15" s="27" t="n">
-        <f aca="false">IF(B15="","",B15+MIN(MOD(הגדרות!$D$18-WEEKDAY(B15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B15)-1,7)+1))</f>
-        <v>46453</v>
+        <f aca="false">$K$1+MIN(MOD(הגדרות!$D$18-WEEKDAY($K$1),7),MOD(הגדרות!$D$19-WEEKDAY($K$1),7))</f>
+        <v>46450</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="38" t="n">
-        <f aca="false">IF(B16="","",ROW()-14)</f>
+        <f aca="false">IF(B16="","",COUNT($B$15:B16))</f>
         <v>2</v>
       </c>
       <c r="B16" s="39" t="n">
-        <f aca="false">IF(K15="","",IF(K15&gt;$K$2,"",K15))</f>
+        <f aca="false">IF(K16="","",K16)</f>
         <v>46453</v>
       </c>
       <c r="C16" s="38" t="str">
@@ -12571,7 +12581,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F16" s="42" t="n">
         <f aca="false">IF(B16="","",IF(E16="לא",0,הגדרות!$C$22))</f>
@@ -12584,17 +12594,17 @@
       <c r="H16" s="44"/>
       <c r="I16" s="45"/>
       <c r="K16" s="27" t="n">
-        <f aca="false">IF(B16="","",B16+MIN(MOD(הגדרות!$D$18-WEEKDAY(B16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B16)-1,7)+1))</f>
-        <v>46457</v>
+        <f aca="false">IF(K15="","",IF(K15+MIN(MOD(הגדרות!$D$18-WEEKDAY(K15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K15)-1,7)+1)&gt;$K$2,"",K15+MIN(MOD(הגדרות!$D$18-WEEKDAY(K15)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K15)-1,7)+1)))</f>
+        <v>46453</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="38" t="n">
-        <f aca="false">IF(B17="","",ROW()-14)</f>
+        <f aca="false">IF(B17="","",COUNT($B$15:B17))</f>
         <v>3</v>
       </c>
       <c r="B17" s="39" t="n">
-        <f aca="false">IF(K16="","",IF(K16&gt;$K$2,"",K16))</f>
+        <f aca="false">IF(K17="","",K17)</f>
         <v>46457</v>
       </c>
       <c r="C17" s="38" t="str">
@@ -12606,7 +12616,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F17" s="42" t="n">
         <f aca="false">IF(B17="","",IF(E17="לא",0,הגדרות!$C$22))</f>
@@ -12619,17 +12629,17 @@
       <c r="H17" s="44"/>
       <c r="I17" s="45"/>
       <c r="K17" s="27" t="n">
-        <f aca="false">IF(B17="","",B17+MIN(MOD(הגדרות!$D$18-WEEKDAY(B17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B17)-1,7)+1))</f>
-        <v>46460</v>
+        <f aca="false">IF(K16="","",IF(K16+MIN(MOD(הגדרות!$D$18-WEEKDAY(K16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K16)-1,7)+1)&gt;$K$2,"",K16+MIN(MOD(הגדרות!$D$18-WEEKDAY(K16)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K16)-1,7)+1)))</f>
+        <v>46457</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="38" t="n">
-        <f aca="false">IF(B18="","",ROW()-14)</f>
+        <f aca="false">IF(B18="","",COUNT($B$15:B18))</f>
         <v>4</v>
       </c>
       <c r="B18" s="39" t="n">
-        <f aca="false">IF(K17="","",IF(K17&gt;$K$2,"",K17))</f>
+        <f aca="false">IF(K18="","",K18)</f>
         <v>46460</v>
       </c>
       <c r="C18" s="38" t="str">
@@ -12641,7 +12651,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F18" s="42" t="n">
         <f aca="false">IF(B18="","",IF(E18="לא",0,הגדרות!$C$22))</f>
@@ -12654,17 +12664,17 @@
       <c r="H18" s="44"/>
       <c r="I18" s="45"/>
       <c r="K18" s="27" t="n">
-        <f aca="false">IF(B18="","",B18+MIN(MOD(הגדרות!$D$18-WEEKDAY(B18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B18)-1,7)+1))</f>
-        <v>46464</v>
+        <f aca="false">IF(K17="","",IF(K17+MIN(MOD(הגדרות!$D$18-WEEKDAY(K17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K17)-1,7)+1)&gt;$K$2,"",K17+MIN(MOD(הגדרות!$D$18-WEEKDAY(K17)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K17)-1,7)+1)))</f>
+        <v>46460</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="38" t="n">
-        <f aca="false">IF(B19="","",ROW()-14)</f>
+        <f aca="false">IF(B19="","",COUNT($B$15:B19))</f>
         <v>5</v>
       </c>
       <c r="B19" s="39" t="n">
-        <f aca="false">IF(K18="","",IF(K18&gt;$K$2,"",K18))</f>
+        <f aca="false">IF(K19="","",K19)</f>
         <v>46464</v>
       </c>
       <c r="C19" s="38" t="str">
@@ -12676,7 +12686,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F19" s="42" t="n">
         <f aca="false">IF(B19="","",IF(E19="לא",0,הגדרות!$C$22))</f>
@@ -12689,17 +12699,17 @@
       <c r="H19" s="44"/>
       <c r="I19" s="45"/>
       <c r="K19" s="27" t="n">
-        <f aca="false">IF(B19="","",B19+MIN(MOD(הגדרות!$D$18-WEEKDAY(B19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B19)-1,7)+1))</f>
-        <v>46467</v>
+        <f aca="false">IF(K18="","",IF(K18+MIN(MOD(הגדרות!$D$18-WEEKDAY(K18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K18)-1,7)+1)&gt;$K$2,"",K18+MIN(MOD(הגדרות!$D$18-WEEKDAY(K18)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K18)-1,7)+1)))</f>
+        <v>46464</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="38" t="n">
-        <f aca="false">IF(B20="","",ROW()-14)</f>
+        <f aca="false">IF(B20="","",COUNT($B$15:B20))</f>
         <v>6</v>
       </c>
       <c r="B20" s="39" t="n">
-        <f aca="false">IF(K19="","",IF(K19&gt;$K$2,"",K19))</f>
+        <f aca="false">IF(K20="","",K20)</f>
         <v>46467</v>
       </c>
       <c r="C20" s="38" t="str">
@@ -12711,7 +12721,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F20" s="42" t="n">
         <f aca="false">IF(B20="","",IF(E20="לא",0,הגדרות!$C$22))</f>
@@ -12724,17 +12734,17 @@
       <c r="H20" s="44"/>
       <c r="I20" s="45"/>
       <c r="K20" s="27" t="n">
-        <f aca="false">IF(B20="","",B20+MIN(MOD(הגדרות!$D$18-WEEKDAY(B20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B20)-1,7)+1))</f>
-        <v>46471</v>
+        <f aca="false">IF(K19="","",IF(K19+MIN(MOD(הגדרות!$D$18-WEEKDAY(K19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K19)-1,7)+1)&gt;$K$2,"",K19+MIN(MOD(הגדרות!$D$18-WEEKDAY(K19)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K19)-1,7)+1)))</f>
+        <v>46467</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="38" t="n">
-        <f aca="false">IF(B21="","",ROW()-14)</f>
+        <f aca="false">IF(B21="","",COUNT($B$15:B21))</f>
         <v>7</v>
       </c>
       <c r="B21" s="39" t="n">
-        <f aca="false">IF(K20="","",IF(K20&gt;$K$2,"",K20))</f>
+        <f aca="false">IF(K21="","",K21)</f>
         <v>46471</v>
       </c>
       <c r="C21" s="38" t="str">
@@ -12746,7 +12756,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F21" s="42" t="n">
         <f aca="false">IF(B21="","",IF(E21="לא",0,הגדרות!$C$22))</f>
@@ -12759,17 +12769,17 @@
       <c r="H21" s="44"/>
       <c r="I21" s="45"/>
       <c r="K21" s="27" t="n">
-        <f aca="false">IF(B21="","",B21+MIN(MOD(הגדרות!$D$18-WEEKDAY(B21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B21)-1,7)+1))</f>
-        <v>46474</v>
+        <f aca="false">IF(K20="","",IF(K20+MIN(MOD(הגדרות!$D$18-WEEKDAY(K20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K20)-1,7)+1)&gt;$K$2,"",K20+MIN(MOD(הגדרות!$D$18-WEEKDAY(K20)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K20)-1,7)+1)))</f>
+        <v>46471</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="38" t="n">
-        <f aca="false">IF(B22="","",ROW()-14)</f>
+        <f aca="false">IF(B22="","",COUNT($B$15:B22))</f>
         <v>8</v>
       </c>
       <c r="B22" s="39" t="n">
-        <f aca="false">IF(K21="","",IF(K21&gt;$K$2,"",K21))</f>
+        <f aca="false">IF(K22="","",K22)</f>
         <v>46474</v>
       </c>
       <c r="C22" s="38" t="str">
@@ -12781,7 +12791,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F22" s="42" t="n">
         <f aca="false">IF(B22="","",IF(E22="לא",0,הגדרות!$C$22))</f>
@@ -12794,17 +12804,17 @@
       <c r="H22" s="44"/>
       <c r="I22" s="45"/>
       <c r="K22" s="27" t="n">
-        <f aca="false">IF(B22="","",B22+MIN(MOD(הגדרות!$D$18-WEEKDAY(B22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B22)-1,7)+1))</f>
-        <v>46478</v>
+        <f aca="false">IF(K21="","",IF(K21+MIN(MOD(הגדרות!$D$18-WEEKDAY(K21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K21)-1,7)+1)&gt;$K$2,"",K21+MIN(MOD(הגדרות!$D$18-WEEKDAY(K21)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K21)-1,7)+1)))</f>
+        <v>46474</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="38" t="str">
-        <f aca="false">IF(B23="","",ROW()-14)</f>
+        <f aca="false">IF(B23="","",COUNT($B$15:B23))</f>
         <v/>
       </c>
       <c r="B23" s="39" t="str">
-        <f aca="false">IF(K22="","",IF(K22&gt;$K$2,"",K22))</f>
+        <f aca="false">IF(K23="","",K23)</f>
         <v/>
       </c>
       <c r="C23" s="38" t="str">
@@ -12816,7 +12826,7 @@
         <v/>
       </c>
       <c r="E23" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F23" s="42" t="str">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
@@ -12829,17 +12839,17 @@
       <c r="H23" s="44"/>
       <c r="I23" s="45"/>
       <c r="K23" s="27" t="str">
-        <f aca="false">IF(B23="","",B23+MIN(MOD(הגדרות!$D$18-WEEKDAY(B23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B23)-1,7)+1))</f>
+        <f aca="false">IF(K22="","",IF(K22+MIN(MOD(הגדרות!$D$18-WEEKDAY(K22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K22)-1,7)+1)&gt;$K$2,"",K22+MIN(MOD(הגדרות!$D$18-WEEKDAY(K22)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K22)-1,7)+1)))</f>
         <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="38" t="str">
-        <f aca="false">IF(B24="","",ROW()-14)</f>
+        <f aca="false">IF(B24="","",COUNT($B$15:B24))</f>
         <v/>
       </c>
       <c r="B24" s="39" t="str">
-        <f aca="false">IF(K23="","",IF(K23&gt;$K$2,"",K23))</f>
+        <f aca="false">IF(K24="","",K24)</f>
         <v/>
       </c>
       <c r="C24" s="38" t="str">
@@ -12851,7 +12861,7 @@
         <v/>
       </c>
       <c r="E24" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F24" s="42" t="str">
         <f aca="false">IF(B24="","",IF(E24="לא",0,הגדרות!$C$22))</f>
@@ -12864,7 +12874,7 @@
       <c r="H24" s="44"/>
       <c r="I24" s="45"/>
       <c r="K24" s="27" t="str">
-        <f aca="false">IF(B24="","",B24+MIN(MOD(הגדרות!$D$18-WEEKDAY(B24)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(B24)-1,7)+1))</f>
+        <f aca="false">IF(K23="","",IF(K23+MIN(MOD(הגדרות!$D$18-WEEKDAY(K23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K23)-1,7)+1)&gt;$K$2,"",K23+MIN(MOD(הגדרות!$D$18-WEEKDAY(K23)-1,7)+1,MOD(הגדרות!$D$19-WEEKDAY(K23)-1,7)+1)))</f>
         <v/>
       </c>
     </row>
@@ -12873,16 +12883,16 @@
         <f aca="false">COUNT($B$15:$B$24)+1</f>
         <v>9</v>
       </c>
-      <c r="B25" s="46"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="38" t="str">
         <f aca="false">IF(B25="","",INDEX(הגדרות!$F$5:$F$11,WEEKDAY(B25)))</f>
         <v/>
       </c>
       <c r="D25" s="40" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F25" s="42" t="n">
         <f aca="false">IF(E25="לא",0,הגדרות!$C$23)</f>
@@ -12897,36 +12907,36 @@
       <c r="K25" s="27"/>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="B26" s="47"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="48" t="n">
+      <c r="A26" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" s="46"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="47" t="n">
         <f aca="false">SUM(F15:F25)</f>
         <v>29</v>
       </c>
-      <c r="G26" s="49" t="n">
+      <c r="G26" s="48" t="n">
         <f aca="false">SUM(G15:G25)</f>
         <v>1450</v>
       </c>
-      <c r="H26" s="47"/>
-      <c r="I26" s="49" t="n">
+      <c r="H26" s="46"/>
+      <c r="I26" s="48" t="n">
         <f aca="false">SUM(I15:I25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
+      <c r="A28" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="49"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="49"/>
       <c r="F28" s="40" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G28" s="40"/>
       <c r="H28" s="40"/>
@@ -12936,14 +12946,14 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="51" t="str">
+      <c r="A29" s="50" t="str">
         <f aca="false">"• "&amp;הגדרות!$C$17&amp;": ימי "&amp;הגדרות!$C$18&amp;" ו"&amp;הגדרות!$C$19&amp;", "&amp;TEXT(HOUR(הגדרות!$C$20),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$20),"00")&amp;"–"&amp;TEXT(HOUR(הגדרות!$C$21),"00")&amp;":"&amp;TEXT(MINUTE(הגדרות!$C$21),"00")&amp;" ("&amp;הגדרות!$C$22&amp;" שעות ליום), וישיבת צוות חודשית ("&amp;הגדרות!$C$23&amp;" ש׳)."</f>
         <v>• הדרכת שיקום: ימי ראשון וחמישי, 09:00–12:30 (3.5 שעות ליום), וישיבת צוות חודשית (1 ש׳).</v>
       </c>
-      <c r="B29" s="51"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
       <c r="F29" s="40" t="str">
         <f aca="false">"הדרכת שיקום ("&amp;TEXT(F26,"0.0")&amp;" שעות × "&amp;הגדרות!$C$24&amp;" ₪)"</f>
         <v>הדרכת שיקום (29.0 שעות × 50 ₪)</v>
@@ -12956,16 +12966,16 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="51" t="str">
+      <c r="A30" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$28="","","• "&amp;הגדרות!$C$28)</f>
         <v>• התעריף השעתי אינו כולל מע״מ. מע״מ יתווסף כחוק.</v>
       </c>
-      <c r="B30" s="51"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
       <c r="F30" s="40" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="40"/>
@@ -12975,33 +12985,33 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="51" t="str">
+      <c r="A31" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$29="","","• "&amp;הגדרות!$C$29)</f>
         <v>• פרויקטים פרטיים מתומחרים בנפרד, לפי הזמנת החווה.</v>
       </c>
-      <c r="B31" s="51"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="52" t="s">
-        <v>89</v>
-      </c>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="53" t="n">
+      <c r="B31" s="50"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="52" t="n">
         <f aca="false">I29+I30</f>
         <v>1450</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="51" t="str">
+      <c r="A32" s="50" t="str">
         <f aca="false">IF(הגדרות!$C$30="","","• "&amp;הגדרות!$C$30)</f>
         <v/>
       </c>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
       <c r="F32" s="40" t="str">
         <f aca="false">"מע״מ "&amp;ROUND(הגדרות!$C$25*100,1)&amp;"%"</f>
         <v>מע״מ 18%</v>
@@ -13014,30 +13024,30 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F33" s="54" t="s">
-        <v>90</v>
-      </c>
-      <c r="G33" s="54"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="55" t="n">
+      <c r="F33" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="54" t="n">
         <f aca="false">I31+I32</f>
         <v>1711</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="56" t="str">
+      <c r="A36" s="55" t="str">
         <f aca="false">"בברכה, "&amp;הגדרות!$C$6</f>
         <v>בברכה, (למילוי)</v>
       </c>
-      <c r="B36" s="56"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="F36" s="56" t="s">
-        <v>91</v>
-      </c>
-      <c r="G36" s="56"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="56"/>
+      <c r="B36" s="55"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="F36" s="55" t="s">
+        <v>93</v>
+      </c>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="44">

--- a/quotes/הצעת-מחיר-חודשית-חוות-רום.xlsx
+++ b/quotes/הצעת-מחיר-חודשית-חוות-רום.xlsx
@@ -805,9 +805,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="96">
   <si>
     <t xml:space="preserve">איך משתמשים בקובץ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">חשוב – הגיליונות נעולים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">אפשר לכתוב רק בתאים הצבעוניים (צהוב בהגדרות, שמנת בהצעה). כל השאר – נוסחאות – נעול, כך שאי אפשר למחוק אותן בטעות. אם ממש צריך לשנות משהו אחר: סקירה ← ביטול הגנת גיליון (אין סיסמה).</t>
   </si>
   <si>
     <t xml:space="preserve">1. פעם אחת</t>
@@ -1496,9 +1502,9 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -1508,29 +1514,29 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
@@ -1556,9 +1562,9 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="170" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
@@ -1584,17 +1590,17 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
@@ -1604,13 +1610,13 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="22" fillId="8" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
@@ -1922,7 +1928,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:C19"/>
+  <dimension ref="B1:C20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2007,41 +2013,49 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4" t="s">
+    <row r="12" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="2" t="s">
         <v>19</v>
       </c>
+      <c r="C12" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="5"/>
-      <c r="C14" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="7"/>
-      <c r="C15" s="8" t="s">
+      <c r="B14" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="5"/>
+      <c r="C15" s="6" t="s">
         <v>22</v>
       </c>
     </row>
+    <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="7"/>
+      <c r="C16" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="9" t="s">
+      <c r="B18" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="C19" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="11" t="n">
         <v>600</v>
       </c>
     </row>
@@ -2078,7 +2092,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -2114,13 +2128,13 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
       <c r="F4" s="29" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
@@ -2128,7 +2142,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
@@ -2137,7 +2151,7 @@
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="31" t="str">
@@ -2148,7 +2162,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="31" t="str">
@@ -2157,7 +2171,7 @@
       </c>
       <c r="D6" s="31"/>
       <c r="F6" s="30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="31" t="str">
@@ -2168,7 +2182,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="31" t="str">
@@ -2177,7 +2191,7 @@
       </c>
       <c r="D7" s="31"/>
       <c r="F7" s="30" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="31" t="str">
@@ -2188,7 +2202,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="31" t="str">
@@ -2199,7 +2213,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="str">
@@ -2211,7 +2225,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
@@ -2220,7 +2234,7 @@
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
@@ -2230,7 +2244,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
@@ -2239,7 +2253,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31" t="str">
@@ -2250,7 +2264,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -2259,37 +2273,37 @@
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2310,7 +2324,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F15" s="42" t="n">
         <f aca="false">IF(B15="","",IF(E15="לא",0,הגדרות!$C$22))</f>
@@ -2345,7 +2359,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F16" s="42" t="n">
         <f aca="false">IF(B16="","",IF(E16="לא",0,הגדרות!$C$22))</f>
@@ -2380,7 +2394,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F17" s="42" t="n">
         <f aca="false">IF(B17="","",IF(E17="לא",0,הגדרות!$C$22))</f>
@@ -2415,7 +2429,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F18" s="42" t="n">
         <f aca="false">IF(B18="","",IF(E18="לא",0,הגדרות!$C$22))</f>
@@ -2450,7 +2464,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F19" s="42" t="n">
         <f aca="false">IF(B19="","",IF(E19="לא",0,הגדרות!$C$22))</f>
@@ -2485,7 +2499,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F20" s="42" t="n">
         <f aca="false">IF(B20="","",IF(E20="לא",0,הגדרות!$C$22))</f>
@@ -2520,7 +2534,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F21" s="42" t="n">
         <f aca="false">IF(B21="","",IF(E21="לא",0,הגדרות!$C$22))</f>
@@ -2555,7 +2569,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F22" s="42" t="n">
         <f aca="false">IF(B22="","",IF(E22="לא",0,הגדרות!$C$22))</f>
@@ -2590,7 +2604,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F23" s="42" t="n">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
@@ -2625,7 +2639,7 @@
         <v/>
       </c>
       <c r="E24" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F24" s="42" t="str">
         <f aca="false">IF(B24="","",IF(E24="לא",0,הגדרות!$C$22))</f>
@@ -2653,10 +2667,10 @@
         <v/>
       </c>
       <c r="D25" s="40" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F25" s="42" t="n">
         <f aca="false">IF(E25="לא",0,הגדרות!$C$23)</f>
@@ -2672,7 +2686,7 @@
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="46" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B26" s="46"/>
       <c r="C26" s="46"/>
@@ -2694,13 +2708,13 @@
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
       <c r="D28" s="49"/>
       <c r="F28" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G28" s="40"/>
       <c r="H28" s="40"/>
@@ -2739,7 +2753,7 @@
       <c r="D30" s="50"/>
       <c r="E30" s="50"/>
       <c r="F30" s="40" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="40"/>
@@ -2758,7 +2772,7 @@
       <c r="D31" s="50"/>
       <c r="E31" s="50"/>
       <c r="F31" s="51" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G31" s="51"/>
       <c r="H31" s="51"/>
@@ -2789,7 +2803,7 @@
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F33" s="53" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G33" s="53"/>
       <c r="H33" s="53"/>
@@ -2807,13 +2821,14 @@
       <c r="C36" s="55"/>
       <c r="D36" s="55"/>
       <c r="F36" s="55" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G36" s="55"/>
       <c r="H36" s="55"/>
       <c r="I36" s="55"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true"/>
   <mergeCells count="44">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -2909,7 +2924,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -2945,13 +2960,13 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
       <c r="F4" s="29" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
@@ -2959,7 +2974,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
@@ -2968,7 +2983,7 @@
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="31" t="str">
@@ -2979,7 +2994,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="31" t="str">
@@ -2988,7 +3003,7 @@
       </c>
       <c r="D6" s="31"/>
       <c r="F6" s="30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="31" t="str">
@@ -2999,7 +3014,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="31" t="str">
@@ -3008,7 +3023,7 @@
       </c>
       <c r="D7" s="31"/>
       <c r="F7" s="30" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="31" t="str">
@@ -3019,7 +3034,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="31" t="str">
@@ -3030,7 +3045,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="str">
@@ -3042,7 +3057,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
@@ -3051,7 +3066,7 @@
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
@@ -3061,7 +3076,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
@@ -3070,7 +3085,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31" t="str">
@@ -3081,7 +3096,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -3090,37 +3105,37 @@
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3141,7 +3156,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F15" s="42" t="n">
         <f aca="false">IF(B15="","",IF(E15="לא",0,הגדרות!$C$22))</f>
@@ -3176,7 +3191,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F16" s="42" t="n">
         <f aca="false">IF(B16="","",IF(E16="לא",0,הגדרות!$C$22))</f>
@@ -3211,7 +3226,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F17" s="42" t="n">
         <f aca="false">IF(B17="","",IF(E17="לא",0,הגדרות!$C$22))</f>
@@ -3246,7 +3261,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F18" s="42" t="n">
         <f aca="false">IF(B18="","",IF(E18="לא",0,הגדרות!$C$22))</f>
@@ -3281,7 +3296,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F19" s="42" t="n">
         <f aca="false">IF(B19="","",IF(E19="לא",0,הגדרות!$C$22))</f>
@@ -3316,7 +3331,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F20" s="42" t="n">
         <f aca="false">IF(B20="","",IF(E20="לא",0,הגדרות!$C$22))</f>
@@ -3351,7 +3366,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F21" s="42" t="n">
         <f aca="false">IF(B21="","",IF(E21="לא",0,הגדרות!$C$22))</f>
@@ -3386,7 +3401,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F22" s="42" t="n">
         <f aca="false">IF(B22="","",IF(E22="לא",0,הגדרות!$C$22))</f>
@@ -3421,7 +3436,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F23" s="42" t="n">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
@@ -3456,7 +3471,7 @@
         <v/>
       </c>
       <c r="E24" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F24" s="42" t="str">
         <f aca="false">IF(B24="","",IF(E24="לא",0,הגדרות!$C$22))</f>
@@ -3484,10 +3499,10 @@
         <v/>
       </c>
       <c r="D25" s="40" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F25" s="42" t="n">
         <f aca="false">IF(E25="לא",0,הגדרות!$C$23)</f>
@@ -3503,7 +3518,7 @@
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="46" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B26" s="46"/>
       <c r="C26" s="46"/>
@@ -3525,13 +3540,13 @@
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
       <c r="D28" s="49"/>
       <c r="F28" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G28" s="40"/>
       <c r="H28" s="40"/>
@@ -3570,7 +3585,7 @@
       <c r="D30" s="50"/>
       <c r="E30" s="50"/>
       <c r="F30" s="40" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="40"/>
@@ -3589,7 +3604,7 @@
       <c r="D31" s="50"/>
       <c r="E31" s="50"/>
       <c r="F31" s="51" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G31" s="51"/>
       <c r="H31" s="51"/>
@@ -3620,7 +3635,7 @@
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F33" s="53" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G33" s="53"/>
       <c r="H33" s="53"/>
@@ -3638,13 +3653,14 @@
       <c r="C36" s="55"/>
       <c r="D36" s="55"/>
       <c r="F36" s="55" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G36" s="55"/>
       <c r="H36" s="55"/>
       <c r="I36" s="55"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true"/>
   <mergeCells count="44">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -3740,7 +3756,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -3776,13 +3792,13 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
       <c r="F4" s="29" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
@@ -3790,7 +3806,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
@@ -3799,7 +3815,7 @@
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="31" t="str">
@@ -3810,7 +3826,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="31" t="str">
@@ -3819,7 +3835,7 @@
       </c>
       <c r="D6" s="31"/>
       <c r="F6" s="30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="31" t="str">
@@ -3830,7 +3846,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="31" t="str">
@@ -3839,7 +3855,7 @@
       </c>
       <c r="D7" s="31"/>
       <c r="F7" s="30" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="31" t="str">
@@ -3850,7 +3866,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="31" t="str">
@@ -3861,7 +3877,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="str">
@@ -3873,7 +3889,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
@@ -3882,7 +3898,7 @@
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
@@ -3892,7 +3908,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
@@ -3901,7 +3917,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31" t="str">
@@ -3912,7 +3928,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -3921,37 +3937,37 @@
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3972,7 +3988,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F15" s="42" t="n">
         <f aca="false">IF(B15="","",IF(E15="לא",0,הגדרות!$C$22))</f>
@@ -4007,7 +4023,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F16" s="42" t="n">
         <f aca="false">IF(B16="","",IF(E16="לא",0,הגדרות!$C$22))</f>
@@ -4042,7 +4058,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F17" s="42" t="n">
         <f aca="false">IF(B17="","",IF(E17="לא",0,הגדרות!$C$22))</f>
@@ -4077,7 +4093,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F18" s="42" t="n">
         <f aca="false">IF(B18="","",IF(E18="לא",0,הגדרות!$C$22))</f>
@@ -4112,7 +4128,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F19" s="42" t="n">
         <f aca="false">IF(B19="","",IF(E19="לא",0,הגדרות!$C$22))</f>
@@ -4147,7 +4163,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F20" s="42" t="n">
         <f aca="false">IF(B20="","",IF(E20="לא",0,הגדרות!$C$22))</f>
@@ -4182,7 +4198,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F21" s="42" t="n">
         <f aca="false">IF(B21="","",IF(E21="לא",0,הגדרות!$C$22))</f>
@@ -4217,7 +4233,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F22" s="42" t="n">
         <f aca="false">IF(B22="","",IF(E22="לא",0,הגדרות!$C$22))</f>
@@ -4252,7 +4268,7 @@
         <v/>
       </c>
       <c r="E23" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F23" s="42" t="str">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
@@ -4287,7 +4303,7 @@
         <v/>
       </c>
       <c r="E24" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F24" s="42" t="str">
         <f aca="false">IF(B24="","",IF(E24="לא",0,הגדרות!$C$22))</f>
@@ -4315,10 +4331,10 @@
         <v/>
       </c>
       <c r="D25" s="40" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F25" s="42" t="n">
         <f aca="false">IF(E25="לא",0,הגדרות!$C$23)</f>
@@ -4334,7 +4350,7 @@
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="46" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B26" s="46"/>
       <c r="C26" s="46"/>
@@ -4356,13 +4372,13 @@
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
       <c r="D28" s="49"/>
       <c r="F28" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G28" s="40"/>
       <c r="H28" s="40"/>
@@ -4401,7 +4417,7 @@
       <c r="D30" s="50"/>
       <c r="E30" s="50"/>
       <c r="F30" s="40" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="40"/>
@@ -4420,7 +4436,7 @@
       <c r="D31" s="50"/>
       <c r="E31" s="50"/>
       <c r="F31" s="51" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G31" s="51"/>
       <c r="H31" s="51"/>
@@ -4451,7 +4467,7 @@
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F33" s="53" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G33" s="53"/>
       <c r="H33" s="53"/>
@@ -4469,13 +4485,14 @@
       <c r="C36" s="55"/>
       <c r="D36" s="55"/>
       <c r="F36" s="55" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G36" s="55"/>
       <c r="H36" s="55"/>
       <c r="I36" s="55"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true"/>
   <mergeCells count="44">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -4571,7 +4588,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -4607,13 +4624,13 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
       <c r="F4" s="29" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
@@ -4621,7 +4638,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
@@ -4630,7 +4647,7 @@
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="31" t="str">
@@ -4641,7 +4658,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="31" t="str">
@@ -4650,7 +4667,7 @@
       </c>
       <c r="D6" s="31"/>
       <c r="F6" s="30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="31" t="str">
@@ -4661,7 +4678,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="31" t="str">
@@ -4670,7 +4687,7 @@
       </c>
       <c r="D7" s="31"/>
       <c r="F7" s="30" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="31" t="str">
@@ -4681,7 +4698,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="31" t="str">
@@ -4692,7 +4709,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="str">
@@ -4704,7 +4721,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
@@ -4713,7 +4730,7 @@
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
@@ -4723,7 +4740,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
@@ -4732,7 +4749,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31" t="str">
@@ -4743,7 +4760,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -4752,37 +4769,37 @@
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4803,7 +4820,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F15" s="42" t="n">
         <f aca="false">IF(B15="","",IF(E15="לא",0,הגדרות!$C$22))</f>
@@ -4838,7 +4855,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F16" s="42" t="n">
         <f aca="false">IF(B16="","",IF(E16="לא",0,הגדרות!$C$22))</f>
@@ -4873,7 +4890,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F17" s="42" t="n">
         <f aca="false">IF(B17="","",IF(E17="לא",0,הגדרות!$C$22))</f>
@@ -4908,7 +4925,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F18" s="42" t="n">
         <f aca="false">IF(B18="","",IF(E18="לא",0,הגדרות!$C$22))</f>
@@ -4943,7 +4960,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F19" s="42" t="n">
         <f aca="false">IF(B19="","",IF(E19="לא",0,הגדרות!$C$22))</f>
@@ -4978,7 +4995,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F20" s="42" t="n">
         <f aca="false">IF(B20="","",IF(E20="לא",0,הגדרות!$C$22))</f>
@@ -5013,7 +5030,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F21" s="42" t="n">
         <f aca="false">IF(B21="","",IF(E21="לא",0,הגדרות!$C$22))</f>
@@ -5048,7 +5065,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F22" s="42" t="n">
         <f aca="false">IF(B22="","",IF(E22="לא",0,הגדרות!$C$22))</f>
@@ -5083,7 +5100,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F23" s="42" t="n">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
@@ -5118,7 +5135,7 @@
         <v/>
       </c>
       <c r="E24" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F24" s="42" t="str">
         <f aca="false">IF(B24="","",IF(E24="לא",0,הגדרות!$C$22))</f>
@@ -5146,10 +5163,10 @@
         <v/>
       </c>
       <c r="D25" s="40" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F25" s="42" t="n">
         <f aca="false">IF(E25="לא",0,הגדרות!$C$23)</f>
@@ -5165,7 +5182,7 @@
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="46" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B26" s="46"/>
       <c r="C26" s="46"/>
@@ -5187,13 +5204,13 @@
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
       <c r="D28" s="49"/>
       <c r="F28" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G28" s="40"/>
       <c r="H28" s="40"/>
@@ -5232,7 +5249,7 @@
       <c r="D30" s="50"/>
       <c r="E30" s="50"/>
       <c r="F30" s="40" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="40"/>
@@ -5251,7 +5268,7 @@
       <c r="D31" s="50"/>
       <c r="E31" s="50"/>
       <c r="F31" s="51" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G31" s="51"/>
       <c r="H31" s="51"/>
@@ -5282,7 +5299,7 @@
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F33" s="53" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G33" s="53"/>
       <c r="H33" s="53"/>
@@ -5300,13 +5317,14 @@
       <c r="C36" s="55"/>
       <c r="D36" s="55"/>
       <c r="F36" s="55" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G36" s="55"/>
       <c r="H36" s="55"/>
       <c r="I36" s="55"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true"/>
   <mergeCells count="44">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -5402,7 +5420,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -5438,13 +5456,13 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
       <c r="F4" s="29" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
@@ -5452,7 +5470,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
@@ -5461,7 +5479,7 @@
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="31" t="str">
@@ -5472,7 +5490,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="31" t="str">
@@ -5481,7 +5499,7 @@
       </c>
       <c r="D6" s="31"/>
       <c r="F6" s="30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="31" t="str">
@@ -5492,7 +5510,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="31" t="str">
@@ -5501,7 +5519,7 @@
       </c>
       <c r="D7" s="31"/>
       <c r="F7" s="30" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="31" t="str">
@@ -5512,7 +5530,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="31" t="str">
@@ -5523,7 +5541,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="str">
@@ -5535,7 +5553,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
@@ -5544,7 +5562,7 @@
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
@@ -5554,7 +5572,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
@@ -5563,7 +5581,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31" t="str">
@@ -5574,7 +5592,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -5583,37 +5601,37 @@
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5634,7 +5652,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F15" s="42" t="n">
         <f aca="false">IF(B15="","",IF(E15="לא",0,הגדרות!$C$22))</f>
@@ -5669,7 +5687,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F16" s="42" t="n">
         <f aca="false">IF(B16="","",IF(E16="לא",0,הגדרות!$C$22))</f>
@@ -5704,7 +5722,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F17" s="42" t="n">
         <f aca="false">IF(B17="","",IF(E17="לא",0,הגדרות!$C$22))</f>
@@ -5739,7 +5757,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F18" s="42" t="n">
         <f aca="false">IF(B18="","",IF(E18="לא",0,הגדרות!$C$22))</f>
@@ -5774,7 +5792,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F19" s="42" t="n">
         <f aca="false">IF(B19="","",IF(E19="לא",0,הגדרות!$C$22))</f>
@@ -5809,7 +5827,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F20" s="42" t="n">
         <f aca="false">IF(B20="","",IF(E20="לא",0,הגדרות!$C$22))</f>
@@ -5844,7 +5862,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F21" s="42" t="n">
         <f aca="false">IF(B21="","",IF(E21="לא",0,הגדרות!$C$22))</f>
@@ -5879,7 +5897,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F22" s="42" t="n">
         <f aca="false">IF(B22="","",IF(E22="לא",0,הגדרות!$C$22))</f>
@@ -5914,7 +5932,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F23" s="42" t="n">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
@@ -5949,7 +5967,7 @@
         <v/>
       </c>
       <c r="E24" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F24" s="42" t="str">
         <f aca="false">IF(B24="","",IF(E24="לא",0,הגדרות!$C$22))</f>
@@ -5977,10 +5995,10 @@
         <v/>
       </c>
       <c r="D25" s="40" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F25" s="42" t="n">
         <f aca="false">IF(E25="לא",0,הגדרות!$C$23)</f>
@@ -5996,7 +6014,7 @@
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="46" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B26" s="46"/>
       <c r="C26" s="46"/>
@@ -6018,13 +6036,13 @@
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
       <c r="D28" s="49"/>
       <c r="F28" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G28" s="40"/>
       <c r="H28" s="40"/>
@@ -6063,7 +6081,7 @@
       <c r="D30" s="50"/>
       <c r="E30" s="50"/>
       <c r="F30" s="40" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="40"/>
@@ -6082,7 +6100,7 @@
       <c r="D31" s="50"/>
       <c r="E31" s="50"/>
       <c r="F31" s="51" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G31" s="51"/>
       <c r="H31" s="51"/>
@@ -6113,7 +6131,7 @@
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F33" s="53" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G33" s="53"/>
       <c r="H33" s="53"/>
@@ -6131,13 +6149,14 @@
       <c r="C36" s="55"/>
       <c r="D36" s="55"/>
       <c r="F36" s="55" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G36" s="55"/>
       <c r="H36" s="55"/>
       <c r="I36" s="55"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true"/>
   <mergeCells count="44">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -6233,7 +6252,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -6269,13 +6288,13 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
       <c r="F4" s="29" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
@@ -6283,7 +6302,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
@@ -6292,7 +6311,7 @@
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="31" t="str">
@@ -6303,7 +6322,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="31" t="str">
@@ -6312,7 +6331,7 @@
       </c>
       <c r="D6" s="31"/>
       <c r="F6" s="30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="31" t="str">
@@ -6323,7 +6342,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="31" t="str">
@@ -6332,7 +6351,7 @@
       </c>
       <c r="D7" s="31"/>
       <c r="F7" s="30" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="31" t="str">
@@ -6343,7 +6362,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="31" t="str">
@@ -6354,7 +6373,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="str">
@@ -6366,7 +6385,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
@@ -6375,7 +6394,7 @@
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
@@ -6385,7 +6404,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
@@ -6394,7 +6413,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31" t="str">
@@ -6405,7 +6424,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -6414,37 +6433,37 @@
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6465,7 +6484,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F15" s="42" t="n">
         <f aca="false">IF(B15="","",IF(E15="לא",0,הגדרות!$C$22))</f>
@@ -6500,7 +6519,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F16" s="42" t="n">
         <f aca="false">IF(B16="","",IF(E16="לא",0,הגדרות!$C$22))</f>
@@ -6535,7 +6554,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F17" s="42" t="n">
         <f aca="false">IF(B17="","",IF(E17="לא",0,הגדרות!$C$22))</f>
@@ -6570,7 +6589,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F18" s="42" t="n">
         <f aca="false">IF(B18="","",IF(E18="לא",0,הגדרות!$C$22))</f>
@@ -6605,7 +6624,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F19" s="42" t="n">
         <f aca="false">IF(B19="","",IF(E19="לא",0,הגדרות!$C$22))</f>
@@ -6640,7 +6659,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F20" s="42" t="n">
         <f aca="false">IF(B20="","",IF(E20="לא",0,הגדרות!$C$22))</f>
@@ -6675,7 +6694,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F21" s="42" t="n">
         <f aca="false">IF(B21="","",IF(E21="לא",0,הגדרות!$C$22))</f>
@@ -6710,7 +6729,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F22" s="42" t="n">
         <f aca="false">IF(B22="","",IF(E22="לא",0,הגדרות!$C$22))</f>
@@ -6745,7 +6764,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F23" s="42" t="n">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
@@ -6780,7 +6799,7 @@
         <v/>
       </c>
       <c r="E24" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F24" s="42" t="str">
         <f aca="false">IF(B24="","",IF(E24="לא",0,הגדרות!$C$22))</f>
@@ -6808,10 +6827,10 @@
         <v/>
       </c>
       <c r="D25" s="40" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F25" s="42" t="n">
         <f aca="false">IF(E25="לא",0,הגדרות!$C$23)</f>
@@ -6827,7 +6846,7 @@
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="46" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B26" s="46"/>
       <c r="C26" s="46"/>
@@ -6849,13 +6868,13 @@
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
       <c r="D28" s="49"/>
       <c r="F28" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G28" s="40"/>
       <c r="H28" s="40"/>
@@ -6894,7 +6913,7 @@
       <c r="D30" s="50"/>
       <c r="E30" s="50"/>
       <c r="F30" s="40" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="40"/>
@@ -6913,7 +6932,7 @@
       <c r="D31" s="50"/>
       <c r="E31" s="50"/>
       <c r="F31" s="51" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G31" s="51"/>
       <c r="H31" s="51"/>
@@ -6944,7 +6963,7 @@
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F33" s="53" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G33" s="53"/>
       <c r="H33" s="53"/>
@@ -6962,13 +6981,14 @@
       <c r="C36" s="55"/>
       <c r="D36" s="55"/>
       <c r="F36" s="55" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G36" s="55"/>
       <c r="H36" s="55"/>
       <c r="I36" s="55"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true"/>
   <mergeCells count="44">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -7060,139 +7080,139 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="12" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="13" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C4" s="14"/>
       <c r="F4" s="15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="16" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="17" t="s">
-        <v>34</v>
-      </c>
       <c r="F7" s="18" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F10" s="18" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C11" s="14"/>
       <c r="F11" s="18" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C16" s="14"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D18" s="19" t="n">
         <f aca="false">MATCH(C18,$F$5:$F$11,0)</f>
@@ -7201,10 +7221,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D19" s="19" t="n">
         <f aca="false">MATCH(C19,$F$5:$F$11,0)</f>
@@ -7213,7 +7233,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="16" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C20" s="20" t="n">
         <v>0.375</v>
@@ -7221,7 +7241,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C21" s="20" t="n">
         <v>0.520833333333333</v>
@@ -7229,7 +7249,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C22" s="21" t="n">
         <f aca="false">(C21-C20)*24</f>
@@ -7238,7 +7258,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C23" s="22" t="n">
         <v>1</v>
@@ -7246,7 +7266,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="16" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C24" s="23" t="n">
         <v>50</v>
@@ -7254,7 +7274,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="16" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>0.18</v>
@@ -7262,33 +7282,34 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C27" s="14"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C28" s="25" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C30" s="25"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true"/>
   <dataValidations count="1">
     <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C18:C19" type="list">
       <formula1>$F$5:$F$11</formula1>
@@ -7328,7 +7349,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -7364,13 +7385,13 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
       <c r="F4" s="29" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
@@ -7378,7 +7399,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
@@ -7387,7 +7408,7 @@
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="31" t="str">
@@ -7398,7 +7419,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="31" t="str">
@@ -7407,7 +7428,7 @@
       </c>
       <c r="D6" s="31"/>
       <c r="F6" s="30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="31" t="str">
@@ -7418,7 +7439,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="31" t="str">
@@ -7427,7 +7448,7 @@
       </c>
       <c r="D7" s="31"/>
       <c r="F7" s="30" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="31" t="str">
@@ -7438,7 +7459,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="31" t="str">
@@ -7449,7 +7470,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="str">
@@ -7461,7 +7482,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
@@ -7470,7 +7491,7 @@
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
@@ -7480,7 +7501,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
@@ -7489,7 +7510,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31" t="str">
@@ -7500,7 +7521,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -7509,37 +7530,37 @@
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7560,7 +7581,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F15" s="42" t="n">
         <f aca="false">IF(B15="","",IF(E15="לא",0,הגדרות!$C$22))</f>
@@ -7595,7 +7616,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F16" s="42" t="n">
         <f aca="false">IF(B16="","",IF(E16="לא",0,הגדרות!$C$22))</f>
@@ -7630,7 +7651,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F17" s="42" t="n">
         <f aca="false">IF(B17="","",IF(E17="לא",0,הגדרות!$C$22))</f>
@@ -7665,7 +7686,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F18" s="42" t="n">
         <f aca="false">IF(B18="","",IF(E18="לא",0,הגדרות!$C$22))</f>
@@ -7700,7 +7721,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F19" s="42" t="n">
         <f aca="false">IF(B19="","",IF(E19="לא",0,הגדרות!$C$22))</f>
@@ -7735,7 +7756,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F20" s="42" t="n">
         <f aca="false">IF(B20="","",IF(E20="לא",0,הגדרות!$C$22))</f>
@@ -7770,7 +7791,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F21" s="42" t="n">
         <f aca="false">IF(B21="","",IF(E21="לא",0,הגדרות!$C$22))</f>
@@ -7805,7 +7826,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F22" s="42" t="n">
         <f aca="false">IF(B22="","",IF(E22="לא",0,הגדרות!$C$22))</f>
@@ -7840,7 +7861,7 @@
         <v/>
       </c>
       <c r="E23" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F23" s="42" t="str">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
@@ -7875,7 +7896,7 @@
         <v/>
       </c>
       <c r="E24" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F24" s="42" t="str">
         <f aca="false">IF(B24="","",IF(E24="לא",0,הגדרות!$C$22))</f>
@@ -7903,10 +7924,10 @@
         <v/>
       </c>
       <c r="D25" s="40" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F25" s="42" t="n">
         <f aca="false">IF(E25="לא",0,הגדרות!$C$23)</f>
@@ -7922,7 +7943,7 @@
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="46" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B26" s="46"/>
       <c r="C26" s="46"/>
@@ -7944,13 +7965,13 @@
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
       <c r="D28" s="49"/>
       <c r="F28" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G28" s="40"/>
       <c r="H28" s="40"/>
@@ -7989,7 +8010,7 @@
       <c r="D30" s="50"/>
       <c r="E30" s="50"/>
       <c r="F30" s="40" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="40"/>
@@ -8008,7 +8029,7 @@
       <c r="D31" s="50"/>
       <c r="E31" s="50"/>
       <c r="F31" s="51" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G31" s="51"/>
       <c r="H31" s="51"/>
@@ -8039,7 +8060,7 @@
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F33" s="53" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G33" s="53"/>
       <c r="H33" s="53"/>
@@ -8057,13 +8078,14 @@
       <c r="C36" s="55"/>
       <c r="D36" s="55"/>
       <c r="F36" s="55" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G36" s="55"/>
       <c r="H36" s="55"/>
       <c r="I36" s="55"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true"/>
   <mergeCells count="44">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -8159,7 +8181,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -8195,13 +8217,13 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
       <c r="F4" s="29" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
@@ -8209,7 +8231,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
@@ -8218,7 +8240,7 @@
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="31" t="str">
@@ -8229,7 +8251,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="31" t="str">
@@ -8238,7 +8260,7 @@
       </c>
       <c r="D6" s="31"/>
       <c r="F6" s="30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="31" t="str">
@@ -8249,7 +8271,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="31" t="str">
@@ -8258,7 +8280,7 @@
       </c>
       <c r="D7" s="31"/>
       <c r="F7" s="30" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="31" t="str">
@@ -8269,7 +8291,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="31" t="str">
@@ -8280,7 +8302,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="str">
@@ -8292,7 +8314,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
@@ -8301,7 +8323,7 @@
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
@@ -8311,7 +8333,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
@@ -8320,7 +8342,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31" t="str">
@@ -8331,7 +8353,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -8340,37 +8362,37 @@
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8391,7 +8413,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F15" s="42" t="n">
         <f aca="false">IF(B15="","",IF(E15="לא",0,הגדרות!$C$22))</f>
@@ -8426,7 +8448,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F16" s="42" t="n">
         <f aca="false">IF(B16="","",IF(E16="לא",0,הגדרות!$C$22))</f>
@@ -8461,7 +8483,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F17" s="42" t="n">
         <f aca="false">IF(B17="","",IF(E17="לא",0,הגדרות!$C$22))</f>
@@ -8496,7 +8518,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F18" s="42" t="n">
         <f aca="false">IF(B18="","",IF(E18="לא",0,הגדרות!$C$22))</f>
@@ -8531,7 +8553,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F19" s="42" t="n">
         <f aca="false">IF(B19="","",IF(E19="לא",0,הגדרות!$C$22))</f>
@@ -8566,7 +8588,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F20" s="42" t="n">
         <f aca="false">IF(B20="","",IF(E20="לא",0,הגדרות!$C$22))</f>
@@ -8601,7 +8623,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F21" s="42" t="n">
         <f aca="false">IF(B21="","",IF(E21="לא",0,הגדרות!$C$22))</f>
@@ -8636,7 +8658,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F22" s="42" t="n">
         <f aca="false">IF(B22="","",IF(E22="לא",0,הגדרות!$C$22))</f>
@@ -8671,7 +8693,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F23" s="42" t="n">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
@@ -8706,7 +8728,7 @@
         <v/>
       </c>
       <c r="E24" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F24" s="42" t="str">
         <f aca="false">IF(B24="","",IF(E24="לא",0,הגדרות!$C$22))</f>
@@ -8734,10 +8756,10 @@
         <v/>
       </c>
       <c r="D25" s="40" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F25" s="42" t="n">
         <f aca="false">IF(E25="לא",0,הגדרות!$C$23)</f>
@@ -8753,7 +8775,7 @@
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="46" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B26" s="46"/>
       <c r="C26" s="46"/>
@@ -8775,13 +8797,13 @@
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
       <c r="D28" s="49"/>
       <c r="F28" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G28" s="40"/>
       <c r="H28" s="40"/>
@@ -8820,7 +8842,7 @@
       <c r="D30" s="50"/>
       <c r="E30" s="50"/>
       <c r="F30" s="40" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="40"/>
@@ -8839,7 +8861,7 @@
       <c r="D31" s="50"/>
       <c r="E31" s="50"/>
       <c r="F31" s="51" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G31" s="51"/>
       <c r="H31" s="51"/>
@@ -8870,7 +8892,7 @@
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F33" s="53" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G33" s="53"/>
       <c r="H33" s="53"/>
@@ -8888,13 +8910,14 @@
       <c r="C36" s="55"/>
       <c r="D36" s="55"/>
       <c r="F36" s="55" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G36" s="55"/>
       <c r="H36" s="55"/>
       <c r="I36" s="55"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true"/>
   <mergeCells count="44">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -8990,7 +9013,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -9026,13 +9049,13 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
       <c r="F4" s="29" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
@@ -9040,7 +9063,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
@@ -9049,7 +9072,7 @@
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="31" t="str">
@@ -9060,7 +9083,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="31" t="str">
@@ -9069,7 +9092,7 @@
       </c>
       <c r="D6" s="31"/>
       <c r="F6" s="30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="31" t="str">
@@ -9080,7 +9103,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="31" t="str">
@@ -9089,7 +9112,7 @@
       </c>
       <c r="D7" s="31"/>
       <c r="F7" s="30" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="31" t="str">
@@ -9100,7 +9123,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="31" t="str">
@@ -9111,7 +9134,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="str">
@@ -9123,7 +9146,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
@@ -9132,7 +9155,7 @@
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
@@ -9142,7 +9165,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
@@ -9151,7 +9174,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31" t="str">
@@ -9162,7 +9185,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -9171,37 +9194,37 @@
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9222,7 +9245,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F15" s="42" t="n">
         <f aca="false">IF(B15="","",IF(E15="לא",0,הגדרות!$C$22))</f>
@@ -9257,7 +9280,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F16" s="42" t="n">
         <f aca="false">IF(B16="","",IF(E16="לא",0,הגדרות!$C$22))</f>
@@ -9292,7 +9315,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F17" s="42" t="n">
         <f aca="false">IF(B17="","",IF(E17="לא",0,הגדרות!$C$22))</f>
@@ -9327,7 +9350,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F18" s="42" t="n">
         <f aca="false">IF(B18="","",IF(E18="לא",0,הגדרות!$C$22))</f>
@@ -9362,7 +9385,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F19" s="42" t="n">
         <f aca="false">IF(B19="","",IF(E19="לא",0,הגדרות!$C$22))</f>
@@ -9397,7 +9420,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F20" s="42" t="n">
         <f aca="false">IF(B20="","",IF(E20="לא",0,הגדרות!$C$22))</f>
@@ -9432,7 +9455,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F21" s="42" t="n">
         <f aca="false">IF(B21="","",IF(E21="לא",0,הגדרות!$C$22))</f>
@@ -9467,7 +9490,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F22" s="42" t="n">
         <f aca="false">IF(B22="","",IF(E22="לא",0,הגדרות!$C$22))</f>
@@ -9502,7 +9525,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F23" s="42" t="n">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
@@ -9537,7 +9560,7 @@
         <v/>
       </c>
       <c r="E24" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F24" s="42" t="str">
         <f aca="false">IF(B24="","",IF(E24="לא",0,הגדרות!$C$22))</f>
@@ -9565,10 +9588,10 @@
         <v/>
       </c>
       <c r="D25" s="40" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F25" s="42" t="n">
         <f aca="false">IF(E25="לא",0,הגדרות!$C$23)</f>
@@ -9584,7 +9607,7 @@
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="46" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B26" s="46"/>
       <c r="C26" s="46"/>
@@ -9606,13 +9629,13 @@
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
       <c r="D28" s="49"/>
       <c r="F28" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G28" s="40"/>
       <c r="H28" s="40"/>
@@ -9651,7 +9674,7 @@
       <c r="D30" s="50"/>
       <c r="E30" s="50"/>
       <c r="F30" s="40" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="40"/>
@@ -9670,7 +9693,7 @@
       <c r="D31" s="50"/>
       <c r="E31" s="50"/>
       <c r="F31" s="51" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G31" s="51"/>
       <c r="H31" s="51"/>
@@ -9701,7 +9724,7 @@
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F33" s="53" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G33" s="53"/>
       <c r="H33" s="53"/>
@@ -9719,13 +9742,14 @@
       <c r="C36" s="55"/>
       <c r="D36" s="55"/>
       <c r="F36" s="55" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G36" s="55"/>
       <c r="H36" s="55"/>
       <c r="I36" s="55"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true"/>
   <mergeCells count="44">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -9821,7 +9845,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -9857,13 +9881,13 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
       <c r="F4" s="29" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
@@ -9871,7 +9895,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
@@ -9880,7 +9904,7 @@
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="31" t="str">
@@ -9891,7 +9915,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="31" t="str">
@@ -9900,7 +9924,7 @@
       </c>
       <c r="D6" s="31"/>
       <c r="F6" s="30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="31" t="str">
@@ -9911,7 +9935,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="31" t="str">
@@ -9920,7 +9944,7 @@
       </c>
       <c r="D7" s="31"/>
       <c r="F7" s="30" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="31" t="str">
@@ -9931,7 +9955,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="31" t="str">
@@ -9942,7 +9966,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="str">
@@ -9954,7 +9978,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
@@ -9963,7 +9987,7 @@
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
@@ -9973,7 +9997,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
@@ -9982,7 +10006,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31" t="str">
@@ -9993,7 +10017,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -10002,37 +10026,37 @@
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10053,7 +10077,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F15" s="42" t="n">
         <f aca="false">IF(B15="","",IF(E15="לא",0,הגדרות!$C$22))</f>
@@ -10088,7 +10112,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F16" s="42" t="n">
         <f aca="false">IF(B16="","",IF(E16="לא",0,הגדרות!$C$22))</f>
@@ -10123,7 +10147,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F17" s="42" t="n">
         <f aca="false">IF(B17="","",IF(E17="לא",0,הגדרות!$C$22))</f>
@@ -10158,7 +10182,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F18" s="42" t="n">
         <f aca="false">IF(B18="","",IF(E18="לא",0,הגדרות!$C$22))</f>
@@ -10193,7 +10217,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F19" s="42" t="n">
         <f aca="false">IF(B19="","",IF(E19="לא",0,הגדרות!$C$22))</f>
@@ -10228,7 +10252,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F20" s="42" t="n">
         <f aca="false">IF(B20="","",IF(E20="לא",0,הגדרות!$C$22))</f>
@@ -10263,7 +10287,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F21" s="42" t="n">
         <f aca="false">IF(B21="","",IF(E21="לא",0,הגדרות!$C$22))</f>
@@ -10298,7 +10322,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F22" s="42" t="n">
         <f aca="false">IF(B22="","",IF(E22="לא",0,הגדרות!$C$22))</f>
@@ -10333,7 +10357,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F23" s="42" t="n">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
@@ -10368,7 +10392,7 @@
         <v/>
       </c>
       <c r="E24" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F24" s="42" t="str">
         <f aca="false">IF(B24="","",IF(E24="לא",0,הגדרות!$C$22))</f>
@@ -10396,10 +10420,10 @@
         <v/>
       </c>
       <c r="D25" s="40" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F25" s="42" t="n">
         <f aca="false">IF(E25="לא",0,הגדרות!$C$23)</f>
@@ -10415,7 +10439,7 @@
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="46" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B26" s="46"/>
       <c r="C26" s="46"/>
@@ -10437,13 +10461,13 @@
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
       <c r="D28" s="49"/>
       <c r="F28" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G28" s="40"/>
       <c r="H28" s="40"/>
@@ -10482,7 +10506,7 @@
       <c r="D30" s="50"/>
       <c r="E30" s="50"/>
       <c r="F30" s="40" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="40"/>
@@ -10501,7 +10525,7 @@
       <c r="D31" s="50"/>
       <c r="E31" s="50"/>
       <c r="F31" s="51" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G31" s="51"/>
       <c r="H31" s="51"/>
@@ -10532,7 +10556,7 @@
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F33" s="53" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G33" s="53"/>
       <c r="H33" s="53"/>
@@ -10550,13 +10574,14 @@
       <c r="C36" s="55"/>
       <c r="D36" s="55"/>
       <c r="F36" s="55" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G36" s="55"/>
       <c r="H36" s="55"/>
       <c r="I36" s="55"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true"/>
   <mergeCells count="44">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -10652,7 +10677,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -10688,13 +10713,13 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
       <c r="F4" s="29" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
@@ -10702,7 +10727,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
@@ -10711,7 +10736,7 @@
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="31" t="str">
@@ -10722,7 +10747,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="31" t="str">
@@ -10731,7 +10756,7 @@
       </c>
       <c r="D6" s="31"/>
       <c r="F6" s="30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="31" t="str">
@@ -10742,7 +10767,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="31" t="str">
@@ -10751,7 +10776,7 @@
       </c>
       <c r="D7" s="31"/>
       <c r="F7" s="30" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="31" t="str">
@@ -10762,7 +10787,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="31" t="str">
@@ -10773,7 +10798,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="str">
@@ -10785,7 +10810,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
@@ -10794,7 +10819,7 @@
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
@@ -10804,7 +10829,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
@@ -10813,7 +10838,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31" t="str">
@@ -10824,7 +10849,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -10833,37 +10858,37 @@
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10884,7 +10909,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F15" s="42" t="n">
         <f aca="false">IF(B15="","",IF(E15="לא",0,הגדרות!$C$22))</f>
@@ -10919,7 +10944,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F16" s="42" t="n">
         <f aca="false">IF(B16="","",IF(E16="לא",0,הגדרות!$C$22))</f>
@@ -10954,7 +10979,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F17" s="42" t="n">
         <f aca="false">IF(B17="","",IF(E17="לא",0,הגדרות!$C$22))</f>
@@ -10989,7 +11014,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F18" s="42" t="n">
         <f aca="false">IF(B18="","",IF(E18="לא",0,הגדרות!$C$22))</f>
@@ -11024,7 +11049,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F19" s="42" t="n">
         <f aca="false">IF(B19="","",IF(E19="לא",0,הגדרות!$C$22))</f>
@@ -11059,7 +11084,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F20" s="42" t="n">
         <f aca="false">IF(B20="","",IF(E20="לא",0,הגדרות!$C$22))</f>
@@ -11094,7 +11119,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F21" s="42" t="n">
         <f aca="false">IF(B21="","",IF(E21="לא",0,הגדרות!$C$22))</f>
@@ -11129,7 +11154,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F22" s="42" t="n">
         <f aca="false">IF(B22="","",IF(E22="לא",0,הגדרות!$C$22))</f>
@@ -11164,7 +11189,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F23" s="42" t="n">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
@@ -11199,7 +11224,7 @@
         <v/>
       </c>
       <c r="E24" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F24" s="42" t="str">
         <f aca="false">IF(B24="","",IF(E24="לא",0,הגדרות!$C$22))</f>
@@ -11227,10 +11252,10 @@
         <v/>
       </c>
       <c r="D25" s="40" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F25" s="42" t="n">
         <f aca="false">IF(E25="לא",0,הגדרות!$C$23)</f>
@@ -11246,7 +11271,7 @@
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="46" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B26" s="46"/>
       <c r="C26" s="46"/>
@@ -11268,13 +11293,13 @@
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
       <c r="D28" s="49"/>
       <c r="F28" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G28" s="40"/>
       <c r="H28" s="40"/>
@@ -11313,7 +11338,7 @@
       <c r="D30" s="50"/>
       <c r="E30" s="50"/>
       <c r="F30" s="40" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="40"/>
@@ -11332,7 +11357,7 @@
       <c r="D31" s="50"/>
       <c r="E31" s="50"/>
       <c r="F31" s="51" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G31" s="51"/>
       <c r="H31" s="51"/>
@@ -11363,7 +11388,7 @@
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F33" s="53" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G33" s="53"/>
       <c r="H33" s="53"/>
@@ -11381,13 +11406,14 @@
       <c r="C36" s="55"/>
       <c r="D36" s="55"/>
       <c r="F36" s="55" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G36" s="55"/>
       <c r="H36" s="55"/>
       <c r="I36" s="55"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true"/>
   <mergeCells count="44">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -11483,7 +11509,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -11519,13 +11545,13 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
       <c r="F4" s="29" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
@@ -11533,7 +11559,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
@@ -11542,7 +11568,7 @@
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="31" t="str">
@@ -11553,7 +11579,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="31" t="str">
@@ -11562,7 +11588,7 @@
       </c>
       <c r="D6" s="31"/>
       <c r="F6" s="30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="31" t="str">
@@ -11573,7 +11599,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="31" t="str">
@@ -11582,7 +11608,7 @@
       </c>
       <c r="D7" s="31"/>
       <c r="F7" s="30" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="31" t="str">
@@ -11593,7 +11619,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="31" t="str">
@@ -11604,7 +11630,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="str">
@@ -11616,7 +11642,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
@@ -11625,7 +11651,7 @@
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
@@ -11635,7 +11661,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
@@ -11644,7 +11670,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31" t="str">
@@ -11655,7 +11681,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -11664,37 +11690,37 @@
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11715,7 +11741,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F15" s="42" t="n">
         <f aca="false">IF(B15="","",IF(E15="לא",0,הגדרות!$C$22))</f>
@@ -11750,7 +11776,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F16" s="42" t="n">
         <f aca="false">IF(B16="","",IF(E16="לא",0,הגדרות!$C$22))</f>
@@ -11785,7 +11811,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F17" s="42" t="n">
         <f aca="false">IF(B17="","",IF(E17="לא",0,הגדרות!$C$22))</f>
@@ -11820,7 +11846,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F18" s="42" t="n">
         <f aca="false">IF(B18="","",IF(E18="לא",0,הגדרות!$C$22))</f>
@@ -11855,7 +11881,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F19" s="42" t="n">
         <f aca="false">IF(B19="","",IF(E19="לא",0,הגדרות!$C$22))</f>
@@ -11890,7 +11916,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F20" s="42" t="n">
         <f aca="false">IF(B20="","",IF(E20="לא",0,הגדרות!$C$22))</f>
@@ -11925,7 +11951,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F21" s="42" t="n">
         <f aca="false">IF(B21="","",IF(E21="לא",0,הגדרות!$C$22))</f>
@@ -11960,7 +11986,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F22" s="42" t="n">
         <f aca="false">IF(B22="","",IF(E22="לא",0,הגדרות!$C$22))</f>
@@ -11995,7 +12021,7 @@
         <v/>
       </c>
       <c r="E23" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F23" s="42" t="str">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
@@ -12030,7 +12056,7 @@
         <v/>
       </c>
       <c r="E24" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F24" s="42" t="str">
         <f aca="false">IF(B24="","",IF(E24="לא",0,הגדרות!$C$22))</f>
@@ -12058,10 +12084,10 @@
         <v/>
       </c>
       <c r="D25" s="40" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F25" s="42" t="n">
         <f aca="false">IF(E25="לא",0,הגדרות!$C$23)</f>
@@ -12077,7 +12103,7 @@
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="46" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B26" s="46"/>
       <c r="C26" s="46"/>
@@ -12099,13 +12125,13 @@
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
       <c r="D28" s="49"/>
       <c r="F28" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G28" s="40"/>
       <c r="H28" s="40"/>
@@ -12144,7 +12170,7 @@
       <c r="D30" s="50"/>
       <c r="E30" s="50"/>
       <c r="F30" s="40" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="40"/>
@@ -12163,7 +12189,7 @@
       <c r="D31" s="50"/>
       <c r="E31" s="50"/>
       <c r="F31" s="51" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G31" s="51"/>
       <c r="H31" s="51"/>
@@ -12194,7 +12220,7 @@
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F33" s="53" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G33" s="53"/>
       <c r="H33" s="53"/>
@@ -12212,13 +12238,14 @@
       <c r="C36" s="55"/>
       <c r="D36" s="55"/>
       <c r="F36" s="55" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G36" s="55"/>
       <c r="H36" s="55"/>
       <c r="I36" s="55"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true"/>
   <mergeCells count="44">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -12314,7 +12341,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -12350,13 +12377,13 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
       <c r="F4" s="29" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
@@ -12364,7 +12391,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
@@ -12373,7 +12400,7 @@
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="31" t="str">
@@ -12384,7 +12411,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="31" t="str">
@@ -12393,7 +12420,7 @@
       </c>
       <c r="D6" s="31"/>
       <c r="F6" s="30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="31" t="str">
@@ -12404,7 +12431,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="31" t="str">
@@ -12413,7 +12440,7 @@
       </c>
       <c r="D7" s="31"/>
       <c r="F7" s="30" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="31" t="str">
@@ -12424,7 +12451,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="31" t="str">
@@ -12435,7 +12462,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="str">
@@ -12447,7 +12474,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="31" t="str">
@@ -12456,7 +12483,7 @@
       </c>
       <c r="D11" s="31"/>
       <c r="F11" s="30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="32" t="n">
@@ -12466,7 +12493,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="33" t="n">
@@ -12475,7 +12502,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="F12" s="30" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31" t="str">
@@ -12486,7 +12513,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -12495,37 +12522,37 @@
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12546,7 +12573,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F15" s="42" t="n">
         <f aca="false">IF(B15="","",IF(E15="לא",0,הגדרות!$C$22))</f>
@@ -12581,7 +12608,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F16" s="42" t="n">
         <f aca="false">IF(B16="","",IF(E16="לא",0,הגדרות!$C$22))</f>
@@ -12616,7 +12643,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F17" s="42" t="n">
         <f aca="false">IF(B17="","",IF(E17="לא",0,הגדרות!$C$22))</f>
@@ -12651,7 +12678,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F18" s="42" t="n">
         <f aca="false">IF(B18="","",IF(E18="לא",0,הגדרות!$C$22))</f>
@@ -12686,7 +12713,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F19" s="42" t="n">
         <f aca="false">IF(B19="","",IF(E19="לא",0,הגדרות!$C$22))</f>
@@ -12721,7 +12748,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F20" s="42" t="n">
         <f aca="false">IF(B20="","",IF(E20="לא",0,הגדרות!$C$22))</f>
@@ -12756,7 +12783,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F21" s="42" t="n">
         <f aca="false">IF(B21="","",IF(E21="לא",0,הגדרות!$C$22))</f>
@@ -12791,7 +12818,7 @@
         <v>הדרכה 09:00–12:30</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F22" s="42" t="n">
         <f aca="false">IF(B22="","",IF(E22="לא",0,הגדרות!$C$22))</f>
@@ -12826,7 +12853,7 @@
         <v/>
       </c>
       <c r="E23" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F23" s="42" t="str">
         <f aca="false">IF(B23="","",IF(E23="לא",0,הגדרות!$C$22))</f>
@@ -12861,7 +12888,7 @@
         <v/>
       </c>
       <c r="E24" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F24" s="42" t="str">
         <f aca="false">IF(B24="","",IF(E24="לא",0,הגדרות!$C$22))</f>
@@ -12889,10 +12916,10 @@
         <v/>
       </c>
       <c r="D25" s="40" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F25" s="42" t="n">
         <f aca="false">IF(E25="לא",0,הגדרות!$C$23)</f>
@@ -12908,7 +12935,7 @@
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="46" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B26" s="46"/>
       <c r="C26" s="46"/>
@@ -12930,13 +12957,13 @@
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
       <c r="D28" s="49"/>
       <c r="F28" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G28" s="40"/>
       <c r="H28" s="40"/>
@@ -12975,7 +13002,7 @@
       <c r="D30" s="50"/>
       <c r="E30" s="50"/>
       <c r="F30" s="40" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="40"/>
@@ -12994,7 +13021,7 @@
       <c r="D31" s="50"/>
       <c r="E31" s="50"/>
       <c r="F31" s="51" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G31" s="51"/>
       <c r="H31" s="51"/>
@@ -13025,7 +13052,7 @@
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F33" s="53" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G33" s="53"/>
       <c r="H33" s="53"/>
@@ -13043,13 +13070,14 @@
       <c r="C36" s="55"/>
       <c r="D36" s="55"/>
       <c r="F36" s="55" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G36" s="55"/>
       <c r="H36" s="55"/>
       <c r="I36" s="55"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true"/>
   <mergeCells count="44">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>

--- a/quotes/הצעת-מחיר-חודשית-חוות-רום.xlsx
+++ b/quotes/הצעת-מחיר-חודשית-חוות-רום.xlsx
@@ -906,7 +906,7 @@
     <t xml:space="preserve">שם העסק</t>
   </si>
   <si>
-    <t xml:space="preserve">הנגרייה</t>
+    <t xml:space="preserve">הנגרייה השיקומית בחוות רום</t>
   </si>
   <si>
     <t xml:space="preserve">ראשון</t>
@@ -2147,7 +2147,7 @@
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
         <f aca="false">הגדרות!$C$5</f>
-        <v>הנגרייה</v>
+        <v>הנגרייה השיקומית בחוות רום</v>
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
@@ -2979,7 +2979,7 @@
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
         <f aca="false">הגדרות!$C$5</f>
-        <v>הנגרייה</v>
+        <v>הנגרייה השיקומית בחוות רום</v>
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
@@ -3811,7 +3811,7 @@
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
         <f aca="false">הגדרות!$C$5</f>
-        <v>הנגרייה</v>
+        <v>הנגרייה השיקומית בחוות רום</v>
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
@@ -4643,7 +4643,7 @@
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
         <f aca="false">הגדרות!$C$5</f>
-        <v>הנגרייה</v>
+        <v>הנגרייה השיקומית בחוות רום</v>
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
@@ -5475,7 +5475,7 @@
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
         <f aca="false">הגדרות!$C$5</f>
-        <v>הנגרייה</v>
+        <v>הנגרייה השיקומית בחוות רום</v>
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
@@ -6307,7 +6307,7 @@
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
         <f aca="false">הגדרות!$C$5</f>
-        <v>הנגרייה</v>
+        <v>הנגרייה השיקומית בחוות רום</v>
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
@@ -7404,7 +7404,7 @@
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
         <f aca="false">הגדרות!$C$5</f>
-        <v>הנגרייה</v>
+        <v>הנגרייה השיקומית בחוות רום</v>
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
@@ -8236,7 +8236,7 @@
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
         <f aca="false">הגדרות!$C$5</f>
-        <v>הנגרייה</v>
+        <v>הנגרייה השיקומית בחוות רום</v>
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
@@ -9068,7 +9068,7 @@
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
         <f aca="false">הגדרות!$C$5</f>
-        <v>הנגרייה</v>
+        <v>הנגרייה השיקומית בחוות רום</v>
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
@@ -9900,7 +9900,7 @@
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
         <f aca="false">הגדרות!$C$5</f>
-        <v>הנגרייה</v>
+        <v>הנגרייה השיקומית בחוות רום</v>
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
@@ -10732,7 +10732,7 @@
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
         <f aca="false">הגדרות!$C$5</f>
-        <v>הנגרייה</v>
+        <v>הנגרייה השיקומית בחוות רום</v>
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
@@ -11564,7 +11564,7 @@
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
         <f aca="false">הגדרות!$C$5</f>
-        <v>הנגרייה</v>
+        <v>הנגרייה השיקומית בחוות רום</v>
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
@@ -12396,7 +12396,7 @@
       <c r="B5" s="30"/>
       <c r="C5" s="31" t="str">
         <f aca="false">הגדרות!$C$5</f>
-        <v>הנגרייה</v>
+        <v>הנגרייה השיקומית בחוות רום</v>
       </c>
       <c r="D5" s="31"/>
       <c r="F5" s="30" t="s">
